--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,54 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Brazilian Serie A</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>Central Cordoba (SdE)</t>
+  </si>
+  <si>
+    <t>CA Independiente</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Atletico Bucaramanga</t>
+  </si>
+  <si>
+    <t>Atl Tucuman</t>
+  </si>
+  <si>
+    <t>Newells</t>
+  </si>
+  <si>
+    <t>Cruzeiro MG</t>
+  </si>
+  <si>
+    <t>Llaneros FC</t>
+  </si>
+  <si>
+    <t>2026-07-29 01:11:05</t>
   </si>
 </sst>
 </file>
@@ -585,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -830,6 +878,974 @@
         <v>79</v>
       </c>
     </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2">
+        <v>3.25</v>
+      </c>
+      <c r="G2">
+        <v>3.55</v>
+      </c>
+      <c r="H2">
+        <v>2.52</v>
+      </c>
+      <c r="I2">
+        <v>2.7</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>3.2</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.13</v>
+      </c>
+      <c r="N2">
+        <v>2.58</v>
+      </c>
+      <c r="O2">
+        <v>1.56</v>
+      </c>
+      <c r="P2">
+        <v>1.53</v>
+      </c>
+      <c r="Q2">
+        <v>2.66</v>
+      </c>
+      <c r="R2">
+        <v>1.19</v>
+      </c>
+      <c r="S2">
+        <v>5.6</v>
+      </c>
+      <c r="T2">
+        <v>2.12</v>
+      </c>
+      <c r="U2">
+        <v>1.79</v>
+      </c>
+      <c r="V2">
+        <v>1.58</v>
+      </c>
+      <c r="W2">
+        <v>1.39</v>
+      </c>
+      <c r="X2">
+        <v>8.6</v>
+      </c>
+      <c r="Y2">
+        <v>7.8</v>
+      </c>
+      <c r="Z2">
+        <v>15</v>
+      </c>
+      <c r="AA2">
+        <v>55</v>
+      </c>
+      <c r="AB2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC2">
+        <v>7.2</v>
+      </c>
+      <c r="AD2">
+        <v>13</v>
+      </c>
+      <c r="AE2">
+        <v>38</v>
+      </c>
+      <c r="AF2">
+        <v>22</v>
+      </c>
+      <c r="AG2">
+        <v>15.5</v>
+      </c>
+      <c r="AH2">
+        <v>24</v>
+      </c>
+      <c r="AI2">
+        <v>95</v>
+      </c>
+      <c r="AJ2">
+        <v>70</v>
+      </c>
+      <c r="AK2">
+        <v>65</v>
+      </c>
+      <c r="AL2">
+        <v>100</v>
+      </c>
+      <c r="AM2">
+        <v>230</v>
+      </c>
+      <c r="AN2">
+        <v>100</v>
+      </c>
+      <c r="AO2">
+        <v>60</v>
+      </c>
+      <c r="AP2">
+        <v>7.6</v>
+      </c>
+      <c r="AQ2">
+        <v>6.8</v>
+      </c>
+      <c r="AR2">
+        <v>13</v>
+      </c>
+      <c r="AS2">
+        <v>28</v>
+      </c>
+      <c r="AT2">
+        <v>8.4</v>
+      </c>
+      <c r="AU2">
+        <v>6.4</v>
+      </c>
+      <c r="AV2">
+        <v>11</v>
+      </c>
+      <c r="AW2">
+        <v>32</v>
+      </c>
+      <c r="AX2">
+        <v>19.5</v>
+      </c>
+      <c r="AY2">
+        <v>13.5</v>
+      </c>
+      <c r="AZ2">
+        <v>21</v>
+      </c>
+      <c r="BA2">
+        <v>13</v>
+      </c>
+      <c r="BB2">
+        <v>13</v>
+      </c>
+      <c r="BC2">
+        <v>36</v>
+      </c>
+      <c r="BD2">
+        <v>13.5</v>
+      </c>
+      <c r="BE2">
+        <v>15</v>
+      </c>
+      <c r="BF2">
+        <v>13.5</v>
+      </c>
+      <c r="BG2">
+        <v>30</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.67</v>
+      </c>
+      <c r="BJ2">
+        <v>16</v>
+      </c>
+      <c r="BK2">
+        <v>1.51</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.67</v>
+      </c>
+      <c r="BN2">
+        <v>9</v>
+      </c>
+      <c r="BO2">
+        <v>4.4</v>
+      </c>
+      <c r="BP2">
+        <v>50</v>
+      </c>
+      <c r="BQ2">
+        <v>1.62</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.64</v>
+      </c>
+      <c r="BT2">
+        <v>7.4</v>
+      </c>
+      <c r="BU2">
+        <v>3.45</v>
+      </c>
+      <c r="BV2">
+        <v>32</v>
+      </c>
+      <c r="BW2">
+        <v>1.59</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.63</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.63</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3">
+        <v>1.66</v>
+      </c>
+      <c r="G3">
+        <v>1.78</v>
+      </c>
+      <c r="H3">
+        <v>6.2</v>
+      </c>
+      <c r="I3">
+        <v>7.2</v>
+      </c>
+      <c r="J3">
+        <v>3.5</v>
+      </c>
+      <c r="K3">
+        <v>3.95</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.09</v>
+      </c>
+      <c r="N3">
+        <v>2.7</v>
+      </c>
+      <c r="O3">
+        <v>1.43</v>
+      </c>
+      <c r="P3">
+        <v>1.59</v>
+      </c>
+      <c r="Q3">
+        <v>2.24</v>
+      </c>
+      <c r="R3">
+        <v>1.12</v>
+      </c>
+      <c r="S3">
+        <v>4.5</v>
+      </c>
+      <c r="T3">
+        <v>1.97</v>
+      </c>
+      <c r="U3">
+        <v>1.55</v>
+      </c>
+      <c r="V3">
+        <v>1.16</v>
+      </c>
+      <c r="W3">
+        <v>2.28</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>21</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>8</v>
+      </c>
+      <c r="AC3">
+        <v>11</v>
+      </c>
+      <c r="AD3">
+        <v>950</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>11.5</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>950</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.69</v>
+      </c>
+      <c r="AQ3">
+        <v>1.56</v>
+      </c>
+      <c r="AR3">
+        <v>1.69</v>
+      </c>
+      <c r="AS3">
+        <v>1.69</v>
+      </c>
+      <c r="AT3">
+        <v>1.39</v>
+      </c>
+      <c r="AU3">
+        <v>1.46</v>
+      </c>
+      <c r="AV3">
+        <v>1.61</v>
+      </c>
+      <c r="AW3">
+        <v>1.69</v>
+      </c>
+      <c r="AX3">
+        <v>1.47</v>
+      </c>
+      <c r="AY3">
+        <v>1.69</v>
+      </c>
+      <c r="AZ3">
+        <v>1.61</v>
+      </c>
+      <c r="BA3">
+        <v>1.69</v>
+      </c>
+      <c r="BB3">
+        <v>1.69</v>
+      </c>
+      <c r="BC3">
+        <v>1.69</v>
+      </c>
+      <c r="BD3">
+        <v>1.69</v>
+      </c>
+      <c r="BE3">
+        <v>1.69</v>
+      </c>
+      <c r="BF3">
+        <v>1.69</v>
+      </c>
+      <c r="BG3">
+        <v>1.69</v>
+      </c>
+      <c r="BH3">
+        <v>3.45</v>
+      </c>
+      <c r="BI3">
+        <v>2.36</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.42</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.42</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.42</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.42</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.42</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.42</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.42</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.42</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.42</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4">
+        <v>3.55</v>
+      </c>
+      <c r="G4">
+        <v>3.65</v>
+      </c>
+      <c r="H4">
+        <v>2.32</v>
+      </c>
+      <c r="I4">
+        <v>2.36</v>
+      </c>
+      <c r="J4">
+        <v>3.4</v>
+      </c>
+      <c r="K4">
+        <v>3.5</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.09</v>
+      </c>
+      <c r="N4">
+        <v>3.25</v>
+      </c>
+      <c r="O4">
+        <v>1.39</v>
+      </c>
+      <c r="P4">
+        <v>1.78</v>
+      </c>
+      <c r="Q4">
+        <v>2.16</v>
+      </c>
+      <c r="R4">
+        <v>1.3</v>
+      </c>
+      <c r="S4">
+        <v>4</v>
+      </c>
+      <c r="T4">
+        <v>1.87</v>
+      </c>
+      <c r="U4">
+        <v>2.02</v>
+      </c>
+      <c r="V4">
+        <v>1.74</v>
+      </c>
+      <c r="W4">
+        <v>1.37</v>
+      </c>
+      <c r="X4">
+        <v>12</v>
+      </c>
+      <c r="Y4">
+        <v>9</v>
+      </c>
+      <c r="Z4">
+        <v>14</v>
+      </c>
+      <c r="AA4">
+        <v>32</v>
+      </c>
+      <c r="AB4">
+        <v>12.5</v>
+      </c>
+      <c r="AC4">
+        <v>7.8</v>
+      </c>
+      <c r="AD4">
+        <v>11.5</v>
+      </c>
+      <c r="AE4">
+        <v>27</v>
+      </c>
+      <c r="AF4">
+        <v>24</v>
+      </c>
+      <c r="AG4">
+        <v>15</v>
+      </c>
+      <c r="AH4">
+        <v>19</v>
+      </c>
+      <c r="AI4">
+        <v>50</v>
+      </c>
+      <c r="AJ4">
+        <v>70</v>
+      </c>
+      <c r="AK4">
+        <v>46</v>
+      </c>
+      <c r="AL4">
+        <v>60</v>
+      </c>
+      <c r="AM4">
+        <v>120</v>
+      </c>
+      <c r="AN4">
+        <v>55</v>
+      </c>
+      <c r="AO4">
+        <v>23</v>
+      </c>
+      <c r="AP4">
+        <v>10.5</v>
+      </c>
+      <c r="AQ4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR4">
+        <v>12.5</v>
+      </c>
+      <c r="AS4">
+        <v>27</v>
+      </c>
+      <c r="AT4">
+        <v>11</v>
+      </c>
+      <c r="AU4">
+        <v>7</v>
+      </c>
+      <c r="AV4">
+        <v>10</v>
+      </c>
+      <c r="AW4">
+        <v>20</v>
+      </c>
+      <c r="AX4">
+        <v>22</v>
+      </c>
+      <c r="AY4">
+        <v>13.5</v>
+      </c>
+      <c r="AZ4">
+        <v>17.5</v>
+      </c>
+      <c r="BA4">
+        <v>34</v>
+      </c>
+      <c r="BB4">
+        <v>15</v>
+      </c>
+      <c r="BC4">
+        <v>40</v>
+      </c>
+      <c r="BD4">
+        <v>50</v>
+      </c>
+      <c r="BE4">
+        <v>14.5</v>
+      </c>
+      <c r="BF4">
+        <v>12.5</v>
+      </c>
+      <c r="BG4">
+        <v>18</v>
+      </c>
+      <c r="BH4">
+        <v>3.6</v>
+      </c>
+      <c r="BI4">
+        <v>2.56</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>3.85</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>9.6</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>2.8</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>6.4</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>8.4</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>2.52</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>5.6</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>7.6</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>6.4</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5">
+        <v>1.47</v>
+      </c>
+      <c r="G5">
+        <v>1.58</v>
+      </c>
+      <c r="H5">
+        <v>7.8</v>
+      </c>
+      <c r="I5">
+        <v>10.5</v>
+      </c>
+      <c r="J5">
+        <v>4.1</v>
+      </c>
+      <c r="K5">
+        <v>4.8</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.08</v>
+      </c>
+      <c r="N5">
+        <v>3.3</v>
+      </c>
+      <c r="O5">
+        <v>1.36</v>
+      </c>
+      <c r="P5">
+        <v>1.83</v>
+      </c>
+      <c r="Q5">
+        <v>1.87</v>
+      </c>
+      <c r="R5">
+        <v>1.29</v>
+      </c>
+      <c r="S5">
+        <v>3.3</v>
+      </c>
+      <c r="T5">
+        <v>2.12</v>
+      </c>
+      <c r="U5">
+        <v>1.74</v>
+      </c>
+      <c r="V5">
+        <v>1.1</v>
+      </c>
+      <c r="W5">
+        <v>2.72</v>
+      </c>
+      <c r="X5">
+        <v>16</v>
+      </c>
+      <c r="Y5">
+        <v>28</v>
+      </c>
+      <c r="Z5">
+        <v>80</v>
+      </c>
+      <c r="AA5">
+        <v>410</v>
+      </c>
+      <c r="AB5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC5">
+        <v>12</v>
+      </c>
+      <c r="AD5">
+        <v>40</v>
+      </c>
+      <c r="AE5">
+        <v>200</v>
+      </c>
+      <c r="AF5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG5">
+        <v>12.5</v>
+      </c>
+      <c r="AH5">
+        <v>36</v>
+      </c>
+      <c r="AI5">
+        <v>180</v>
+      </c>
+      <c r="AJ5">
+        <v>16.5</v>
+      </c>
+      <c r="AK5">
+        <v>22</v>
+      </c>
+      <c r="AL5">
+        <v>60</v>
+      </c>
+      <c r="AM5">
+        <v>250</v>
+      </c>
+      <c r="AN5">
+        <v>12.5</v>
+      </c>
+      <c r="AO5">
+        <v>340</v>
+      </c>
+      <c r="AP5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ5">
+        <v>19</v>
+      </c>
+      <c r="AR5">
+        <v>4.1</v>
+      </c>
+      <c r="AS5">
+        <v>4.3</v>
+      </c>
+      <c r="AT5">
+        <v>5.8</v>
+      </c>
+      <c r="AU5">
+        <v>8.4</v>
+      </c>
+      <c r="AV5">
+        <v>3.95</v>
+      </c>
+      <c r="AW5">
+        <v>4.3</v>
+      </c>
+      <c r="AX5">
+        <v>7</v>
+      </c>
+      <c r="AY5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ5">
+        <v>3.9</v>
+      </c>
+      <c r="BA5">
+        <v>4.3</v>
+      </c>
+      <c r="BB5">
+        <v>11.5</v>
+      </c>
+      <c r="BC5">
+        <v>15.5</v>
+      </c>
+      <c r="BD5">
+        <v>4.1</v>
+      </c>
+      <c r="BE5">
+        <v>4.3</v>
+      </c>
+      <c r="BF5">
+        <v>7</v>
+      </c>
+      <c r="BG5">
+        <v>4.3</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.78</v>
+      </c>
+      <c r="BJ5">
+        <v>18</v>
+      </c>
+      <c r="BK5">
+        <v>1.63</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.78</v>
+      </c>
+      <c r="BN5">
+        <v>5.1</v>
+      </c>
+      <c r="BO5">
+        <v>2.64</v>
+      </c>
+      <c r="BP5">
+        <v>14.5</v>
+      </c>
+      <c r="BQ5">
+        <v>1.59</v>
+      </c>
+      <c r="BR5">
+        <v>46</v>
+      </c>
+      <c r="BS5">
+        <v>1.72</v>
+      </c>
+      <c r="BT5">
+        <v>16</v>
+      </c>
+      <c r="BU5">
+        <v>1.61</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.78</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.78</v>
+      </c>
+      <c r="BZ5">
+        <v>30</v>
+      </c>
+      <c r="CA5">
+        <v>1.69</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -301,7 +301,7 @@
     <t>Llaneros FC</t>
   </si>
   <si>
-    <t>2026-07-29 01:11:05</t>
+    <t>2026-07-29 03:18:48</t>
   </si>
 </sst>
 </file>
@@ -913,7 +913,7 @@
         <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M2">
         <v>1.13</v>
@@ -1137,7 +1137,7 @@
         <v>92</v>
       </c>
       <c r="F3">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="G3">
         <v>1.78</v>
@@ -1149,40 +1149,40 @@
         <v>7.2</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O3">
         <v>1.43</v>
       </c>
       <c r="P3">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q3">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
         <v>4.5</v>
       </c>
       <c r="T3">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="U3">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="V3">
         <v>1.16</v>
@@ -1191,112 +1191,112 @@
         <v>2.28</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y3">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB3">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AC3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD3">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF3">
+        <v>9.6</v>
+      </c>
+      <c r="AG3">
+        <v>13</v>
+      </c>
+      <c r="AH3">
+        <v>36</v>
+      </c>
+      <c r="AI3">
+        <v>160</v>
+      </c>
+      <c r="AJ3">
+        <v>22</v>
+      </c>
+      <c r="AK3">
+        <v>28</v>
+      </c>
+      <c r="AL3">
+        <v>65</v>
+      </c>
+      <c r="AM3">
+        <v>260</v>
+      </c>
+      <c r="AN3">
+        <v>19.5</v>
+      </c>
+      <c r="AO3">
+        <v>270</v>
+      </c>
+      <c r="AP3">
+        <v>9</v>
+      </c>
+      <c r="AQ3">
+        <v>13.5</v>
+      </c>
+      <c r="AR3">
+        <v>5.5</v>
+      </c>
+      <c r="AS3">
+        <v>5.9</v>
+      </c>
+      <c r="AT3">
+        <v>5.6</v>
+      </c>
+      <c r="AU3">
+        <v>7.2</v>
+      </c>
+      <c r="AV3">
+        <v>4.9</v>
+      </c>
+      <c r="AW3">
+        <v>5.8</v>
+      </c>
+      <c r="AX3">
+        <v>7.8</v>
+      </c>
+      <c r="AY3">
+        <v>9</v>
+      </c>
+      <c r="AZ3">
+        <v>4.9</v>
+      </c>
+      <c r="BA3">
+        <v>5.8</v>
+      </c>
+      <c r="BB3">
+        <v>15</v>
+      </c>
+      <c r="BC3">
+        <v>19</v>
+      </c>
+      <c r="BD3">
+        <v>5.5</v>
+      </c>
+      <c r="BE3">
+        <v>5.9</v>
+      </c>
+      <c r="BF3">
         <v>11.5</v>
       </c>
-      <c r="AG3">
-        <v>1000</v>
-      </c>
-      <c r="AH3">
-        <v>950</v>
-      </c>
-      <c r="AI3">
-        <v>1000</v>
-      </c>
-      <c r="AJ3">
-        <v>1000</v>
-      </c>
-      <c r="AK3">
-        <v>1000</v>
-      </c>
-      <c r="AL3">
-        <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>1.69</v>
-      </c>
-      <c r="AQ3">
-        <v>1.56</v>
-      </c>
-      <c r="AR3">
-        <v>1.69</v>
-      </c>
-      <c r="AS3">
-        <v>1.69</v>
-      </c>
-      <c r="AT3">
-        <v>1.39</v>
-      </c>
-      <c r="AU3">
-        <v>1.46</v>
-      </c>
-      <c r="AV3">
-        <v>1.61</v>
-      </c>
-      <c r="AW3">
-        <v>1.69</v>
-      </c>
-      <c r="AX3">
-        <v>1.47</v>
-      </c>
-      <c r="AY3">
-        <v>1.69</v>
-      </c>
-      <c r="AZ3">
-        <v>1.61</v>
-      </c>
-      <c r="BA3">
-        <v>1.69</v>
-      </c>
-      <c r="BB3">
-        <v>1.69</v>
-      </c>
-      <c r="BC3">
-        <v>1.69</v>
-      </c>
-      <c r="BD3">
-        <v>1.69</v>
-      </c>
-      <c r="BE3">
-        <v>1.69</v>
-      </c>
-      <c r="BF3">
-        <v>1.69</v>
-      </c>
       <c r="BG3">
-        <v>1.69</v>
+        <v>5.9</v>
       </c>
       <c r="BH3">
         <v>3.45</v>
@@ -1388,7 +1388,7 @@
         <v>2.32</v>
       </c>
       <c r="I4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J4">
         <v>3.4</v>
@@ -1436,7 +1436,7 @@
         <v>12</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z4">
         <v>14</v>
@@ -1523,7 +1523,7 @@
         <v>34</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC4">
         <v>40</v>
@@ -1532,10 +1532,10 @@
         <v>50</v>
       </c>
       <c r="BE4">
+        <v>15</v>
+      </c>
+      <c r="BF4">
         <v>14.5</v>
-      </c>
-      <c r="BF4">
-        <v>12.5</v>
       </c>
       <c r="BG4">
         <v>18</v>
@@ -1621,22 +1621,22 @@
         <v>94</v>
       </c>
       <c r="F5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G5">
         <v>1.58</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1645,31 +1645,31 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
         <v>1.83</v>
       </c>
       <c r="Q5">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W5">
         <v>2.72</v>
@@ -1678,79 +1678,79 @@
         <v>16</v>
       </c>
       <c r="Y5">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Z5">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA5">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="AB5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC5">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
         <v>40</v>
       </c>
       <c r="AE5">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AF5">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG5">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI5">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ5">
         <v>16.5</v>
       </c>
       <c r="AK5">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL5">
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AN5">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO5">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="AP5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR5">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="AS5">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT5">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV5">
-        <v>3.95</v>
+        <v>26</v>
       </c>
       <c r="AW5">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AX5">
         <v>7</v>
@@ -1759,28 +1759,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>3.9</v>
+        <v>23</v>
       </c>
       <c r="BA5">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BB5">
         <v>11.5</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE5">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BF5">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG5">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BH5">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -301,7 +301,7 @@
     <t>Llaneros FC</t>
   </si>
   <si>
-    <t>2026-07-29 03:18:48</t>
+    <t>2026-07-29 05:26:39</t>
   </si>
 </sst>
 </file>
@@ -1161,10 +1161,10 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="O3">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
         <v>1.61</v>
@@ -1179,10 +1179,10 @@
         <v>4.5</v>
       </c>
       <c r="T3">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V3">
         <v>1.16</v>
@@ -1385,7 +1385,7 @@
         <v>3.65</v>
       </c>
       <c r="H4">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I4">
         <v>2.34</v>
@@ -1460,7 +1460,7 @@
         <v>24</v>
       </c>
       <c r="AG4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH4">
         <v>19</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX4">
         <v>22</v>
@@ -1621,7 +1621,7 @@
         <v>94</v>
       </c>
       <c r="F5">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G5">
         <v>1.58</v>
@@ -1630,10 +1630,10 @@
         <v>7.6</v>
       </c>
       <c r="I5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
         <v>4.7</v>
@@ -1645,13 +1645,13 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O5">
         <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q5">
         <v>2.06</v>
@@ -1660,7 +1660,7 @@
         <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T5">
         <v>2.18</v>
@@ -1669,19 +1669,19 @@
         <v>1.71</v>
       </c>
       <c r="V5">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W5">
         <v>2.72</v>
       </c>
       <c r="X5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y5">
         <v>24</v>
       </c>
       <c r="Z5">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AA5">
         <v>380</v>
@@ -1693,7 +1693,7 @@
         <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AE5">
         <v>190</v>
@@ -1735,22 +1735,22 @@
         <v>19.5</v>
       </c>
       <c r="AR5">
+        <v>6</v>
+      </c>
+      <c r="AS5">
+        <v>6.4</v>
+      </c>
+      <c r="AT5">
         <v>5.8</v>
-      </c>
-      <c r="AS5">
-        <v>6.2</v>
-      </c>
-      <c r="AT5">
-        <v>6.2</v>
       </c>
       <c r="AU5">
         <v>8.6</v>
       </c>
       <c r="AV5">
-        <v>26</v>
+        <v>5.4</v>
       </c>
       <c r="AW5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX5">
         <v>7</v>
@@ -1759,10 +1759,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>23</v>
+        <v>5.4</v>
       </c>
       <c r="BA5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB5">
         <v>11.5</v>
@@ -1771,10 +1771,10 @@
         <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF5">
         <v>8.800000000000001</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -301,7 +301,7 @@
     <t>Llaneros FC</t>
   </si>
   <si>
-    <t>2026-07-29 05:26:39</t>
+    <t>2026-07-29 07:34:29</t>
   </si>
 </sst>
 </file>
@@ -904,19 +904,19 @@
         <v>2.52</v>
       </c>
       <c r="I2">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="M2">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
         <v>2.58</v>
@@ -925,25 +925,25 @@
         <v>1.56</v>
       </c>
       <c r="P2">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q2">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R2">
         <v>1.19</v>
       </c>
       <c r="S2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T2">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U2">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V2">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W2">
         <v>1.39</v>
@@ -958,7 +958,7 @@
         <v>15</v>
       </c>
       <c r="AA2">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AB2">
         <v>9.199999999999999</v>
@@ -982,25 +982,25 @@
         <v>24</v>
       </c>
       <c r="AI2">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
         <v>70</v>
       </c>
       <c r="AK2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AM2">
         <v>230</v>
       </c>
       <c r="AN2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AO2">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AP2">
         <v>7.6</v>
@@ -1012,7 +1012,7 @@
         <v>13</v>
       </c>
       <c r="AS2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AT2">
         <v>8.4</v>
@@ -1042,7 +1042,7 @@
         <v>13</v>
       </c>
       <c r="BC2">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="BD2">
         <v>13.5</v>
@@ -1054,67 +1054,67 @@
         <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="BI2">
-        <v>1.67</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>1.51</v>
+        <v>6.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.67</v>
+        <v>15.5</v>
       </c>
       <c r="BN2">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="BO2">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BP2">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BQ2">
-        <v>1.62</v>
+        <v>11</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS2">
-        <v>1.64</v>
+        <v>13</v>
       </c>
       <c r="BT2">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU2">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BW2">
-        <v>1.59</v>
+        <v>9.6</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY2">
-        <v>1.63</v>
+        <v>12</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA2">
-        <v>1.63</v>
+        <v>12.5</v>
       </c>
       <c r="CB2" t="s">
         <v>95</v>
@@ -1149,7 +1149,7 @@
         <v>7.2</v>
       </c>
       <c r="J3">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
         <v>3.9</v>
@@ -1170,10 +1170,10 @@
         <v>1.61</v>
       </c>
       <c r="Q3">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
         <v>4.5</v>
@@ -1194,7 +1194,7 @@
         <v>12.5</v>
       </c>
       <c r="Y3">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Z3">
         <v>65</v>
@@ -1203,25 +1203,25 @@
         <v>270</v>
       </c>
       <c r="AB3">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AE3">
         <v>160</v>
       </c>
       <c r="AF3">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AG3">
         <v>13</v>
       </c>
       <c r="AH3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI3">
         <v>160</v>
@@ -1248,13 +1248,13 @@
         <v>9</v>
       </c>
       <c r="AQ3">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AR3">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AS3">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="AT3">
         <v>5.6</v>
@@ -1263,22 +1263,22 @@
         <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="AW3">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="AX3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY3">
         <v>9</v>
       </c>
       <c r="AZ3">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BA3">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB3">
         <v>15</v>
@@ -1287,76 +1287,76 @@
         <v>19</v>
       </c>
       <c r="BD3">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="BE3">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="BF3">
         <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="BH3">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>95</v>
@@ -1397,7 +1397,7 @@
         <v>3.5</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1415,7 +1415,7 @@
         <v>2.16</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
         <v>4</v>
@@ -1424,7 +1424,7 @@
         <v>1.87</v>
       </c>
       <c r="U4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V4">
         <v>1.74</v>
@@ -1466,7 +1466,7 @@
         <v>19</v>
       </c>
       <c r="AI4">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ4">
         <v>70</v>
@@ -1520,7 +1520,7 @@
         <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>34</v>
+        <v>13.5</v>
       </c>
       <c r="BB4">
         <v>15.5</v>
@@ -1535,70 +1535,70 @@
         <v>15</v>
       </c>
       <c r="BF4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG4">
         <v>18</v>
       </c>
       <c r="BH4">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.56</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="s">
         <v>95</v>
@@ -1621,22 +1621,22 @@
         <v>94</v>
       </c>
       <c r="F5">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G5">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>9.4</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1645,202 +1645,202 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q5">
         <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="V5">
         <v>1.12</v>
       </c>
       <c r="W5">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="X5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA5">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC5">
+        <v>11.5</v>
+      </c>
+      <c r="AD5">
+        <v>38</v>
+      </c>
+      <c r="AE5">
+        <v>180</v>
+      </c>
+      <c r="AF5">
         <v>10.5</v>
       </c>
-      <c r="AD5">
-        <v>950</v>
-      </c>
-      <c r="AE5">
-        <v>190</v>
-      </c>
-      <c r="AF5">
-        <v>8.6</v>
-      </c>
       <c r="AG5">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH5">
         <v>34</v>
       </c>
       <c r="AI5">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ5">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AK5">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AL5">
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN5">
+        <v>13</v>
+      </c>
+      <c r="AO5">
+        <v>280</v>
+      </c>
+      <c r="AP5">
         <v>11</v>
       </c>
-      <c r="AO5">
-        <v>290</v>
-      </c>
-      <c r="AP5">
+      <c r="AQ5">
+        <v>15</v>
+      </c>
+      <c r="AR5">
+        <v>4</v>
+      </c>
+      <c r="AS5">
+        <v>4.2</v>
+      </c>
+      <c r="AT5">
+        <v>5.9</v>
+      </c>
+      <c r="AU5">
+        <v>8</v>
+      </c>
+      <c r="AV5">
+        <v>21</v>
+      </c>
+      <c r="AW5">
+        <v>4.2</v>
+      </c>
+      <c r="AX5">
+        <v>7.2</v>
+      </c>
+      <c r="AY5">
+        <v>7.4</v>
+      </c>
+      <c r="AZ5">
+        <v>19.5</v>
+      </c>
+      <c r="BA5">
+        <v>4.2</v>
+      </c>
+      <c r="BB5">
         <v>10.5</v>
       </c>
-      <c r="AQ5">
-        <v>19.5</v>
-      </c>
-      <c r="AR5">
-        <v>6</v>
-      </c>
-      <c r="AS5">
-        <v>6.4</v>
-      </c>
-      <c r="AT5">
-        <v>5.8</v>
-      </c>
-      <c r="AU5">
-        <v>8.6</v>
-      </c>
-      <c r="AV5">
-        <v>5.4</v>
-      </c>
-      <c r="AW5">
-        <v>6.2</v>
-      </c>
-      <c r="AX5">
-        <v>7</v>
-      </c>
-      <c r="AY5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ5">
-        <v>5.4</v>
-      </c>
-      <c r="BA5">
-        <v>6.2</v>
-      </c>
-      <c r="BB5">
-        <v>11.5</v>
-      </c>
       <c r="BC5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD5">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="BE5">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BF5">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BG5">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BJ5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BK5">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BN5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BO5">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BP5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ5">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BR5">
         <v>46</v>
       </c>
       <c r="BS5">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="BT5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BU5">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BZ5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="CA5">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CB5" t="s">
         <v>95</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Chinese Super League</t>
+  </si>
+  <si>
     <t>2026-07-31</t>
   </si>
   <si>
@@ -277,6 +280,9 @@
     <t>01:00:00</t>
   </si>
   <si>
+    <t>11:35:00</t>
+  </si>
+  <si>
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
@@ -289,6 +295,9 @@
     <t>Atletico Bucaramanga</t>
   </si>
   <si>
+    <t>Henan Songshan Longmen</t>
+  </si>
+  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
@@ -301,7 +310,10 @@
     <t>Llaneros FC</t>
   </si>
   <si>
-    <t>2026-07-29 07:34:29</t>
+    <t>Dalian Yingbo</t>
+  </si>
+  <si>
+    <t>2026-07-29 09:42:01</t>
   </si>
 </sst>
 </file>
@@ -633,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -883,16 +895,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F2">
         <v>3.25</v>
@@ -901,7 +913,7 @@
         <v>3.55</v>
       </c>
       <c r="H2">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I2">
         <v>2.68</v>
@@ -910,25 +922,25 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L2">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O2">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="P2">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q2">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R2">
         <v>1.19</v>
@@ -937,10 +949,10 @@
         <v>5.5</v>
       </c>
       <c r="T2">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U2">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V2">
         <v>1.59</v>
@@ -949,115 +961,115 @@
         <v>1.39</v>
       </c>
       <c r="X2">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z2">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AA2">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AB2">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD2">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AE2">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AF2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AG2">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AL2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AP2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2">
         <v>6.8</v>
       </c>
       <c r="AR2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AS2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AT2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AX2">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AY2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA2">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="BB2">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="BC2">
-        <v>12.5</v>
+        <v>38</v>
       </c>
       <c r="BD2">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="BE2">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="BF2">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="BG2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BH2">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BI2">
         <v>2.26</v>
@@ -1066,19 +1078,19 @@
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>15.5</v>
+        <v>2.24</v>
       </c>
       <c r="BN2">
         <v>6.6</v>
       </c>
       <c r="BO2">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP2">
         <v>36</v>
@@ -1090,19 +1102,19 @@
         <v>60</v>
       </c>
       <c r="BS2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT2">
         <v>5.3</v>
       </c>
       <c r="BU2">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BV2">
         <v>23</v>
       </c>
       <c r="BW2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>48</v>
@@ -1114,10 +1126,10 @@
         <v>55</v>
       </c>
       <c r="CA2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CB2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1125,19 +1137,19 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F3">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G3">
         <v>1.78</v>
@@ -1155,7 +1167,7 @@
         <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M3">
         <v>1.1</v>
@@ -1176,7 +1188,7 @@
         <v>1.22</v>
       </c>
       <c r="S3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T3">
         <v>2.2</v>
@@ -1194,7 +1206,7 @@
         <v>12.5</v>
       </c>
       <c r="Y3">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Z3">
         <v>65</v>
@@ -1203,7 +1215,7 @@
         <v>270</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC3">
         <v>10.5</v>
@@ -1215,7 +1227,7 @@
         <v>160</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AG3">
         <v>13</v>
@@ -1227,10 +1239,10 @@
         <v>160</v>
       </c>
       <c r="AJ3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AL3">
         <v>65</v>
@@ -1239,7 +1251,7 @@
         <v>260</v>
       </c>
       <c r="AN3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO3">
         <v>270</v>
@@ -1251,10 +1263,10 @@
         <v>12</v>
       </c>
       <c r="AR3">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS3">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT3">
         <v>5.6</v>
@@ -1266,7 +1278,7 @@
         <v>19</v>
       </c>
       <c r="AW3">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX3">
         <v>7.6</v>
@@ -1275,10 +1287,10 @@
         <v>9</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BA3">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB3">
         <v>15</v>
@@ -1287,79 +1299,79 @@
         <v>19</v>
       </c>
       <c r="BD3">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE3">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF3">
         <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1367,16 +1379,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F4">
         <v>3.55</v>
@@ -1397,7 +1409,7 @@
         <v>3.5</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1457,10 +1469,10 @@
         <v>27</v>
       </c>
       <c r="AF4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH4">
         <v>19</v>
@@ -1508,7 +1520,7 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AX4">
         <v>22</v>
@@ -1541,67 +1553,67 @@
         <v>18</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK4">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO4">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU4">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1609,37 +1621,37 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F5">
         <v>1.51</v>
       </c>
       <c r="G5">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H5">
         <v>7.2</v>
       </c>
       <c r="I5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -1654,25 +1666,25 @@
         <v>1.79</v>
       </c>
       <c r="Q5">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R5">
         <v>1.29</v>
       </c>
       <c r="S5">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T5">
         <v>2.12</v>
       </c>
       <c r="U5">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V5">
         <v>1.12</v>
       </c>
       <c r="W5">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X5">
         <v>16</v>
@@ -1756,7 +1768,7 @@
         <v>7.2</v>
       </c>
       <c r="AY5">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5">
         <v>19.5</v>
@@ -1768,7 +1780,7 @@
         <v>10.5</v>
       </c>
       <c r="BC5">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
         <v>4</v>
@@ -1783,67 +1795,309 @@
         <v>4.2</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI5">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.75</v>
+        <v>10</v>
       </c>
       <c r="BN5">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="BO5">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="BP5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BQ5">
-        <v>1.57</v>
+        <v>5.4</v>
       </c>
       <c r="BR5">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BS5">
-        <v>1.69</v>
+        <v>8</v>
       </c>
       <c r="BT5">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU5">
-        <v>1.58</v>
+        <v>5.6</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.75</v>
+        <v>9.6</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.75</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5">
+        <v>24</v>
+      </c>
+      <c r="CA5">
+        <v>7.4</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6">
+        <v>1.84</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>3.85</v>
+      </c>
+      <c r="I6">
+        <v>4.4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>4.6</v>
+      </c>
+      <c r="L6">
+        <v>1.27</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>5.2</v>
+      </c>
+      <c r="O6">
+        <v>1.19</v>
+      </c>
+      <c r="P6">
+        <v>2.46</v>
+      </c>
+      <c r="Q6">
+        <v>1.55</v>
+      </c>
+      <c r="R6">
+        <v>1.58</v>
+      </c>
+      <c r="S6">
+        <v>2.4</v>
+      </c>
+      <c r="T6">
+        <v>1.57</v>
+      </c>
+      <c r="U6">
+        <v>2.4</v>
+      </c>
+      <c r="V6">
+        <v>1.29</v>
+      </c>
+      <c r="W6">
+        <v>2</v>
+      </c>
+      <c r="X6">
+        <v>30</v>
+      </c>
+      <c r="Y6">
+        <v>26</v>
+      </c>
+      <c r="Z6">
+        <v>42</v>
+      </c>
+      <c r="AA6">
+        <v>95</v>
+      </c>
+      <c r="AB6">
+        <v>16</v>
+      </c>
+      <c r="AC6">
+        <v>12.5</v>
+      </c>
+      <c r="AD6">
+        <v>21</v>
+      </c>
+      <c r="AE6">
+        <v>55</v>
+      </c>
+      <c r="AF6">
+        <v>15.5</v>
+      </c>
+      <c r="AG6">
+        <v>13</v>
+      </c>
+      <c r="AH6">
+        <v>19.5</v>
+      </c>
+      <c r="AI6">
+        <v>55</v>
+      </c>
+      <c r="AJ6">
+        <v>23</v>
+      </c>
+      <c r="AK6">
+        <v>18.5</v>
+      </c>
+      <c r="AL6">
         <v>34</v>
       </c>
-      <c r="CA5">
-        <v>1.67</v>
-      </c>
-      <c r="CB5" t="s">
-        <v>95</v>
+      <c r="AM6">
+        <v>65</v>
+      </c>
+      <c r="AN6">
+        <v>10.5</v>
+      </c>
+      <c r="AO6">
+        <v>38</v>
+      </c>
+      <c r="AP6">
+        <v>17.5</v>
+      </c>
+      <c r="AQ6">
+        <v>15</v>
+      </c>
+      <c r="AR6">
+        <v>24</v>
+      </c>
+      <c r="AS6">
+        <v>4.5</v>
+      </c>
+      <c r="AT6">
+        <v>9.6</v>
+      </c>
+      <c r="AU6">
+        <v>7.4</v>
+      </c>
+      <c r="AV6">
+        <v>12.5</v>
+      </c>
+      <c r="AW6">
+        <v>4.4</v>
+      </c>
+      <c r="AX6">
+        <v>12</v>
+      </c>
+      <c r="AY6">
+        <v>8</v>
+      </c>
+      <c r="AZ6">
+        <v>11.5</v>
+      </c>
+      <c r="BA6">
+        <v>4.4</v>
+      </c>
+      <c r="BB6">
+        <v>18.5</v>
+      </c>
+      <c r="BC6">
+        <v>15</v>
+      </c>
+      <c r="BD6">
+        <v>19.5</v>
+      </c>
+      <c r="BE6">
+        <v>4.4</v>
+      </c>
+      <c r="BF6">
+        <v>7.4</v>
+      </c>
+      <c r="BG6">
+        <v>4.2</v>
+      </c>
+      <c r="BH6">
+        <v>4.5</v>
+      </c>
+      <c r="BI6">
+        <v>3.4</v>
+      </c>
+      <c r="BJ6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK6">
+        <v>6.6</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>15</v>
+      </c>
+      <c r="BN6">
+        <v>5.2</v>
+      </c>
+      <c r="BO6">
+        <v>3.9</v>
+      </c>
+      <c r="BP6">
+        <v>13</v>
+      </c>
+      <c r="BQ6">
+        <v>9</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>15.5</v>
+      </c>
+      <c r="BT6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU6">
+        <v>5.8</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>20</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>23</v>
+      </c>
+      <c r="BZ6">
+        <v>16</v>
+      </c>
+      <c r="CA6">
+        <v>11</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -313,7 +313,7 @@
     <t>Dalian Yingbo</t>
   </si>
   <si>
-    <t>2026-07-29 09:42:01</t>
+    <t>2026-07-29 11:49:36</t>
   </si>
 </sst>
 </file>
@@ -907,13 +907,13 @@
         <v>94</v>
       </c>
       <c r="F2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G2">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H2">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I2">
         <v>2.68</v>
@@ -922,31 +922,31 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M2">
         <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O2">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="P2">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T2">
         <v>2.16</v>
@@ -955,43 +955,43 @@
         <v>1.79</v>
       </c>
       <c r="V2">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X2">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z2">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AB2">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2">
         <v>7</v>
       </c>
       <c r="AD2">
+        <v>13</v>
+      </c>
+      <c r="AE2">
+        <v>38</v>
+      </c>
+      <c r="AF2">
+        <v>22</v>
+      </c>
+      <c r="AG2">
         <v>15.5</v>
       </c>
-      <c r="AE2">
-        <v>80</v>
-      </c>
-      <c r="AF2">
-        <v>27</v>
-      </c>
-      <c r="AG2">
-        <v>20</v>
-      </c>
       <c r="AH2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AI2">
         <v>1000</v>
@@ -1012,61 +1012,61 @@
         <v>1000</v>
       </c>
       <c r="AO2">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AP2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AS2">
         <v>23</v>
       </c>
       <c r="AT2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
         <v>11.5</v>
       </c>
       <c r="AW2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AX2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AY2">
         <v>14</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BB2">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BC2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BD2">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BE2">
         <v>46</v>
       </c>
       <c r="BF2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BG2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BH2">
         <v>2.64</v>
@@ -1149,7 +1149,7 @@
         <v>95</v>
       </c>
       <c r="F3">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G3">
         <v>1.78</v>
@@ -1164,16 +1164,16 @@
         <v>3.5</v>
       </c>
       <c r="K3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L3">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O3">
         <v>1.46</v>
@@ -1188,7 +1188,7 @@
         <v>1.22</v>
       </c>
       <c r="S3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T3">
         <v>2.2</v>
@@ -1206,7 +1206,7 @@
         <v>12.5</v>
       </c>
       <c r="Y3">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Z3">
         <v>65</v>
@@ -1215,7 +1215,7 @@
         <v>270</v>
       </c>
       <c r="AB3">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC3">
         <v>10.5</v>
@@ -1227,7 +1227,7 @@
         <v>160</v>
       </c>
       <c r="AF3">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AG3">
         <v>13</v>
@@ -1239,10 +1239,10 @@
         <v>160</v>
       </c>
       <c r="AJ3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AL3">
         <v>65</v>
@@ -1251,7 +1251,7 @@
         <v>260</v>
       </c>
       <c r="AN3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO3">
         <v>270</v>
@@ -1263,10 +1263,10 @@
         <v>12</v>
       </c>
       <c r="AR3">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="AS3">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="AT3">
         <v>5.6</v>
@@ -1275,10 +1275,10 @@
         <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW3">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="AX3">
         <v>7.6</v>
@@ -1287,10 +1287,10 @@
         <v>9</v>
       </c>
       <c r="AZ3">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="BA3">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB3">
         <v>15</v>
@@ -1299,16 +1299,16 @@
         <v>19</v>
       </c>
       <c r="BD3">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BE3">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BF3">
         <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BH3">
         <v>3.05</v>
@@ -1320,7 +1320,7 @@
         <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1335,7 +1335,7 @@
         <v>3.15</v>
       </c>
       <c r="BP3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ3">
         <v>5.9</v>
@@ -1344,31 +1344,31 @@
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3">
         <v>10</v>
       </c>
       <c r="BU3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ3">
         <v>34</v>
       </c>
       <c r="CA3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="s">
         <v>99</v>
@@ -1448,7 +1448,7 @@
         <v>12</v>
       </c>
       <c r="Y4">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
         <v>14</v>
@@ -1520,7 +1520,7 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX4">
         <v>22</v>
@@ -1532,10 +1532,10 @@
         <v>17.5</v>
       </c>
       <c r="BA4">
+        <v>12</v>
+      </c>
+      <c r="BB4">
         <v>13.5</v>
-      </c>
-      <c r="BB4">
-        <v>15.5</v>
       </c>
       <c r="BC4">
         <v>40</v>
@@ -1544,10 +1544,10 @@
         <v>50</v>
       </c>
       <c r="BE4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BF4">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="BG4">
         <v>18</v>
@@ -1633,7 +1633,7 @@
         <v>97</v>
       </c>
       <c r="F5">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="G5">
         <v>1.64</v>
@@ -1642,10 +1642,10 @@
         <v>7.2</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
         <v>4.6</v>
@@ -1657,25 +1657,25 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O5">
         <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q5">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
         <v>3.85</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U5">
         <v>1.74</v>
@@ -1693,7 +1693,7 @@
         <v>26</v>
       </c>
       <c r="Z5">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA5">
         <v>350</v>
@@ -1720,10 +1720,10 @@
         <v>34</v>
       </c>
       <c r="AI5">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK5">
         <v>23</v>
@@ -1732,13 +1732,13 @@
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AN5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO5">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AP5">
         <v>11</v>
@@ -1762,19 +1762,19 @@
         <v>21</v>
       </c>
       <c r="AW5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX5">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AY5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
         <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB5">
         <v>10.5</v>
@@ -1783,13 +1783,13 @@
         <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF5">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG5">
         <v>4.2</v>
@@ -1798,7 +1798,7 @@
         <v>3.35</v>
       </c>
       <c r="BI5">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
@@ -1816,7 +1816,7 @@
         <v>4</v>
       </c>
       <c r="BO5">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BP5">
         <v>11</v>
@@ -1875,13 +1875,13 @@
         <v>98</v>
       </c>
       <c r="F6">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
       <c r="H6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I6">
         <v>4.4</v>
@@ -1893,7 +1893,7 @@
         <v>4.6</v>
       </c>
       <c r="L6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M6">
         <v>1.01</v>
@@ -1905,10 +1905,10 @@
         <v>1.19</v>
       </c>
       <c r="P6">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q6">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="R6">
         <v>1.58</v>
@@ -1932,7 +1932,7 @@
         <v>30</v>
       </c>
       <c r="Y6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z6">
         <v>42</v>
@@ -1941,13 +1941,13 @@
         <v>95</v>
       </c>
       <c r="AB6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE6">
         <v>55</v>
@@ -1956,67 +1956,67 @@
         <v>15.5</v>
       </c>
       <c r="AG6">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI6">
         <v>55</v>
       </c>
       <c r="AJ6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AK6">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AL6">
         <v>34</v>
       </c>
       <c r="AM6">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AN6">
         <v>10.5</v>
       </c>
       <c r="AO6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP6">
+        <v>20</v>
+      </c>
+      <c r="AQ6">
         <v>17.5</v>
       </c>
-      <c r="AQ6">
-        <v>15</v>
-      </c>
       <c r="AR6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS6">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT6">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AU6">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV6">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW6">
-        <v>4.4</v>
+        <v>30</v>
       </c>
       <c r="AX6">
         <v>12</v>
       </c>
       <c r="AY6">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>4.4</v>
+        <v>30</v>
       </c>
       <c r="BB6">
         <v>18.5</v>
@@ -2025,16 +2025,16 @@
         <v>15</v>
       </c>
       <c r="BD6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE6">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BF6">
         <v>7.4</v>
       </c>
       <c r="BG6">
-        <v>4.2</v>
+        <v>23</v>
       </c>
       <c r="BH6">
         <v>4.5</v>
@@ -2046,13 +2046,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK6">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN6">
         <v>5.2</v>
@@ -2064,13 +2064,13 @@
         <v>13</v>
       </c>
       <c r="BQ6">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>15.5</v>
+        <v>7</v>
       </c>
       <c r="BT6">
         <v>8.199999999999999</v>
@@ -2082,19 +2082,19 @@
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="BZ6">
         <v>16</v>
       </c>
       <c r="CA6">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="CB6" t="s">
         <v>99</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="160">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,33 @@
     <t>Chinese Super League</t>
   </si>
   <si>
+    <t>Czech 2 Liga</t>
+  </si>
+  <si>
+    <t>Ukrainian Premier League</t>
+  </si>
+  <si>
+    <t>Romanian Liga I</t>
+  </si>
+  <si>
+    <t>Polish I Liga</t>
+  </si>
+  <si>
+    <t>Estonian Premier League</t>
+  </si>
+  <si>
+    <t>Danish 1st Division</t>
+  </si>
+  <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Bulgarian A League</t>
+  </si>
+  <si>
+    <t>Austrian Erste Liga</t>
+  </si>
+  <si>
     <t>2026-07-31</t>
   </si>
   <si>
@@ -283,6 +310,27 @@
     <t>11:35:00</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:15:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
@@ -298,6 +346,72 @@
     <t>Henan Songshan Longmen</t>
   </si>
   <si>
+    <t>Zizkov</t>
+  </si>
+  <si>
+    <t>Zorya</t>
+  </si>
+  <si>
+    <t>Arges Pitesti</t>
+  </si>
+  <si>
+    <t>LKS Lodz</t>
+  </si>
+  <si>
+    <t>Nomme Utd</t>
+  </si>
+  <si>
+    <t>Aarhus Fremad</t>
+  </si>
+  <si>
+    <t>Wisla Plock</t>
+  </si>
+  <si>
+    <t>MFK Karvina</t>
+  </si>
+  <si>
+    <t>Slavia Sofia</t>
+  </si>
+  <si>
+    <t>SK Kladno</t>
+  </si>
+  <si>
+    <t>Austria Wien (A)</t>
+  </si>
+  <si>
+    <t>KSV 1919</t>
+  </si>
+  <si>
+    <t>Voitsberg</t>
+  </si>
+  <si>
+    <t>Admira Wacker</t>
+  </si>
+  <si>
+    <t>FC Wacker Innsbruck</t>
+  </si>
+  <si>
+    <t>MAS Taborsko</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>HB Koge</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>LKP Motor Lublin</t>
+  </si>
+  <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>Otelul Galati</t>
+  </si>
+  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
@@ -313,7 +427,73 @@
     <t>Dalian Yingbo</t>
   </si>
   <si>
-    <t>2026-07-29 11:49:36</t>
+    <t>Prostejov</t>
+  </si>
+  <si>
+    <t>Kolos Kovalyovka</t>
+  </si>
+  <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Trans Narva</t>
+  </si>
+  <si>
+    <t>AaB</t>
+  </si>
+  <si>
+    <t>Widzew Lodz</t>
+  </si>
+  <si>
+    <t>FC Sellier &amp; Bellot Vlasim</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia</t>
+  </si>
+  <si>
+    <t>Banik Ostrava B</t>
+  </si>
+  <si>
+    <t>FC Blau Weiss Linz</t>
+  </si>
+  <si>
+    <t>FC Liefering</t>
+  </si>
+  <si>
+    <t>SKU Amstetten</t>
+  </si>
+  <si>
+    <t>Rapid Vienna (Am)</t>
+  </si>
+  <si>
+    <t>Bregenz</t>
+  </si>
+  <si>
+    <t>Dukla Prague</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Vejle</t>
+  </si>
+  <si>
+    <t>Arda</t>
+  </si>
+  <si>
+    <t>Jagiellonia Bialystock</t>
+  </si>
+  <si>
+    <t>St Polten</t>
+  </si>
+  <si>
+    <t>Dinamo Bucharest</t>
+  </si>
+  <si>
+    <t>2026-07-29 13:57:47</t>
   </si>
 </sst>
 </file>
@@ -645,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -895,25 +1075,25 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="F2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G2">
         <v>3.45</v>
       </c>
       <c r="H2">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="I2">
         <v>2.68</v>
@@ -922,28 +1102,28 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M2">
         <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="O2">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q2">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S2">
         <v>5.7</v>
@@ -967,7 +1147,7 @@
         <v>7.8</v>
       </c>
       <c r="Z2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA2">
         <v>42</v>
@@ -985,7 +1165,7 @@
         <v>38</v>
       </c>
       <c r="AF2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG2">
         <v>15.5</v>
@@ -1000,7 +1180,7 @@
         <v>1000</v>
       </c>
       <c r="AK2">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="AL2">
         <v>1000</v>
@@ -1033,7 +1213,7 @@
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW2">
         <v>32</v>
@@ -1048,7 +1228,7 @@
         <v>21</v>
       </c>
       <c r="BA2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB2">
         <v>32</v>
@@ -1129,7 +1309,7 @@
         <v>12</v>
       </c>
       <c r="CB2" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1137,19 +1317,19 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="F3">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G3">
         <v>1.78</v>
@@ -1164,10 +1344,10 @@
         <v>3.5</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="M3">
         <v>1.1</v>
@@ -1188,7 +1368,7 @@
         <v>1.22</v>
       </c>
       <c r="S3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T3">
         <v>2.2</v>
@@ -1371,7 +1551,7 @@
         <v>8</v>
       </c>
       <c r="CB3" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1379,16 +1559,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="F4">
         <v>3.55</v>
@@ -1448,7 +1628,7 @@
         <v>12</v>
       </c>
       <c r="Y4">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z4">
         <v>14</v>
@@ -1520,7 +1700,7 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX4">
         <v>22</v>
@@ -1532,10 +1712,10 @@
         <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC4">
         <v>40</v>
@@ -1544,7 +1724,7 @@
         <v>50</v>
       </c>
       <c r="BE4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF4">
         <v>40</v>
@@ -1613,7 +1793,7 @@
         <v>10.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1621,34 +1801,34 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="F5">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G5">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>9.199999999999999</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L5">
         <v>1.36</v>
@@ -1657,25 +1837,25 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
         <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
         <v>3.85</v>
       </c>
       <c r="T5">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
         <v>1.74</v>
@@ -1684,13 +1864,13 @@
         <v>1.12</v>
       </c>
       <c r="W5">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="X5">
         <v>16</v>
       </c>
       <c r="Y5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z5">
         <v>85</v>
@@ -1699,10 +1879,10 @@
         <v>350</v>
       </c>
       <c r="AB5">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD5">
         <v>38</v>
@@ -1711,10 +1891,10 @@
         <v>180</v>
       </c>
       <c r="AF5">
+        <v>8.6</v>
+      </c>
+      <c r="AG5">
         <v>10.5</v>
-      </c>
-      <c r="AG5">
-        <v>12.5</v>
       </c>
       <c r="AH5">
         <v>34</v>
@@ -1723,7 +1903,7 @@
         <v>170</v>
       </c>
       <c r="AJ5">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AK5">
         <v>23</v>
@@ -1735,7 +1915,7 @@
         <v>240</v>
       </c>
       <c r="AN5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO5">
         <v>290</v>
@@ -1744,37 +1924,37 @@
         <v>11</v>
       </c>
       <c r="AQ5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR5">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="AS5">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT5">
         <v>5.9</v>
       </c>
       <c r="AU5">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AV5">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="AW5">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="AX5">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5">
         <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BB5">
         <v>10.5</v>
@@ -1783,16 +1963,16 @@
         <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>3.95</v>
+        <v>34</v>
       </c>
       <c r="BE5">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BF5">
         <v>9.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH5">
         <v>3.35</v>
@@ -1855,7 +2035,7 @@
         <v>7.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1863,19 +2043,19 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="F6">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1887,13 +2067,13 @@
         <v>4.4</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K6">
         <v>4.6</v>
       </c>
       <c r="L6">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M6">
         <v>1.01</v>
@@ -1941,7 +2121,7 @@
         <v>95</v>
       </c>
       <c r="AB6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC6">
         <v>12</v>
@@ -1989,10 +2169,10 @@
         <v>17.5</v>
       </c>
       <c r="AR6">
-        <v>25</v>
+        <v>4.7</v>
       </c>
       <c r="AS6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT6">
         <v>11</v>
@@ -2004,7 +2184,7 @@
         <v>14.5</v>
       </c>
       <c r="AW6">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX6">
         <v>12</v>
@@ -2016,7 +2196,7 @@
         <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BB6">
         <v>18.5</v>
@@ -2025,16 +2205,16 @@
         <v>15</v>
       </c>
       <c r="BD6">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="BE6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BF6">
         <v>7.4</v>
       </c>
       <c r="BG6">
-        <v>23</v>
+        <v>4.6</v>
       </c>
       <c r="BH6">
         <v>4.5</v>
@@ -2097,7 +2277,5331 @@
         <v>6.2</v>
       </c>
       <c r="CB6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7">
+        <v>2.12</v>
+      </c>
+      <c r="G7">
+        <v>2.32</v>
+      </c>
+      <c r="H7">
+        <v>3.3</v>
+      </c>
+      <c r="I7">
+        <v>3.75</v>
+      </c>
+      <c r="J7">
+        <v>3.3</v>
+      </c>
+      <c r="K7">
+        <v>3.95</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>3.1</v>
+      </c>
+      <c r="O7">
+        <v>1.25</v>
+      </c>
+      <c r="P7">
+        <v>2.06</v>
+      </c>
+      <c r="Q7">
+        <v>1.8</v>
+      </c>
+      <c r="R7">
+        <v>1.33</v>
+      </c>
+      <c r="S7">
+        <v>2.92</v>
+      </c>
+      <c r="T7">
+        <v>1.46</v>
+      </c>
+      <c r="U7">
+        <v>1.84</v>
+      </c>
+      <c r="V7">
+        <v>1.36</v>
+      </c>
+      <c r="W7">
+        <v>1.75</v>
+      </c>
+      <c r="X7">
+        <v>25</v>
+      </c>
+      <c r="Y7">
+        <v>21</v>
+      </c>
+      <c r="Z7">
+        <v>38</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>16</v>
+      </c>
+      <c r="AC7">
+        <v>12.5</v>
+      </c>
+      <c r="AD7">
+        <v>21</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>22</v>
+      </c>
+      <c r="AG7">
+        <v>16</v>
+      </c>
+      <c r="AH7">
+        <v>24</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>40</v>
+      </c>
+      <c r="AK7">
+        <v>34</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>10.5</v>
+      </c>
+      <c r="AQ7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR7">
+        <v>15.5</v>
+      </c>
+      <c r="AS7">
+        <v>2.02</v>
+      </c>
+      <c r="AT7">
+        <v>7</v>
+      </c>
+      <c r="AU7">
+        <v>1.74</v>
+      </c>
+      <c r="AV7">
+        <v>1.85</v>
+      </c>
+      <c r="AW7">
+        <v>2.02</v>
+      </c>
+      <c r="AX7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY7">
+        <v>1.8</v>
+      </c>
+      <c r="AZ7">
+        <v>10</v>
+      </c>
+      <c r="BA7">
+        <v>2.02</v>
+      </c>
+      <c r="BB7">
+        <v>16.5</v>
+      </c>
+      <c r="BC7">
+        <v>14</v>
+      </c>
+      <c r="BD7">
+        <v>2.02</v>
+      </c>
+      <c r="BE7">
+        <v>2.02</v>
+      </c>
+      <c r="BF7">
+        <v>2.02</v>
+      </c>
+      <c r="BG7">
+        <v>2.02</v>
+      </c>
+      <c r="BH7">
+        <v>5.1</v>
+      </c>
+      <c r="BI7">
+        <v>2.56</v>
+      </c>
+      <c r="BJ7">
+        <v>13</v>
+      </c>
+      <c r="BK7">
+        <v>2.4</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>2.94</v>
+      </c>
+      <c r="BN7">
+        <v>7.4</v>
+      </c>
+      <c r="BO7">
+        <v>2.1</v>
+      </c>
+      <c r="BP7">
+        <v>22</v>
+      </c>
+      <c r="BQ7">
+        <v>2.6</v>
+      </c>
+      <c r="BR7">
+        <v>38</v>
+      </c>
+      <c r="BS7">
+        <v>2.72</v>
+      </c>
+      <c r="BT7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU7">
+        <v>2.26</v>
+      </c>
+      <c r="BV7">
+        <v>40</v>
+      </c>
+      <c r="BW7">
+        <v>2.74</v>
+      </c>
+      <c r="BX7">
+        <v>50</v>
+      </c>
+      <c r="BY7">
+        <v>2.78</v>
+      </c>
+      <c r="BZ7">
+        <v>30</v>
+      </c>
+      <c r="CA7">
+        <v>2.68</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F8">
+        <v>1.04</v>
+      </c>
+      <c r="G8">
+        <v>600</v>
+      </c>
+      <c r="H8">
+        <v>1.04</v>
+      </c>
+      <c r="I8">
+        <v>870</v>
+      </c>
+      <c r="J8">
+        <v>1.02</v>
+      </c>
+      <c r="K8">
+        <v>950</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>1.08</v>
+      </c>
+      <c r="O8">
+        <v>1.01</v>
+      </c>
+      <c r="P8">
+        <v>1.07</v>
+      </c>
+      <c r="Q8">
+        <v>1.4</v>
+      </c>
+      <c r="R8">
+        <v>1.07</v>
+      </c>
+      <c r="S8">
+        <v>1.41</v>
+      </c>
+      <c r="T8">
+        <v>1.01</v>
+      </c>
+      <c r="U8">
+        <v>1.01</v>
+      </c>
+      <c r="V8">
+        <v>1.01</v>
+      </c>
+      <c r="W8">
+        <v>1.01</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8">
+        <v>1.03</v>
+      </c>
+      <c r="AR8">
+        <v>1.03</v>
+      </c>
+      <c r="AS8">
+        <v>1.03</v>
+      </c>
+      <c r="AT8">
+        <v>1.03</v>
+      </c>
+      <c r="AU8">
+        <v>1.03</v>
+      </c>
+      <c r="AV8">
+        <v>1.03</v>
+      </c>
+      <c r="AW8">
+        <v>1.03</v>
+      </c>
+      <c r="AX8">
+        <v>1.03</v>
+      </c>
+      <c r="AY8">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8">
+        <v>1.03</v>
+      </c>
+      <c r="BA8">
+        <v>1.03</v>
+      </c>
+      <c r="BB8">
+        <v>1.03</v>
+      </c>
+      <c r="BC8">
+        <v>1.03</v>
+      </c>
+      <c r="BD8">
+        <v>1.03</v>
+      </c>
+      <c r="BE8">
+        <v>1.03</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.01</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.01</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" t="s">
         <v>99</v>
+      </c>
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F9">
+        <v>1.7</v>
+      </c>
+      <c r="G9">
+        <v>1.81</v>
+      </c>
+      <c r="H9">
+        <v>5.7</v>
+      </c>
+      <c r="I9">
+        <v>6.6</v>
+      </c>
+      <c r="J9">
+        <v>3.5</v>
+      </c>
+      <c r="K9">
+        <v>3.95</v>
+      </c>
+      <c r="L9">
+        <v>1.45</v>
+      </c>
+      <c r="M9">
+        <v>1.09</v>
+      </c>
+      <c r="N9">
+        <v>3</v>
+      </c>
+      <c r="O9">
+        <v>1.42</v>
+      </c>
+      <c r="P9">
+        <v>1.67</v>
+      </c>
+      <c r="Q9">
+        <v>2.26</v>
+      </c>
+      <c r="R9">
+        <v>1.25</v>
+      </c>
+      <c r="S9">
+        <v>4.2</v>
+      </c>
+      <c r="T9">
+        <v>2.1</v>
+      </c>
+      <c r="U9">
+        <v>1.74</v>
+      </c>
+      <c r="V9">
+        <v>1.18</v>
+      </c>
+      <c r="W9">
+        <v>2.22</v>
+      </c>
+      <c r="X9">
+        <v>13</v>
+      </c>
+      <c r="Y9">
+        <v>19</v>
+      </c>
+      <c r="Z9">
+        <v>60</v>
+      </c>
+      <c r="AA9">
+        <v>230</v>
+      </c>
+      <c r="AB9">
+        <v>7</v>
+      </c>
+      <c r="AC9">
+        <v>10</v>
+      </c>
+      <c r="AD9">
+        <v>29</v>
+      </c>
+      <c r="AE9">
+        <v>130</v>
+      </c>
+      <c r="AF9">
+        <v>11.5</v>
+      </c>
+      <c r="AG9">
+        <v>12.5</v>
+      </c>
+      <c r="AH9">
+        <v>32</v>
+      </c>
+      <c r="AI9">
+        <v>140</v>
+      </c>
+      <c r="AJ9">
+        <v>22</v>
+      </c>
+      <c r="AK9">
+        <v>26</v>
+      </c>
+      <c r="AL9">
+        <v>60</v>
+      </c>
+      <c r="AM9">
+        <v>230</v>
+      </c>
+      <c r="AN9">
+        <v>18</v>
+      </c>
+      <c r="AO9">
+        <v>220</v>
+      </c>
+      <c r="AP9">
+        <v>9.4</v>
+      </c>
+      <c r="AQ9">
+        <v>14</v>
+      </c>
+      <c r="AR9">
+        <v>4.7</v>
+      </c>
+      <c r="AS9">
+        <v>5</v>
+      </c>
+      <c r="AT9">
+        <v>5.9</v>
+      </c>
+      <c r="AU9">
+        <v>7.2</v>
+      </c>
+      <c r="AV9">
+        <v>20</v>
+      </c>
+      <c r="AW9">
+        <v>4.9</v>
+      </c>
+      <c r="AX9">
+        <v>8</v>
+      </c>
+      <c r="AY9">
+        <v>9</v>
+      </c>
+      <c r="AZ9">
+        <v>21</v>
+      </c>
+      <c r="BA9">
+        <v>4.9</v>
+      </c>
+      <c r="BB9">
+        <v>15</v>
+      </c>
+      <c r="BC9">
+        <v>18</v>
+      </c>
+      <c r="BD9">
+        <v>4.7</v>
+      </c>
+      <c r="BE9">
+        <v>5</v>
+      </c>
+      <c r="BF9">
+        <v>11</v>
+      </c>
+      <c r="BG9">
+        <v>5</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>16</v>
+      </c>
+      <c r="BK9">
+        <v>7.6</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>5.4</v>
+      </c>
+      <c r="BO9">
+        <v>2.88</v>
+      </c>
+      <c r="BP9">
+        <v>17</v>
+      </c>
+      <c r="BQ9">
+        <v>8</v>
+      </c>
+      <c r="BR9">
+        <v>46</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>13</v>
+      </c>
+      <c r="BU9">
+        <v>6.2</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>42</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F10">
+        <v>1.71</v>
+      </c>
+      <c r="G10">
+        <v>1.82</v>
+      </c>
+      <c r="H10">
+        <v>4.7</v>
+      </c>
+      <c r="I10">
+        <v>5.9</v>
+      </c>
+      <c r="J10">
+        <v>4.1</v>
+      </c>
+      <c r="K10">
+        <v>4.6</v>
+      </c>
+      <c r="L10">
+        <v>1.28</v>
+      </c>
+      <c r="M10">
+        <v>1.04</v>
+      </c>
+      <c r="N10">
+        <v>4.6</v>
+      </c>
+      <c r="O10">
+        <v>1.23</v>
+      </c>
+      <c r="P10">
+        <v>2.24</v>
+      </c>
+      <c r="Q10">
+        <v>1.67</v>
+      </c>
+      <c r="R10">
+        <v>1.5</v>
+      </c>
+      <c r="S10">
+        <v>2.62</v>
+      </c>
+      <c r="T10">
+        <v>1.7</v>
+      </c>
+      <c r="U10">
+        <v>2.22</v>
+      </c>
+      <c r="V10">
+        <v>1.2</v>
+      </c>
+      <c r="W10">
+        <v>2.22</v>
+      </c>
+      <c r="X10">
+        <v>24</v>
+      </c>
+      <c r="Y10">
+        <v>24</v>
+      </c>
+      <c r="Z10">
+        <v>46</v>
+      </c>
+      <c r="AA10">
+        <v>130</v>
+      </c>
+      <c r="AB10">
+        <v>12.5</v>
+      </c>
+      <c r="AC10">
+        <v>10</v>
+      </c>
+      <c r="AD10">
+        <v>23</v>
+      </c>
+      <c r="AE10">
+        <v>70</v>
+      </c>
+      <c r="AF10">
+        <v>14</v>
+      </c>
+      <c r="AG10">
+        <v>12</v>
+      </c>
+      <c r="AH10">
+        <v>21</v>
+      </c>
+      <c r="AI10">
+        <v>65</v>
+      </c>
+      <c r="AJ10">
+        <v>22</v>
+      </c>
+      <c r="AK10">
+        <v>20</v>
+      </c>
+      <c r="AL10">
+        <v>36</v>
+      </c>
+      <c r="AM10">
+        <v>85</v>
+      </c>
+      <c r="AN10">
+        <v>10</v>
+      </c>
+      <c r="AO10">
+        <v>65</v>
+      </c>
+      <c r="AP10">
+        <v>15.5</v>
+      </c>
+      <c r="AQ10">
+        <v>16</v>
+      </c>
+      <c r="AR10">
+        <v>30</v>
+      </c>
+      <c r="AS10">
+        <v>80</v>
+      </c>
+      <c r="AT10">
+        <v>8.4</v>
+      </c>
+      <c r="AU10">
+        <v>8.6</v>
+      </c>
+      <c r="AV10">
+        <v>15</v>
+      </c>
+      <c r="AW10">
+        <v>42</v>
+      </c>
+      <c r="AX10">
+        <v>9.4</v>
+      </c>
+      <c r="AY10">
+        <v>8</v>
+      </c>
+      <c r="AZ10">
+        <v>13.5</v>
+      </c>
+      <c r="BA10">
+        <v>42</v>
+      </c>
+      <c r="BB10">
+        <v>14</v>
+      </c>
+      <c r="BC10">
+        <v>13</v>
+      </c>
+      <c r="BD10">
+        <v>22</v>
+      </c>
+      <c r="BE10">
+        <v>60</v>
+      </c>
+      <c r="BF10">
+        <v>6.8</v>
+      </c>
+      <c r="BG10">
+        <v>40</v>
+      </c>
+      <c r="BH10">
+        <v>4.1</v>
+      </c>
+      <c r="BI10">
+        <v>3.6</v>
+      </c>
+      <c r="BJ10">
+        <v>9.6</v>
+      </c>
+      <c r="BK10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>21</v>
+      </c>
+      <c r="BN10">
+        <v>4.7</v>
+      </c>
+      <c r="BO10">
+        <v>4.1</v>
+      </c>
+      <c r="BP10">
+        <v>11.5</v>
+      </c>
+      <c r="BQ10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>19.5</v>
+      </c>
+      <c r="BT10">
+        <v>8.6</v>
+      </c>
+      <c r="BU10">
+        <v>7.4</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>28</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>30</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" t="s">
+        <v>141</v>
+      </c>
+      <c r="F11">
+        <v>1.8</v>
+      </c>
+      <c r="G11">
+        <v>2.32</v>
+      </c>
+      <c r="H11">
+        <v>3.05</v>
+      </c>
+      <c r="I11">
+        <v>3.9</v>
+      </c>
+      <c r="J11">
+        <v>3.65</v>
+      </c>
+      <c r="K11">
+        <v>950</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>2.96</v>
+      </c>
+      <c r="O11">
+        <v>1.13</v>
+      </c>
+      <c r="P11">
+        <v>2.42</v>
+      </c>
+      <c r="Q11">
+        <v>1.5</v>
+      </c>
+      <c r="R11">
+        <v>1.6</v>
+      </c>
+      <c r="S11">
+        <v>2.12</v>
+      </c>
+      <c r="T11">
+        <v>1.11</v>
+      </c>
+      <c r="U11">
+        <v>1.11</v>
+      </c>
+      <c r="V11">
+        <v>1.31</v>
+      </c>
+      <c r="W11">
+        <v>1.75</v>
+      </c>
+      <c r="X11">
+        <v>1000</v>
+      </c>
+      <c r="Y11">
+        <v>1000</v>
+      </c>
+      <c r="Z11">
+        <v>1000</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>1000</v>
+      </c>
+      <c r="AC11">
+        <v>1000</v>
+      </c>
+      <c r="AD11">
+        <v>1000</v>
+      </c>
+      <c r="AE11">
+        <v>1000</v>
+      </c>
+      <c r="AF11">
+        <v>1000</v>
+      </c>
+      <c r="AG11">
+        <v>1000</v>
+      </c>
+      <c r="AH11">
+        <v>1000</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
+        <v>1000</v>
+      </c>
+      <c r="AK11">
+        <v>1000</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>1000</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11">
+        <v>1.01</v>
+      </c>
+      <c r="AR11">
+        <v>1.01</v>
+      </c>
+      <c r="AS11">
+        <v>1.01</v>
+      </c>
+      <c r="AT11">
+        <v>1.01</v>
+      </c>
+      <c r="AU11">
+        <v>1.01</v>
+      </c>
+      <c r="AV11">
+        <v>1.01</v>
+      </c>
+      <c r="AW11">
+        <v>1.01</v>
+      </c>
+      <c r="AX11">
+        <v>1.01</v>
+      </c>
+      <c r="AY11">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11">
+        <v>1.01</v>
+      </c>
+      <c r="BA11">
+        <v>1.01</v>
+      </c>
+      <c r="BB11">
+        <v>1.01</v>
+      </c>
+      <c r="BC11">
+        <v>1.01</v>
+      </c>
+      <c r="BD11">
+        <v>1.01</v>
+      </c>
+      <c r="BE11">
+        <v>1.01</v>
+      </c>
+      <c r="BF11">
+        <v>1.01</v>
+      </c>
+      <c r="BG11">
+        <v>1.01</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>1.01</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.01</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>1.01</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.01</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.01</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>1.01</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.01</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12">
+        <v>2.5</v>
+      </c>
+      <c r="G12">
+        <v>2.8</v>
+      </c>
+      <c r="H12">
+        <v>2.64</v>
+      </c>
+      <c r="I12">
+        <v>3.05</v>
+      </c>
+      <c r="J12">
+        <v>3.65</v>
+      </c>
+      <c r="K12">
+        <v>4.3</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.04</v>
+      </c>
+      <c r="N12">
+        <v>4.4</v>
+      </c>
+      <c r="O12">
+        <v>1.21</v>
+      </c>
+      <c r="P12">
+        <v>2.3</v>
+      </c>
+      <c r="Q12">
+        <v>1.61</v>
+      </c>
+      <c r="R12">
+        <v>1.5</v>
+      </c>
+      <c r="S12">
+        <v>2.56</v>
+      </c>
+      <c r="T12">
+        <v>1.57</v>
+      </c>
+      <c r="U12">
+        <v>2.44</v>
+      </c>
+      <c r="V12">
+        <v>1.5</v>
+      </c>
+      <c r="W12">
+        <v>1.57</v>
+      </c>
+      <c r="X12">
+        <v>27</v>
+      </c>
+      <c r="Y12">
+        <v>19</v>
+      </c>
+      <c r="Z12">
+        <v>26</v>
+      </c>
+      <c r="AA12">
+        <v>50</v>
+      </c>
+      <c r="AB12">
+        <v>18</v>
+      </c>
+      <c r="AC12">
+        <v>11.5</v>
+      </c>
+      <c r="AD12">
+        <v>16</v>
+      </c>
+      <c r="AE12">
+        <v>34</v>
+      </c>
+      <c r="AF12">
+        <v>24</v>
+      </c>
+      <c r="AG12">
+        <v>15</v>
+      </c>
+      <c r="AH12">
+        <v>18.5</v>
+      </c>
+      <c r="AI12">
+        <v>40</v>
+      </c>
+      <c r="AJ12">
+        <v>44</v>
+      </c>
+      <c r="AK12">
+        <v>30</v>
+      </c>
+      <c r="AL12">
+        <v>38</v>
+      </c>
+      <c r="AM12">
+        <v>75</v>
+      </c>
+      <c r="AN12">
+        <v>19</v>
+      </c>
+      <c r="AO12">
+        <v>22</v>
+      </c>
+      <c r="AP12">
+        <v>16</v>
+      </c>
+      <c r="AQ12">
+        <v>11</v>
+      </c>
+      <c r="AR12">
+        <v>15.5</v>
+      </c>
+      <c r="AS12">
+        <v>3.9</v>
+      </c>
+      <c r="AT12">
+        <v>10.5</v>
+      </c>
+      <c r="AU12">
+        <v>7</v>
+      </c>
+      <c r="AV12">
+        <v>9.6</v>
+      </c>
+      <c r="AW12">
+        <v>19.5</v>
+      </c>
+      <c r="AX12">
+        <v>14</v>
+      </c>
+      <c r="AY12">
+        <v>9</v>
+      </c>
+      <c r="AZ12">
+        <v>11</v>
+      </c>
+      <c r="BA12">
+        <v>3.85</v>
+      </c>
+      <c r="BB12">
+        <v>3.85</v>
+      </c>
+      <c r="BC12">
+        <v>18</v>
+      </c>
+      <c r="BD12">
+        <v>3.8</v>
+      </c>
+      <c r="BE12">
+        <v>4</v>
+      </c>
+      <c r="BF12">
+        <v>11</v>
+      </c>
+      <c r="BG12">
+        <v>12.5</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.01</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.01</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>1.01</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.01</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.01</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>1.01</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.01</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F13">
+        <v>3.5</v>
+      </c>
+      <c r="G13">
+        <v>3.7</v>
+      </c>
+      <c r="H13">
+        <v>2.48</v>
+      </c>
+      <c r="I13">
+        <v>2.64</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13">
+        <v>3.35</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.09</v>
+      </c>
+      <c r="N13">
+        <v>2.82</v>
+      </c>
+      <c r="O13">
+        <v>1.43</v>
+      </c>
+      <c r="P13">
+        <v>1.63</v>
+      </c>
+      <c r="Q13">
+        <v>2.32</v>
+      </c>
+      <c r="R13">
+        <v>1.22</v>
+      </c>
+      <c r="S13">
+        <v>4.1</v>
+      </c>
+      <c r="T13">
+        <v>1.11</v>
+      </c>
+      <c r="U13">
+        <v>1.9</v>
+      </c>
+      <c r="V13">
+        <v>1.61</v>
+      </c>
+      <c r="W13">
+        <v>1.37</v>
+      </c>
+      <c r="X13">
+        <v>11.5</v>
+      </c>
+      <c r="Y13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>1000</v>
+      </c>
+      <c r="AC13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>1000</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.28</v>
+      </c>
+      <c r="AQ13">
+        <v>7.2</v>
+      </c>
+      <c r="AR13">
+        <v>1.45</v>
+      </c>
+      <c r="AS13">
+        <v>1.45</v>
+      </c>
+      <c r="AT13">
+        <v>1.45</v>
+      </c>
+      <c r="AU13">
+        <v>6</v>
+      </c>
+      <c r="AV13">
+        <v>1.45</v>
+      </c>
+      <c r="AW13">
+        <v>1.45</v>
+      </c>
+      <c r="AX13">
+        <v>1.45</v>
+      </c>
+      <c r="AY13">
+        <v>1.45</v>
+      </c>
+      <c r="AZ13">
+        <v>1.45</v>
+      </c>
+      <c r="BA13">
+        <v>1.45</v>
+      </c>
+      <c r="BB13">
+        <v>1.45</v>
+      </c>
+      <c r="BC13">
+        <v>1.45</v>
+      </c>
+      <c r="BD13">
+        <v>1.45</v>
+      </c>
+      <c r="BE13">
+        <v>1.45</v>
+      </c>
+      <c r="BF13">
+        <v>1.45</v>
+      </c>
+      <c r="BG13">
+        <v>1.45</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13">
+        <v>14.5</v>
+      </c>
+      <c r="BK13">
+        <v>6.8</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>21</v>
+      </c>
+      <c r="BN13">
+        <v>8.6</v>
+      </c>
+      <c r="BO13">
+        <v>4.3</v>
+      </c>
+      <c r="BP13">
+        <v>44</v>
+      </c>
+      <c r="BQ13">
+        <v>18.5</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>21</v>
+      </c>
+      <c r="BT13">
+        <v>7</v>
+      </c>
+      <c r="BU13">
+        <v>3.55</v>
+      </c>
+      <c r="BV13">
+        <v>29</v>
+      </c>
+      <c r="BW13">
+        <v>13</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>21</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" t="s">
+        <v>144</v>
+      </c>
+      <c r="F14">
+        <v>1.69</v>
+      </c>
+      <c r="G14">
+        <v>1.78</v>
+      </c>
+      <c r="H14">
+        <v>5.1</v>
+      </c>
+      <c r="I14">
+        <v>5.9</v>
+      </c>
+      <c r="J14">
+        <v>3.75</v>
+      </c>
+      <c r="K14">
+        <v>4.3</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.06</v>
+      </c>
+      <c r="N14">
+        <v>3.95</v>
+      </c>
+      <c r="O14">
+        <v>1.28</v>
+      </c>
+      <c r="P14">
+        <v>2.02</v>
+      </c>
+      <c r="Q14">
+        <v>1.72</v>
+      </c>
+      <c r="R14">
+        <v>1.4</v>
+      </c>
+      <c r="S14">
+        <v>2.9</v>
+      </c>
+      <c r="T14">
+        <v>1.73</v>
+      </c>
+      <c r="U14">
+        <v>2.04</v>
+      </c>
+      <c r="V14">
+        <v>1.2</v>
+      </c>
+      <c r="W14">
+        <v>2.28</v>
+      </c>
+      <c r="X14">
+        <v>17.5</v>
+      </c>
+      <c r="Y14">
+        <v>20</v>
+      </c>
+      <c r="Z14">
+        <v>44</v>
+      </c>
+      <c r="AA14">
+        <v>130</v>
+      </c>
+      <c r="AB14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC14">
+        <v>10.5</v>
+      </c>
+      <c r="AD14">
+        <v>23</v>
+      </c>
+      <c r="AE14">
+        <v>75</v>
+      </c>
+      <c r="AF14">
+        <v>12.5</v>
+      </c>
+      <c r="AG14">
+        <v>11.5</v>
+      </c>
+      <c r="AH14">
+        <v>23</v>
+      </c>
+      <c r="AI14">
+        <v>80</v>
+      </c>
+      <c r="AJ14">
+        <v>21</v>
+      </c>
+      <c r="AK14">
+        <v>21</v>
+      </c>
+      <c r="AL14">
+        <v>38</v>
+      </c>
+      <c r="AM14">
+        <v>130</v>
+      </c>
+      <c r="AN14">
+        <v>12</v>
+      </c>
+      <c r="AO14">
+        <v>85</v>
+      </c>
+      <c r="AP14">
+        <v>12</v>
+      </c>
+      <c r="AQ14">
+        <v>13</v>
+      </c>
+      <c r="AR14">
+        <v>28</v>
+      </c>
+      <c r="AS14">
+        <v>95</v>
+      </c>
+      <c r="AT14">
+        <v>6.8</v>
+      </c>
+      <c r="AU14">
+        <v>7.4</v>
+      </c>
+      <c r="AV14">
+        <v>14.5</v>
+      </c>
+      <c r="AW14">
+        <v>55</v>
+      </c>
+      <c r="AX14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY14">
+        <v>7.6</v>
+      </c>
+      <c r="AZ14">
+        <v>15</v>
+      </c>
+      <c r="BA14">
+        <v>50</v>
+      </c>
+      <c r="BB14">
+        <v>15</v>
+      </c>
+      <c r="BC14">
+        <v>14.5</v>
+      </c>
+      <c r="BD14">
+        <v>26</v>
+      </c>
+      <c r="BE14">
+        <v>90</v>
+      </c>
+      <c r="BF14">
+        <v>8.6</v>
+      </c>
+      <c r="BG14">
+        <v>50</v>
+      </c>
+      <c r="BH14">
+        <v>4.4</v>
+      </c>
+      <c r="BI14">
+        <v>2.74</v>
+      </c>
+      <c r="BJ14">
+        <v>13.5</v>
+      </c>
+      <c r="BK14">
+        <v>6.4</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>21</v>
+      </c>
+      <c r="BN14">
+        <v>5.9</v>
+      </c>
+      <c r="BO14">
+        <v>3.15</v>
+      </c>
+      <c r="BP14">
+        <v>17</v>
+      </c>
+      <c r="BQ14">
+        <v>7.8</v>
+      </c>
+      <c r="BR14">
+        <v>36</v>
+      </c>
+      <c r="BS14">
+        <v>16.5</v>
+      </c>
+      <c r="BT14">
+        <v>11.5</v>
+      </c>
+      <c r="BU14">
+        <v>5.6</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>21</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>21</v>
+      </c>
+      <c r="BZ14">
+        <v>29</v>
+      </c>
+      <c r="CA14">
+        <v>13</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" t="s">
+        <v>145</v>
+      </c>
+      <c r="F15">
+        <v>2.98</v>
+      </c>
+      <c r="G15">
+        <v>3.35</v>
+      </c>
+      <c r="H15">
+        <v>2.4</v>
+      </c>
+      <c r="I15">
+        <v>2.64</v>
+      </c>
+      <c r="J15">
+        <v>3.25</v>
+      </c>
+      <c r="K15">
+        <v>3.65</v>
+      </c>
+      <c r="L15">
+        <v>1.39</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>1.01</v>
+      </c>
+      <c r="O15">
+        <v>1.33</v>
+      </c>
+      <c r="P15">
+        <v>1.83</v>
+      </c>
+      <c r="Q15">
+        <v>1.99</v>
+      </c>
+      <c r="R15">
+        <v>1.18</v>
+      </c>
+      <c r="S15">
+        <v>1.99</v>
+      </c>
+      <c r="T15">
+        <v>1.01</v>
+      </c>
+      <c r="U15">
+        <v>1.01</v>
+      </c>
+      <c r="V15">
+        <v>1.61</v>
+      </c>
+      <c r="W15">
+        <v>1.44</v>
+      </c>
+      <c r="X15">
+        <v>18.5</v>
+      </c>
+      <c r="Y15">
+        <v>14.5</v>
+      </c>
+      <c r="Z15">
+        <v>23</v>
+      </c>
+      <c r="AA15">
+        <v>50</v>
+      </c>
+      <c r="AB15">
+        <v>16.5</v>
+      </c>
+      <c r="AC15">
+        <v>10.5</v>
+      </c>
+      <c r="AD15">
+        <v>16.5</v>
+      </c>
+      <c r="AE15">
+        <v>40</v>
+      </c>
+      <c r="AF15">
+        <v>30</v>
+      </c>
+      <c r="AG15">
+        <v>19</v>
+      </c>
+      <c r="AH15">
+        <v>25</v>
+      </c>
+      <c r="AI15">
+        <v>60</v>
+      </c>
+      <c r="AJ15">
+        <v>75</v>
+      </c>
+      <c r="AK15">
+        <v>50</v>
+      </c>
+      <c r="AL15">
+        <v>65</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>2.3</v>
+      </c>
+      <c r="AQ15">
+        <v>2.22</v>
+      </c>
+      <c r="AR15">
+        <v>11.5</v>
+      </c>
+      <c r="AS15">
+        <v>2.48</v>
+      </c>
+      <c r="AT15">
+        <v>2.26</v>
+      </c>
+      <c r="AU15">
+        <v>2.1</v>
+      </c>
+      <c r="AV15">
+        <v>2.26</v>
+      </c>
+      <c r="AW15">
+        <v>19.5</v>
+      </c>
+      <c r="AX15">
+        <v>2.4</v>
+      </c>
+      <c r="AY15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ15">
+        <v>2.36</v>
+      </c>
+      <c r="BA15">
+        <v>2.5</v>
+      </c>
+      <c r="BB15">
+        <v>2.52</v>
+      </c>
+      <c r="BC15">
+        <v>23</v>
+      </c>
+      <c r="BD15">
+        <v>2.52</v>
+      </c>
+      <c r="BE15">
+        <v>2.62</v>
+      </c>
+      <c r="BF15">
+        <v>2.62</v>
+      </c>
+      <c r="BG15">
+        <v>2.62</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15">
+        <v>13.5</v>
+      </c>
+      <c r="BK15">
+        <v>5.9</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>21</v>
+      </c>
+      <c r="BN15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO15">
+        <v>4.1</v>
+      </c>
+      <c r="BP15">
+        <v>36</v>
+      </c>
+      <c r="BQ15">
+        <v>15</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>21</v>
+      </c>
+      <c r="BT15">
+        <v>7.6</v>
+      </c>
+      <c r="BU15">
+        <v>3.55</v>
+      </c>
+      <c r="BV15">
+        <v>28</v>
+      </c>
+      <c r="BW15">
+        <v>12</v>
+      </c>
+      <c r="BX15">
+        <v>48</v>
+      </c>
+      <c r="BY15">
+        <v>19</v>
+      </c>
+      <c r="BZ15">
+        <v>44</v>
+      </c>
+      <c r="CA15">
+        <v>16.5</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16">
+        <v>2.92</v>
+      </c>
+      <c r="G16">
+        <v>3.25</v>
+      </c>
+      <c r="H16">
+        <v>2.46</v>
+      </c>
+      <c r="I16">
+        <v>2.72</v>
+      </c>
+      <c r="J16">
+        <v>3.3</v>
+      </c>
+      <c r="K16">
+        <v>3.6</v>
+      </c>
+      <c r="L16">
+        <v>1.36</v>
+      </c>
+      <c r="M16">
+        <v>1.08</v>
+      </c>
+      <c r="N16">
+        <v>3.4</v>
+      </c>
+      <c r="O16">
+        <v>1.34</v>
+      </c>
+      <c r="P16">
+        <v>1.84</v>
+      </c>
+      <c r="Q16">
+        <v>2.02</v>
+      </c>
+      <c r="R16">
+        <v>1.32</v>
+      </c>
+      <c r="S16">
+        <v>3.6</v>
+      </c>
+      <c r="T16">
+        <v>1.78</v>
+      </c>
+      <c r="U16">
+        <v>2.1</v>
+      </c>
+      <c r="V16">
+        <v>1.58</v>
+      </c>
+      <c r="W16">
+        <v>1.44</v>
+      </c>
+      <c r="X16">
+        <v>16</v>
+      </c>
+      <c r="Y16">
+        <v>12.5</v>
+      </c>
+      <c r="Z16">
+        <v>21</v>
+      </c>
+      <c r="AA16">
+        <v>46</v>
+      </c>
+      <c r="AB16">
+        <v>14</v>
+      </c>
+      <c r="AC16">
+        <v>9.4</v>
+      </c>
+      <c r="AD16">
+        <v>14.5</v>
+      </c>
+      <c r="AE16">
+        <v>36</v>
+      </c>
+      <c r="AF16">
+        <v>26</v>
+      </c>
+      <c r="AG16">
+        <v>16.5</v>
+      </c>
+      <c r="AH16">
+        <v>22</v>
+      </c>
+      <c r="AI16">
+        <v>55</v>
+      </c>
+      <c r="AJ16">
+        <v>65</v>
+      </c>
+      <c r="AK16">
+        <v>44</v>
+      </c>
+      <c r="AL16">
+        <v>60</v>
+      </c>
+      <c r="AM16">
+        <v>120</v>
+      </c>
+      <c r="AN16">
+        <v>42</v>
+      </c>
+      <c r="AO16">
+        <v>32</v>
+      </c>
+      <c r="AP16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ16">
+        <v>7.6</v>
+      </c>
+      <c r="AR16">
+        <v>12</v>
+      </c>
+      <c r="AS16">
+        <v>27</v>
+      </c>
+      <c r="AT16">
+        <v>8.6</v>
+      </c>
+      <c r="AU16">
+        <v>5.9</v>
+      </c>
+      <c r="AV16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW16">
+        <v>21</v>
+      </c>
+      <c r="AX16">
+        <v>15</v>
+      </c>
+      <c r="AY16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ16">
+        <v>12.5</v>
+      </c>
+      <c r="BA16">
+        <v>30</v>
+      </c>
+      <c r="BB16">
+        <v>36</v>
+      </c>
+      <c r="BC16">
+        <v>26</v>
+      </c>
+      <c r="BD16">
+        <v>34</v>
+      </c>
+      <c r="BE16">
+        <v>70</v>
+      </c>
+      <c r="BF16">
+        <v>24</v>
+      </c>
+      <c r="BG16">
+        <v>18</v>
+      </c>
+      <c r="BH16">
+        <v>3.3</v>
+      </c>
+      <c r="BI16">
+        <v>2.98</v>
+      </c>
+      <c r="BJ16">
+        <v>9.6</v>
+      </c>
+      <c r="BK16">
+        <v>5.9</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>21</v>
+      </c>
+      <c r="BN16">
+        <v>6.2</v>
+      </c>
+      <c r="BO16">
+        <v>4.6</v>
+      </c>
+      <c r="BP16">
+        <v>25</v>
+      </c>
+      <c r="BQ16">
+        <v>14</v>
+      </c>
+      <c r="BR16">
+        <v>38</v>
+      </c>
+      <c r="BS16">
+        <v>21</v>
+      </c>
+      <c r="BT16">
+        <v>5.6</v>
+      </c>
+      <c r="BU16">
+        <v>4.2</v>
+      </c>
+      <c r="BV16">
+        <v>20</v>
+      </c>
+      <c r="BW16">
+        <v>17</v>
+      </c>
+      <c r="BX16">
+        <v>34</v>
+      </c>
+      <c r="BY16">
+        <v>20</v>
+      </c>
+      <c r="BZ16">
+        <v>30</v>
+      </c>
+      <c r="CA16">
+        <v>21</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17">
+        <v>3.55</v>
+      </c>
+      <c r="G17">
+        <v>4.2</v>
+      </c>
+      <c r="H17">
+        <v>1.99</v>
+      </c>
+      <c r="I17">
+        <v>2.12</v>
+      </c>
+      <c r="J17">
+        <v>3.8</v>
+      </c>
+      <c r="K17">
+        <v>4.2</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.03</v>
+      </c>
+      <c r="N17">
+        <v>2.22</v>
+      </c>
+      <c r="O17">
+        <v>1.21</v>
+      </c>
+      <c r="P17">
+        <v>2.22</v>
+      </c>
+      <c r="Q17">
+        <v>1.67</v>
+      </c>
+      <c r="R17">
+        <v>1.48</v>
+      </c>
+      <c r="S17">
+        <v>2.52</v>
+      </c>
+      <c r="T17">
+        <v>1.01</v>
+      </c>
+      <c r="U17">
+        <v>1.01</v>
+      </c>
+      <c r="V17">
+        <v>1.89</v>
+      </c>
+      <c r="W17">
+        <v>1.31</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>1000</v>
+      </c>
+      <c r="AC17">
+        <v>1000</v>
+      </c>
+      <c r="AD17">
+        <v>1000</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
+        <v>1000</v>
+      </c>
+      <c r="AH17">
+        <v>1000</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17">
+        <v>1.01</v>
+      </c>
+      <c r="AR17">
+        <v>1.01</v>
+      </c>
+      <c r="AS17">
+        <v>1.01</v>
+      </c>
+      <c r="AT17">
+        <v>1.01</v>
+      </c>
+      <c r="AU17">
+        <v>1.01</v>
+      </c>
+      <c r="AV17">
+        <v>1.01</v>
+      </c>
+      <c r="AW17">
+        <v>1.01</v>
+      </c>
+      <c r="AX17">
+        <v>1.01</v>
+      </c>
+      <c r="AY17">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17">
+        <v>1.01</v>
+      </c>
+      <c r="BA17">
+        <v>1.01</v>
+      </c>
+      <c r="BB17">
+        <v>1.01</v>
+      </c>
+      <c r="BC17">
+        <v>1.01</v>
+      </c>
+      <c r="BD17">
+        <v>1.01</v>
+      </c>
+      <c r="BE17">
+        <v>1.01</v>
+      </c>
+      <c r="BF17">
+        <v>1.01</v>
+      </c>
+      <c r="BG17">
+        <v>1.01</v>
+      </c>
+      <c r="BH17">
+        <v>5.3</v>
+      </c>
+      <c r="BI17">
+        <v>2.86</v>
+      </c>
+      <c r="BJ17">
+        <v>12.5</v>
+      </c>
+      <c r="BK17">
+        <v>5.9</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>21</v>
+      </c>
+      <c r="BN17">
+        <v>10</v>
+      </c>
+      <c r="BO17">
+        <v>4.9</v>
+      </c>
+      <c r="BP17">
+        <v>38</v>
+      </c>
+      <c r="BQ17">
+        <v>17.5</v>
+      </c>
+      <c r="BR17">
+        <v>48</v>
+      </c>
+      <c r="BS17">
+        <v>21</v>
+      </c>
+      <c r="BT17">
+        <v>6.6</v>
+      </c>
+      <c r="BU17">
+        <v>3.45</v>
+      </c>
+      <c r="BV17">
+        <v>18.5</v>
+      </c>
+      <c r="BW17">
+        <v>8.4</v>
+      </c>
+      <c r="BX17">
+        <v>34</v>
+      </c>
+      <c r="BY17">
+        <v>15</v>
+      </c>
+      <c r="BZ17">
+        <v>25</v>
+      </c>
+      <c r="CA17">
+        <v>11.5</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18">
+        <v>3.9</v>
+      </c>
+      <c r="G18">
+        <v>4.6</v>
+      </c>
+      <c r="H18">
+        <v>1.79</v>
+      </c>
+      <c r="I18">
+        <v>1.97</v>
+      </c>
+      <c r="J18">
+        <v>3.65</v>
+      </c>
+      <c r="K18">
+        <v>4.8</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.03</v>
+      </c>
+      <c r="N18">
+        <v>4.8</v>
+      </c>
+      <c r="O18">
+        <v>1.16</v>
+      </c>
+      <c r="P18">
+        <v>2.44</v>
+      </c>
+      <c r="Q18">
+        <v>1.55</v>
+      </c>
+      <c r="R18">
+        <v>1.56</v>
+      </c>
+      <c r="S18">
+        <v>2.32</v>
+      </c>
+      <c r="T18">
+        <v>1.01</v>
+      </c>
+      <c r="U18">
+        <v>1.01</v>
+      </c>
+      <c r="V18">
+        <v>2.02</v>
+      </c>
+      <c r="W18">
+        <v>1.27</v>
+      </c>
+      <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>1000</v>
+      </c>
+      <c r="AC18">
+        <v>1000</v>
+      </c>
+      <c r="AD18">
+        <v>1000</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>1000</v>
+      </c>
+      <c r="AG18">
+        <v>1000</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18">
+        <v>1.01</v>
+      </c>
+      <c r="AR18">
+        <v>1.01</v>
+      </c>
+      <c r="AS18">
+        <v>1.01</v>
+      </c>
+      <c r="AT18">
+        <v>1.01</v>
+      </c>
+      <c r="AU18">
+        <v>1.01</v>
+      </c>
+      <c r="AV18">
+        <v>1.01</v>
+      </c>
+      <c r="AW18">
+        <v>1.01</v>
+      </c>
+      <c r="AX18">
+        <v>1.01</v>
+      </c>
+      <c r="AY18">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18">
+        <v>1.01</v>
+      </c>
+      <c r="BA18">
+        <v>1.01</v>
+      </c>
+      <c r="BB18">
+        <v>1.01</v>
+      </c>
+      <c r="BC18">
+        <v>1.01</v>
+      </c>
+      <c r="BD18">
+        <v>1.01</v>
+      </c>
+      <c r="BE18">
+        <v>1.01</v>
+      </c>
+      <c r="BF18">
+        <v>1.01</v>
+      </c>
+      <c r="BG18">
+        <v>1.01</v>
+      </c>
+      <c r="BH18">
+        <v>5.7</v>
+      </c>
+      <c r="BI18">
+        <v>3.2</v>
+      </c>
+      <c r="BJ18">
+        <v>12</v>
+      </c>
+      <c r="BK18">
+        <v>6.2</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>22</v>
+      </c>
+      <c r="BN18">
+        <v>10.5</v>
+      </c>
+      <c r="BO18">
+        <v>5.5</v>
+      </c>
+      <c r="BP18">
+        <v>38</v>
+      </c>
+      <c r="BQ18">
+        <v>19</v>
+      </c>
+      <c r="BR18">
+        <v>44</v>
+      </c>
+      <c r="BS18">
+        <v>22</v>
+      </c>
+      <c r="BT18">
+        <v>6.4</v>
+      </c>
+      <c r="BU18">
+        <v>3.55</v>
+      </c>
+      <c r="BV18">
+        <v>16</v>
+      </c>
+      <c r="BW18">
+        <v>8</v>
+      </c>
+      <c r="BX18">
+        <v>29</v>
+      </c>
+      <c r="BY18">
+        <v>14</v>
+      </c>
+      <c r="BZ18">
+        <v>19.5</v>
+      </c>
+      <c r="CA18">
+        <v>9.6</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" t="s">
+        <v>149</v>
+      </c>
+      <c r="F19">
+        <v>2.16</v>
+      </c>
+      <c r="G19">
+        <v>2.34</v>
+      </c>
+      <c r="H19">
+        <v>3.15</v>
+      </c>
+      <c r="I19">
+        <v>3.55</v>
+      </c>
+      <c r="J19">
+        <v>3.8</v>
+      </c>
+      <c r="K19">
+        <v>4.1</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.04</v>
+      </c>
+      <c r="N19">
+        <v>2.26</v>
+      </c>
+      <c r="O19">
+        <v>1.21</v>
+      </c>
+      <c r="P19">
+        <v>2.26</v>
+      </c>
+      <c r="Q19">
+        <v>1.67</v>
+      </c>
+      <c r="R19">
+        <v>1.47</v>
+      </c>
+      <c r="S19">
+        <v>2.56</v>
+      </c>
+      <c r="T19">
+        <v>1.01</v>
+      </c>
+      <c r="U19">
+        <v>1.01</v>
+      </c>
+      <c r="V19">
+        <v>1.39</v>
+      </c>
+      <c r="W19">
+        <v>1.74</v>
+      </c>
+      <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>1000</v>
+      </c>
+      <c r="AC19">
+        <v>1000</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>1000</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>1.01</v>
+      </c>
+      <c r="AQ19">
+        <v>1.01</v>
+      </c>
+      <c r="AR19">
+        <v>1.01</v>
+      </c>
+      <c r="AS19">
+        <v>1.01</v>
+      </c>
+      <c r="AT19">
+        <v>1.01</v>
+      </c>
+      <c r="AU19">
+        <v>1.01</v>
+      </c>
+      <c r="AV19">
+        <v>1.01</v>
+      </c>
+      <c r="AW19">
+        <v>1.01</v>
+      </c>
+      <c r="AX19">
+        <v>1.01</v>
+      </c>
+      <c r="AY19">
+        <v>1.01</v>
+      </c>
+      <c r="AZ19">
+        <v>1.01</v>
+      </c>
+      <c r="BA19">
+        <v>1.01</v>
+      </c>
+      <c r="BB19">
+        <v>1.01</v>
+      </c>
+      <c r="BC19">
+        <v>1.01</v>
+      </c>
+      <c r="BD19">
+        <v>1.01</v>
+      </c>
+      <c r="BE19">
+        <v>1.01</v>
+      </c>
+      <c r="BF19">
+        <v>1.01</v>
+      </c>
+      <c r="BG19">
+        <v>1.01</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.01</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.01</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.01</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.01</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.01</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.01</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.01</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>1.01</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20">
+        <v>2.38</v>
+      </c>
+      <c r="G20">
+        <v>2.6</v>
+      </c>
+      <c r="H20">
+        <v>2.82</v>
+      </c>
+      <c r="I20">
+        <v>3.2</v>
+      </c>
+      <c r="J20">
+        <v>3.75</v>
+      </c>
+      <c r="K20">
+        <v>4.1</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.04</v>
+      </c>
+      <c r="N20">
+        <v>4</v>
+      </c>
+      <c r="O20">
+        <v>1.21</v>
+      </c>
+      <c r="P20">
+        <v>2.24</v>
+      </c>
+      <c r="Q20">
+        <v>1.61</v>
+      </c>
+      <c r="R20">
+        <v>1.05</v>
+      </c>
+      <c r="S20">
+        <v>1.71</v>
+      </c>
+      <c r="T20">
+        <v>1.6</v>
+      </c>
+      <c r="U20">
+        <v>2.36</v>
+      </c>
+      <c r="V20">
+        <v>1.45</v>
+      </c>
+      <c r="W20">
+        <v>1.62</v>
+      </c>
+      <c r="X20">
+        <v>1000</v>
+      </c>
+      <c r="Y20">
+        <v>1000</v>
+      </c>
+      <c r="Z20">
+        <v>1000</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>1000</v>
+      </c>
+      <c r="AC20">
+        <v>1000</v>
+      </c>
+      <c r="AD20">
+        <v>1000</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>1000</v>
+      </c>
+      <c r="AH20">
+        <v>1000</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20">
+        <v>1.01</v>
+      </c>
+      <c r="AR20">
+        <v>1.01</v>
+      </c>
+      <c r="AS20">
+        <v>1.01</v>
+      </c>
+      <c r="AT20">
+        <v>1.01</v>
+      </c>
+      <c r="AU20">
+        <v>1.01</v>
+      </c>
+      <c r="AV20">
+        <v>1.01</v>
+      </c>
+      <c r="AW20">
+        <v>1.01</v>
+      </c>
+      <c r="AX20">
+        <v>1.01</v>
+      </c>
+      <c r="AY20">
+        <v>1.01</v>
+      </c>
+      <c r="AZ20">
+        <v>1.01</v>
+      </c>
+      <c r="BA20">
+        <v>1.01</v>
+      </c>
+      <c r="BB20">
+        <v>1.01</v>
+      </c>
+      <c r="BC20">
+        <v>1.01</v>
+      </c>
+      <c r="BD20">
+        <v>1.01</v>
+      </c>
+      <c r="BE20">
+        <v>1.01</v>
+      </c>
+      <c r="BF20">
+        <v>1.01</v>
+      </c>
+      <c r="BG20">
+        <v>1.01</v>
+      </c>
+      <c r="BH20">
+        <v>5.1</v>
+      </c>
+      <c r="BI20">
+        <v>2.82</v>
+      </c>
+      <c r="BJ20">
+        <v>12</v>
+      </c>
+      <c r="BK20">
+        <v>5.8</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>21</v>
+      </c>
+      <c r="BN20">
+        <v>7.6</v>
+      </c>
+      <c r="BO20">
+        <v>3.85</v>
+      </c>
+      <c r="BP20">
+        <v>23</v>
+      </c>
+      <c r="BQ20">
+        <v>11</v>
+      </c>
+      <c r="BR20">
+        <v>38</v>
+      </c>
+      <c r="BS20">
+        <v>16.5</v>
+      </c>
+      <c r="BT20">
+        <v>8.6</v>
+      </c>
+      <c r="BU20">
+        <v>4.3</v>
+      </c>
+      <c r="BV20">
+        <v>30</v>
+      </c>
+      <c r="BW20">
+        <v>13.5</v>
+      </c>
+      <c r="BX20">
+        <v>40</v>
+      </c>
+      <c r="BY20">
+        <v>18.5</v>
+      </c>
+      <c r="BZ20">
+        <v>28</v>
+      </c>
+      <c r="CA20">
+        <v>12</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" t="s">
+        <v>151</v>
+      </c>
+      <c r="F21">
+        <v>2.14</v>
+      </c>
+      <c r="G21">
+        <v>2.4</v>
+      </c>
+      <c r="H21">
+        <v>3.2</v>
+      </c>
+      <c r="I21">
+        <v>3.85</v>
+      </c>
+      <c r="J21">
+        <v>3.7</v>
+      </c>
+      <c r="K21">
+        <v>4.2</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.04</v>
+      </c>
+      <c r="N21">
+        <v>2.24</v>
+      </c>
+      <c r="O21">
+        <v>1.2</v>
+      </c>
+      <c r="P21">
+        <v>2.24</v>
+      </c>
+      <c r="Q21">
+        <v>1.67</v>
+      </c>
+      <c r="R21">
+        <v>1.34</v>
+      </c>
+      <c r="S21">
+        <v>2.14</v>
+      </c>
+      <c r="T21">
+        <v>1.01</v>
+      </c>
+      <c r="U21">
+        <v>1.01</v>
+      </c>
+      <c r="V21">
+        <v>1.35</v>
+      </c>
+      <c r="W21">
+        <v>1.71</v>
+      </c>
+      <c r="X21">
+        <v>1000</v>
+      </c>
+      <c r="Y21">
+        <v>1000</v>
+      </c>
+      <c r="Z21">
+        <v>1000</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>1000</v>
+      </c>
+      <c r="AC21">
+        <v>1000</v>
+      </c>
+      <c r="AD21">
+        <v>1000</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>1000</v>
+      </c>
+      <c r="AG21">
+        <v>1000</v>
+      </c>
+      <c r="AH21">
+        <v>1000</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>1000</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1000</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21">
+        <v>1.01</v>
+      </c>
+      <c r="AR21">
+        <v>1.01</v>
+      </c>
+      <c r="AS21">
+        <v>1.01</v>
+      </c>
+      <c r="AT21">
+        <v>1.01</v>
+      </c>
+      <c r="AU21">
+        <v>1.01</v>
+      </c>
+      <c r="AV21">
+        <v>1.01</v>
+      </c>
+      <c r="AW21">
+        <v>1.01</v>
+      </c>
+      <c r="AX21">
+        <v>1.01</v>
+      </c>
+      <c r="AY21">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21">
+        <v>1.01</v>
+      </c>
+      <c r="BA21">
+        <v>1.01</v>
+      </c>
+      <c r="BB21">
+        <v>1.01</v>
+      </c>
+      <c r="BC21">
+        <v>1.01</v>
+      </c>
+      <c r="BD21">
+        <v>1.01</v>
+      </c>
+      <c r="BE21">
+        <v>1.01</v>
+      </c>
+      <c r="BF21">
+        <v>1.01</v>
+      </c>
+      <c r="BG21">
+        <v>1.01</v>
+      </c>
+      <c r="BH21">
+        <v>5.5</v>
+      </c>
+      <c r="BI21">
+        <v>2.76</v>
+      </c>
+      <c r="BJ21">
+        <v>12.5</v>
+      </c>
+      <c r="BK21">
+        <v>5.6</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>21</v>
+      </c>
+      <c r="BN21">
+        <v>7.6</v>
+      </c>
+      <c r="BO21">
+        <v>3.55</v>
+      </c>
+      <c r="BP21">
+        <v>21</v>
+      </c>
+      <c r="BQ21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR21">
+        <v>36</v>
+      </c>
+      <c r="BS21">
+        <v>14.5</v>
+      </c>
+      <c r="BT21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU21">
+        <v>4.4</v>
+      </c>
+      <c r="BV21">
+        <v>34</v>
+      </c>
+      <c r="BW21">
+        <v>14</v>
+      </c>
+      <c r="BX21">
+        <v>46</v>
+      </c>
+      <c r="BY21">
+        <v>18.5</v>
+      </c>
+      <c r="BZ21">
+        <v>28</v>
+      </c>
+      <c r="CA21">
+        <v>11.5</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F22">
+        <v>2.84</v>
+      </c>
+      <c r="G22">
+        <v>3.65</v>
+      </c>
+      <c r="H22">
+        <v>2.26</v>
+      </c>
+      <c r="I22">
+        <v>2.78</v>
+      </c>
+      <c r="J22">
+        <v>2.76</v>
+      </c>
+      <c r="K22">
+        <v>4.2</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>2</v>
+      </c>
+      <c r="Q22">
+        <v>1.69</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" t="s">
+        <v>126</v>
+      </c>
+      <c r="E23" t="s">
+        <v>153</v>
+      </c>
+      <c r="F23">
+        <v>2.96</v>
+      </c>
+      <c r="G23">
+        <v>3.35</v>
+      </c>
+      <c r="H23">
+        <v>2.24</v>
+      </c>
+      <c r="I23">
+        <v>2.42</v>
+      </c>
+      <c r="J23">
+        <v>3.8</v>
+      </c>
+      <c r="K23">
+        <v>4.3</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1.04</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>2.32</v>
+      </c>
+      <c r="Q23">
+        <v>1.61</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>1.58</v>
+      </c>
+      <c r="U23">
+        <v>2.44</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>28</v>
+      </c>
+      <c r="Y23">
+        <v>17</v>
+      </c>
+      <c r="Z23">
+        <v>22</v>
+      </c>
+      <c r="AA23">
+        <v>38</v>
+      </c>
+      <c r="AB23">
+        <v>21</v>
+      </c>
+      <c r="AC23">
+        <v>11.5</v>
+      </c>
+      <c r="AD23">
+        <v>14.5</v>
+      </c>
+      <c r="AE23">
+        <v>27</v>
+      </c>
+      <c r="AF23">
+        <v>30</v>
+      </c>
+      <c r="AG23">
+        <v>17</v>
+      </c>
+      <c r="AH23">
+        <v>18.5</v>
+      </c>
+      <c r="AI23">
+        <v>36</v>
+      </c>
+      <c r="AJ23">
+        <v>60</v>
+      </c>
+      <c r="AK23">
+        <v>38</v>
+      </c>
+      <c r="AL23">
+        <v>42</v>
+      </c>
+      <c r="AM23">
+        <v>75</v>
+      </c>
+      <c r="AN23">
+        <v>26</v>
+      </c>
+      <c r="AO23">
+        <v>15.5</v>
+      </c>
+      <c r="AP23">
+        <v>16</v>
+      </c>
+      <c r="AQ23">
+        <v>10</v>
+      </c>
+      <c r="AR23">
+        <v>12.5</v>
+      </c>
+      <c r="AS23">
+        <v>21</v>
+      </c>
+      <c r="AT23">
+        <v>12</v>
+      </c>
+      <c r="AU23">
+        <v>7</v>
+      </c>
+      <c r="AV23">
+        <v>8.6</v>
+      </c>
+      <c r="AW23">
+        <v>16</v>
+      </c>
+      <c r="AX23">
+        <v>17.5</v>
+      </c>
+      <c r="AY23">
+        <v>10</v>
+      </c>
+      <c r="AZ23">
+        <v>11</v>
+      </c>
+      <c r="BA23">
+        <v>21</v>
+      </c>
+      <c r="BB23">
+        <v>3.95</v>
+      </c>
+      <c r="BC23">
+        <v>3.8</v>
+      </c>
+      <c r="BD23">
+        <v>3.85</v>
+      </c>
+      <c r="BE23">
+        <v>4</v>
+      </c>
+      <c r="BF23">
+        <v>15</v>
+      </c>
+      <c r="BG23">
+        <v>9.4</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F24">
+        <v>4.3</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24">
+        <v>1.77</v>
+      </c>
+      <c r="I24">
+        <v>1.89</v>
+      </c>
+      <c r="J24">
+        <v>3.95</v>
+      </c>
+      <c r="K24">
+        <v>4.4</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>1.05</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>2.24</v>
+      </c>
+      <c r="Q24">
+        <v>1.67</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>1.67</v>
+      </c>
+      <c r="U24">
+        <v>2.22</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>24</v>
+      </c>
+      <c r="Y24">
+        <v>11.5</v>
+      </c>
+      <c r="Z24">
+        <v>13.5</v>
+      </c>
+      <c r="AA24">
+        <v>21</v>
+      </c>
+      <c r="AB24">
+        <v>21</v>
+      </c>
+      <c r="AC24">
+        <v>10.5</v>
+      </c>
+      <c r="AD24">
+        <v>11</v>
+      </c>
+      <c r="AE24">
+        <v>19</v>
+      </c>
+      <c r="AF24">
+        <v>38</v>
+      </c>
+      <c r="AG24">
+        <v>19</v>
+      </c>
+      <c r="AH24">
+        <v>18.5</v>
+      </c>
+      <c r="AI24">
+        <v>34</v>
+      </c>
+      <c r="AJ24">
+        <v>110</v>
+      </c>
+      <c r="AK24">
+        <v>55</v>
+      </c>
+      <c r="AL24">
+        <v>55</v>
+      </c>
+      <c r="AM24">
+        <v>90</v>
+      </c>
+      <c r="AN24">
+        <v>55</v>
+      </c>
+      <c r="AO24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP24">
+        <v>15.5</v>
+      </c>
+      <c r="AQ24">
+        <v>8.6</v>
+      </c>
+      <c r="AR24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS24">
+        <v>15</v>
+      </c>
+      <c r="AT24">
+        <v>15</v>
+      </c>
+      <c r="AU24">
+        <v>7.4</v>
+      </c>
+      <c r="AV24">
+        <v>8</v>
+      </c>
+      <c r="AW24">
+        <v>13.5</v>
+      </c>
+      <c r="AX24">
+        <v>6.6</v>
+      </c>
+      <c r="AY24">
+        <v>14</v>
+      </c>
+      <c r="AZ24">
+        <v>13</v>
+      </c>
+      <c r="BA24">
+        <v>6.6</v>
+      </c>
+      <c r="BB24">
+        <v>7.6</v>
+      </c>
+      <c r="BC24">
+        <v>7</v>
+      </c>
+      <c r="BD24">
+        <v>38</v>
+      </c>
+      <c r="BE24">
+        <v>7.4</v>
+      </c>
+      <c r="BF24">
+        <v>7</v>
+      </c>
+      <c r="BG24">
+        <v>7.4</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
+        <v>0</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>0</v>
+      </c>
+      <c r="BY24">
+        <v>0</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" t="s">
+        <v>155</v>
+      </c>
+      <c r="F25">
+        <v>2.2</v>
+      </c>
+      <c r="G25">
+        <v>2.28</v>
+      </c>
+      <c r="H25">
+        <v>3.8</v>
+      </c>
+      <c r="I25">
+        <v>3.85</v>
+      </c>
+      <c r="J25">
+        <v>3.3</v>
+      </c>
+      <c r="K25">
+        <v>3.5</v>
+      </c>
+      <c r="L25">
+        <v>1.48</v>
+      </c>
+      <c r="M25">
+        <v>1.09</v>
+      </c>
+      <c r="N25">
+        <v>3</v>
+      </c>
+      <c r="O25">
+        <v>1.42</v>
+      </c>
+      <c r="P25">
+        <v>1.69</v>
+      </c>
+      <c r="Q25">
+        <v>2.22</v>
+      </c>
+      <c r="R25">
+        <v>1.26</v>
+      </c>
+      <c r="S25">
+        <v>4.2</v>
+      </c>
+      <c r="T25">
+        <v>1.92</v>
+      </c>
+      <c r="U25">
+        <v>1.91</v>
+      </c>
+      <c r="V25">
+        <v>1.35</v>
+      </c>
+      <c r="W25">
+        <v>1.79</v>
+      </c>
+      <c r="X25">
+        <v>13</v>
+      </c>
+      <c r="Y25">
+        <v>14.5</v>
+      </c>
+      <c r="Z25">
+        <v>34</v>
+      </c>
+      <c r="AA25">
+        <v>110</v>
+      </c>
+      <c r="AB25">
+        <v>9.4</v>
+      </c>
+      <c r="AC25">
+        <v>7.8</v>
+      </c>
+      <c r="AD25">
+        <v>19.5</v>
+      </c>
+      <c r="AE25">
+        <v>70</v>
+      </c>
+      <c r="AF25">
+        <v>15</v>
+      </c>
+      <c r="AG25">
+        <v>13</v>
+      </c>
+      <c r="AH25">
+        <v>24</v>
+      </c>
+      <c r="AI25">
+        <v>75</v>
+      </c>
+      <c r="AJ25">
+        <v>34</v>
+      </c>
+      <c r="AK25">
+        <v>32</v>
+      </c>
+      <c r="AL25">
+        <v>55</v>
+      </c>
+      <c r="AM25">
+        <v>160</v>
+      </c>
+      <c r="AN25">
+        <v>26</v>
+      </c>
+      <c r="AO25">
+        <v>80</v>
+      </c>
+      <c r="AP25">
+        <v>9.6</v>
+      </c>
+      <c r="AQ25">
+        <v>9.6</v>
+      </c>
+      <c r="AR25">
+        <v>21</v>
+      </c>
+      <c r="AS25">
+        <v>5.2</v>
+      </c>
+      <c r="AT25">
+        <v>7</v>
+      </c>
+      <c r="AU25">
+        <v>6.6</v>
+      </c>
+      <c r="AV25">
+        <v>14.5</v>
+      </c>
+      <c r="AW25">
+        <v>5.1</v>
+      </c>
+      <c r="AX25">
+        <v>11</v>
+      </c>
+      <c r="AY25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ25">
+        <v>17.5</v>
+      </c>
+      <c r="BA25">
+        <v>5.1</v>
+      </c>
+      <c r="BB25">
+        <v>21</v>
+      </c>
+      <c r="BC25">
+        <v>20</v>
+      </c>
+      <c r="BD25">
+        <v>5</v>
+      </c>
+      <c r="BE25">
+        <v>5.3</v>
+      </c>
+      <c r="BF25">
+        <v>17</v>
+      </c>
+      <c r="BG25">
+        <v>5.1</v>
+      </c>
+      <c r="BH25">
+        <v>3.05</v>
+      </c>
+      <c r="BI25">
+        <v>2.54</v>
+      </c>
+      <c r="BJ25">
+        <v>10.5</v>
+      </c>
+      <c r="BK25">
+        <v>6.2</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>14</v>
+      </c>
+      <c r="BN25">
+        <v>4.8</v>
+      </c>
+      <c r="BO25">
+        <v>3.85</v>
+      </c>
+      <c r="BP25">
+        <v>17</v>
+      </c>
+      <c r="BQ25">
+        <v>8</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>10.5</v>
+      </c>
+      <c r="BT25">
+        <v>7.2</v>
+      </c>
+      <c r="BU25">
+        <v>5.6</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>11</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>12</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>10.5</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F26">
+        <v>2.9</v>
+      </c>
+      <c r="G26">
+        <v>3.3</v>
+      </c>
+      <c r="H26">
+        <v>2.34</v>
+      </c>
+      <c r="I26">
+        <v>2.6</v>
+      </c>
+      <c r="J26">
+        <v>3.55</v>
+      </c>
+      <c r="K26">
+        <v>4.1</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>2.14</v>
+      </c>
+      <c r="Q26">
+        <v>1.63</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <v>0</v>
+      </c>
+      <c r="AX26">
+        <v>0</v>
+      </c>
+      <c r="AY26">
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26">
+        <v>0</v>
+      </c>
+      <c r="BB26">
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+      <c r="BG26">
+        <v>0</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26">
+        <v>0</v>
+      </c>
+      <c r="BK26">
+        <v>0</v>
+      </c>
+      <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
+        <v>0</v>
+      </c>
+      <c r="BN26">
+        <v>0</v>
+      </c>
+      <c r="BO26">
+        <v>0</v>
+      </c>
+      <c r="BP26">
+        <v>0</v>
+      </c>
+      <c r="BQ26">
+        <v>0</v>
+      </c>
+      <c r="BR26">
+        <v>0</v>
+      </c>
+      <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
+        <v>0</v>
+      </c>
+      <c r="BU26">
+        <v>0</v>
+      </c>
+      <c r="BV26">
+        <v>0</v>
+      </c>
+      <c r="BW26">
+        <v>0</v>
+      </c>
+      <c r="BX26">
+        <v>0</v>
+      </c>
+      <c r="BY26">
+        <v>0</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D27" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" t="s">
+        <v>157</v>
+      </c>
+      <c r="F27">
+        <v>3.05</v>
+      </c>
+      <c r="G27">
+        <v>3.9</v>
+      </c>
+      <c r="H27">
+        <v>2.38</v>
+      </c>
+      <c r="I27">
+        <v>2.88</v>
+      </c>
+      <c r="J27">
+        <v>3.1</v>
+      </c>
+      <c r="K27">
+        <v>3.55</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>1.73</v>
+      </c>
+      <c r="Q27">
+        <v>2.12</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>0</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27">
+        <v>0</v>
+      </c>
+      <c r="AV27">
+        <v>0</v>
+      </c>
+      <c r="AW27">
+        <v>0</v>
+      </c>
+      <c r="AX27">
+        <v>0</v>
+      </c>
+      <c r="AY27">
+        <v>0</v>
+      </c>
+      <c r="AZ27">
+        <v>0</v>
+      </c>
+      <c r="BA27">
+        <v>0</v>
+      </c>
+      <c r="BB27">
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <v>0</v>
+      </c>
+      <c r="BD27">
+        <v>0</v>
+      </c>
+      <c r="BE27">
+        <v>0</v>
+      </c>
+      <c r="BF27">
+        <v>0</v>
+      </c>
+      <c r="BG27">
+        <v>0</v>
+      </c>
+      <c r="BH27">
+        <v>0</v>
+      </c>
+      <c r="BI27">
+        <v>0</v>
+      </c>
+      <c r="BJ27">
+        <v>0</v>
+      </c>
+      <c r="BK27">
+        <v>0</v>
+      </c>
+      <c r="BL27">
+        <v>0</v>
+      </c>
+      <c r="BM27">
+        <v>0</v>
+      </c>
+      <c r="BN27">
+        <v>0</v>
+      </c>
+      <c r="BO27">
+        <v>0</v>
+      </c>
+      <c r="BP27">
+        <v>0</v>
+      </c>
+      <c r="BQ27">
+        <v>0</v>
+      </c>
+      <c r="BR27">
+        <v>0</v>
+      </c>
+      <c r="BS27">
+        <v>0</v>
+      </c>
+      <c r="BT27">
+        <v>0</v>
+      </c>
+      <c r="BU27">
+        <v>0</v>
+      </c>
+      <c r="BV27">
+        <v>0</v>
+      </c>
+      <c r="BW27">
+        <v>0</v>
+      </c>
+      <c r="BX27">
+        <v>0</v>
+      </c>
+      <c r="BY27">
+        <v>0</v>
+      </c>
+      <c r="BZ27">
+        <v>0</v>
+      </c>
+      <c r="CA27">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" t="s">
+        <v>158</v>
+      </c>
+      <c r="F28">
+        <v>3.65</v>
+      </c>
+      <c r="G28">
+        <v>4.2</v>
+      </c>
+      <c r="H28">
+        <v>2.14</v>
+      </c>
+      <c r="I28">
+        <v>2.38</v>
+      </c>
+      <c r="J28">
+        <v>3.15</v>
+      </c>
+      <c r="K28">
+        <v>3.55</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>1.73</v>
+      </c>
+      <c r="Q28">
+        <v>2.22</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <v>0</v>
+      </c>
+      <c r="BH28">
+        <v>0</v>
+      </c>
+      <c r="BI28">
+        <v>0</v>
+      </c>
+      <c r="BJ28">
+        <v>0</v>
+      </c>
+      <c r="BK28">
+        <v>0</v>
+      </c>
+      <c r="BL28">
+        <v>0</v>
+      </c>
+      <c r="BM28">
+        <v>0</v>
+      </c>
+      <c r="BN28">
+        <v>0</v>
+      </c>
+      <c r="BO28">
+        <v>0</v>
+      </c>
+      <c r="BP28">
+        <v>0</v>
+      </c>
+      <c r="BQ28">
+        <v>0</v>
+      </c>
+      <c r="BR28">
+        <v>0</v>
+      </c>
+      <c r="BS28">
+        <v>0</v>
+      </c>
+      <c r="BT28">
+        <v>0</v>
+      </c>
+      <c r="BU28">
+        <v>0</v>
+      </c>
+      <c r="BV28">
+        <v>0</v>
+      </c>
+      <c r="BW28">
+        <v>0</v>
+      </c>
+      <c r="BX28">
+        <v>0</v>
+      </c>
+      <c r="BY28">
+        <v>0</v>
+      </c>
+      <c r="BZ28">
+        <v>0</v>
+      </c>
+      <c r="CA28">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="221">
   <si>
     <t>League</t>
   </si>
@@ -319,15 +319,18 @@
     <t>Hungarian NB I</t>
   </si>
   <si>
+    <t>Irish Premier Division</t>
+  </si>
+  <si>
     <t>Irish Division 1</t>
   </si>
   <si>
-    <t>Irish Premier Division</t>
-  </si>
-  <si>
     <t>Scottish Premiership</t>
   </si>
   <si>
+    <t>Peruvian Primera Division</t>
+  </si>
+  <si>
     <t>2026-07-31</t>
   </si>
   <si>
@@ -376,6 +379,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
@@ -448,18 +454,18 @@
     <t>Roskilde</t>
   </si>
   <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>MAS Taborsko</t>
+  </si>
+  <si>
+    <t>Sparta Prague</t>
+  </si>
+  <si>
     <t>HB Koge</t>
   </si>
   <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>MAS Taborsko</t>
-  </si>
-  <si>
-    <t>Sparta Prague</t>
-  </si>
-  <si>
     <t>Lask Linz</t>
   </si>
   <si>
@@ -493,6 +499,9 @@
     <t>LKP Motor Lublin</t>
   </si>
   <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
     <t>Finn Harps</t>
   </si>
   <si>
@@ -508,16 +517,16 @@
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
     <t>Bodo Glimt</t>
   </si>
   <si>
+    <t>Dundee Utd</t>
+  </si>
+  <si>
     <t>Drogheda</t>
   </si>
   <si>
-    <t>Dundee Utd</t>
+    <t>CD Los Chankas</t>
   </si>
   <si>
     <t>Atl Tucuman</t>
@@ -592,18 +601,18 @@
     <t>Naestved</t>
   </si>
   <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>Dukla Prague</t>
+  </si>
+  <si>
+    <t>Zlin</t>
+  </si>
+  <si>
     <t>Vejle</t>
   </si>
   <si>
-    <t>Fredericia</t>
-  </si>
-  <si>
-    <t>Dukla Prague</t>
-  </si>
-  <si>
-    <t>Zlin</t>
-  </si>
-  <si>
     <t>Grazer AK</t>
   </si>
   <si>
@@ -637,6 +646,9 @@
     <t>Jagiellonia Bialystock</t>
   </si>
   <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
     <t>Cork City</t>
   </si>
   <si>
@@ -652,19 +664,19 @@
     <t>Longford</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
     <t>Lillestrom</t>
   </si>
   <si>
+    <t>Rangers</t>
+  </si>
+  <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>2026-07-29 16:07:01</t>
+    <t>Comerciantes Unidos</t>
+  </si>
+  <si>
+    <t>2026-07-29 18:15:31</t>
   </si>
 </sst>
 </file>
@@ -996,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB49"/>
+  <dimension ref="A1:CB50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1246,37 +1258,37 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H2">
+        <v>2.6</v>
+      </c>
+      <c r="I2">
         <v>2.62</v>
       </c>
-      <c r="I2">
-        <v>2.66</v>
-      </c>
       <c r="J2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="M2">
         <v>1.13</v>
@@ -1285,7 +1297,7 @@
         <v>2.62</v>
       </c>
       <c r="O2">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P2">
         <v>1.54</v>
@@ -1294,34 +1306,34 @@
         <v>2.72</v>
       </c>
       <c r="R2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="T2">
         <v>2.18</v>
       </c>
       <c r="U2">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W2">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y2">
         <v>7.8</v>
       </c>
       <c r="Z2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA2">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AB2">
         <v>9.199999999999999</v>
@@ -1330,10 +1342,10 @@
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE2">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AF2">
         <v>21</v>
@@ -1351,7 +1363,7 @@
         <v>1000</v>
       </c>
       <c r="AK2">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2">
         <v>1000</v>
@@ -1363,13 +1375,13 @@
         <v>1000</v>
       </c>
       <c r="AO2">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AP2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR2">
         <v>13</v>
@@ -1378,10 +1390,10 @@
         <v>23</v>
       </c>
       <c r="AT2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
         <v>12</v>
@@ -1390,7 +1402,7 @@
         <v>32</v>
       </c>
       <c r="AX2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY2">
         <v>14</v>
@@ -1480,7 +1492,7 @@
         <v>12</v>
       </c>
       <c r="CB2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1488,16 +1500,16 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F3">
         <v>1.7</v>
@@ -1518,7 +1530,7 @@
         <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="M3">
         <v>1.1</v>
@@ -1530,7 +1542,7 @@
         <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q3">
         <v>2.34</v>
@@ -1542,7 +1554,7 @@
         <v>4.6</v>
       </c>
       <c r="T3">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U3">
         <v>1.7</v>
@@ -1722,7 +1734,7 @@
         <v>8</v>
       </c>
       <c r="CB3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1730,16 +1742,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F4">
         <v>3.55</v>
@@ -1784,7 +1796,7 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U4">
         <v>2.04</v>
@@ -1964,7 +1976,7 @@
         <v>10.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1972,22 +1984,22 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F5">
         <v>1.49</v>
       </c>
       <c r="G5">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H5">
         <v>7.6</v>
@@ -2002,7 +2014,7 @@
         <v>4.8</v>
       </c>
       <c r="L5">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -2014,10 +2026,10 @@
         <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="Q5">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R5">
         <v>1.29</v>
@@ -2026,7 +2038,7 @@
         <v>3.85</v>
       </c>
       <c r="T5">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U5">
         <v>1.74</v>
@@ -2035,7 +2047,7 @@
         <v>1.12</v>
       </c>
       <c r="W5">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X5">
         <v>16</v>
@@ -2185,13 +2197,13 @@
         <v>11.5</v>
       </c>
       <c r="BU5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX5">
         <v>1000</v>
@@ -2206,7 +2218,7 @@
         <v>7.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2214,16 +2226,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F6">
         <v>1.83</v>
@@ -2244,7 +2256,7 @@
         <v>4.6</v>
       </c>
       <c r="L6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M6">
         <v>1.01</v>
@@ -2259,7 +2271,7 @@
         <v>2.44</v>
       </c>
       <c r="Q6">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="R6">
         <v>1.58</v>
@@ -2397,7 +2409,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK6">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2448,7 +2460,7 @@
         <v>6.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2456,16 +2468,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F7">
         <v>2.12</v>
@@ -2507,19 +2519,19 @@
         <v>1.33</v>
       </c>
       <c r="S7">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V7">
         <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="X7">
         <v>25</v>
@@ -2576,19 +2588,19 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.95</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7">
-        <v>1.92</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7">
-        <v>2</v>
+        <v>15.5</v>
       </c>
       <c r="AS7">
         <v>2.1</v>
       </c>
       <c r="AT7">
-        <v>1.87</v>
+        <v>7</v>
       </c>
       <c r="AU7">
         <v>1.81</v>
@@ -2600,22 +2612,22 @@
         <v>2.1</v>
       </c>
       <c r="AX7">
-        <v>1.93</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7">
         <v>1.87</v>
       </c>
       <c r="AZ7">
-        <v>1.94</v>
+        <v>10</v>
       </c>
       <c r="BA7">
         <v>2.1</v>
       </c>
       <c r="BB7">
-        <v>2</v>
+        <v>16.5</v>
       </c>
       <c r="BC7">
-        <v>1.99</v>
+        <v>14</v>
       </c>
       <c r="BD7">
         <v>2.02</v>
@@ -2690,7 +2702,7 @@
         <v>2.68</v>
       </c>
       <c r="CB7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2698,16 +2710,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F8">
         <v>1.04</v>
@@ -2722,7 +2734,7 @@
         <v>870</v>
       </c>
       <c r="J8">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2932,7 +2944,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2940,22 +2952,22 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E9" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F9">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="G9">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H9">
         <v>5.7</v>
@@ -2964,10 +2976,10 @@
         <v>6.6</v>
       </c>
       <c r="J9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K9">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L9">
         <v>1.45</v>
@@ -2976,7 +2988,7 @@
         <v>1.09</v>
       </c>
       <c r="N9">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>1.42</v>
@@ -2997,13 +3009,13 @@
         <v>2.1</v>
       </c>
       <c r="U9">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V9">
         <v>1.18</v>
       </c>
       <c r="W9">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X9">
         <v>13</v>
@@ -3057,7 +3069,7 @@
         <v>18</v>
       </c>
       <c r="AO9">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP9">
         <v>9.4</v>
@@ -3174,7 +3186,7 @@
         <v>1.59</v>
       </c>
       <c r="CB9" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3182,19 +3194,19 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F10">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="G10">
         <v>1.82</v>
@@ -3230,7 +3242,7 @@
         <v>1.67</v>
       </c>
       <c r="R10">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S10">
         <v>2.7</v>
@@ -3239,7 +3251,7 @@
         <v>1.69</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V10">
         <v>1.2</v>
@@ -3416,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3424,16 +3436,16 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F11">
         <v>3.5</v>
@@ -3601,19 +3613,19 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="BJ11">
         <v>14.5</v>
       </c>
       <c r="BK11">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="BN11">
         <v>8.6</v>
@@ -3622,34 +3634,34 @@
         <v>4.3</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ11">
-        <v>1.28</v>
+        <v>1.71</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU11">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW11">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.26</v>
+        <v>1.72</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3658,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3666,19 +3678,19 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F12">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G12">
         <v>2.32</v>
@@ -3687,13 +3699,13 @@
         <v>3.05</v>
       </c>
       <c r="I12">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J12">
         <v>3.65</v>
       </c>
       <c r="K12">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3702,19 +3714,19 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O12">
         <v>1.14</v>
       </c>
       <c r="P12">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q12">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R12">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="S12">
         <v>2.08</v>
@@ -3726,10 +3738,10 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3900,7 +3912,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3908,16 +3920,16 @@
         <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F13">
         <v>2.5</v>
@@ -3944,25 +3956,25 @@
         <v>1.04</v>
       </c>
       <c r="N13">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O13">
         <v>1.21</v>
       </c>
       <c r="P13">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q13">
         <v>1.63</v>
       </c>
       <c r="R13">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S13">
         <v>2.52</v>
       </c>
       <c r="T13">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="U13">
         <v>2.44</v>
@@ -4142,7 +4154,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4150,16 +4162,16 @@
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F14">
         <v>2.92</v>
@@ -4171,7 +4183,7 @@
         <v>2.46</v>
       </c>
       <c r="I14">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J14">
         <v>3.3</v>
@@ -4198,7 +4210,7 @@
         <v>2.02</v>
       </c>
       <c r="R14">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S14">
         <v>3.6</v>
@@ -4210,7 +4222,7 @@
         <v>2.1</v>
       </c>
       <c r="V14">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W14">
         <v>1.44</v>
@@ -4231,7 +4243,7 @@
         <v>14</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD14">
         <v>14.5</v>
@@ -4270,37 +4282,37 @@
         <v>32</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA14">
         <v>1.01</v>
@@ -4309,10 +4321,10 @@
         <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE14">
         <v>1.01</v>
@@ -4321,7 +4333,7 @@
         <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH14">
         <v>3.3</v>
@@ -4384,7 +4396,7 @@
         <v>10</v>
       </c>
       <c r="CB14" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4392,31 +4404,31 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E15" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F15">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G15">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H15">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>5.8</v>
       </c>
       <c r="J15">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K15">
         <v>4.4</v>
@@ -4455,7 +4467,7 @@
         <v>1.2</v>
       </c>
       <c r="W15">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X15">
         <v>17.5</v>
@@ -4512,10 +4524,10 @@
         <v>85</v>
       </c>
       <c r="AP15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ15">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR15">
         <v>1.01</v>
@@ -4530,16 +4542,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV15">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW15">
         <v>1.01</v>
       </c>
       <c r="AX15">
+        <v>8.4</v>
+      </c>
+      <c r="AY15">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AY15">
-        <v>7.6</v>
       </c>
       <c r="AZ15">
         <v>15</v>
@@ -4548,10 +4560,10 @@
         <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BC15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD15">
         <v>1.03</v>
@@ -4569,19 +4581,19 @@
         <v>4.4</v>
       </c>
       <c r="BI15">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="BJ15">
         <v>13.5</v>
       </c>
       <c r="BK15">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BN15">
         <v>5.9</v>
@@ -4593,7 +4605,7 @@
         <v>17</v>
       </c>
       <c r="BQ15">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BR15">
         <v>36</v>
@@ -4605,7 +4617,7 @@
         <v>11.5</v>
       </c>
       <c r="BU15">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BV15">
         <v>1000</v>
@@ -4617,16 +4629,16 @@
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BZ15">
         <v>29</v>
       </c>
       <c r="CA15">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="CB15" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4634,16 +4646,16 @@
         <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F16">
         <v>2.98</v>
@@ -4670,7 +4682,7 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="O16">
         <v>1.32</v>
@@ -4679,13 +4691,13 @@
         <v>1.83</v>
       </c>
       <c r="Q16">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="R16">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S16">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4754,7 +4766,7 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>10.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ16">
         <v>2.22</v>
@@ -4811,19 +4823,19 @@
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="BJ16">
         <v>13.5</v>
       </c>
       <c r="BK16">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="BN16">
         <v>8.800000000000001</v>
@@ -4835,40 +4847,40 @@
         <v>36</v>
       </c>
       <c r="BQ16">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU16">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BV16">
         <v>28</v>
       </c>
       <c r="BW16">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="BX16">
         <v>48</v>
       </c>
       <c r="BY16">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="BZ16">
         <v>44</v>
       </c>
       <c r="CA16">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="CB16" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4876,16 +4888,16 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F17">
         <v>3.55</v>
@@ -4912,7 +4924,7 @@
         <v>1.03</v>
       </c>
       <c r="N17">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O17">
         <v>1.21</v>
@@ -4948,7 +4960,7 @@
         <v>1000</v>
       </c>
       <c r="Z17">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA17">
         <v>1000</v>
@@ -5110,7 +5122,7 @@
         <v>2.86</v>
       </c>
       <c r="CB17" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5118,16 +5130,16 @@
         <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E18" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F18">
         <v>3.9</v>
@@ -5142,7 +5154,7 @@
         <v>1.97</v>
       </c>
       <c r="J18">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K18">
         <v>4.8</v>
@@ -5166,7 +5178,7 @@
         <v>1.55</v>
       </c>
       <c r="R18">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="S18">
         <v>2.32</v>
@@ -5175,7 +5187,7 @@
         <v>1.48</v>
       </c>
       <c r="U18">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="V18">
         <v>2.02</v>
@@ -5208,7 +5220,7 @@
         <v>22</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG18">
         <v>22</v>
@@ -5244,7 +5256,7 @@
         <v>1.03</v>
       </c>
       <c r="AR18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS18">
         <v>1.03</v>
@@ -5331,7 +5343,7 @@
         <v>6.4</v>
       </c>
       <c r="BU18">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BV18">
         <v>16</v>
@@ -5352,7 +5364,7 @@
         <v>9.6</v>
       </c>
       <c r="CB18" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5360,16 +5372,16 @@
         <v>92</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E19" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F19">
         <v>2.16</v>
@@ -5594,7 +5606,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5602,25 +5614,25 @@
         <v>92</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E20" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F20">
         <v>2.36</v>
       </c>
       <c r="G20">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H20">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="I20">
         <v>3.15</v>
@@ -5644,10 +5656,10 @@
         <v>1.23</v>
       </c>
       <c r="P20">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q20">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="R20">
         <v>1.48</v>
@@ -5665,19 +5677,19 @@
         <v>1.47</v>
       </c>
       <c r="W20">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X20">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y20">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z20">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA20">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB20">
         <v>15.5</v>
@@ -5686,7 +5698,7 @@
         <v>10.5</v>
       </c>
       <c r="AD20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE20">
         <v>34</v>
@@ -5728,7 +5740,7 @@
         <v>11</v>
       </c>
       <c r="AR20">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS20">
         <v>1.01</v>
@@ -5779,10 +5791,10 @@
         <v>5.1</v>
       </c>
       <c r="BI20">
-        <v>2.82</v>
+        <v>1.96</v>
       </c>
       <c r="BJ20">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK20">
         <v>2.54</v>
@@ -5791,52 +5803,52 @@
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BN20">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO20">
         <v>3.85</v>
       </c>
       <c r="BP20">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BQ20">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BR20">
         <v>38</v>
       </c>
       <c r="BS20">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BT20">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU20">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV20">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW20">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BX20">
         <v>40</v>
       </c>
       <c r="BY20">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BZ20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA20">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CB20" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5844,31 +5856,31 @@
         <v>92</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E21" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F21">
         <v>2.14</v>
       </c>
       <c r="G21">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="H21">
         <v>3.2</v>
       </c>
       <c r="I21">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J21">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K21">
         <v>4.2</v>
@@ -5880,7 +5892,7 @@
         <v>1.04</v>
       </c>
       <c r="N21">
-        <v>2.24</v>
+        <v>1.1</v>
       </c>
       <c r="O21">
         <v>1.2</v>
@@ -5895,19 +5907,19 @@
         <v>1.37</v>
       </c>
       <c r="S21">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="T21">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="U21">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -6021,7 +6033,7 @@
         <v>5.5</v>
       </c>
       <c r="BI21">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BJ21">
         <v>12.5</v>
@@ -6078,7 +6090,7 @@
         <v>2.64</v>
       </c>
       <c r="CB21" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6086,22 +6098,22 @@
         <v>93</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F22">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G22">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H22">
         <v>4.8</v>
@@ -6113,7 +6125,7 @@
         <v>4</v>
       </c>
       <c r="K22">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6128,22 +6140,22 @@
         <v>1.21</v>
       </c>
       <c r="P22">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q22">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R22">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S22">
         <v>2.46</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V22">
         <v>1.2</v>
@@ -6320,7 +6332,7 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6328,16 +6340,16 @@
         <v>94</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E23" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F23">
         <v>1.64</v>
@@ -6373,19 +6385,19 @@
         <v>2.76</v>
       </c>
       <c r="Q23">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="R23">
         <v>1.71</v>
       </c>
       <c r="S23">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T23">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="U23">
-        <v>2.48</v>
+        <v>1.11</v>
       </c>
       <c r="V23">
         <v>1.01</v>
@@ -6436,7 +6448,7 @@
         <v>19</v>
       </c>
       <c r="AL23">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM23">
         <v>75</v>
@@ -6469,7 +6481,7 @@
         <v>4</v>
       </c>
       <c r="AW23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX23">
         <v>11.5</v>
@@ -6499,19 +6511,19 @@
         <v>4.8</v>
       </c>
       <c r="BG23">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
         <v>1000</v>
@@ -6523,13 +6535,13 @@
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
         <v>1000</v>
@@ -6541,7 +6553,7 @@
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
         <v>1000</v>
@@ -6562,7 +6574,7 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6570,31 +6582,31 @@
         <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E24" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G24">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I24">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J24">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K24">
         <v>950</v>
@@ -6606,7 +6618,7 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O24">
         <v>1.02</v>
@@ -6624,16 +6636,16 @@
         <v>2.1</v>
       </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6804,7 +6816,7 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6812,16 +6824,16 @@
         <v>95</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F25">
         <v>2.26</v>
@@ -6836,7 +6848,7 @@
         <v>3.45</v>
       </c>
       <c r="J25">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K25">
         <v>3.9</v>
@@ -6866,10 +6878,10 @@
         <v>2.36</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V25">
         <v>1.4</v>
@@ -7046,7 +7058,7 @@
         <v>1.29</v>
       </c>
       <c r="CB25" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7054,967 +7066,967 @@
         <v>90</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F26">
+        <v>2.96</v>
+      </c>
+      <c r="G26">
+        <v>3.35</v>
+      </c>
+      <c r="H26">
+        <v>2.24</v>
+      </c>
+      <c r="I26">
+        <v>2.42</v>
+      </c>
+      <c r="J26">
+        <v>3.8</v>
+      </c>
+      <c r="K26">
         <v>4.3</v>
       </c>
-      <c r="G26">
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.03</v>
+      </c>
+      <c r="N26">
         <v>5</v>
       </c>
-      <c r="H26">
-        <v>1.77</v>
-      </c>
-      <c r="I26">
-        <v>1.89</v>
-      </c>
-      <c r="J26">
-        <v>3.95</v>
-      </c>
-      <c r="K26">
-        <v>4.4</v>
-      </c>
-      <c r="L26">
-        <v>1.01</v>
-      </c>
-      <c r="M26">
-        <v>1.05</v>
-      </c>
-      <c r="N26">
-        <v>4.6</v>
-      </c>
       <c r="O26">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P26">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q26">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="R26">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S26">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="T26">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="U26">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="V26">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="W26">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="X26">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Y26">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="Z26">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AA26">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AB26">
         <v>21</v>
       </c>
       <c r="AC26">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD26">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AE26">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AF26">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AG26">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH26">
         <v>18.5</v>
       </c>
       <c r="AI26">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ26">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AK26">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AL26">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM26">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN26">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="AO26">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="AP26">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ26">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AR26">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AS26">
+        <v>21</v>
+      </c>
+      <c r="AT26">
+        <v>12</v>
+      </c>
+      <c r="AU26">
+        <v>7</v>
+      </c>
+      <c r="AV26">
+        <v>10</v>
+      </c>
+      <c r="AW26">
+        <v>16</v>
+      </c>
+      <c r="AX26">
+        <v>17.5</v>
+      </c>
+      <c r="AY26">
+        <v>10</v>
+      </c>
+      <c r="AZ26">
+        <v>11</v>
+      </c>
+      <c r="BA26">
+        <v>21</v>
+      </c>
+      <c r="BB26">
+        <v>3.95</v>
+      </c>
+      <c r="BC26">
+        <v>3.8</v>
+      </c>
+      <c r="BD26">
+        <v>3.85</v>
+      </c>
+      <c r="BE26">
+        <v>4</v>
+      </c>
+      <c r="BF26">
         <v>15</v>
       </c>
-      <c r="AT26">
-        <v>15</v>
-      </c>
-      <c r="AU26">
-        <v>7.4</v>
-      </c>
-      <c r="AV26">
-        <v>8</v>
-      </c>
-      <c r="AW26">
-        <v>13.5</v>
-      </c>
-      <c r="AX26">
-        <v>6.6</v>
-      </c>
-      <c r="AY26">
-        <v>14</v>
-      </c>
-      <c r="AZ26">
-        <v>13</v>
-      </c>
-      <c r="BA26">
-        <v>6.6</v>
-      </c>
-      <c r="BB26">
-        <v>7.6</v>
-      </c>
-      <c r="BC26">
-        <v>7</v>
-      </c>
-      <c r="BD26">
-        <v>38</v>
-      </c>
-      <c r="BE26">
-        <v>7.4</v>
-      </c>
-      <c r="BF26">
-        <v>7</v>
-      </c>
       <c r="BG26">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH26">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E27" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F27">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G27">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="H27">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I27">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="J27">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="K27">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L27">
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="O27">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="P27">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="Q27">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="R27">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="S27">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="T27">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U27">
-        <v>2.44</v>
+        <v>1.96</v>
       </c>
       <c r="V27">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="W27">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="X27">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="Y27">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA27">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB27">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE27">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH27">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AQ27">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR27">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS27">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AT27">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AU27">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV27">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW27">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AX27">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY27">
         <v>10</v>
       </c>
       <c r="AZ27">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA27">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BB27">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BC27">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="BD27">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE27">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BF27">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI27">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="CB27" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E28" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F28">
-        <v>3.05</v>
+        <v>1.23</v>
       </c>
       <c r="G28">
-        <v>3.85</v>
+        <v>1.29</v>
       </c>
       <c r="H28">
-        <v>2.26</v>
+        <v>14.5</v>
       </c>
       <c r="I28">
+        <v>21</v>
+      </c>
+      <c r="J28">
+        <v>6.4</v>
+      </c>
+      <c r="K28">
+        <v>7.8</v>
+      </c>
+      <c r="L28">
+        <v>1.01</v>
+      </c>
+      <c r="M28">
+        <v>1.04</v>
+      </c>
+      <c r="N28">
+        <v>5.3</v>
+      </c>
+      <c r="O28">
+        <v>1.16</v>
+      </c>
+      <c r="P28">
+        <v>2.5</v>
+      </c>
+      <c r="Q28">
+        <v>1.53</v>
+      </c>
+      <c r="R28">
+        <v>1.6</v>
+      </c>
+      <c r="S28">
+        <v>2.32</v>
+      </c>
+      <c r="T28">
+        <v>1.9</v>
+      </c>
+      <c r="U28">
+        <v>1.57</v>
+      </c>
+      <c r="V28">
+        <v>1.05</v>
+      </c>
+      <c r="W28">
+        <v>4.4</v>
+      </c>
+      <c r="X28">
+        <v>1000</v>
+      </c>
+      <c r="Y28">
+        <v>1000</v>
+      </c>
+      <c r="Z28">
+        <v>1000</v>
+      </c>
+      <c r="AA28">
+        <v>1000</v>
+      </c>
+      <c r="AB28">
+        <v>1000</v>
+      </c>
+      <c r="AC28">
+        <v>1000</v>
+      </c>
+      <c r="AD28">
+        <v>1000</v>
+      </c>
+      <c r="AE28">
+        <v>1000</v>
+      </c>
+      <c r="AF28">
+        <v>1000</v>
+      </c>
+      <c r="AG28">
+        <v>1000</v>
+      </c>
+      <c r="AH28">
+        <v>1000</v>
+      </c>
+      <c r="AI28">
+        <v>1000</v>
+      </c>
+      <c r="AJ28">
+        <v>11.5</v>
+      </c>
+      <c r="AK28">
+        <v>18.5</v>
+      </c>
+      <c r="AL28">
+        <v>1000</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>5</v>
+      </c>
+      <c r="AO28">
+        <v>1000</v>
+      </c>
+      <c r="AP28">
+        <v>1.51</v>
+      </c>
+      <c r="AQ28">
+        <v>1.51</v>
+      </c>
+      <c r="AR28">
+        <v>1.51</v>
+      </c>
+      <c r="AS28">
+        <v>1.51</v>
+      </c>
+      <c r="AT28">
+        <v>1.51</v>
+      </c>
+      <c r="AU28">
+        <v>1.51</v>
+      </c>
+      <c r="AV28">
+        <v>1.51</v>
+      </c>
+      <c r="AW28">
+        <v>1.51</v>
+      </c>
+      <c r="AX28">
+        <v>1.51</v>
+      </c>
+      <c r="AY28">
+        <v>1.51</v>
+      </c>
+      <c r="AZ28">
+        <v>1.51</v>
+      </c>
+      <c r="BA28">
+        <v>1.51</v>
+      </c>
+      <c r="BB28">
+        <v>1.34</v>
+      </c>
+      <c r="BC28">
+        <v>10</v>
+      </c>
+      <c r="BD28">
+        <v>1.51</v>
+      </c>
+      <c r="BE28">
+        <v>1.51</v>
+      </c>
+      <c r="BF28">
+        <v>1.16</v>
+      </c>
+      <c r="BG28">
+        <v>1.51</v>
+      </c>
+      <c r="BH28">
+        <v>6.4</v>
+      </c>
+      <c r="BI28">
+        <v>3.1</v>
+      </c>
+      <c r="BJ28">
+        <v>19</v>
+      </c>
+      <c r="BK28">
         <v>2.54</v>
       </c>
-      <c r="J28">
-        <v>3.1</v>
-      </c>
-      <c r="K28">
-        <v>3.75</v>
-      </c>
-      <c r="L28">
-        <v>1.01</v>
-      </c>
-      <c r="M28">
-        <v>1.05</v>
-      </c>
-      <c r="N28">
-        <v>3.55</v>
-      </c>
-      <c r="O28">
-        <v>1.26</v>
-      </c>
-      <c r="P28">
-        <v>1.91</v>
-      </c>
-      <c r="Q28">
-        <v>1.9</v>
-      </c>
-      <c r="R28">
-        <v>1.3</v>
-      </c>
-      <c r="S28">
-        <v>2.88</v>
-      </c>
-      <c r="T28">
-        <v>1.59</v>
-      </c>
-      <c r="U28">
-        <v>1.95</v>
-      </c>
-      <c r="V28">
-        <v>1.64</v>
-      </c>
-      <c r="W28">
-        <v>1.35</v>
-      </c>
-      <c r="X28">
-        <v>1000</v>
-      </c>
-      <c r="Y28">
-        <v>1000</v>
-      </c>
-      <c r="Z28">
-        <v>19.5</v>
-      </c>
-      <c r="AA28">
-        <v>40</v>
-      </c>
-      <c r="AB28">
-        <v>1000</v>
-      </c>
-      <c r="AC28">
-        <v>1000</v>
-      </c>
-      <c r="AD28">
-        <v>1000</v>
-      </c>
-      <c r="AE28">
-        <v>1000</v>
-      </c>
-      <c r="AF28">
-        <v>1000</v>
-      </c>
-      <c r="AG28">
-        <v>17.5</v>
-      </c>
-      <c r="AH28">
-        <v>1000</v>
-      </c>
-      <c r="AI28">
-        <v>1000</v>
-      </c>
-      <c r="AJ28">
-        <v>1000</v>
-      </c>
-      <c r="AK28">
-        <v>1000</v>
-      </c>
-      <c r="AL28">
-        <v>1000</v>
-      </c>
-      <c r="AM28">
-        <v>1000</v>
-      </c>
-      <c r="AN28">
-        <v>1000</v>
-      </c>
-      <c r="AO28">
-        <v>1000</v>
-      </c>
-      <c r="AP28">
-        <v>1.03</v>
-      </c>
-      <c r="AQ28">
-        <v>1.03</v>
-      </c>
-      <c r="AR28">
-        <v>1.03</v>
-      </c>
-      <c r="AS28">
-        <v>1.03</v>
-      </c>
-      <c r="AT28">
-        <v>1.03</v>
-      </c>
-      <c r="AU28">
-        <v>1.03</v>
-      </c>
-      <c r="AV28">
-        <v>1.03</v>
-      </c>
-      <c r="AW28">
-        <v>1.03</v>
-      </c>
-      <c r="AX28">
-        <v>1.03</v>
-      </c>
-      <c r="AY28">
-        <v>10</v>
-      </c>
-      <c r="AZ28">
-        <v>1.03</v>
-      </c>
-      <c r="BA28">
-        <v>1.03</v>
-      </c>
-      <c r="BB28">
-        <v>1.03</v>
-      </c>
-      <c r="BC28">
-        <v>1.03</v>
-      </c>
-      <c r="BD28">
-        <v>1.03</v>
-      </c>
-      <c r="BE28">
-        <v>1.03</v>
-      </c>
-      <c r="BF28">
-        <v>1.01</v>
-      </c>
-      <c r="BG28">
-        <v>1.01</v>
-      </c>
-      <c r="BH28">
-        <v>4.1</v>
-      </c>
-      <c r="BI28">
-        <v>1.87</v>
-      </c>
-      <c r="BJ28">
-        <v>13</v>
-      </c>
-      <c r="BK28">
-        <v>2.72</v>
-      </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="BN28">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BO28">
-        <v>4.4</v>
+        <v>2.64</v>
       </c>
       <c r="BP28">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="BQ28">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="BR28">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BS28">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="BT28">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="BU28">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="BV28">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BX28">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="BZ28">
-        <v>36</v>
+        <v>13.5</v>
       </c>
       <c r="CA28">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="CB28" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E29" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F29">
+        <v>4.3</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="H29">
+        <v>1.77</v>
+      </c>
+      <c r="I29">
+        <v>1.89</v>
+      </c>
+      <c r="J29">
+        <v>3.95</v>
+      </c>
+      <c r="K29">
+        <v>4.4</v>
+      </c>
+      <c r="L29">
+        <v>1.01</v>
+      </c>
+      <c r="M29">
+        <v>1.05</v>
+      </c>
+      <c r="N29">
+        <v>4.6</v>
+      </c>
+      <c r="O29">
         <v>1.23</v>
       </c>
-      <c r="G29">
-        <v>1.29</v>
-      </c>
-      <c r="H29">
+      <c r="P29">
+        <v>2.24</v>
+      </c>
+      <c r="Q29">
+        <v>1.67</v>
+      </c>
+      <c r="R29">
+        <v>1.49</v>
+      </c>
+      <c r="S29">
+        <v>2.66</v>
+      </c>
+      <c r="T29">
+        <v>1.67</v>
+      </c>
+      <c r="U29">
+        <v>2.26</v>
+      </c>
+      <c r="V29">
+        <v>2.12</v>
+      </c>
+      <c r="W29">
+        <v>1.25</v>
+      </c>
+      <c r="X29">
+        <v>24</v>
+      </c>
+      <c r="Y29">
+        <v>11.5</v>
+      </c>
+      <c r="Z29">
+        <v>13.5</v>
+      </c>
+      <c r="AA29">
+        <v>21</v>
+      </c>
+      <c r="AB29">
+        <v>21</v>
+      </c>
+      <c r="AC29">
+        <v>10.5</v>
+      </c>
+      <c r="AD29">
+        <v>11</v>
+      </c>
+      <c r="AE29">
+        <v>19</v>
+      </c>
+      <c r="AF29">
+        <v>38</v>
+      </c>
+      <c r="AG29">
+        <v>19</v>
+      </c>
+      <c r="AH29">
+        <v>18.5</v>
+      </c>
+      <c r="AI29">
+        <v>34</v>
+      </c>
+      <c r="AJ29">
+        <v>110</v>
+      </c>
+      <c r="AK29">
+        <v>55</v>
+      </c>
+      <c r="AL29">
+        <v>55</v>
+      </c>
+      <c r="AM29">
+        <v>90</v>
+      </c>
+      <c r="AN29">
+        <v>55</v>
+      </c>
+      <c r="AO29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP29">
+        <v>15.5</v>
+      </c>
+      <c r="AQ29">
+        <v>8.6</v>
+      </c>
+      <c r="AR29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS29">
+        <v>15</v>
+      </c>
+      <c r="AT29">
+        <v>15</v>
+      </c>
+      <c r="AU29">
+        <v>7.4</v>
+      </c>
+      <c r="AV29">
+        <v>8</v>
+      </c>
+      <c r="AW29">
+        <v>13.5</v>
+      </c>
+      <c r="AX29">
+        <v>6.6</v>
+      </c>
+      <c r="AY29">
         <v>14</v>
       </c>
-      <c r="I29">
-        <v>21</v>
-      </c>
-      <c r="J29">
+      <c r="AZ29">
+        <v>13</v>
+      </c>
+      <c r="BA29">
+        <v>6.6</v>
+      </c>
+      <c r="BB29">
+        <v>7.6</v>
+      </c>
+      <c r="BC29">
+        <v>7</v>
+      </c>
+      <c r="BD29">
+        <v>38</v>
+      </c>
+      <c r="BE29">
+        <v>7.4</v>
+      </c>
+      <c r="BF29">
+        <v>7</v>
+      </c>
+      <c r="BG29">
+        <v>7.4</v>
+      </c>
+      <c r="BH29">
+        <v>5.3</v>
+      </c>
+      <c r="BI29">
+        <v>2.84</v>
+      </c>
+      <c r="BJ29">
+        <v>13</v>
+      </c>
+      <c r="BK29">
+        <v>2.54</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>3.15</v>
+      </c>
+      <c r="BN29">
+        <v>11</v>
+      </c>
+      <c r="BO29">
+        <v>5.3</v>
+      </c>
+      <c r="BP29">
+        <v>48</v>
+      </c>
+      <c r="BQ29">
+        <v>2.96</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>2.98</v>
+      </c>
+      <c r="BT29">
         <v>6.4</v>
       </c>
-      <c r="K29">
-        <v>7.8</v>
-      </c>
-      <c r="L29">
-        <v>1.01</v>
-      </c>
-      <c r="M29">
-        <v>1.04</v>
-      </c>
-      <c r="N29">
-        <v>5.3</v>
-      </c>
-      <c r="O29">
-        <v>1.16</v>
-      </c>
-      <c r="P29">
-        <v>2.5</v>
-      </c>
-      <c r="Q29">
-        <v>1.53</v>
-      </c>
-      <c r="R29">
-        <v>1.6</v>
-      </c>
-      <c r="S29">
-        <v>2.32</v>
-      </c>
-      <c r="T29">
-        <v>1.9</v>
-      </c>
-      <c r="U29">
-        <v>1.57</v>
-      </c>
-      <c r="V29">
-        <v>1.05</v>
-      </c>
-      <c r="W29">
-        <v>4.4</v>
-      </c>
-      <c r="X29">
-        <v>1000</v>
-      </c>
-      <c r="Y29">
-        <v>1000</v>
-      </c>
-      <c r="Z29">
-        <v>1000</v>
-      </c>
-      <c r="AA29">
-        <v>1000</v>
-      </c>
-      <c r="AB29">
-        <v>1000</v>
-      </c>
-      <c r="AC29">
-        <v>1000</v>
-      </c>
-      <c r="AD29">
-        <v>1000</v>
-      </c>
-      <c r="AE29">
-        <v>1000</v>
-      </c>
-      <c r="AF29">
-        <v>1000</v>
-      </c>
-      <c r="AG29">
-        <v>1000</v>
-      </c>
-      <c r="AH29">
-        <v>1000</v>
-      </c>
-      <c r="AI29">
-        <v>1000</v>
-      </c>
-      <c r="AJ29">
-        <v>1000</v>
-      </c>
-      <c r="AK29">
-        <v>18.5</v>
-      </c>
-      <c r="AL29">
-        <v>1000</v>
-      </c>
-      <c r="AM29">
-        <v>1000</v>
-      </c>
-      <c r="AN29">
-        <v>1000</v>
-      </c>
-      <c r="AO29">
-        <v>1000</v>
-      </c>
-      <c r="AP29">
-        <v>1.05</v>
-      </c>
-      <c r="AQ29">
-        <v>1.05</v>
-      </c>
-      <c r="AR29">
-        <v>1.05</v>
-      </c>
-      <c r="AS29">
-        <v>1.05</v>
-      </c>
-      <c r="AT29">
-        <v>1.05</v>
-      </c>
-      <c r="AU29">
-        <v>1.05</v>
-      </c>
-      <c r="AV29">
-        <v>1.05</v>
-      </c>
-      <c r="AW29">
-        <v>1.05</v>
-      </c>
-      <c r="AX29">
-        <v>1.05</v>
-      </c>
-      <c r="AY29">
-        <v>1.05</v>
-      </c>
-      <c r="AZ29">
-        <v>1.05</v>
-      </c>
-      <c r="BA29">
-        <v>1.05</v>
-      </c>
-      <c r="BB29">
-        <v>1.05</v>
-      </c>
-      <c r="BC29">
-        <v>10</v>
-      </c>
-      <c r="BD29">
-        <v>1.05</v>
-      </c>
-      <c r="BE29">
-        <v>1.05</v>
-      </c>
-      <c r="BF29">
-        <v>1.05</v>
-      </c>
-      <c r="BG29">
-        <v>1.05</v>
-      </c>
-      <c r="BH29">
-        <v>6.4</v>
-      </c>
-      <c r="BI29">
-        <v>3.1</v>
-      </c>
-      <c r="BJ29">
-        <v>19</v>
-      </c>
-      <c r="BK29">
-        <v>2.5</v>
-      </c>
-      <c r="BL29">
-        <v>1000</v>
-      </c>
-      <c r="BM29">
-        <v>2.88</v>
-      </c>
-      <c r="BN29">
-        <v>5.1</v>
-      </c>
-      <c r="BO29">
-        <v>2.6</v>
-      </c>
-      <c r="BP29">
-        <v>9.6</v>
-      </c>
-      <c r="BQ29">
-        <v>4.3</v>
-      </c>
-      <c r="BR29">
-        <v>34</v>
-      </c>
-      <c r="BS29">
+      <c r="BU29">
+        <v>3.3</v>
+      </c>
+      <c r="BV29">
+        <v>17</v>
+      </c>
+      <c r="BW29">
         <v>2.66</v>
       </c>
-      <c r="BT29">
-        <v>25</v>
-      </c>
-      <c r="BU29">
-        <v>2.6</v>
-      </c>
-      <c r="BV29">
-        <v>1000</v>
-      </c>
-      <c r="BW29">
-        <v>2.88</v>
-      </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY29">
         <v>2.88</v>
       </c>
       <c r="BZ29">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="CA29">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="CB29" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8022,19 +8034,19 @@
         <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E30" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F30">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G30">
         <v>1.73</v>
@@ -8043,13 +8055,13 @@
         <v>5.4</v>
       </c>
       <c r="I30">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J30">
         <v>4.1</v>
       </c>
       <c r="K30">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L30">
         <v>1.31</v>
@@ -8058,7 +8070,7 @@
         <v>1.05</v>
       </c>
       <c r="N30">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O30">
         <v>1.24</v>
@@ -8079,7 +8091,7 @@
         <v>1.81</v>
       </c>
       <c r="U30">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V30">
         <v>1.2</v>
@@ -8124,7 +8136,7 @@
         <v>80</v>
       </c>
       <c r="AJ30">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AK30">
         <v>23</v>
@@ -8217,7 +8229,7 @@
         <v>5.8</v>
       </c>
       <c r="BO30">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BP30">
         <v>15.5</v>
@@ -8256,7 +8268,7 @@
         <v>1.82</v>
       </c>
       <c r="CB30" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8264,16 +8276,16 @@
         <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E31" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F31">
         <v>1.78</v>
@@ -8300,40 +8312,40 @@
         <v>1.03</v>
       </c>
       <c r="N31">
-        <v>2.56</v>
+        <v>1.1</v>
       </c>
       <c r="O31">
         <v>1.15</v>
       </c>
       <c r="P31">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q31">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R31">
         <v>1.49</v>
       </c>
       <c r="S31">
-        <v>2.24</v>
+        <v>1.89</v>
       </c>
       <c r="T31">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U31">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V31">
         <v>1.27</v>
       </c>
       <c r="W31">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X31">
         <v>1000</v>
       </c>
       <c r="Y31">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z31">
         <v>1000</v>
@@ -8342,37 +8354,37 @@
         <v>1000</v>
       </c>
       <c r="AB31">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC31">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD31">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE31">
         <v>1000</v>
       </c>
       <c r="AF31">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG31">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH31">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI31">
         <v>1000</v>
       </c>
       <c r="AJ31">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK31">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL31">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM31">
         <v>1000</v>
@@ -8384,52 +8396,52 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ31">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT31">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU31">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV31">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX31">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY31">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AZ31">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB31">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC31">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD31">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BE31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF31">
         <v>1.01</v>
@@ -8447,13 +8459,13 @@
         <v>12.5</v>
       </c>
       <c r="BK31">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="BN31">
         <v>6.6</v>
@@ -8465,22 +8477,22 @@
         <v>16</v>
       </c>
       <c r="BQ31">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="BR31">
         <v>29</v>
       </c>
       <c r="BS31">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="BT31">
         <v>11</v>
       </c>
       <c r="BU31">
-        <v>2.36</v>
+        <v>5.3</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW31">
         <v>3</v>
@@ -8489,7 +8501,7 @@
         <v>46</v>
       </c>
       <c r="BY31">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BZ31">
         <v>0</v>
@@ -8498,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8506,19 +8518,19 @@
         <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E32" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F32">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G32">
         <v>2.72</v>
@@ -8527,7 +8539,7 @@
         <v>2.5</v>
       </c>
       <c r="I32">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="J32">
         <v>4</v>
@@ -8542,31 +8554,31 @@
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O32">
         <v>1.14</v>
       </c>
       <c r="P32">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q32">
         <v>1.46</v>
       </c>
       <c r="R32">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S32">
         <v>2.16</v>
       </c>
       <c r="T32">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U32">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V32">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W32">
         <v>1.58</v>
@@ -8602,10 +8614,10 @@
         <v>1000</v>
       </c>
       <c r="AH32">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI32">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ32">
         <v>1000</v>
@@ -8614,7 +8626,7 @@
         <v>1000</v>
       </c>
       <c r="AL32">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM32">
         <v>1000</v>
@@ -8626,52 +8638,52 @@
         <v>1000</v>
       </c>
       <c r="AP32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF32">
         <v>1.01</v>
@@ -8740,7 +8752,7 @@
         <v>0</v>
       </c>
       <c r="CB32" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8748,22 +8760,22 @@
         <v>98</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E33" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F33">
         <v>2.24</v>
       </c>
       <c r="G33">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H33">
         <v>2.82</v>
@@ -8772,7 +8784,7 @@
         <v>3.45</v>
       </c>
       <c r="J33">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K33">
         <v>4.6</v>
@@ -8802,16 +8814,16 @@
         <v>2.18</v>
       </c>
       <c r="T33">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U33">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V33">
         <v>1.41</v>
       </c>
       <c r="W33">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -8868,52 +8880,52 @@
         <v>1000</v>
       </c>
       <c r="AP33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF33">
         <v>1.01</v>
@@ -8982,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -8990,22 +9002,22 @@
         <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E34" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F34">
         <v>1.26</v>
       </c>
       <c r="G34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H34">
         <v>12.5</v>
@@ -9089,7 +9101,7 @@
         <v>38</v>
       </c>
       <c r="AI34">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ34">
         <v>12.5</v>
@@ -9104,22 +9116,22 @@
         <v>170</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="AO34">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AP34">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ34">
-        <v>2.24</v>
+        <v>5.6</v>
       </c>
       <c r="AR34">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="AS34">
-        <v>2.32</v>
+        <v>6</v>
       </c>
       <c r="AT34">
         <v>10</v>
@@ -9128,10 +9140,10 @@
         <v>14</v>
       </c>
       <c r="AV34">
-        <v>2.24</v>
+        <v>5.6</v>
       </c>
       <c r="AW34">
-        <v>2.32</v>
+        <v>6</v>
       </c>
       <c r="AX34">
         <v>8</v>
@@ -9140,10 +9152,10 @@
         <v>10</v>
       </c>
       <c r="AZ34">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA34">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="BB34">
         <v>8.6</v>
@@ -9152,16 +9164,16 @@
         <v>10</v>
       </c>
       <c r="BD34">
-        <v>2.22</v>
+        <v>5.4</v>
       </c>
       <c r="BE34">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="BF34">
         <v>3</v>
       </c>
       <c r="BG34">
-        <v>2.32</v>
+        <v>6</v>
       </c>
       <c r="BH34">
         <v>0</v>
@@ -9224,7 +9236,7 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9232,16 +9244,16 @@
         <v>100</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D35" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E35" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F35">
         <v>1.77</v>
@@ -9262,7 +9274,7 @@
         <v>4.1</v>
       </c>
       <c r="L35">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M35">
         <v>1.07</v>
@@ -9286,10 +9298,10 @@
         <v>3.55</v>
       </c>
       <c r="T35">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U35">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V35">
         <v>1.21</v>
@@ -9358,10 +9370,10 @@
         <v>12</v>
       </c>
       <c r="AR35">
-        <v>28</v>
+        <v>5.1</v>
       </c>
       <c r="AS35">
-        <v>90</v>
+        <v>5.5</v>
       </c>
       <c r="AT35">
         <v>6.2</v>
@@ -9373,7 +9385,7 @@
         <v>14.5</v>
       </c>
       <c r="AW35">
-        <v>50</v>
+        <v>5.3</v>
       </c>
       <c r="AX35">
         <v>8</v>
@@ -9385,7 +9397,7 @@
         <v>14.5</v>
       </c>
       <c r="BA35">
-        <v>50</v>
+        <v>5.4</v>
       </c>
       <c r="BB35">
         <v>14.5</v>
@@ -9394,16 +9406,16 @@
         <v>14.5</v>
       </c>
       <c r="BD35">
-        <v>27</v>
+        <v>5.1</v>
       </c>
       <c r="BE35">
-        <v>85</v>
+        <v>5.5</v>
       </c>
       <c r="BF35">
         <v>9.6</v>
       </c>
       <c r="BG35">
-        <v>60</v>
+        <v>5.5</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9466,7 +9478,7 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9474,16 +9486,16 @@
         <v>91</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D36" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E36" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F36">
         <v>2.2</v>
@@ -9504,7 +9516,7 @@
         <v>3.5</v>
       </c>
       <c r="L36">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M36">
         <v>1.09</v>
@@ -9516,7 +9528,7 @@
         <v>1.42</v>
       </c>
       <c r="P36">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q36">
         <v>2.22</v>
@@ -9708,7 +9720,7 @@
         <v>10.5</v>
       </c>
       <c r="CB36" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9716,22 +9728,22 @@
         <v>98</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D37" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E37" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F37">
         <v>3.35</v>
       </c>
       <c r="G37">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="H37">
         <v>2.02</v>
@@ -9752,7 +9764,7 @@
         <v>1.04</v>
       </c>
       <c r="N37">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="O37">
         <v>1.19</v>
@@ -9761,61 +9773,61 @@
         <v>2.5</v>
       </c>
       <c r="Q37">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="R37">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="S37">
         <v>2.28</v>
       </c>
       <c r="T37">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="U37">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V37">
         <v>1.83</v>
       </c>
       <c r="W37">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="X37">
         <v>1000</v>
       </c>
       <c r="Y37">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z37">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA37">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB37">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC37">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD37">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE37">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF37">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG37">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH37">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI37">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ37">
         <v>1000</v>
@@ -9836,52 +9848,52 @@
         <v>1000</v>
       </c>
       <c r="AP37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ37">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR37">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS37">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AT37">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU37">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV37">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AW37">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX37">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY37">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ37">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BA37">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BB37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF37">
         <v>1.01</v>
@@ -9905,7 +9917,7 @@
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>21</v>
+        <v>2.88</v>
       </c>
       <c r="BN37">
         <v>10</v>
@@ -9917,13 +9929,13 @@
         <v>38</v>
       </c>
       <c r="BQ37">
-        <v>15</v>
+        <v>2.7</v>
       </c>
       <c r="BR37">
         <v>46</v>
       </c>
       <c r="BS37">
-        <v>18.5</v>
+        <v>2.72</v>
       </c>
       <c r="BT37">
         <v>7.4</v>
@@ -9935,13 +9947,13 @@
         <v>20</v>
       </c>
       <c r="BW37">
-        <v>8.4</v>
+        <v>2.52</v>
       </c>
       <c r="BX37">
         <v>34</v>
       </c>
       <c r="BY37">
-        <v>14</v>
+        <v>2.66</v>
       </c>
       <c r="BZ37">
         <v>0</v>
@@ -9950,7 +9962,7 @@
         <v>0</v>
       </c>
       <c r="CB37" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -9958,16 +9970,16 @@
         <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E38" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F38">
         <v>3.65</v>
@@ -9979,7 +9991,7 @@
         <v>2.12</v>
       </c>
       <c r="I38">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J38">
         <v>3.1</v>
@@ -9988,19 +10000,19 @@
         <v>3.6</v>
       </c>
       <c r="L38">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M38">
         <v>1.08</v>
       </c>
       <c r="N38">
-        <v>1.73</v>
+        <v>2.86</v>
       </c>
       <c r="O38">
         <v>1.42</v>
       </c>
       <c r="P38">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q38">
         <v>2.22</v>
@@ -10009,16 +10021,16 @@
         <v>1.18</v>
       </c>
       <c r="S38">
-        <v>2.22</v>
+        <v>1.05</v>
       </c>
       <c r="T38">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U38">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V38">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W38">
         <v>1.31</v>
@@ -10192,7 +10204,7 @@
         <v>1.01</v>
       </c>
       <c r="CB38" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10200,16 +10212,16 @@
         <v>92</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D39" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E39" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F39">
         <v>3.05</v>
@@ -10236,7 +10248,7 @@
         <v>1.07</v>
       </c>
       <c r="N39">
-        <v>1.74</v>
+        <v>2.74</v>
       </c>
       <c r="O39">
         <v>1.37</v>
@@ -10245,7 +10257,7 @@
         <v>1.74</v>
       </c>
       <c r="Q39">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="R39">
         <v>1.25</v>
@@ -10254,10 +10266,10 @@
         <v>3.35</v>
       </c>
       <c r="T39">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U39">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V39">
         <v>1.59</v>
@@ -10269,34 +10281,34 @@
         <v>1000</v>
       </c>
       <c r="Y39">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z39">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA39">
         <v>1000</v>
       </c>
       <c r="AB39">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC39">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD39">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE39">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF39">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG39">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH39">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI39">
         <v>1000</v>
@@ -10320,52 +10332,52 @@
         <v>1000</v>
       </c>
       <c r="AP39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AR39">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT39">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU39">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV39">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AW39">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX39">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY39">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ39">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF39">
         <v>1.01</v>
@@ -10383,13 +10395,13 @@
         <v>14.5</v>
       </c>
       <c r="BK39">
-        <v>6.2</v>
+        <v>2.66</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>21</v>
+        <v>3.2</v>
       </c>
       <c r="BN39">
         <v>8.800000000000001</v>
@@ -10401,13 +10413,13 @@
         <v>40</v>
       </c>
       <c r="BQ39">
-        <v>16.5</v>
+        <v>3</v>
       </c>
       <c r="BR39">
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>21</v>
+        <v>3.1</v>
       </c>
       <c r="BT39">
         <v>7.6</v>
@@ -10419,22 +10431,22 @@
         <v>29</v>
       </c>
       <c r="BW39">
-        <v>12</v>
+        <v>2.92</v>
       </c>
       <c r="BX39">
         <v>50</v>
       </c>
       <c r="BY39">
-        <v>21</v>
+        <v>3.05</v>
       </c>
       <c r="BZ39">
         <v>50</v>
       </c>
       <c r="CA39">
-        <v>20</v>
+        <v>3.05</v>
       </c>
       <c r="CB39" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="40" spans="1:80">
@@ -10442,16 +10454,16 @@
         <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D40" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E40" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F40">
         <v>2.9</v>
@@ -10472,7 +10484,7 @@
         <v>4.1</v>
       </c>
       <c r="L40">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M40">
         <v>1.05</v>
@@ -10490,7 +10502,7 @@
         <v>1.72</v>
       </c>
       <c r="R40">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S40">
         <v>2.82</v>
@@ -10499,13 +10511,13 @@
         <v>1.62</v>
       </c>
       <c r="U40">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V40">
         <v>1.63</v>
       </c>
       <c r="W40">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X40">
         <v>22</v>
@@ -10562,10 +10574,10 @@
         <v>19</v>
       </c>
       <c r="AP40">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ40">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AR40">
         <v>13.5</v>
@@ -10586,7 +10598,7 @@
         <v>18.5</v>
       </c>
       <c r="AX40">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY40">
         <v>10</v>
@@ -10625,13 +10637,13 @@
         <v>12.5</v>
       </c>
       <c r="BK40">
-        <v>5.8</v>
+        <v>1.69</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>21</v>
+        <v>1.95</v>
       </c>
       <c r="BN40">
         <v>8.6</v>
@@ -10643,13 +10655,13 @@
         <v>30</v>
       </c>
       <c r="BQ40">
-        <v>14</v>
+        <v>1.83</v>
       </c>
       <c r="BR40">
         <v>44</v>
       </c>
       <c r="BS40">
-        <v>19</v>
+        <v>1.87</v>
       </c>
       <c r="BT40">
         <v>7.6</v>
@@ -10661,13 +10673,13 @@
         <v>24</v>
       </c>
       <c r="BW40">
-        <v>11</v>
+        <v>1.8</v>
       </c>
       <c r="BX40">
         <v>38</v>
       </c>
       <c r="BY40">
-        <v>16.5</v>
+        <v>1.85</v>
       </c>
       <c r="BZ40">
         <v>0</v>
@@ -10676,7 +10688,7 @@
         <v>0</v>
       </c>
       <c r="CB40" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="41" spans="1:80">
@@ -10684,178 +10696,178 @@
         <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D41" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E41" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F41">
-        <v>8.800000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="G41">
-        <v>1000</v>
+        <v>1.54</v>
       </c>
       <c r="H41">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="I41">
-        <v>1.42</v>
+        <v>8</v>
       </c>
       <c r="J41">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="K41">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="L41">
         <v>1.01</v>
       </c>
       <c r="M41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N41">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="O41">
+        <v>1.16</v>
+      </c>
+      <c r="P41">
+        <v>2.5</v>
+      </c>
+      <c r="Q41">
+        <v>1.55</v>
+      </c>
+      <c r="R41">
+        <v>1.5</v>
+      </c>
+      <c r="S41">
+        <v>2.18</v>
+      </c>
+      <c r="T41">
+        <v>1.53</v>
+      </c>
+      <c r="U41">
+        <v>1.81</v>
+      </c>
+      <c r="V41">
         <v>1.15</v>
       </c>
-      <c r="P41">
-        <v>2.44</v>
-      </c>
-      <c r="Q41">
-        <v>1.51</v>
-      </c>
-      <c r="R41">
-        <v>1.57</v>
-      </c>
-      <c r="S41">
-        <v>2.3</v>
-      </c>
-      <c r="T41">
-        <v>1.01</v>
-      </c>
-      <c r="U41">
-        <v>1.01</v>
-      </c>
-      <c r="V41">
-        <v>3.4</v>
-      </c>
       <c r="W41">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="X41">
         <v>1000</v>
       </c>
       <c r="Y41">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z41">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA41">
         <v>1000</v>
       </c>
       <c r="AB41">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC41">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD41">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE41">
         <v>1000</v>
       </c>
       <c r="AF41">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG41">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH41">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI41">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ41">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK41">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL41">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM41">
         <v>1000</v>
       </c>
       <c r="AN41">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO41">
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AQ41">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR41">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AS41">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AT41">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU41">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV41">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AW41">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AX41">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY41">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ41">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA41">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BB41">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BC41">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BD41">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BE41">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BF41">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG41">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -10918,42 +10930,42 @@
         <v>0</v>
       </c>
       <c r="CB41" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B42" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C42" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D42" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E42" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F42">
-        <v>2.78</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G42">
-        <v>3.3</v>
+        <v>990</v>
       </c>
       <c r="H42">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="I42">
-        <v>2.8</v>
+        <v>1.42</v>
       </c>
       <c r="J42">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K42">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="L42">
         <v>1.01</v>
@@ -10962,34 +10974,34 @@
         <v>1.01</v>
       </c>
       <c r="N42">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="O42">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="P42">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="Q42">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="R42">
-        <v>1.07</v>
+        <v>1.57</v>
       </c>
       <c r="S42">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="T42">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U42">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V42">
-        <v>1.56</v>
+        <v>3.4</v>
       </c>
       <c r="W42">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="X42">
         <v>1000</v>
@@ -11046,52 +11058,52 @@
         <v>1000</v>
       </c>
       <c r="AP42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF42">
         <v>1.01</v>
@@ -11100,10 +11112,10 @@
         <v>1.01</v>
       </c>
       <c r="BH42">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI42">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BJ42">
         <v>1000</v>
@@ -11160,42 +11172,42 @@
         <v>0</v>
       </c>
       <c r="CB42" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="43" spans="1:80">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D43" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E43" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F43">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="G43">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="H43">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="I43">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J43">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K43">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11204,34 +11216,34 @@
         <v>1.01</v>
       </c>
       <c r="N43">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="O43">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P43">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="Q43">
-        <v>1.23</v>
+        <v>1.77</v>
       </c>
       <c r="R43">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S43">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="T43">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U43">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V43">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="W43">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="X43">
         <v>1000</v>
@@ -11288,52 +11300,52 @@
         <v>1000</v>
       </c>
       <c r="AP43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF43">
         <v>1.01</v>
@@ -11342,58 +11354,58 @@
         <v>1.01</v>
       </c>
       <c r="BH43">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BI43">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="BJ43">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK43">
-        <v>5.8</v>
+        <v>1.29</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>22</v>
+        <v>1.29</v>
       </c>
       <c r="BN43">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO43">
-        <v>3.85</v>
+        <v>1.29</v>
       </c>
       <c r="BP43">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ43">
-        <v>11</v>
+        <v>1.29</v>
       </c>
       <c r="BR43">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS43">
-        <v>16.5</v>
+        <v>1.29</v>
       </c>
       <c r="BT43">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU43">
-        <v>4.3</v>
+        <v>1.29</v>
       </c>
       <c r="BV43">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW43">
-        <v>13</v>
+        <v>1.29</v>
       </c>
       <c r="BX43">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY43">
-        <v>18</v>
+        <v>1.29</v>
       </c>
       <c r="BZ43">
         <v>0</v>
@@ -11402,42 +11414,42 @@
         <v>0</v>
       </c>
       <c r="CB43" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" spans="1:80">
       <c r="A44" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B44" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C44" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D44" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E44" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F44">
-        <v>1.52</v>
+        <v>2.28</v>
       </c>
       <c r="G44">
-        <v>1.88</v>
+        <v>2.96</v>
       </c>
       <c r="H44">
-        <v>4.5</v>
+        <v>2.52</v>
       </c>
       <c r="I44">
-        <v>8.4</v>
+        <v>3.6</v>
       </c>
       <c r="J44">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="K44">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="L44">
         <v>1.01</v>
@@ -11446,34 +11458,34 @@
         <v>1.01</v>
       </c>
       <c r="N44">
-        <v>1.94</v>
+        <v>3.9</v>
       </c>
       <c r="O44">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="P44">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q44">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="R44">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S44">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="T44">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U44">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V44">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="W44">
-        <v>2.12</v>
+        <v>1.51</v>
       </c>
       <c r="X44">
         <v>1000</v>
@@ -11530,52 +11542,52 @@
         <v>1000</v>
       </c>
       <c r="AP44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF44">
         <v>1.01</v>
@@ -11584,58 +11596,58 @@
         <v>1.01</v>
       </c>
       <c r="BH44">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BI44">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="BJ44">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BK44">
-        <v>6.6</v>
+        <v>2.52</v>
       </c>
       <c r="BL44">
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>22</v>
+        <v>3.15</v>
       </c>
       <c r="BN44">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO44">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="BP44">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BQ44">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="BR44">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS44">
-        <v>15.5</v>
+        <v>2.92</v>
       </c>
       <c r="BT44">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BU44">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="BV44">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW44">
-        <v>22</v>
+        <v>2.88</v>
       </c>
       <c r="BX44">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY44">
-        <v>22</v>
+        <v>2.96</v>
       </c>
       <c r="BZ44">
         <v>0</v>
@@ -11644,240 +11656,240 @@
         <v>0</v>
       </c>
       <c r="CB44" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="45" spans="1:80">
       <c r="A45" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B45" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C45" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D45" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E45" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F45">
-        <v>2.38</v>
+        <v>1.6</v>
       </c>
       <c r="G45">
+        <v>1.88</v>
+      </c>
+      <c r="H45">
+        <v>4.5</v>
+      </c>
+      <c r="I45">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J45">
+        <v>3.75</v>
+      </c>
+      <c r="K45">
+        <v>6.4</v>
+      </c>
+      <c r="L45">
+        <v>1.01</v>
+      </c>
+      <c r="M45">
+        <v>1.01</v>
+      </c>
+      <c r="N45">
+        <v>2.18</v>
+      </c>
+      <c r="O45">
+        <v>1.25</v>
+      </c>
+      <c r="P45">
+        <v>1.94</v>
+      </c>
+      <c r="Q45">
+        <v>1.63</v>
+      </c>
+      <c r="R45">
+        <v>1.34</v>
+      </c>
+      <c r="S45">
+        <v>2.58</v>
+      </c>
+      <c r="T45">
+        <v>1.11</v>
+      </c>
+      <c r="U45">
+        <v>1.11</v>
+      </c>
+      <c r="V45">
+        <v>1.13</v>
+      </c>
+      <c r="W45">
+        <v>2.12</v>
+      </c>
+      <c r="X45">
+        <v>1000</v>
+      </c>
+      <c r="Y45">
+        <v>1000</v>
+      </c>
+      <c r="Z45">
+        <v>1000</v>
+      </c>
+      <c r="AA45">
+        <v>1000</v>
+      </c>
+      <c r="AB45">
+        <v>1000</v>
+      </c>
+      <c r="AC45">
+        <v>1000</v>
+      </c>
+      <c r="AD45">
+        <v>1000</v>
+      </c>
+      <c r="AE45">
+        <v>1000</v>
+      </c>
+      <c r="AF45">
+        <v>1000</v>
+      </c>
+      <c r="AG45">
+        <v>1000</v>
+      </c>
+      <c r="AH45">
+        <v>1000</v>
+      </c>
+      <c r="AI45">
+        <v>1000</v>
+      </c>
+      <c r="AJ45">
+        <v>1000</v>
+      </c>
+      <c r="AK45">
+        <v>1000</v>
+      </c>
+      <c r="AL45">
+        <v>1000</v>
+      </c>
+      <c r="AM45">
+        <v>1000</v>
+      </c>
+      <c r="AN45">
+        <v>1000</v>
+      </c>
+      <c r="AO45">
+        <v>1000</v>
+      </c>
+      <c r="AP45">
+        <v>1.03</v>
+      </c>
+      <c r="AQ45">
+        <v>1.03</v>
+      </c>
+      <c r="AR45">
+        <v>1.03</v>
+      </c>
+      <c r="AS45">
+        <v>1.03</v>
+      </c>
+      <c r="AT45">
+        <v>1.03</v>
+      </c>
+      <c r="AU45">
+        <v>1.03</v>
+      </c>
+      <c r="AV45">
+        <v>1.03</v>
+      </c>
+      <c r="AW45">
+        <v>1.03</v>
+      </c>
+      <c r="AX45">
+        <v>1.03</v>
+      </c>
+      <c r="AY45">
+        <v>1.03</v>
+      </c>
+      <c r="AZ45">
+        <v>1.03</v>
+      </c>
+      <c r="BA45">
+        <v>1.03</v>
+      </c>
+      <c r="BB45">
+        <v>1.03</v>
+      </c>
+      <c r="BC45">
+        <v>1.03</v>
+      </c>
+      <c r="BD45">
+        <v>1.03</v>
+      </c>
+      <c r="BE45">
+        <v>1.03</v>
+      </c>
+      <c r="BF45">
+        <v>1.01</v>
+      </c>
+      <c r="BG45">
+        <v>1.01</v>
+      </c>
+      <c r="BH45">
+        <v>4.7</v>
+      </c>
+      <c r="BI45">
+        <v>2.94</v>
+      </c>
+      <c r="BJ45">
+        <v>13.5</v>
+      </c>
+      <c r="BK45">
+        <v>2.7</v>
+      </c>
+      <c r="BL45">
+        <v>1000</v>
+      </c>
+      <c r="BM45">
+        <v>3.35</v>
+      </c>
+      <c r="BN45">
+        <v>5.8</v>
+      </c>
+      <c r="BO45">
+        <v>3</v>
+      </c>
+      <c r="BP45">
+        <v>15</v>
+      </c>
+      <c r="BQ45">
+        <v>2.76</v>
+      </c>
+      <c r="BR45">
+        <v>34</v>
+      </c>
+      <c r="BS45">
+        <v>3.05</v>
+      </c>
+      <c r="BT45">
+        <v>12.5</v>
+      </c>
+      <c r="BU45">
         <v>2.66</v>
       </c>
-      <c r="H45">
-        <v>2.92</v>
-      </c>
-      <c r="I45">
-        <v>3.5</v>
-      </c>
-      <c r="J45">
-        <v>3.25</v>
-      </c>
-      <c r="K45">
-        <v>3.75</v>
-      </c>
-      <c r="L45">
-        <v>1.01</v>
-      </c>
-      <c r="M45">
-        <v>1.01</v>
-      </c>
-      <c r="N45">
-        <v>1.83</v>
-      </c>
-      <c r="O45">
-        <v>1.32</v>
-      </c>
-      <c r="P45">
-        <v>1.83</v>
-      </c>
-      <c r="Q45">
-        <v>1.94</v>
-      </c>
-      <c r="R45">
-        <v>1.35</v>
-      </c>
-      <c r="S45">
-        <v>1.94</v>
-      </c>
-      <c r="T45">
-        <v>1.01</v>
-      </c>
-      <c r="U45">
-        <v>1.01</v>
-      </c>
-      <c r="V45">
-        <v>1.4</v>
-      </c>
-      <c r="W45">
-        <v>1.6</v>
-      </c>
-      <c r="X45">
-        <v>1000</v>
-      </c>
-      <c r="Y45">
-        <v>1000</v>
-      </c>
-      <c r="Z45">
-        <v>1000</v>
-      </c>
-      <c r="AA45">
-        <v>1000</v>
-      </c>
-      <c r="AB45">
-        <v>1000</v>
-      </c>
-      <c r="AC45">
-        <v>1000</v>
-      </c>
-      <c r="AD45">
-        <v>1000</v>
-      </c>
-      <c r="AE45">
-        <v>1000</v>
-      </c>
-      <c r="AF45">
-        <v>1000</v>
-      </c>
-      <c r="AG45">
-        <v>1000</v>
-      </c>
-      <c r="AH45">
-        <v>1000</v>
-      </c>
-      <c r="AI45">
-        <v>1000</v>
-      </c>
-      <c r="AJ45">
-        <v>1000</v>
-      </c>
-      <c r="AK45">
-        <v>1000</v>
-      </c>
-      <c r="AL45">
-        <v>1000</v>
-      </c>
-      <c r="AM45">
-        <v>1000</v>
-      </c>
-      <c r="AN45">
-        <v>1000</v>
-      </c>
-      <c r="AO45">
-        <v>1000</v>
-      </c>
-      <c r="AP45">
-        <v>1.01</v>
-      </c>
-      <c r="AQ45">
-        <v>1.01</v>
-      </c>
-      <c r="AR45">
-        <v>1.01</v>
-      </c>
-      <c r="AS45">
-        <v>1.01</v>
-      </c>
-      <c r="AT45">
-        <v>1.01</v>
-      </c>
-      <c r="AU45">
-        <v>1.01</v>
-      </c>
-      <c r="AV45">
-        <v>1.01</v>
-      </c>
-      <c r="AW45">
-        <v>1.01</v>
-      </c>
-      <c r="AX45">
-        <v>1.01</v>
-      </c>
-      <c r="AY45">
-        <v>1.01</v>
-      </c>
-      <c r="AZ45">
-        <v>1.01</v>
-      </c>
-      <c r="BA45">
-        <v>1.01</v>
-      </c>
-      <c r="BB45">
-        <v>1.01</v>
-      </c>
-      <c r="BC45">
-        <v>1.01</v>
-      </c>
-      <c r="BD45">
-        <v>1.01</v>
-      </c>
-      <c r="BE45">
-        <v>1.01</v>
-      </c>
-      <c r="BF45">
-        <v>1.01</v>
-      </c>
-      <c r="BG45">
-        <v>1.01</v>
-      </c>
-      <c r="BH45">
-        <v>4.1</v>
-      </c>
-      <c r="BI45">
-        <v>2.66</v>
-      </c>
-      <c r="BJ45">
-        <v>1000</v>
-      </c>
-      <c r="BK45">
-        <v>1.01</v>
-      </c>
-      <c r="BL45">
-        <v>1000</v>
-      </c>
-      <c r="BM45">
-        <v>1.01</v>
-      </c>
-      <c r="BN45">
-        <v>1000</v>
-      </c>
-      <c r="BO45">
-        <v>1.01</v>
-      </c>
-      <c r="BP45">
-        <v>1000</v>
-      </c>
-      <c r="BQ45">
-        <v>1.01</v>
-      </c>
-      <c r="BR45">
-        <v>1000</v>
-      </c>
-      <c r="BS45">
-        <v>1.01</v>
-      </c>
-      <c r="BT45">
-        <v>1000</v>
-      </c>
-      <c r="BU45">
-        <v>1.01</v>
-      </c>
       <c r="BV45">
         <v>1000</v>
       </c>
       <c r="BW45">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BX45">
         <v>1000</v>
       </c>
       <c r="BY45">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BZ45">
         <v>0</v>
@@ -11886,7 +11898,7 @@
         <v>0</v>
       </c>
       <c r="CB45" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46" spans="1:80">
@@ -11894,115 +11906,115 @@
         <v>102</v>
       </c>
       <c r="B46" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D46" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E46" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F46">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="G46">
-        <v>1.54</v>
+        <v>2.66</v>
       </c>
       <c r="H46">
-        <v>6.6</v>
+        <v>2.92</v>
       </c>
       <c r="I46">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="J46">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="K46">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="L46">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M46">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N46">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="O46">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="P46">
-        <v>2.52</v>
+        <v>1.83</v>
       </c>
       <c r="Q46">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="R46">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="S46">
-        <v>2.18</v>
+        <v>2.82</v>
       </c>
       <c r="T46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U46">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V46">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="W46">
-        <v>2.76</v>
+        <v>1.6</v>
       </c>
       <c r="X46">
         <v>1000</v>
       </c>
       <c r="Y46">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Z46">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA46">
         <v>1000</v>
       </c>
       <c r="AB46">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC46">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AD46">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE46">
         <v>1000</v>
       </c>
       <c r="AF46">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG46">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH46">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI46">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ46">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK46">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL46">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM46">
         <v>1000</v>
@@ -12014,112 +12026,112 @@
         <v>1000</v>
       </c>
       <c r="AP46">
-        <v>1.9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ46">
-        <v>1.83</v>
+        <v>1.03</v>
       </c>
       <c r="AR46">
-        <v>1.86</v>
+        <v>1.03</v>
       </c>
       <c r="AS46">
-        <v>1.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT46">
-        <v>1.7</v>
+        <v>1.03</v>
       </c>
       <c r="AU46">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="AV46">
-        <v>1.81</v>
+        <v>1.03</v>
       </c>
       <c r="AW46">
-        <v>1.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX46">
-        <v>1.7</v>
+        <v>1.03</v>
       </c>
       <c r="AY46">
-        <v>1.69</v>
+        <v>1.03</v>
       </c>
       <c r="AZ46">
-        <v>1.79</v>
+        <v>1.03</v>
       </c>
       <c r="BA46">
-        <v>1.87</v>
+        <v>1.03</v>
       </c>
       <c r="BB46">
-        <v>1.74</v>
+        <v>1.03</v>
       </c>
       <c r="BC46">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BD46">
-        <v>1.83</v>
+        <v>1.03</v>
       </c>
       <c r="BE46">
-        <v>1.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF46">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG46">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH46">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI46">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ46">
         <v>1000</v>
       </c>
       <c r="BK46">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BL46">
         <v>1000</v>
       </c>
       <c r="BM46">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BN46">
         <v>1000</v>
       </c>
       <c r="BO46">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BP46">
         <v>1000</v>
       </c>
       <c r="BQ46">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BR46">
         <v>1000</v>
       </c>
       <c r="BS46">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BT46">
         <v>1000</v>
       </c>
       <c r="BU46">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BV46">
         <v>1000</v>
       </c>
       <c r="BW46">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BX46">
         <v>1000</v>
       </c>
       <c r="BY46">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BZ46">
         <v>0</v>
@@ -12128,7 +12140,7 @@
         <v>0</v>
       </c>
       <c r="CB46" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:80">
@@ -12136,474 +12148,474 @@
         <v>94</v>
       </c>
       <c r="B47" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D47" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E47" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F47">
         <v>1.27</v>
       </c>
       <c r="G47">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H47">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="I47">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J47">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="K47">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P47">
         <v>3.65</v>
       </c>
       <c r="Q47">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH47">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL47">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN47">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AO47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP47">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AU47">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AV47">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AW47">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AX47">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY47">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ47">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA47">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BB47">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BC47">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BD47">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BE47">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BF47">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BG47">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BH47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ47">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB47" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="48" spans="1:80">
       <c r="A48" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D48" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E48" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F48">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="G48">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="H48">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="I48">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="J48">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="K48">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P48">
-        <v>1.79</v>
+        <v>2.56</v>
       </c>
       <c r="Q48">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH48">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI48">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL48">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM48">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN48">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO48">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AP48">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AQ48">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR48">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS48">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT48">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU48">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV48">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW48">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AX48">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AY48">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AZ48">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA48">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BB48">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BC48">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BD48">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BE48">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BF48">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BG48">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BH48">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BI48">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BJ48">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK48">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BL48">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM48">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN48">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BO48">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BP48">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ48">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR48">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS48">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT48">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BU48">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BV48">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW48">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BX48">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BY48">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BZ48">
         <v>0</v>
@@ -12612,240 +12624,240 @@
         <v>0</v>
       </c>
       <c r="CB48" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:80">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D49" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E49" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F49">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="G49">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H49">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="I49">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="J49">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="K49">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M49">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N49">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="O49">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="P49">
-        <v>2.56</v>
+        <v>1.8</v>
       </c>
       <c r="Q49">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="R49">
-        <v>1.63</v>
+        <v>1.23</v>
       </c>
       <c r="S49">
-        <v>2.3</v>
+        <v>1.05</v>
       </c>
       <c r="T49">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="U49">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X49">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y49">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z49">
         <v>13</v>
       </c>
-      <c r="Z49">
-        <v>14.5</v>
-      </c>
       <c r="AA49">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="AB49">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="AC49">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AD49">
         <v>12.5</v>
       </c>
       <c r="AE49">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AF49">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG49">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AH49">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI49">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ49">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AK49">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL49">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM49">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN49">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO49">
+        <v>1000</v>
+      </c>
+      <c r="AP49">
+        <v>2.28</v>
+      </c>
+      <c r="AQ49">
+        <v>5.5</v>
+      </c>
+      <c r="AR49">
+        <v>7.4</v>
+      </c>
+      <c r="AS49">
+        <v>13</v>
+      </c>
+      <c r="AT49">
+        <v>10</v>
+      </c>
+      <c r="AU49">
+        <v>1.89</v>
+      </c>
+      <c r="AV49">
         <v>6.8</v>
       </c>
-      <c r="AP49">
-        <v>5</v>
-      </c>
-      <c r="AQ49">
-        <v>10.5</v>
-      </c>
-      <c r="AR49">
-        <v>10</v>
-      </c>
-      <c r="AS49">
-        <v>13.5</v>
-      </c>
-      <c r="AT49">
-        <v>19.5</v>
-      </c>
-      <c r="AU49">
-        <v>10</v>
-      </c>
-      <c r="AV49">
-        <v>9</v>
-      </c>
       <c r="AW49">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX49">
-        <v>36</v>
+        <v>2.28</v>
       </c>
       <c r="AY49">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ49">
-        <v>16</v>
+        <v>2.08</v>
       </c>
       <c r="BA49">
-        <v>20</v>
+        <v>2.28</v>
       </c>
       <c r="BB49">
-        <v>5.7</v>
+        <v>2.28</v>
       </c>
       <c r="BC49">
-        <v>5.4</v>
+        <v>2.28</v>
       </c>
       <c r="BD49">
-        <v>5.5</v>
+        <v>2.28</v>
       </c>
       <c r="BE49">
-        <v>40</v>
+        <v>2.28</v>
       </c>
       <c r="BF49">
-        <v>5.4</v>
+        <v>2.28</v>
       </c>
       <c r="BG49">
-        <v>4.6</v>
+        <v>2.28</v>
       </c>
       <c r="BH49">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI49">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BJ49">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK49">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL49">
         <v>1000</v>
       </c>
       <c r="BM49">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN49">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO49">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP49">
         <v>1000</v>
       </c>
       <c r="BQ49">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR49">
         <v>1000</v>
       </c>
       <c r="BS49">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT49">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU49">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV49">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BW49">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX49">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BY49">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ49">
         <v>0</v>
@@ -12854,7 +12866,249 @@
         <v>0</v>
       </c>
       <c r="CB49" t="s">
-        <v>216</v>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="50" spans="1:80">
+      <c r="A50" t="s">
+        <v>104</v>
+      </c>
+      <c r="B50" t="s">
+        <v>105</v>
+      </c>
+      <c r="C50" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50" t="s">
+        <v>170</v>
+      </c>
+      <c r="E50" t="s">
+        <v>219</v>
+      </c>
+      <c r="F50">
+        <v>1.75</v>
+      </c>
+      <c r="G50">
+        <v>2.2</v>
+      </c>
+      <c r="H50">
+        <v>3.85</v>
+      </c>
+      <c r="I50">
+        <v>7.2</v>
+      </c>
+      <c r="J50">
+        <v>2.46</v>
+      </c>
+      <c r="K50">
+        <v>950</v>
+      </c>
+      <c r="L50">
+        <v>1.01</v>
+      </c>
+      <c r="M50">
+        <v>1.01</v>
+      </c>
+      <c r="N50">
+        <v>1.71</v>
+      </c>
+      <c r="O50">
+        <v>1.32</v>
+      </c>
+      <c r="P50">
+        <v>1.71</v>
+      </c>
+      <c r="Q50">
+        <v>1.83</v>
+      </c>
+      <c r="R50">
+        <v>1.18</v>
+      </c>
+      <c r="S50">
+        <v>2.72</v>
+      </c>
+      <c r="T50">
+        <v>1.01</v>
+      </c>
+      <c r="U50">
+        <v>1.01</v>
+      </c>
+      <c r="V50">
+        <v>1.2</v>
+      </c>
+      <c r="W50">
+        <v>1.83</v>
+      </c>
+      <c r="X50">
+        <v>18.5</v>
+      </c>
+      <c r="Y50">
+        <v>21</v>
+      </c>
+      <c r="Z50">
+        <v>48</v>
+      </c>
+      <c r="AA50">
+        <v>1000</v>
+      </c>
+      <c r="AB50">
+        <v>11</v>
+      </c>
+      <c r="AC50">
+        <v>11</v>
+      </c>
+      <c r="AD50">
+        <v>25</v>
+      </c>
+      <c r="AE50">
+        <v>85</v>
+      </c>
+      <c r="AF50">
+        <v>15.5</v>
+      </c>
+      <c r="AG50">
+        <v>13.5</v>
+      </c>
+      <c r="AH50">
+        <v>26</v>
+      </c>
+      <c r="AI50">
+        <v>90</v>
+      </c>
+      <c r="AJ50">
+        <v>30</v>
+      </c>
+      <c r="AK50">
+        <v>29</v>
+      </c>
+      <c r="AL50">
+        <v>50</v>
+      </c>
+      <c r="AM50">
+        <v>1000</v>
+      </c>
+      <c r="AN50">
+        <v>1000</v>
+      </c>
+      <c r="AO50">
+        <v>1000</v>
+      </c>
+      <c r="AP50">
+        <v>10</v>
+      </c>
+      <c r="AQ50">
+        <v>11.5</v>
+      </c>
+      <c r="AR50">
+        <v>2.56</v>
+      </c>
+      <c r="AS50">
+        <v>2.7</v>
+      </c>
+      <c r="AT50">
+        <v>2.16</v>
+      </c>
+      <c r="AU50">
+        <v>2.16</v>
+      </c>
+      <c r="AV50">
+        <v>2.44</v>
+      </c>
+      <c r="AW50">
+        <v>2.62</v>
+      </c>
+      <c r="AX50">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY50">
+        <v>2.26</v>
+      </c>
+      <c r="AZ50">
+        <v>2.46</v>
+      </c>
+      <c r="BA50">
+        <v>2.62</v>
+      </c>
+      <c r="BB50">
+        <v>16</v>
+      </c>
+      <c r="BC50">
+        <v>15.5</v>
+      </c>
+      <c r="BD50">
+        <v>2.56</v>
+      </c>
+      <c r="BE50">
+        <v>2.7</v>
+      </c>
+      <c r="BF50">
+        <v>2.7</v>
+      </c>
+      <c r="BG50">
+        <v>2.7</v>
+      </c>
+      <c r="BH50">
+        <v>1000</v>
+      </c>
+      <c r="BI50">
+        <v>1.01</v>
+      </c>
+      <c r="BJ50">
+        <v>1000</v>
+      </c>
+      <c r="BK50">
+        <v>1.01</v>
+      </c>
+      <c r="BL50">
+        <v>1000</v>
+      </c>
+      <c r="BM50">
+        <v>1.01</v>
+      </c>
+      <c r="BN50">
+        <v>1000</v>
+      </c>
+      <c r="BO50">
+        <v>1.01</v>
+      </c>
+      <c r="BP50">
+        <v>1000</v>
+      </c>
+      <c r="BQ50">
+        <v>1.01</v>
+      </c>
+      <c r="BR50">
+        <v>1000</v>
+      </c>
+      <c r="BS50">
+        <v>1.01</v>
+      </c>
+      <c r="BT50">
+        <v>1000</v>
+      </c>
+      <c r="BU50">
+        <v>1.01</v>
+      </c>
+      <c r="BV50">
+        <v>1000</v>
+      </c>
+      <c r="BW50">
+        <v>1.01</v>
+      </c>
+      <c r="BX50">
+        <v>1000</v>
+      </c>
+      <c r="BY50">
+        <v>1.01</v>
+      </c>
+      <c r="BZ50">
+        <v>0</v>
+      </c>
+      <c r="CA50">
+        <v>0</v>
+      </c>
+      <c r="CB50" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="223">
   <si>
     <t>League</t>
   </si>
@@ -484,15 +484,18 @@
     <t>Puskas Akademia</t>
   </si>
   <si>
+    <t>Kriens</t>
+  </si>
+  <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
-    <t>Kriens</t>
-  </si>
-  <si>
     <t>Otelul Galati</t>
   </si>
   <si>
+    <t>Lechia Gdansk</t>
+  </si>
+  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
@@ -631,15 +634,18 @@
     <t>Kisvarda</t>
   </si>
   <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
     <t>Arda</t>
   </si>
   <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
     <t>Dinamo Bucharest</t>
   </si>
   <si>
+    <t>Warta Poznan</t>
+  </si>
+  <si>
     <t>St Polten</t>
   </si>
   <si>
@@ -676,7 +682,7 @@
     <t>Comerciantes Unidos</t>
   </si>
   <si>
-    <t>2026-07-29 18:15:31</t>
+    <t>2026-07-29 20:24:43</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB50"/>
+  <dimension ref="A1:CB51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1267,7 +1273,7 @@
         <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F2">
         <v>3.3</v>
@@ -1279,13 +1285,13 @@
         <v>2.6</v>
       </c>
       <c r="I2">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J2">
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
         <v>1.61</v>
@@ -1297,7 +1303,7 @@
         <v>2.62</v>
       </c>
       <c r="O2">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P2">
         <v>1.54</v>
@@ -1315,7 +1321,7 @@
         <v>2.18</v>
       </c>
       <c r="U2">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V2">
         <v>1.61</v>
@@ -1324,16 +1330,16 @@
         <v>1.41</v>
       </c>
       <c r="X2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y2">
         <v>7.8</v>
       </c>
       <c r="Z2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA2">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AB2">
         <v>9.199999999999999</v>
@@ -1342,10 +1348,10 @@
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE2">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AF2">
         <v>21</v>
@@ -1357,40 +1363,40 @@
         <v>24</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK2">
-        <v>260</v>
+        <v>55</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO2">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="AP2">
         <v>7.6</v>
       </c>
       <c r="AQ2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS2">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AT2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
@@ -1402,25 +1408,25 @@
         <v>32</v>
       </c>
       <c r="AX2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY2">
         <v>14</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BB2">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BC2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BE2">
         <v>46</v>
@@ -1492,7 +1498,7 @@
         <v>12</v>
       </c>
       <c r="CB2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1509,7 +1515,7 @@
         <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F3">
         <v>1.7</v>
@@ -1527,10 +1533,10 @@
         <v>3.5</v>
       </c>
       <c r="K3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="M3">
         <v>1.1</v>
@@ -1551,7 +1557,7 @@
         <v>1.22</v>
       </c>
       <c r="S3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T3">
         <v>2.22</v>
@@ -1581,7 +1587,7 @@
         <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD3">
         <v>32</v>
@@ -1626,10 +1632,10 @@
         <v>12</v>
       </c>
       <c r="AR3">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT3">
         <v>5.6</v>
@@ -1641,7 +1647,7 @@
         <v>19.5</v>
       </c>
       <c r="AW3">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX3">
         <v>7.6</v>
@@ -1650,10 +1656,10 @@
         <v>9</v>
       </c>
       <c r="AZ3">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BA3">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB3">
         <v>15</v>
@@ -1662,16 +1668,16 @@
         <v>19</v>
       </c>
       <c r="BD3">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF3">
         <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH3">
         <v>3.05</v>
@@ -1734,7 +1740,7 @@
         <v>8</v>
       </c>
       <c r="CB3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1751,7 +1757,7 @@
         <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F4">
         <v>3.55</v>
@@ -1760,7 +1766,7 @@
         <v>3.65</v>
       </c>
       <c r="H4">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I4">
         <v>2.34</v>
@@ -1778,25 +1784,25 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
         <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S4">
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U4">
         <v>2.04</v>
@@ -1805,7 +1811,7 @@
         <v>1.74</v>
       </c>
       <c r="W4">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X4">
         <v>12</v>
@@ -1823,13 +1829,13 @@
         <v>12.5</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
         <v>11.5</v>
       </c>
       <c r="AE4">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AF4">
         <v>24</v>
@@ -1838,7 +1844,7 @@
         <v>15</v>
       </c>
       <c r="AH4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI4">
         <v>44</v>
@@ -1856,13 +1862,13 @@
         <v>120</v>
       </c>
       <c r="AN4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO4">
         <v>23</v>
       </c>
       <c r="AP4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
         <v>8.199999999999999</v>
@@ -1880,10 +1886,10 @@
         <v>7</v>
       </c>
       <c r="AV4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX4">
         <v>22</v>
@@ -1895,10 +1901,10 @@
         <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>12.5</v>
+        <v>38</v>
       </c>
       <c r="BB4">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="BC4">
         <v>40</v>
@@ -1907,13 +1913,13 @@
         <v>50</v>
       </c>
       <c r="BE4">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="BF4">
         <v>40</v>
       </c>
       <c r="BG4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH4">
         <v>3.15</v>
@@ -1976,7 +1982,7 @@
         <v>10.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1993,7 +1999,7 @@
         <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F5">
         <v>1.49</v>
@@ -2005,7 +2011,7 @@
         <v>7.6</v>
       </c>
       <c r="I5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -2014,7 +2020,7 @@
         <v>4.8</v>
       </c>
       <c r="L5">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -2065,7 +2071,7 @@
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD5">
         <v>38</v>
@@ -2089,7 +2095,7 @@
         <v>15</v>
       </c>
       <c r="AK5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL5">
         <v>60</v>
@@ -2122,10 +2128,10 @@
         <v>8.6</v>
       </c>
       <c r="AV5">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="AW5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX5">
         <v>7</v>
@@ -2134,7 +2140,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ5">
-        <v>19.5</v>
+        <v>5.3</v>
       </c>
       <c r="BA5">
         <v>6</v>
@@ -2149,7 +2155,7 @@
         <v>34</v>
       </c>
       <c r="BE5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF5">
         <v>9.199999999999999</v>
@@ -2218,7 +2224,7 @@
         <v>7.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2235,16 +2241,16 @@
         <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F6">
         <v>1.83</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I6">
         <v>4.4</v>
@@ -2256,7 +2262,7 @@
         <v>4.6</v>
       </c>
       <c r="L6">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M6">
         <v>1.01</v>
@@ -2460,7 +2466,7 @@
         <v>6.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2477,7 +2483,7 @@
         <v>127</v>
       </c>
       <c r="E7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F7">
         <v>2.12</v>
@@ -2702,7 +2708,7 @@
         <v>2.68</v>
       </c>
       <c r="CB7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2719,22 +2725,22 @@
         <v>128</v>
       </c>
       <c r="E8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G8">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I8">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2746,7 +2752,7 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="O8">
         <v>1.01</v>
@@ -2761,13 +2767,13 @@
         <v>1.07</v>
       </c>
       <c r="S8">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
         <v>1.02</v>
@@ -2830,52 +2836,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2887,64 +2893,64 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2961,10 +2967,10 @@
         <v>129</v>
       </c>
       <c r="E9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F9">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G9">
         <v>1.81</v>
@@ -3003,7 +3009,7 @@
         <v>1.25</v>
       </c>
       <c r="S9">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T9">
         <v>2.1</v>
@@ -3021,7 +3027,7 @@
         <v>13</v>
       </c>
       <c r="Y9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z9">
         <v>60</v>
@@ -3054,7 +3060,7 @@
         <v>140</v>
       </c>
       <c r="AJ9">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK9">
         <v>26</v>
@@ -3066,7 +3072,7 @@
         <v>230</v>
       </c>
       <c r="AN9">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO9">
         <v>210</v>
@@ -3078,10 +3084,10 @@
         <v>14</v>
       </c>
       <c r="AR9">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AS9">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT9">
         <v>5.9</v>
@@ -3093,7 +3099,7 @@
         <v>20</v>
       </c>
       <c r="AW9">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AX9">
         <v>8</v>
@@ -3105,7 +3111,7 @@
         <v>21</v>
       </c>
       <c r="BA9">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BB9">
         <v>15</v>
@@ -3114,22 +3120,22 @@
         <v>18</v>
       </c>
       <c r="BD9">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE9">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF9">
         <v>11</v>
       </c>
       <c r="BG9">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BH9">
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="BJ9">
         <v>16</v>
@@ -3141,7 +3147,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="BN9">
         <v>5.4</v>
@@ -3150,43 +3156,43 @@
         <v>2.88</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ9">
-        <v>1.59</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS9">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="BT9">
         <v>13</v>
       </c>
       <c r="BU9">
-        <v>1.41</v>
+        <v>6.8</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA9">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="CB9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3203,10 +3209,10 @@
         <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F10">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="G10">
         <v>1.82</v>
@@ -3215,7 +3221,7 @@
         <v>4.7</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J10">
         <v>4.1</v>
@@ -3242,16 +3248,16 @@
         <v>1.67</v>
       </c>
       <c r="R10">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S10">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T10">
         <v>1.69</v>
       </c>
       <c r="U10">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
         <v>1.2</v>
@@ -3320,10 +3326,10 @@
         <v>16</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT10">
         <v>8.4</v>
@@ -3335,7 +3341,7 @@
         <v>15</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX10">
         <v>9.4</v>
@@ -3347,7 +3353,7 @@
         <v>13.5</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB10">
         <v>14</v>
@@ -3356,16 +3362,16 @@
         <v>13</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF10">
         <v>6.8</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH10">
         <v>4.1</v>
@@ -3428,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3445,7 +3451,7 @@
         <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F11">
         <v>3.5</v>
@@ -3454,7 +3460,7 @@
         <v>3.7</v>
       </c>
       <c r="H11">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="I11">
         <v>2.64</v>
@@ -3463,7 +3469,7 @@
         <v>3</v>
       </c>
       <c r="K11">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3484,16 +3490,16 @@
         <v>2.32</v>
       </c>
       <c r="R11">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S11">
         <v>4.1</v>
       </c>
       <c r="T11">
+        <v>1.92</v>
+      </c>
+      <c r="U11">
         <v>1.11</v>
-      </c>
-      <c r="U11">
-        <v>1.91</v>
       </c>
       <c r="V11">
         <v>1.61</v>
@@ -3556,16 +3562,16 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AQ11">
         <v>7.2</v>
       </c>
       <c r="AR11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AS11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AT11">
         <v>1.45</v>
@@ -3577,10 +3583,10 @@
         <v>1.45</v>
       </c>
       <c r="AW11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AX11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AY11">
         <v>1.45</v>
@@ -3589,25 +3595,25 @@
         <v>1.45</v>
       </c>
       <c r="BA11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BB11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BC11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BD11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BE11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BF11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BG11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3670,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3687,25 +3693,25 @@
         <v>132</v>
       </c>
       <c r="E12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H12">
         <v>3.05</v>
       </c>
       <c r="I12">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="J12">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K12">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3738,10 +3744,10 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3798,52 +3804,52 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
         <v>1.01</v>
@@ -3855,64 +3861,64 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3929,7 +3935,7 @@
         <v>133</v>
       </c>
       <c r="E13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F13">
         <v>2.5</v>
@@ -3956,7 +3962,7 @@
         <v>1.04</v>
       </c>
       <c r="N13">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O13">
         <v>1.21</v>
@@ -3968,10 +3974,10 @@
         <v>1.63</v>
       </c>
       <c r="R13">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S13">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T13">
         <v>1.54</v>
@@ -4097,64 +4103,64 @@
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4171,7 +4177,7 @@
         <v>134</v>
       </c>
       <c r="E14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F14">
         <v>2.92</v>
@@ -4192,7 +4198,7 @@
         <v>3.6</v>
       </c>
       <c r="L14">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M14">
         <v>1.08</v>
@@ -4219,7 +4225,7 @@
         <v>1.78</v>
       </c>
       <c r="U14">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V14">
         <v>1.59</v>
@@ -4243,7 +4249,7 @@
         <v>14</v>
       </c>
       <c r="AC14">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD14">
         <v>14.5</v>
@@ -4303,7 +4309,7 @@
         <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX14">
         <v>18</v>
@@ -4315,10 +4321,10 @@
         <v>15.5</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BC14">
         <v>22</v>
@@ -4327,13 +4333,13 @@
         <v>29</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG14">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH14">
         <v>3.3</v>
@@ -4396,7 +4402,7 @@
         <v>10</v>
       </c>
       <c r="CB14" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4413,7 +4419,7 @@
         <v>135</v>
       </c>
       <c r="E15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F15">
         <v>1.71</v>
@@ -4530,10 +4536,10 @@
         <v>14.5</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT15">
         <v>7</v>
@@ -4545,7 +4551,7 @@
         <v>15.5</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX15">
         <v>8.4</v>
@@ -4557,7 +4563,7 @@
         <v>15</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB15">
         <v>14</v>
@@ -4566,16 +4572,16 @@
         <v>14</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF15">
         <v>9.199999999999999</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH15">
         <v>4.4</v>
@@ -4638,7 +4644,7 @@
         <v>3.1</v>
       </c>
       <c r="CB15" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4655,7 +4661,7 @@
         <v>136</v>
       </c>
       <c r="E16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F16">
         <v>2.98</v>
@@ -4697,13 +4703,13 @@
         <v>1.25</v>
       </c>
       <c r="S16">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16">
         <v>1.61</v>
@@ -4859,7 +4865,7 @@
         <v>7.6</v>
       </c>
       <c r="BU16">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BV16">
         <v>28</v>
@@ -4880,7 +4886,7 @@
         <v>1.73</v>
       </c>
       <c r="CB16" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4897,7 +4903,7 @@
         <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F17">
         <v>3.55</v>
@@ -4924,7 +4930,7 @@
         <v>1.03</v>
       </c>
       <c r="N17">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="O17">
         <v>1.21</v>
@@ -5008,64 +5014,64 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="AR17">
         <v>10.5</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BH17">
         <v>5.3</v>
       </c>
       <c r="BI17">
-        <v>2.86</v>
+        <v>2</v>
       </c>
       <c r="BJ17">
         <v>12.5</v>
@@ -5101,7 +5107,7 @@
         <v>6.6</v>
       </c>
       <c r="BU17">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BV17">
         <v>18.5</v>
@@ -5122,7 +5128,7 @@
         <v>2.86</v>
       </c>
       <c r="CB17" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5139,7 +5145,7 @@
         <v>138</v>
       </c>
       <c r="E18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F18">
         <v>3.9</v>
@@ -5250,58 +5256,58 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AQ18">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AR18">
         <v>10</v>
       </c>
       <c r="AS18">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AV18">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AW18">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AZ18">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="BA18">
         <v>19</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BD18">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BE18">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BH18">
         <v>5.7</v>
@@ -5343,7 +5349,7 @@
         <v>6.4</v>
       </c>
       <c r="BU18">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="BV18">
         <v>16</v>
@@ -5364,7 +5370,7 @@
         <v>9.6</v>
       </c>
       <c r="CB18" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5381,13 +5387,13 @@
         <v>139</v>
       </c>
       <c r="E19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F19">
         <v>2.16</v>
       </c>
       <c r="G19">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H19">
         <v>3.15</v>
@@ -5426,16 +5432,16 @@
         <v>2.56</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
         <v>1.39</v>
       </c>
       <c r="W19">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5492,52 +5498,52 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
         <v>1.01</v>
@@ -5549,64 +5555,64 @@
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5623,7 +5629,7 @@
         <v>140</v>
       </c>
       <c r="E20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F20">
         <v>2.36</v>
@@ -5740,10 +5746,10 @@
         <v>11</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT20">
         <v>10</v>
@@ -5755,7 +5761,7 @@
         <v>10</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX20">
         <v>13.5</v>
@@ -5767,19 +5773,19 @@
         <v>12</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB20">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC20">
         <v>18.5</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF20">
         <v>12</v>
@@ -5791,10 +5797,10 @@
         <v>5.1</v>
       </c>
       <c r="BI20">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="BJ20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK20">
         <v>2.54</v>
@@ -5803,52 +5809,52 @@
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BN20">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO20">
         <v>3.85</v>
       </c>
       <c r="BP20">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BQ20">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BR20">
         <v>38</v>
       </c>
       <c r="BS20">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BT20">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU20">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BV20">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW20">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BX20">
         <v>40</v>
       </c>
       <c r="BY20">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BZ20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA20">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CB20" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5865,19 +5871,19 @@
         <v>141</v>
       </c>
       <c r="E21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F21">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G21">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H21">
         <v>3.2</v>
       </c>
       <c r="I21">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J21">
         <v>3.75</v>
@@ -5892,7 +5898,7 @@
         <v>1.04</v>
       </c>
       <c r="N21">
-        <v>1.1</v>
+        <v>2.22</v>
       </c>
       <c r="O21">
         <v>1.2</v>
@@ -5907,19 +5913,19 @@
         <v>1.37</v>
       </c>
       <c r="S21">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T21">
         <v>1.45</v>
       </c>
       <c r="U21">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V21">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5937,7 +5943,7 @@
         <v>18.5</v>
       </c>
       <c r="AC21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD21">
         <v>21</v>
@@ -5976,7 +5982,7 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="AQ21">
         <v>10</v>
@@ -5985,7 +5991,7 @@
         <v>15.5</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="AT21">
         <v>8</v>
@@ -5997,19 +6003,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW21">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AX21">
         <v>9.6</v>
       </c>
       <c r="AY21">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AZ21">
         <v>9.6</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="BB21">
         <v>16.5</v>
@@ -6021,13 +6027,13 @@
         <v>18.5</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BH21">
         <v>5.5</v>
@@ -6090,7 +6096,7 @@
         <v>2.64</v>
       </c>
       <c r="CB21" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6107,13 +6113,13 @@
         <v>142</v>
       </c>
       <c r="E22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F22">
         <v>1.68</v>
       </c>
       <c r="G22">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="H22">
         <v>4.8</v>
@@ -6146,22 +6152,22 @@
         <v>1.69</v>
       </c>
       <c r="R22">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S22">
         <v>2.46</v>
       </c>
       <c r="T22">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="U22">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="V22">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W22">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6218,52 +6224,52 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF22">
         <v>1.01</v>
@@ -6275,55 +6281,55 @@
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
         <v>0</v>
@@ -6332,7 +6338,7 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6349,7 +6355,7 @@
         <v>143</v>
       </c>
       <c r="E23" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F23">
         <v>1.64</v>
@@ -6364,7 +6370,7 @@
         <v>5.8</v>
       </c>
       <c r="J23">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K23">
         <v>5.1</v>
@@ -6376,10 +6382,10 @@
         <v>1.03</v>
       </c>
       <c r="N23">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P23">
         <v>2.76</v>
@@ -6388,16 +6394,16 @@
         <v>1.49</v>
       </c>
       <c r="R23">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S23">
-        <v>1.05</v>
+        <v>2.22</v>
       </c>
       <c r="T23">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="U23">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V23">
         <v>1.01</v>
@@ -6502,7 +6508,7 @@
         <v>13.5</v>
       </c>
       <c r="BD23">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="BE23">
         <v>4.5</v>
@@ -6517,64 +6523,64 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6591,7 +6597,7 @@
         <v>144</v>
       </c>
       <c r="E24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F24">
         <v>1.04</v>
@@ -6621,7 +6627,7 @@
         <v>1.26</v>
       </c>
       <c r="O24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P24">
         <v>1.25</v>
@@ -6642,10 +6648,10 @@
         <v>1.11</v>
       </c>
       <c r="V24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6702,52 +6708,52 @@
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
         <v>1.01</v>
@@ -6759,64 +6765,64 @@
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
       </c>
       <c r="BK24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN24">
         <v>1000</v>
       </c>
       <c r="BO24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP24">
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT24">
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6833,7 +6839,7 @@
         <v>145</v>
       </c>
       <c r="E25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F25">
         <v>2.26</v>
@@ -6863,7 +6869,7 @@
         <v>3.25</v>
       </c>
       <c r="O25">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P25">
         <v>1.86</v>
@@ -6944,52 +6950,52 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
         <v>1.01</v>
@@ -7058,7 +7064,7 @@
         <v>1.29</v>
       </c>
       <c r="CB25" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7075,7 +7081,7 @@
         <v>146</v>
       </c>
       <c r="E26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F26">
         <v>2.96</v>
@@ -7105,10 +7111,10 @@
         <v>5</v>
       </c>
       <c r="O26">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P26">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q26">
         <v>1.61</v>
@@ -7117,7 +7123,7 @@
         <v>1.53</v>
       </c>
       <c r="S26">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T26">
         <v>1.58</v>
@@ -7135,16 +7141,16 @@
         <v>28</v>
       </c>
       <c r="Y26">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z26">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA26">
         <v>38</v>
       </c>
       <c r="AB26">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AC26">
         <v>11.5</v>
@@ -7156,13 +7162,13 @@
         <v>27</v>
       </c>
       <c r="AF26">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AG26">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH26">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI26">
         <v>36</v>
@@ -7183,10 +7189,10 @@
         <v>26</v>
       </c>
       <c r="AO26">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AP26">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ26">
         <v>10</v>
@@ -7204,7 +7210,7 @@
         <v>7</v>
       </c>
       <c r="AV26">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AW26">
         <v>16</v>
@@ -7222,16 +7228,16 @@
         <v>21</v>
       </c>
       <c r="BB26">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="BC26">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BD26">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="BE26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BF26">
         <v>15</v>
@@ -7243,64 +7249,64 @@
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7317,13 +7323,13 @@
         <v>147</v>
       </c>
       <c r="E27" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F27">
         <v>3.05</v>
       </c>
       <c r="G27">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="H27">
         <v>2.26</v>
@@ -7344,7 +7350,7 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O27">
         <v>1.26</v>
@@ -7431,55 +7437,55 @@
         <v>11</v>
       </c>
       <c r="AQ27">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AR27">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AS27">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AT27">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AU27">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AV27">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AW27">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AX27">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AY27">
         <v>10</v>
       </c>
       <c r="AZ27">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BA27">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BB27">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BC27">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BD27">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BE27">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BF27">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BG27">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BH27">
         <v>4.1</v>
@@ -7542,7 +7548,7 @@
         <v>3.15</v>
       </c>
       <c r="CB27" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7559,7 +7565,7 @@
         <v>148</v>
       </c>
       <c r="E28" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F28">
         <v>1.23</v>
@@ -7589,13 +7595,13 @@
         <v>5.3</v>
       </c>
       <c r="O28">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P28">
         <v>2.5</v>
       </c>
       <c r="Q28">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R28">
         <v>1.6</v>
@@ -7604,10 +7610,10 @@
         <v>2.32</v>
       </c>
       <c r="T28">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="U28">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="V28">
         <v>1.05</v>
@@ -7616,112 +7622,112 @@
         <v>4.4</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AA28">
         <v>1000</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ28">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AK28">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN28">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AP28">
-        <v>1.51</v>
+        <v>19.5</v>
       </c>
       <c r="AQ28">
-        <v>1.51</v>
+        <v>5.7</v>
       </c>
       <c r="AR28">
-        <v>1.51</v>
+        <v>6</v>
       </c>
       <c r="AS28">
-        <v>1.51</v>
+        <v>6.2</v>
       </c>
       <c r="AT28">
-        <v>1.51</v>
+        <v>7.2</v>
       </c>
       <c r="AU28">
-        <v>1.51</v>
+        <v>13.5</v>
       </c>
       <c r="AV28">
-        <v>1.51</v>
+        <v>5.8</v>
       </c>
       <c r="AW28">
-        <v>1.51</v>
+        <v>6.2</v>
       </c>
       <c r="AX28">
-        <v>1.51</v>
+        <v>6.8</v>
       </c>
       <c r="AY28">
-        <v>1.51</v>
+        <v>8.6</v>
       </c>
       <c r="AZ28">
-        <v>1.51</v>
+        <v>5.5</v>
       </c>
       <c r="BA28">
-        <v>1.51</v>
+        <v>6.2</v>
       </c>
       <c r="BB28">
-        <v>1.34</v>
+        <v>6.8</v>
       </c>
       <c r="BC28">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD28">
-        <v>1.51</v>
+        <v>5.7</v>
       </c>
       <c r="BE28">
-        <v>1.51</v>
+        <v>6.2</v>
       </c>
       <c r="BF28">
-        <v>1.16</v>
+        <v>3.25</v>
       </c>
       <c r="BG28">
-        <v>1.51</v>
+        <v>6.2</v>
       </c>
       <c r="BH28">
         <v>6.4</v>
@@ -7733,19 +7739,19 @@
         <v>19</v>
       </c>
       <c r="BK28">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BN28">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO28">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BP28">
         <v>9.6</v>
@@ -7757,34 +7763,34 @@
         <v>34</v>
       </c>
       <c r="BS28">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BT28">
         <v>25</v>
       </c>
       <c r="BU28">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BZ28">
         <v>13.5</v>
       </c>
       <c r="CA28">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CB28" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7801,7 +7807,7 @@
         <v>149</v>
       </c>
       <c r="E29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F29">
         <v>4.3</v>
@@ -8026,7 +8032,7 @@
         <v>2.78</v>
       </c>
       <c r="CB29" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8043,7 +8049,7 @@
         <v>150</v>
       </c>
       <c r="E30" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F30">
         <v>1.66</v>
@@ -8061,7 +8067,7 @@
         <v>4.1</v>
       </c>
       <c r="K30">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L30">
         <v>1.31</v>
@@ -8070,16 +8076,16 @@
         <v>1.05</v>
       </c>
       <c r="N30">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="O30">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P30">
         <v>2.1</v>
       </c>
       <c r="Q30">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R30">
         <v>1.43</v>
@@ -8109,13 +8115,13 @@
         <v>50</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB30">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC30">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD30">
         <v>25</v>
@@ -8124,10 +8130,10 @@
         <v>85</v>
       </c>
       <c r="AF30">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH30">
         <v>24</v>
@@ -8136,7 +8142,7 @@
         <v>80</v>
       </c>
       <c r="AJ30">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AK30">
         <v>23</v>
@@ -8145,67 +8151,67 @@
         <v>38</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN30">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP30">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ30">
         <v>15.5</v>
       </c>
       <c r="AR30">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="AS30">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="AT30">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU30">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV30">
         <v>16.5</v>
       </c>
       <c r="AW30">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AX30">
+        <v>9.4</v>
+      </c>
+      <c r="AY30">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY30">
-        <v>8.4</v>
-      </c>
       <c r="AZ30">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA30">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="BB30">
         <v>14</v>
       </c>
       <c r="BC30">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD30">
         <v>24</v>
       </c>
       <c r="BE30">
-        <v>4.4</v>
+        <v>12</v>
       </c>
       <c r="BF30">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG30">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8217,58 +8223,58 @@
         <v>13.5</v>
       </c>
       <c r="BK30">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="BN30">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO30">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BP30">
         <v>15.5</v>
       </c>
       <c r="BQ30">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BR30">
         <v>34</v>
       </c>
       <c r="BS30">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="BT30">
         <v>12.5</v>
       </c>
       <c r="BU30">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="BZ30">
         <v>26</v>
       </c>
       <c r="CA30">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CB30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8285,7 +8291,7 @@
         <v>151</v>
       </c>
       <c r="E31" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F31">
         <v>1.78</v>
@@ -8321,7 +8327,7 @@
         <v>2.54</v>
       </c>
       <c r="Q31">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="R31">
         <v>1.49</v>
@@ -8345,7 +8351,7 @@
         <v>1000</v>
       </c>
       <c r="Y31">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="Z31">
         <v>1000</v>
@@ -8390,22 +8396,22 @@
         <v>1000</v>
       </c>
       <c r="AN31">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO31">
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="AQ31">
         <v>14</v>
       </c>
       <c r="AR31">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="AS31">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="AT31">
         <v>8.4</v>
@@ -8417,7 +8423,7 @@
         <v>11.5</v>
       </c>
       <c r="AW31">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="AX31">
         <v>8.800000000000001</v>
@@ -8429,7 +8435,7 @@
         <v>10.5</v>
       </c>
       <c r="BA31">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="BB31">
         <v>13</v>
@@ -8441,13 +8447,13 @@
         <v>16.5</v>
       </c>
       <c r="BE31">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="BF31">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG31">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BH31">
         <v>6</v>
@@ -8510,7 +8516,7 @@
         <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8527,19 +8533,19 @@
         <v>152</v>
       </c>
       <c r="E32" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F32">
         <v>2.44</v>
       </c>
       <c r="G32">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="H32">
         <v>2.5</v>
       </c>
       <c r="I32">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="J32">
         <v>4</v>
@@ -8554,7 +8560,7 @@
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>2.72</v>
+        <v>5.1</v>
       </c>
       <c r="O32">
         <v>1.14</v>
@@ -8566,22 +8572,22 @@
         <v>1.46</v>
       </c>
       <c r="R32">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="S32">
         <v>2.16</v>
       </c>
       <c r="T32">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="U32">
-        <v>1.11</v>
+        <v>2.46</v>
       </c>
       <c r="V32">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W32">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8638,58 +8644,58 @@
         <v>1000</v>
       </c>
       <c r="AP32">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AQ32">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AR32">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AS32">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AT32">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AU32">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AV32">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AW32">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AX32">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AY32">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AZ32">
         <v>10.5</v>
       </c>
       <c r="BA32">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BB32">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BC32">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BD32">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BE32">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BF32">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BG32">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BH32">
         <v>6.4</v>
@@ -8752,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="CB32" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8769,7 +8775,7 @@
         <v>153</v>
       </c>
       <c r="E33" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F33">
         <v>2.24</v>
@@ -8784,7 +8790,7 @@
         <v>3.45</v>
       </c>
       <c r="J33">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K33">
         <v>4.6</v>
@@ -8808,7 +8814,7 @@
         <v>1.49</v>
       </c>
       <c r="R33">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S33">
         <v>2.18</v>
@@ -8823,7 +8829,7 @@
         <v>1.41</v>
       </c>
       <c r="W33">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -8880,52 +8886,52 @@
         <v>1000</v>
       </c>
       <c r="AP33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF33">
         <v>1.01</v>
@@ -8937,55 +8943,55 @@
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN33">
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT33">
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33">
         <v>0</v>
@@ -8994,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -9011,7 +9017,7 @@
         <v>154</v>
       </c>
       <c r="E34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F34">
         <v>1.26</v>
@@ -9023,7 +9029,7 @@
         <v>12.5</v>
       </c>
       <c r="I34">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J34">
         <v>6.6</v>
@@ -9107,7 +9113,7 @@
         <v>12.5</v>
       </c>
       <c r="AK34">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL34">
         <v>42</v>
@@ -9116,22 +9122,22 @@
         <v>170</v>
       </c>
       <c r="AN34">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AO34">
         <v>250</v>
       </c>
       <c r="AP34">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ34">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR34">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AS34">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AT34">
         <v>10</v>
@@ -9140,10 +9146,10 @@
         <v>14</v>
       </c>
       <c r="AV34">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AW34">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AX34">
         <v>8</v>
@@ -9152,10 +9158,10 @@
         <v>10</v>
       </c>
       <c r="AZ34">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BA34">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BB34">
         <v>8.6</v>
@@ -9164,16 +9170,16 @@
         <v>10</v>
       </c>
       <c r="BD34">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE34">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BF34">
         <v>3</v>
       </c>
       <c r="BG34">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BH34">
         <v>0</v>
@@ -9236,7 +9242,7 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9253,7 +9259,7 @@
         <v>155</v>
       </c>
       <c r="E35" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F35">
         <v>1.77</v>
@@ -9298,10 +9304,10 @@
         <v>3.55</v>
       </c>
       <c r="T35">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U35">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V35">
         <v>1.21</v>
@@ -9421,55 +9427,55 @@
         <v>1000</v>
       </c>
       <c r="BI35">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BJ35">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK35">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BN35">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO35">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BP35">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ35">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BR35">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS35">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BT35">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU35">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV35">
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BZ35">
         <v>0</v>
@@ -9478,12 +9484,12 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
         <v>105</v>
@@ -9495,237 +9501,237 @@
         <v>156</v>
       </c>
       <c r="E36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F36">
+        <v>3.35</v>
+      </c>
+      <c r="G36">
+        <v>3.8</v>
+      </c>
+      <c r="H36">
+        <v>2.02</v>
+      </c>
+      <c r="I36">
+        <v>2.22</v>
+      </c>
+      <c r="J36">
+        <v>3.95</v>
+      </c>
+      <c r="K36">
+        <v>4.3</v>
+      </c>
+      <c r="L36">
+        <v>1.01</v>
+      </c>
+      <c r="M36">
+        <v>1.04</v>
+      </c>
+      <c r="N36">
+        <v>3.35</v>
+      </c>
+      <c r="O36">
+        <v>1.19</v>
+      </c>
+      <c r="P36">
+        <v>2.5</v>
+      </c>
+      <c r="Q36">
+        <v>1.63</v>
+      </c>
+      <c r="R36">
+        <v>1.44</v>
+      </c>
+      <c r="S36">
+        <v>2.28</v>
+      </c>
+      <c r="T36">
+        <v>1.48</v>
+      </c>
+      <c r="U36">
+        <v>1.11</v>
+      </c>
+      <c r="V36">
+        <v>1.81</v>
+      </c>
+      <c r="W36">
+        <v>1.35</v>
+      </c>
+      <c r="X36">
+        <v>1000</v>
+      </c>
+      <c r="Y36">
+        <v>18.5</v>
+      </c>
+      <c r="Z36">
+        <v>22</v>
+      </c>
+      <c r="AA36">
+        <v>36</v>
+      </c>
+      <c r="AB36">
+        <v>25</v>
+      </c>
+      <c r="AC36">
+        <v>13.5</v>
+      </c>
+      <c r="AD36">
+        <v>15.5</v>
+      </c>
+      <c r="AE36">
+        <v>29</v>
+      </c>
+      <c r="AF36">
+        <v>40</v>
+      </c>
+      <c r="AG36">
+        <v>21</v>
+      </c>
+      <c r="AH36">
+        <v>22</v>
+      </c>
+      <c r="AI36">
+        <v>40</v>
+      </c>
+      <c r="AJ36">
+        <v>1000</v>
+      </c>
+      <c r="AK36">
+        <v>1000</v>
+      </c>
+      <c r="AL36">
+        <v>1000</v>
+      </c>
+      <c r="AM36">
+        <v>1000</v>
+      </c>
+      <c r="AN36">
+        <v>1000</v>
+      </c>
+      <c r="AO36">
+        <v>15.5</v>
+      </c>
+      <c r="AP36">
         <v>2.2</v>
       </c>
-      <c r="G36">
-        <v>2.28</v>
-      </c>
-      <c r="H36">
-        <v>3.8</v>
-      </c>
-      <c r="I36">
-        <v>3.85</v>
-      </c>
-      <c r="J36">
-        <v>3.3</v>
-      </c>
-      <c r="K36">
-        <v>3.5</v>
-      </c>
-      <c r="L36">
-        <v>1.42</v>
-      </c>
-      <c r="M36">
-        <v>1.09</v>
-      </c>
-      <c r="N36">
-        <v>3</v>
-      </c>
-      <c r="O36">
-        <v>1.42</v>
-      </c>
-      <c r="P36">
-        <v>1.69</v>
-      </c>
-      <c r="Q36">
-        <v>2.22</v>
-      </c>
-      <c r="R36">
-        <v>1.26</v>
-      </c>
-      <c r="S36">
-        <v>4.2</v>
-      </c>
-      <c r="T36">
-        <v>1.92</v>
-      </c>
-      <c r="U36">
-        <v>1.91</v>
-      </c>
-      <c r="V36">
-        <v>1.35</v>
-      </c>
-      <c r="W36">
-        <v>1.79</v>
-      </c>
-      <c r="X36">
-        <v>13</v>
-      </c>
-      <c r="Y36">
-        <v>14.5</v>
-      </c>
-      <c r="Z36">
+      <c r="AQ36">
+        <v>8</v>
+      </c>
+      <c r="AR36">
+        <v>9.6</v>
+      </c>
+      <c r="AS36">
+        <v>15.5</v>
+      </c>
+      <c r="AT36">
+        <v>11</v>
+      </c>
+      <c r="AU36">
+        <v>6.2</v>
+      </c>
+      <c r="AV36">
+        <v>7</v>
+      </c>
+      <c r="AW36">
+        <v>12</v>
+      </c>
+      <c r="AX36">
+        <v>16.5</v>
+      </c>
+      <c r="AY36">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ36">
+        <v>9.6</v>
+      </c>
+      <c r="BA36">
+        <v>16.5</v>
+      </c>
+      <c r="BB36">
+        <v>2.2</v>
+      </c>
+      <c r="BC36">
+        <v>2.2</v>
+      </c>
+      <c r="BD36">
+        <v>2.2</v>
+      </c>
+      <c r="BE36">
+        <v>2.2</v>
+      </c>
+      <c r="BF36">
+        <v>2.2</v>
+      </c>
+      <c r="BG36">
+        <v>8</v>
+      </c>
+      <c r="BH36">
+        <v>5.8</v>
+      </c>
+      <c r="BI36">
+        <v>2.86</v>
+      </c>
+      <c r="BJ36">
+        <v>12.5</v>
+      </c>
+      <c r="BK36">
+        <v>5.4</v>
+      </c>
+      <c r="BL36">
+        <v>1000</v>
+      </c>
+      <c r="BM36">
+        <v>2.88</v>
+      </c>
+      <c r="BN36">
+        <v>10</v>
+      </c>
+      <c r="BO36">
+        <v>4.6</v>
+      </c>
+      <c r="BP36">
+        <v>38</v>
+      </c>
+      <c r="BQ36">
+        <v>2.7</v>
+      </c>
+      <c r="BR36">
+        <v>46</v>
+      </c>
+      <c r="BS36">
+        <v>2.72</v>
+      </c>
+      <c r="BT36">
+        <v>7.4</v>
+      </c>
+      <c r="BU36">
+        <v>3.45</v>
+      </c>
+      <c r="BV36">
+        <v>20</v>
+      </c>
+      <c r="BW36">
+        <v>2.52</v>
+      </c>
+      <c r="BX36">
         <v>34</v>
       </c>
-      <c r="AA36">
-        <v>110</v>
-      </c>
-      <c r="AB36">
-        <v>9.4</v>
-      </c>
-      <c r="AC36">
-        <v>7.8</v>
-      </c>
-      <c r="AD36">
-        <v>19.5</v>
-      </c>
-      <c r="AE36">
-        <v>70</v>
-      </c>
-      <c r="AF36">
-        <v>15</v>
-      </c>
-      <c r="AG36">
-        <v>13</v>
-      </c>
-      <c r="AH36">
-        <v>24</v>
-      </c>
-      <c r="AI36">
-        <v>75</v>
-      </c>
-      <c r="AJ36">
-        <v>34</v>
-      </c>
-      <c r="AK36">
-        <v>32</v>
-      </c>
-      <c r="AL36">
-        <v>55</v>
-      </c>
-      <c r="AM36">
-        <v>160</v>
-      </c>
-      <c r="AN36">
-        <v>26</v>
-      </c>
-      <c r="AO36">
-        <v>80</v>
-      </c>
-      <c r="AP36">
-        <v>9.6</v>
-      </c>
-      <c r="AQ36">
-        <v>9.6</v>
-      </c>
-      <c r="AR36">
-        <v>21</v>
-      </c>
-      <c r="AS36">
-        <v>5.2</v>
-      </c>
-      <c r="AT36">
-        <v>7</v>
-      </c>
-      <c r="AU36">
-        <v>6.6</v>
-      </c>
-      <c r="AV36">
-        <v>14.5</v>
-      </c>
-      <c r="AW36">
-        <v>5.1</v>
-      </c>
-      <c r="AX36">
-        <v>11</v>
-      </c>
-      <c r="AY36">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ36">
-        <v>17.5</v>
-      </c>
-      <c r="BA36">
-        <v>5.1</v>
-      </c>
-      <c r="BB36">
-        <v>21</v>
-      </c>
-      <c r="BC36">
-        <v>20</v>
-      </c>
-      <c r="BD36">
-        <v>5</v>
-      </c>
-      <c r="BE36">
-        <v>5.3</v>
-      </c>
-      <c r="BF36">
-        <v>17</v>
-      </c>
-      <c r="BG36">
-        <v>5.1</v>
-      </c>
-      <c r="BH36">
-        <v>3.05</v>
-      </c>
-      <c r="BI36">
-        <v>2.54</v>
-      </c>
-      <c r="BJ36">
-        <v>10.5</v>
-      </c>
-      <c r="BK36">
-        <v>6.2</v>
-      </c>
-      <c r="BL36">
-        <v>1000</v>
-      </c>
-      <c r="BM36">
-        <v>14</v>
-      </c>
-      <c r="BN36">
-        <v>4.8</v>
-      </c>
-      <c r="BO36">
-        <v>3.85</v>
-      </c>
-      <c r="BP36">
-        <v>17</v>
-      </c>
-      <c r="BQ36">
-        <v>8</v>
-      </c>
-      <c r="BR36">
-        <v>1000</v>
-      </c>
-      <c r="BS36">
-        <v>10.5</v>
-      </c>
-      <c r="BT36">
-        <v>7.2</v>
-      </c>
-      <c r="BU36">
-        <v>5.6</v>
-      </c>
-      <c r="BV36">
-        <v>1000</v>
-      </c>
-      <c r="BW36">
-        <v>11</v>
-      </c>
-      <c r="BX36">
-        <v>1000</v>
-      </c>
       <c r="BY36">
-        <v>12</v>
+        <v>2.66</v>
       </c>
       <c r="BZ36">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA36">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB36" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" spans="1:80">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B37" t="s">
         <v>105</v>
@@ -9737,232 +9743,232 @@
         <v>157</v>
       </c>
       <c r="E37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F37">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="G37">
+        <v>2.28</v>
+      </c>
+      <c r="H37">
         <v>3.8</v>
       </c>
-      <c r="H37">
-        <v>2.02</v>
-      </c>
       <c r="I37">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="J37">
+        <v>3.3</v>
+      </c>
+      <c r="K37">
+        <v>3.5</v>
+      </c>
+      <c r="L37">
+        <v>1.42</v>
+      </c>
+      <c r="M37">
+        <v>1.1</v>
+      </c>
+      <c r="N37">
+        <v>3</v>
+      </c>
+      <c r="O37">
+        <v>1.42</v>
+      </c>
+      <c r="P37">
+        <v>1.69</v>
+      </c>
+      <c r="Q37">
+        <v>2.22</v>
+      </c>
+      <c r="R37">
+        <v>1.26</v>
+      </c>
+      <c r="S37">
+        <v>4.2</v>
+      </c>
+      <c r="T37">
+        <v>1.92</v>
+      </c>
+      <c r="U37">
+        <v>1.91</v>
+      </c>
+      <c r="V37">
+        <v>1.35</v>
+      </c>
+      <c r="W37">
+        <v>1.79</v>
+      </c>
+      <c r="X37">
+        <v>13</v>
+      </c>
+      <c r="Y37">
+        <v>14.5</v>
+      </c>
+      <c r="Z37">
+        <v>34</v>
+      </c>
+      <c r="AA37">
+        <v>110</v>
+      </c>
+      <c r="AB37">
+        <v>9.4</v>
+      </c>
+      <c r="AC37">
+        <v>7.8</v>
+      </c>
+      <c r="AD37">
+        <v>19.5</v>
+      </c>
+      <c r="AE37">
+        <v>70</v>
+      </c>
+      <c r="AF37">
+        <v>15</v>
+      </c>
+      <c r="AG37">
+        <v>13</v>
+      </c>
+      <c r="AH37">
+        <v>24</v>
+      </c>
+      <c r="AI37">
+        <v>75</v>
+      </c>
+      <c r="AJ37">
+        <v>34</v>
+      </c>
+      <c r="AK37">
+        <v>32</v>
+      </c>
+      <c r="AL37">
+        <v>55</v>
+      </c>
+      <c r="AM37">
+        <v>160</v>
+      </c>
+      <c r="AN37">
+        <v>26</v>
+      </c>
+      <c r="AO37">
+        <v>80</v>
+      </c>
+      <c r="AP37">
+        <v>9.6</v>
+      </c>
+      <c r="AQ37">
+        <v>9.6</v>
+      </c>
+      <c r="AR37">
+        <v>21</v>
+      </c>
+      <c r="AS37">
+        <v>5.5</v>
+      </c>
+      <c r="AT37">
+        <v>7</v>
+      </c>
+      <c r="AU37">
+        <v>6.6</v>
+      </c>
+      <c r="AV37">
+        <v>14.5</v>
+      </c>
+      <c r="AW37">
+        <v>5.4</v>
+      </c>
+      <c r="AX37">
+        <v>11</v>
+      </c>
+      <c r="AY37">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ37">
+        <v>17.5</v>
+      </c>
+      <c r="BA37">
+        <v>5.4</v>
+      </c>
+      <c r="BB37">
+        <v>21</v>
+      </c>
+      <c r="BC37">
+        <v>20</v>
+      </c>
+      <c r="BD37">
+        <v>5.2</v>
+      </c>
+      <c r="BE37">
+        <v>5.6</v>
+      </c>
+      <c r="BF37">
+        <v>17</v>
+      </c>
+      <c r="BG37">
+        <v>5.4</v>
+      </c>
+      <c r="BH37">
+        <v>3.05</v>
+      </c>
+      <c r="BI37">
+        <v>2.54</v>
+      </c>
+      <c r="BJ37">
+        <v>10.5</v>
+      </c>
+      <c r="BK37">
+        <v>6.2</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>14</v>
+      </c>
+      <c r="BN37">
+        <v>4.8</v>
+      </c>
+      <c r="BO37">
         <v>3.85</v>
       </c>
-      <c r="K37">
-        <v>4.3</v>
-      </c>
-      <c r="L37">
-        <v>1.01</v>
-      </c>
-      <c r="M37">
-        <v>1.04</v>
-      </c>
-      <c r="N37">
-        <v>4.7</v>
-      </c>
-      <c r="O37">
-        <v>1.19</v>
-      </c>
-      <c r="P37">
-        <v>2.5</v>
-      </c>
-      <c r="Q37">
-        <v>1.63</v>
-      </c>
-      <c r="R37">
-        <v>1.44</v>
-      </c>
-      <c r="S37">
-        <v>2.28</v>
-      </c>
-      <c r="T37">
-        <v>1.48</v>
-      </c>
-      <c r="U37">
-        <v>2.34</v>
-      </c>
-      <c r="V37">
-        <v>1.83</v>
-      </c>
-      <c r="W37">
-        <v>1.35</v>
-      </c>
-      <c r="X37">
-        <v>1000</v>
-      </c>
-      <c r="Y37">
-        <v>18.5</v>
-      </c>
-      <c r="Z37">
-        <v>22</v>
-      </c>
-      <c r="AA37">
-        <v>36</v>
-      </c>
-      <c r="AB37">
-        <v>25</v>
-      </c>
-      <c r="AC37">
-        <v>13.5</v>
-      </c>
-      <c r="AD37">
-        <v>15.5</v>
-      </c>
-      <c r="AE37">
-        <v>29</v>
-      </c>
-      <c r="AF37">
-        <v>40</v>
-      </c>
-      <c r="AG37">
-        <v>21</v>
-      </c>
-      <c r="AH37">
-        <v>22</v>
-      </c>
-      <c r="AI37">
-        <v>40</v>
-      </c>
-      <c r="AJ37">
-        <v>1000</v>
-      </c>
-      <c r="AK37">
-        <v>1000</v>
-      </c>
-      <c r="AL37">
-        <v>1000</v>
-      </c>
-      <c r="AM37">
-        <v>1000</v>
-      </c>
-      <c r="AN37">
-        <v>1000</v>
-      </c>
-      <c r="AO37">
-        <v>1000</v>
-      </c>
-      <c r="AP37">
-        <v>1.03</v>
-      </c>
-      <c r="AQ37">
-        <v>8.4</v>
-      </c>
-      <c r="AR37">
-        <v>10</v>
-      </c>
-      <c r="AS37">
-        <v>16</v>
-      </c>
-      <c r="AT37">
-        <v>11.5</v>
-      </c>
-      <c r="AU37">
-        <v>6.4</v>
-      </c>
-      <c r="AV37">
-        <v>7.4</v>
-      </c>
-      <c r="AW37">
-        <v>12.5</v>
-      </c>
-      <c r="AX37">
-        <v>17.5</v>
-      </c>
-      <c r="AY37">
-        <v>9.6</v>
-      </c>
-      <c r="AZ37">
-        <v>10</v>
-      </c>
-      <c r="BA37">
-        <v>17.5</v>
-      </c>
-      <c r="BB37">
-        <v>1.03</v>
-      </c>
-      <c r="BC37">
-        <v>1.03</v>
-      </c>
-      <c r="BD37">
-        <v>1.03</v>
-      </c>
-      <c r="BE37">
-        <v>1.03</v>
-      </c>
-      <c r="BF37">
-        <v>1.01</v>
-      </c>
-      <c r="BG37">
-        <v>1.01</v>
-      </c>
-      <c r="BH37">
-        <v>5.8</v>
-      </c>
-      <c r="BI37">
-        <v>2.86</v>
-      </c>
-      <c r="BJ37">
-        <v>12.5</v>
-      </c>
-      <c r="BK37">
-        <v>5.4</v>
-      </c>
-      <c r="BL37">
-        <v>1000</v>
-      </c>
-      <c r="BM37">
-        <v>2.88</v>
-      </c>
-      <c r="BN37">
-        <v>10</v>
-      </c>
-      <c r="BO37">
-        <v>4.6</v>
-      </c>
       <c r="BP37">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="BQ37">
-        <v>2.7</v>
+        <v>8</v>
       </c>
       <c r="BR37">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS37">
-        <v>2.72</v>
+        <v>10.5</v>
       </c>
       <c r="BT37">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU37">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="BV37">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW37">
-        <v>2.52</v>
+        <v>11</v>
       </c>
       <c r="BX37">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY37">
-        <v>2.66</v>
+        <v>12</v>
       </c>
       <c r="BZ37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA37">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="CB37" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -9979,7 +9985,7 @@
         <v>158</v>
       </c>
       <c r="E38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F38">
         <v>3.65</v>
@@ -9991,7 +9997,7 @@
         <v>2.12</v>
       </c>
       <c r="I38">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J38">
         <v>3.1</v>
@@ -10030,7 +10036,7 @@
         <v>1.75</v>
       </c>
       <c r="V38">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W38">
         <v>1.31</v>
@@ -10090,126 +10096,126 @@
         <v>1000</v>
       </c>
       <c r="AP38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AQ38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AR38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AS38">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AT38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AU38">
         <v>1.17</v>
       </c>
       <c r="AV38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AW38">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AX38">
         <v>19</v>
       </c>
       <c r="AY38">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AZ38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BA38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BB38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BC38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BD38">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BE38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BG38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BH38">
         <v>1000</v>
       </c>
       <c r="BI38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ38">
         <v>1000</v>
       </c>
       <c r="BK38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN38">
         <v>1000</v>
       </c>
       <c r="BO38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP38">
         <v>1000</v>
       </c>
       <c r="BQ38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR38">
         <v>1000</v>
       </c>
       <c r="BS38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT38">
         <v>1000</v>
       </c>
       <c r="BU38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ38">
         <v>1000</v>
       </c>
       <c r="CA38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB38" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39" spans="1:80">
       <c r="A39" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
         <v>105</v>
@@ -10221,49 +10227,49 @@
         <v>159</v>
       </c>
       <c r="E39" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F39">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G39">
-        <v>3.9</v>
+        <v>990</v>
       </c>
       <c r="H39">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="I39">
-        <v>2.68</v>
+        <v>990</v>
       </c>
       <c r="J39">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="K39">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L39">
         <v>1.01</v>
       </c>
       <c r="M39">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N39">
-        <v>2.74</v>
+        <v>1.24</v>
       </c>
       <c r="O39">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="P39">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q39">
-        <v>1.96</v>
+        <v>1.21</v>
       </c>
       <c r="R39">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S39">
-        <v>3.35</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
         <v>1.11</v>
@@ -10272,43 +10278,43 @@
         <v>1.11</v>
       </c>
       <c r="V39">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="W39">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="X39">
         <v>1000</v>
       </c>
       <c r="Y39">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z39">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA39">
         <v>1000</v>
       </c>
       <c r="AB39">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC39">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD39">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE39">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF39">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG39">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH39">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI39">
         <v>1000</v>
@@ -10332,52 +10338,52 @@
         <v>1000</v>
       </c>
       <c r="AP39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR39">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT39">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU39">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV39">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW39">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX39">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY39">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF39">
         <v>1.01</v>
@@ -10386,72 +10392,72 @@
         <v>1.01</v>
       </c>
       <c r="BH39">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI39">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ39">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK39">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN39">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO39">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP39">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ39">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BR39">
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BT39">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU39">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BV39">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW39">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="BX39">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY39">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BZ39">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="CA39">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="CB39" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B40" t="s">
         <v>105</v>
@@ -10463,465 +10469,465 @@
         <v>160</v>
       </c>
       <c r="E40" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F40">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="G40">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="H40">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I40">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="J40">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="K40">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="L40">
         <v>1.01</v>
       </c>
       <c r="M40">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N40">
-        <v>4.3</v>
+        <v>2.74</v>
       </c>
       <c r="O40">
+        <v>1.37</v>
+      </c>
+      <c r="P40">
+        <v>1.74</v>
+      </c>
+      <c r="Q40">
+        <v>2.12</v>
+      </c>
+      <c r="R40">
         <v>1.25</v>
       </c>
-      <c r="P40">
-        <v>2.14</v>
-      </c>
-      <c r="Q40">
-        <v>1.72</v>
-      </c>
-      <c r="R40">
-        <v>1.45</v>
-      </c>
       <c r="S40">
-        <v>2.82</v>
+        <v>3.35</v>
       </c>
       <c r="T40">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="U40">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="V40">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="W40">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="X40">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y40">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z40">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA40">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB40">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC40">
         <v>10.5</v>
       </c>
       <c r="AD40">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AE40">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AF40">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AG40">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AH40">
-        <v>18.5</v>
+        <v>950</v>
       </c>
       <c r="AI40">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ40">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK40">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL40">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM40">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN40">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO40">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP40">
-        <v>16</v>
+        <v>1.89</v>
       </c>
       <c r="AQ40">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="AR40">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS40">
-        <v>4.3</v>
+        <v>1.89</v>
       </c>
       <c r="AT40">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AU40">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="AV40">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AW40">
         <v>18.5</v>
       </c>
       <c r="AX40">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="AY40">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AZ40">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA40">
-        <v>4.3</v>
+        <v>1.89</v>
       </c>
       <c r="BB40">
-        <v>4.5</v>
+        <v>1.89</v>
       </c>
       <c r="BC40">
-        <v>4.3</v>
+        <v>1.89</v>
       </c>
       <c r="BD40">
-        <v>4.4</v>
+        <v>1.89</v>
       </c>
       <c r="BE40">
-        <v>4.6</v>
+        <v>1.89</v>
       </c>
       <c r="BF40">
-        <v>17.5</v>
+        <v>1.89</v>
       </c>
       <c r="BG40">
-        <v>12.5</v>
+        <v>1.89</v>
       </c>
       <c r="BH40">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI40">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="BJ40">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK40">
-        <v>1.69</v>
+        <v>2.66</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="BN40">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO40">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP40">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BQ40">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="BR40">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS40">
-        <v>1.87</v>
+        <v>3.1</v>
       </c>
       <c r="BT40">
         <v>7.6</v>
       </c>
       <c r="BU40">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BV40">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BW40">
-        <v>1.8</v>
+        <v>2.92</v>
       </c>
       <c r="BX40">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BY40">
-        <v>1.85</v>
+        <v>3.05</v>
       </c>
       <c r="BZ40">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CA40">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="CB40" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B41" t="s">
         <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D41" t="s">
         <v>161</v>
       </c>
       <c r="E41" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F41">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="G41">
-        <v>1.54</v>
+        <v>3.3</v>
       </c>
       <c r="H41">
-        <v>6.6</v>
+        <v>2.34</v>
       </c>
       <c r="I41">
-        <v>8</v>
+        <v>2.58</v>
       </c>
       <c r="J41">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="K41">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="L41">
         <v>1.01</v>
       </c>
       <c r="M41">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N41">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="O41">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="P41">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q41">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="R41">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S41">
-        <v>2.18</v>
+        <v>2.8</v>
       </c>
       <c r="T41">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="U41">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="V41">
-        <v>1.15</v>
+        <v>1.64</v>
       </c>
       <c r="W41">
-        <v>2.84</v>
+        <v>1.44</v>
       </c>
       <c r="X41">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y41">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="Z41">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="AA41">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB41">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC41">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AD41">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="AE41">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF41">
+        <v>26</v>
+      </c>
+      <c r="AG41">
         <v>15.5</v>
       </c>
-      <c r="AG41">
-        <v>15</v>
-      </c>
       <c r="AH41">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="AI41">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AJ41">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AK41">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AL41">
         <v>44</v>
       </c>
       <c r="AM41">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN41">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AO41">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP41">
-        <v>2.48</v>
+        <v>14</v>
       </c>
       <c r="AQ41">
+        <v>11</v>
+      </c>
+      <c r="AR41">
+        <v>13.5</v>
+      </c>
+      <c r="AS41">
+        <v>4.3</v>
+      </c>
+      <c r="AT41">
+        <v>11</v>
+      </c>
+      <c r="AU41">
+        <v>7.6</v>
+      </c>
+      <c r="AV41">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW41">
+        <v>18.5</v>
+      </c>
+      <c r="AX41">
+        <v>17</v>
+      </c>
+      <c r="AY41">
+        <v>10</v>
+      </c>
+      <c r="AZ41">
+        <v>12</v>
+      </c>
+      <c r="BA41">
+        <v>4.3</v>
+      </c>
+      <c r="BB41">
+        <v>4.5</v>
+      </c>
+      <c r="BC41">
+        <v>4.3</v>
+      </c>
+      <c r="BD41">
+        <v>4.4</v>
+      </c>
+      <c r="BE41">
+        <v>4.6</v>
+      </c>
+      <c r="BF41">
         <v>17.5</v>
       </c>
-      <c r="AR41">
-        <v>2.42</v>
-      </c>
-      <c r="AS41">
-        <v>2.48</v>
-      </c>
-      <c r="AT41">
-        <v>7</v>
-      </c>
-      <c r="AU41">
-        <v>7.2</v>
-      </c>
-      <c r="AV41">
-        <v>16</v>
-      </c>
-      <c r="AW41">
-        <v>2.48</v>
-      </c>
-      <c r="AX41">
-        <v>6.8</v>
-      </c>
-      <c r="AY41">
-        <v>6.4</v>
-      </c>
-      <c r="AZ41">
+      <c r="BG41">
         <v>12.5</v>
       </c>
-      <c r="BA41">
-        <v>2.42</v>
-      </c>
-      <c r="BB41">
-        <v>8.4</v>
-      </c>
-      <c r="BC41">
-        <v>10</v>
-      </c>
-      <c r="BD41">
-        <v>2.34</v>
-      </c>
-      <c r="BE41">
-        <v>2.48</v>
-      </c>
-      <c r="BF41">
+      <c r="BH41">
+        <v>1000</v>
+      </c>
+      <c r="BI41">
+        <v>2.76</v>
+      </c>
+      <c r="BJ41">
+        <v>12.5</v>
+      </c>
+      <c r="BK41">
+        <v>1.69</v>
+      </c>
+      <c r="BL41">
+        <v>1000</v>
+      </c>
+      <c r="BM41">
+        <v>1.95</v>
+      </c>
+      <c r="BN41">
+        <v>8.6</v>
+      </c>
+      <c r="BO41">
+        <v>4.3</v>
+      </c>
+      <c r="BP41">
+        <v>30</v>
+      </c>
+      <c r="BQ41">
+        <v>1.83</v>
+      </c>
+      <c r="BR41">
+        <v>44</v>
+      </c>
+      <c r="BS41">
+        <v>1.87</v>
+      </c>
+      <c r="BT41">
+        <v>7.6</v>
+      </c>
+      <c r="BU41">
         <v>3.85</v>
       </c>
-      <c r="BG41">
-        <v>2.48</v>
-      </c>
-      <c r="BH41">
-        <v>1000</v>
-      </c>
-      <c r="BI41">
-        <v>1.01</v>
-      </c>
-      <c r="BJ41">
-        <v>1000</v>
-      </c>
-      <c r="BK41">
-        <v>1.01</v>
-      </c>
-      <c r="BL41">
-        <v>1000</v>
-      </c>
-      <c r="BM41">
-        <v>1.01</v>
-      </c>
-      <c r="BN41">
-        <v>1000</v>
-      </c>
-      <c r="BO41">
-        <v>1.01</v>
-      </c>
-      <c r="BP41">
-        <v>1000</v>
-      </c>
-      <c r="BQ41">
-        <v>1.01</v>
-      </c>
-      <c r="BR41">
-        <v>1000</v>
-      </c>
-      <c r="BS41">
-        <v>1.01</v>
-      </c>
-      <c r="BT41">
-        <v>1000</v>
-      </c>
-      <c r="BU41">
-        <v>1.01</v>
-      </c>
       <c r="BV41">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW41">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BX41">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY41">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BZ41">
         <v>0</v>
@@ -10930,12 +10936,12 @@
         <v>0</v>
       </c>
       <c r="CB41" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B42" t="s">
         <v>105</v>
@@ -10947,223 +10953,223 @@
         <v>162</v>
       </c>
       <c r="E42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F42">
-        <v>8.800000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="G42">
-        <v>990</v>
+        <v>1.57</v>
       </c>
       <c r="H42">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="I42">
-        <v>1.42</v>
+        <v>8</v>
       </c>
       <c r="J42">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="K42">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="L42">
         <v>1.01</v>
       </c>
       <c r="M42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N42">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="O42">
+        <v>1.16</v>
+      </c>
+      <c r="P42">
+        <v>2.54</v>
+      </c>
+      <c r="Q42">
+        <v>1.47</v>
+      </c>
+      <c r="R42">
+        <v>1.5</v>
+      </c>
+      <c r="S42">
+        <v>2.18</v>
+      </c>
+      <c r="T42">
+        <v>1.53</v>
+      </c>
+      <c r="U42">
+        <v>1.81</v>
+      </c>
+      <c r="V42">
         <v>1.15</v>
       </c>
-      <c r="P42">
-        <v>2.44</v>
-      </c>
-      <c r="Q42">
-        <v>1.51</v>
-      </c>
-      <c r="R42">
-        <v>1.57</v>
-      </c>
-      <c r="S42">
-        <v>2.3</v>
-      </c>
-      <c r="T42">
-        <v>1.11</v>
-      </c>
-      <c r="U42">
-        <v>1.11</v>
-      </c>
-      <c r="V42">
-        <v>3.4</v>
-      </c>
       <c r="W42">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="X42">
         <v>1000</v>
       </c>
       <c r="Y42">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z42">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA42">
         <v>1000</v>
       </c>
       <c r="AB42">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC42">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD42">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE42">
         <v>1000</v>
       </c>
       <c r="AF42">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG42">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH42">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI42">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ42">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK42">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL42">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM42">
         <v>1000</v>
       </c>
       <c r="AN42">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO42">
         <v>1000</v>
       </c>
       <c r="AP42">
-        <v>1.03</v>
+        <v>2.48</v>
       </c>
       <c r="AQ42">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AR42">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="AS42">
-        <v>1.03</v>
+        <v>2.48</v>
       </c>
       <c r="AT42">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU42">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV42">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AW42">
-        <v>1.03</v>
+        <v>2.48</v>
       </c>
       <c r="AX42">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AY42">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AZ42">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA42">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="BB42">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BC42">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BD42">
-        <v>1.03</v>
+        <v>2.36</v>
       </c>
       <c r="BE42">
-        <v>1.03</v>
+        <v>2.48</v>
       </c>
       <c r="BF42">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG42">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BH42">
         <v>1000</v>
       </c>
       <c r="BI42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ42">
         <v>1000</v>
       </c>
       <c r="BK42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN42">
         <v>1000</v>
       </c>
       <c r="BO42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP42">
         <v>1000</v>
       </c>
       <c r="BQ42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR42">
         <v>1000</v>
       </c>
       <c r="BS42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT42">
         <v>1000</v>
       </c>
       <c r="BU42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV42">
         <v>1000</v>
       </c>
       <c r="BW42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX42">
         <v>1000</v>
       </c>
       <c r="BY42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ42">
         <v>0</v>
@@ -11172,7 +11178,7 @@
         <v>0</v>
       </c>
       <c r="CB42" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:80">
@@ -11189,25 +11195,25 @@
         <v>163</v>
       </c>
       <c r="E43" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F43">
-        <v>2.78</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G43">
-        <v>3.3</v>
+        <v>990</v>
       </c>
       <c r="H43">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="I43">
-        <v>2.8</v>
+        <v>1.42</v>
       </c>
       <c r="J43">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K43">
-        <v>3.85</v>
+        <v>7.4</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11216,22 +11222,22 @@
         <v>1.01</v>
       </c>
       <c r="N43">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O43">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="P43">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="Q43">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="R43">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="S43">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="T43">
         <v>1.11</v>
@@ -11240,10 +11246,10 @@
         <v>1.11</v>
       </c>
       <c r="V43">
-        <v>1.56</v>
+        <v>3.4</v>
       </c>
       <c r="W43">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="X43">
         <v>1000</v>
@@ -11300,52 +11306,52 @@
         <v>1000</v>
       </c>
       <c r="AP43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF43">
         <v>1.01</v>
@@ -11354,58 +11360,58 @@
         <v>1.01</v>
       </c>
       <c r="BH43">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI43">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="BJ43">
         <v>1000</v>
       </c>
       <c r="BK43">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BN43">
         <v>1000</v>
       </c>
       <c r="BO43">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BP43">
         <v>1000</v>
       </c>
       <c r="BQ43">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BR43">
         <v>1000</v>
       </c>
       <c r="BS43">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BT43">
         <v>1000</v>
       </c>
       <c r="BU43">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BV43">
         <v>1000</v>
       </c>
       <c r="BW43">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BX43">
         <v>1000</v>
       </c>
       <c r="BY43">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BZ43">
         <v>0</v>
@@ -11414,7 +11420,7 @@
         <v>0</v>
       </c>
       <c r="CB43" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44" spans="1:80">
@@ -11431,25 +11437,25 @@
         <v>164</v>
       </c>
       <c r="E44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F44">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="G44">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="H44">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="I44">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J44">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K44">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="L44">
         <v>1.01</v>
@@ -11458,22 +11464,22 @@
         <v>1.01</v>
       </c>
       <c r="N44">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O44">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="P44">
         <v>2</v>
       </c>
       <c r="Q44">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="R44">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S44">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="T44">
         <v>1.11</v>
@@ -11482,10 +11488,10 @@
         <v>1.11</v>
       </c>
       <c r="V44">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="W44">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="X44">
         <v>1000</v>
@@ -11542,52 +11548,52 @@
         <v>1000</v>
       </c>
       <c r="AP44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF44">
         <v>1.01</v>
@@ -11596,58 +11602,58 @@
         <v>1.01</v>
       </c>
       <c r="BH44">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BI44">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="BJ44">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK44">
-        <v>2.52</v>
+        <v>1.29</v>
       </c>
       <c r="BL44">
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>3.15</v>
+        <v>1.29</v>
       </c>
       <c r="BN44">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO44">
-        <v>3.85</v>
+        <v>1.29</v>
       </c>
       <c r="BP44">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ44">
-        <v>2.8</v>
+        <v>1.29</v>
       </c>
       <c r="BR44">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS44">
-        <v>2.92</v>
+        <v>1.29</v>
       </c>
       <c r="BT44">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU44">
-        <v>4.3</v>
+        <v>1.29</v>
       </c>
       <c r="BV44">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW44">
-        <v>2.88</v>
+        <v>1.29</v>
       </c>
       <c r="BX44">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY44">
-        <v>2.96</v>
+        <v>1.29</v>
       </c>
       <c r="BZ44">
         <v>0</v>
@@ -11656,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="CB44" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" spans="1:80">
@@ -11673,25 +11679,25 @@
         <v>165</v>
       </c>
       <c r="E45" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F45">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="G45">
-        <v>1.88</v>
+        <v>2.96</v>
       </c>
       <c r="H45">
-        <v>4.5</v>
+        <v>2.52</v>
       </c>
       <c r="I45">
-        <v>8.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="J45">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="K45">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="L45">
         <v>1.01</v>
@@ -11700,22 +11706,22 @@
         <v>1.01</v>
       </c>
       <c r="N45">
-        <v>2.18</v>
+        <v>3.9</v>
       </c>
       <c r="O45">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P45">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q45">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="R45">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S45">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="T45">
         <v>1.11</v>
@@ -11724,10 +11730,10 @@
         <v>1.11</v>
       </c>
       <c r="V45">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="W45">
-        <v>2.12</v>
+        <v>1.51</v>
       </c>
       <c r="X45">
         <v>1000</v>
@@ -11784,52 +11790,52 @@
         <v>1000</v>
       </c>
       <c r="AP45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF45">
         <v>1.01</v>
@@ -11838,58 +11844,58 @@
         <v>1.01</v>
       </c>
       <c r="BH45">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BI45">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="BJ45">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BK45">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="BL45">
         <v>1000</v>
       </c>
       <c r="BM45">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="BN45">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO45">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="BP45">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BQ45">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BR45">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS45">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="BT45">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BU45">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="BV45">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW45">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="BX45">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY45">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="BZ45">
         <v>0</v>
@@ -11898,7 +11904,7 @@
         <v>0</v>
       </c>
       <c r="CB45" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:80">
@@ -11915,25 +11921,25 @@
         <v>166</v>
       </c>
       <c r="E46" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F46">
-        <v>2.38</v>
+        <v>1.51</v>
       </c>
       <c r="G46">
-        <v>2.66</v>
+        <v>1.8</v>
       </c>
       <c r="H46">
-        <v>2.92</v>
+        <v>4.5</v>
       </c>
       <c r="I46">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J46">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="K46">
-        <v>3.75</v>
+        <v>8.6</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -11942,34 +11948,34 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>3.15</v>
+        <v>2.18</v>
       </c>
       <c r="O46">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="P46">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q46">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="R46">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S46">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="T46">
         <v>1.11</v>
       </c>
       <c r="U46">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="V46">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="W46">
-        <v>1.6</v>
+        <v>2.24</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12026,52 +12032,52 @@
         <v>1000</v>
       </c>
       <c r="AP46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF46">
         <v>1.01</v>
@@ -12080,58 +12086,58 @@
         <v>1.01</v>
       </c>
       <c r="BH46">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BI46">
+        <v>2.94</v>
+      </c>
+      <c r="BJ46">
+        <v>13.5</v>
+      </c>
+      <c r="BK46">
+        <v>2.7</v>
+      </c>
+      <c r="BL46">
+        <v>1000</v>
+      </c>
+      <c r="BM46">
+        <v>3.35</v>
+      </c>
+      <c r="BN46">
+        <v>5.8</v>
+      </c>
+      <c r="BO46">
+        <v>3</v>
+      </c>
+      <c r="BP46">
+        <v>15</v>
+      </c>
+      <c r="BQ46">
+        <v>2.76</v>
+      </c>
+      <c r="BR46">
+        <v>34</v>
+      </c>
+      <c r="BS46">
+        <v>3.05</v>
+      </c>
+      <c r="BT46">
+        <v>12.5</v>
+      </c>
+      <c r="BU46">
         <v>2.66</v>
       </c>
-      <c r="BJ46">
-        <v>1000</v>
-      </c>
-      <c r="BK46">
-        <v>1.33</v>
-      </c>
-      <c r="BL46">
-        <v>1000</v>
-      </c>
-      <c r="BM46">
-        <v>1.33</v>
-      </c>
-      <c r="BN46">
-        <v>1000</v>
-      </c>
-      <c r="BO46">
-        <v>1.33</v>
-      </c>
-      <c r="BP46">
-        <v>1000</v>
-      </c>
-      <c r="BQ46">
-        <v>1.33</v>
-      </c>
-      <c r="BR46">
-        <v>1000</v>
-      </c>
-      <c r="BS46">
-        <v>1.33</v>
-      </c>
-      <c r="BT46">
-        <v>1000</v>
-      </c>
-      <c r="BU46">
-        <v>1.33</v>
-      </c>
       <c r="BV46">
         <v>1000</v>
       </c>
       <c r="BW46">
-        <v>1.33</v>
+        <v>3.2</v>
       </c>
       <c r="BX46">
         <v>1000</v>
       </c>
       <c r="BY46">
-        <v>1.33</v>
+        <v>3.2</v>
       </c>
       <c r="BZ46">
         <v>0</v>
@@ -12140,84 +12146,84 @@
         <v>0</v>
       </c>
       <c r="CB46" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:80">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B47" t="s">
         <v>105</v>
       </c>
       <c r="C47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D47" t="s">
         <v>167</v>
       </c>
       <c r="E47" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F47">
+        <v>2.38</v>
+      </c>
+      <c r="G47">
+        <v>2.66</v>
+      </c>
+      <c r="H47">
+        <v>2.92</v>
+      </c>
+      <c r="I47">
+        <v>3.55</v>
+      </c>
+      <c r="J47">
+        <v>3.25</v>
+      </c>
+      <c r="K47">
+        <v>3.8</v>
+      </c>
+      <c r="L47">
+        <v>1.01</v>
+      </c>
+      <c r="M47">
+        <v>1.01</v>
+      </c>
+      <c r="N47">
+        <v>4.3</v>
+      </c>
+      <c r="O47">
+        <v>1.28</v>
+      </c>
+      <c r="P47">
+        <v>1.83</v>
+      </c>
+      <c r="Q47">
+        <v>1.94</v>
+      </c>
+      <c r="R47">
         <v>1.27</v>
       </c>
-      <c r="G47">
-        <v>1.31</v>
-      </c>
-      <c r="H47">
-        <v>9.4</v>
-      </c>
-      <c r="I47">
-        <v>11.5</v>
-      </c>
-      <c r="J47">
-        <v>6.8</v>
-      </c>
-      <c r="K47">
-        <v>7.6</v>
-      </c>
-      <c r="L47">
-        <v>1.01</v>
-      </c>
-      <c r="M47">
-        <v>1.01</v>
-      </c>
-      <c r="N47">
-        <v>3.65</v>
-      </c>
-      <c r="O47">
-        <v>1.08</v>
-      </c>
-      <c r="P47">
-        <v>3.65</v>
-      </c>
-      <c r="Q47">
-        <v>1.34</v>
-      </c>
-      <c r="R47">
-        <v>1.98</v>
-      </c>
       <c r="S47">
-        <v>1.79</v>
+        <v>2.96</v>
       </c>
       <c r="T47">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="U47">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V47">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="W47">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="X47">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="Y47">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="Z47">
         <v>1000</v>
@@ -12226,168 +12232,168 @@
         <v>1000</v>
       </c>
       <c r="AB47">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC47">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AD47">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE47">
         <v>1000</v>
       </c>
       <c r="AF47">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG47">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH47">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI47">
         <v>1000</v>
       </c>
       <c r="AJ47">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK47">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL47">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM47">
         <v>1000</v>
       </c>
       <c r="AN47">
+        <v>1000</v>
+      </c>
+      <c r="AO47">
+        <v>1000</v>
+      </c>
+      <c r="AP47">
+        <v>1.01</v>
+      </c>
+      <c r="AQ47">
+        <v>1.01</v>
+      </c>
+      <c r="AR47">
+        <v>1.01</v>
+      </c>
+      <c r="AS47">
+        <v>1.01</v>
+      </c>
+      <c r="AT47">
+        <v>1.01</v>
+      </c>
+      <c r="AU47">
+        <v>1.01</v>
+      </c>
+      <c r="AV47">
+        <v>1.01</v>
+      </c>
+      <c r="AW47">
+        <v>1.01</v>
+      </c>
+      <c r="AX47">
+        <v>1.01</v>
+      </c>
+      <c r="AY47">
+        <v>1.01</v>
+      </c>
+      <c r="AZ47">
+        <v>1.01</v>
+      </c>
+      <c r="BA47">
+        <v>1.01</v>
+      </c>
+      <c r="BB47">
+        <v>1.01</v>
+      </c>
+      <c r="BC47">
+        <v>1.01</v>
+      </c>
+      <c r="BD47">
+        <v>1.01</v>
+      </c>
+      <c r="BE47">
+        <v>1.01</v>
+      </c>
+      <c r="BF47">
+        <v>1.01</v>
+      </c>
+      <c r="BG47">
+        <v>1.01</v>
+      </c>
+      <c r="BH47">
         <v>4.1</v>
       </c>
-      <c r="AO47">
-        <v>1000</v>
-      </c>
-      <c r="AP47">
-        <v>2.8</v>
-      </c>
-      <c r="AQ47">
-        <v>2.8</v>
-      </c>
-      <c r="AR47">
-        <v>2.92</v>
-      </c>
-      <c r="AS47">
-        <v>2.92</v>
-      </c>
-      <c r="AT47">
-        <v>12.5</v>
-      </c>
-      <c r="AU47">
-        <v>13.5</v>
-      </c>
-      <c r="AV47">
-        <v>2.76</v>
-      </c>
-      <c r="AW47">
-        <v>2.92</v>
-      </c>
-      <c r="AX47">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY47">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ47">
-        <v>18</v>
-      </c>
-      <c r="BA47">
-        <v>2.92</v>
-      </c>
-      <c r="BB47">
-        <v>9.6</v>
-      </c>
-      <c r="BC47">
-        <v>9.6</v>
-      </c>
-      <c r="BD47">
-        <v>19</v>
-      </c>
-      <c r="BE47">
-        <v>2.92</v>
-      </c>
-      <c r="BF47">
-        <v>2.58</v>
-      </c>
-      <c r="BG47">
-        <v>2.92</v>
-      </c>
-      <c r="BH47">
-        <v>1000</v>
-      </c>
       <c r="BI47">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ47">
         <v>1000</v>
       </c>
       <c r="BK47">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BL47">
         <v>1000</v>
       </c>
       <c r="BM47">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BN47">
         <v>1000</v>
       </c>
       <c r="BO47">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BP47">
         <v>1000</v>
       </c>
       <c r="BQ47">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BR47">
         <v>1000</v>
       </c>
       <c r="BS47">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BT47">
         <v>1000</v>
       </c>
       <c r="BU47">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BV47">
         <v>1000</v>
       </c>
       <c r="BW47">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BX47">
         <v>1000</v>
       </c>
       <c r="BY47">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BZ47">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA47">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB47" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48" spans="1:80">
       <c r="A48" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B48" t="s">
         <v>105</v>
@@ -12399,237 +12405,237 @@
         <v>168</v>
       </c>
       <c r="E48" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F48">
-        <v>5.7</v>
+        <v>1.28</v>
       </c>
       <c r="G48">
-        <v>6.6</v>
+        <v>1.31</v>
       </c>
       <c r="H48">
-        <v>1.57</v>
+        <v>9.6</v>
       </c>
       <c r="I48">
-        <v>1.62</v>
+        <v>11.5</v>
       </c>
       <c r="J48">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="K48">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="L48">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N48">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="O48">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="P48">
-        <v>2.56</v>
+        <v>3.65</v>
       </c>
       <c r="Q48">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="R48">
-        <v>1.63</v>
+        <v>2.04</v>
       </c>
       <c r="S48">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="T48">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="U48">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V48">
-        <v>2.62</v>
+        <v>1.09</v>
       </c>
       <c r="W48">
-        <v>1.18</v>
+        <v>4.1</v>
       </c>
       <c r="X48">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="Y48">
+        <v>950</v>
+      </c>
+      <c r="Z48">
+        <v>140</v>
+      </c>
+      <c r="AA48">
+        <v>390</v>
+      </c>
+      <c r="AB48">
+        <v>17.5</v>
+      </c>
+      <c r="AC48">
+        <v>18.5</v>
+      </c>
+      <c r="AD48">
+        <v>55</v>
+      </c>
+      <c r="AE48">
+        <v>150</v>
+      </c>
+      <c r="AF48">
         <v>13</v>
       </c>
-      <c r="Z48">
+      <c r="AG48">
+        <v>13.5</v>
+      </c>
+      <c r="AH48">
+        <v>26</v>
+      </c>
+      <c r="AI48">
+        <v>110</v>
+      </c>
+      <c r="AJ48">
+        <v>13</v>
+      </c>
+      <c r="AK48">
         <v>14</v>
       </c>
-      <c r="AA48">
-        <v>16.5</v>
-      </c>
-      <c r="AB48">
-        <v>34</v>
-      </c>
-      <c r="AC48">
-        <v>13</v>
-      </c>
-      <c r="AD48">
-        <v>11.5</v>
-      </c>
-      <c r="AE48">
-        <v>15.5</v>
-      </c>
-      <c r="AF48">
-        <v>60</v>
-      </c>
-      <c r="AG48">
-        <v>26</v>
-      </c>
-      <c r="AH48">
-        <v>21</v>
-      </c>
-      <c r="AI48">
-        <v>27</v>
-      </c>
-      <c r="AJ48">
-        <v>170</v>
-      </c>
-      <c r="AK48">
-        <v>70</v>
-      </c>
       <c r="AL48">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AM48">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AN48">
-        <v>60</v>
+        <v>3.25</v>
       </c>
       <c r="AO48">
-        <v>6.8</v>
+        <v>120</v>
       </c>
       <c r="AP48">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AQ48">
+        <v>8</v>
+      </c>
+      <c r="AR48">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS48">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT48">
+        <v>14</v>
+      </c>
+      <c r="AU48">
+        <v>15</v>
+      </c>
+      <c r="AV48">
+        <v>30</v>
+      </c>
+      <c r="AW48">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX48">
+        <v>10</v>
+      </c>
+      <c r="AY48">
+        <v>10.5</v>
+      </c>
+      <c r="AZ48">
+        <v>20</v>
+      </c>
+      <c r="BA48">
+        <v>8.6</v>
+      </c>
+      <c r="BB48">
+        <v>10</v>
+      </c>
+      <c r="BC48">
         <v>11</v>
       </c>
-      <c r="AR48">
-        <v>10</v>
-      </c>
-      <c r="AS48">
-        <v>14</v>
-      </c>
-      <c r="AT48">
-        <v>23</v>
-      </c>
-      <c r="AU48">
-        <v>10</v>
-      </c>
-      <c r="AV48">
-        <v>9</v>
-      </c>
-      <c r="AW48">
-        <v>13</v>
-      </c>
-      <c r="AX48">
-        <v>44</v>
-      </c>
-      <c r="AY48">
-        <v>20</v>
-      </c>
-      <c r="AZ48">
-        <v>16</v>
-      </c>
-      <c r="BA48">
-        <v>22</v>
-      </c>
-      <c r="BB48">
-        <v>6.6</v>
-      </c>
-      <c r="BC48">
-        <v>55</v>
-      </c>
       <c r="BD48">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BE48">
-        <v>60</v>
+        <v>8.6</v>
       </c>
       <c r="BF48">
-        <v>38</v>
+        <v>2.84</v>
       </c>
       <c r="BG48">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH48">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI48">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BJ48">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK48">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL48">
         <v>1000</v>
       </c>
       <c r="BM48">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN48">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO48">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP48">
         <v>1000</v>
       </c>
       <c r="BQ48">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR48">
         <v>1000</v>
       </c>
       <c r="BS48">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT48">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU48">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV48">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BW48">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX48">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BY48">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ48">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB48" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="49" spans="1:80">
       <c r="A49" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B49" t="s">
         <v>105</v>
@@ -12641,223 +12647,223 @@
         <v>169</v>
       </c>
       <c r="E49" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F49">
+        <v>5.7</v>
+      </c>
+      <c r="G49">
+        <v>6.6</v>
+      </c>
+      <c r="H49">
+        <v>1.55</v>
+      </c>
+      <c r="I49">
+        <v>1.62</v>
+      </c>
+      <c r="J49">
         <v>4.7</v>
       </c>
-      <c r="G49">
-        <v>6.2</v>
-      </c>
-      <c r="H49">
-        <v>1.81</v>
-      </c>
-      <c r="I49">
-        <v>1.99</v>
-      </c>
-      <c r="J49">
-        <v>3.45</v>
-      </c>
       <c r="K49">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="L49">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="M49">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N49">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="O49">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="P49">
-        <v>1.8</v>
+        <v>2.56</v>
       </c>
       <c r="Q49">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="R49">
-        <v>1.23</v>
+        <v>1.63</v>
       </c>
       <c r="S49">
-        <v>1.05</v>
+        <v>2.3</v>
       </c>
       <c r="T49">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="U49">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="V49">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="W49">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X49">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y49">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="Z49">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA49">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AB49">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="AC49">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD49">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE49">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="AF49">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG49">
         <v>24</v>
       </c>
       <c r="AH49">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI49">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ49">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AK49">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL49">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM49">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN49">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO49">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AP49">
-        <v>2.28</v>
+        <v>6.4</v>
       </c>
       <c r="AQ49">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR49">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AS49">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT49">
+        <v>23</v>
+      </c>
+      <c r="AU49">
         <v>10</v>
       </c>
-      <c r="AU49">
-        <v>1.89</v>
-      </c>
       <c r="AV49">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AW49">
         <v>13</v>
       </c>
       <c r="AX49">
-        <v>2.28</v>
+        <v>44</v>
       </c>
       <c r="AY49">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="AZ49">
-        <v>2.08</v>
+        <v>16</v>
       </c>
       <c r="BA49">
-        <v>2.28</v>
+        <v>22</v>
       </c>
       <c r="BB49">
-        <v>2.28</v>
+        <v>8</v>
       </c>
       <c r="BC49">
-        <v>2.28</v>
+        <v>55</v>
       </c>
       <c r="BD49">
-        <v>2.28</v>
+        <v>7.4</v>
       </c>
       <c r="BE49">
-        <v>2.28</v>
+        <v>60</v>
       </c>
       <c r="BF49">
-        <v>2.28</v>
+        <v>38</v>
       </c>
       <c r="BG49">
-        <v>2.28</v>
+        <v>5.3</v>
       </c>
       <c r="BH49">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI49">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BJ49">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK49">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL49">
         <v>1000</v>
       </c>
       <c r="BM49">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN49">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO49">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BP49">
         <v>1000</v>
       </c>
       <c r="BQ49">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR49">
         <v>1000</v>
       </c>
       <c r="BS49">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT49">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU49">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV49">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW49">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BX49">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY49">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ49">
         <v>0</v>
@@ -12866,240 +12872,240 @@
         <v>0</v>
       </c>
       <c r="CB49" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="50" spans="1:80">
       <c r="A50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B50" t="s">
         <v>105</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D50" t="s">
         <v>170</v>
       </c>
       <c r="E50" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F50">
-        <v>1.75</v>
+        <v>4.7</v>
       </c>
       <c r="G50">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="H50">
+        <v>1.9</v>
+      </c>
+      <c r="I50">
+        <v>1.99</v>
+      </c>
+      <c r="J50">
+        <v>3.45</v>
+      </c>
+      <c r="K50">
         <v>3.85</v>
       </c>
-      <c r="I50">
-        <v>7.2</v>
-      </c>
-      <c r="J50">
-        <v>2.46</v>
-      </c>
-      <c r="K50">
-        <v>950</v>
-      </c>
       <c r="L50">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M50">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N50">
-        <v>1.71</v>
+        <v>3.4</v>
       </c>
       <c r="O50">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P50">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="Q50">
+        <v>2.04</v>
+      </c>
+      <c r="R50">
+        <v>1.3</v>
+      </c>
+      <c r="S50">
+        <v>3.7</v>
+      </c>
+      <c r="T50">
+        <v>1.89</v>
+      </c>
+      <c r="U50">
+        <v>1.92</v>
+      </c>
+      <c r="V50">
+        <v>2</v>
+      </c>
+      <c r="W50">
+        <v>1.23</v>
+      </c>
+      <c r="X50">
+        <v>15.5</v>
+      </c>
+      <c r="Y50">
+        <v>8.6</v>
+      </c>
+      <c r="Z50">
+        <v>12</v>
+      </c>
+      <c r="AA50">
+        <v>22</v>
+      </c>
+      <c r="AB50">
+        <v>16.5</v>
+      </c>
+      <c r="AC50">
+        <v>8.6</v>
+      </c>
+      <c r="AD50">
+        <v>11</v>
+      </c>
+      <c r="AE50">
+        <v>22</v>
+      </c>
+      <c r="AF50">
+        <v>40</v>
+      </c>
+      <c r="AG50">
+        <v>21</v>
+      </c>
+      <c r="AH50">
+        <v>21</v>
+      </c>
+      <c r="AI50">
+        <v>42</v>
+      </c>
+      <c r="AJ50">
+        <v>150</v>
+      </c>
+      <c r="AK50">
+        <v>75</v>
+      </c>
+      <c r="AL50">
+        <v>80</v>
+      </c>
+      <c r="AM50">
+        <v>150</v>
+      </c>
+      <c r="AN50">
+        <v>110</v>
+      </c>
+      <c r="AO50">
+        <v>15.5</v>
+      </c>
+      <c r="AP50">
+        <v>9.6</v>
+      </c>
+      <c r="AQ50">
+        <v>7</v>
+      </c>
+      <c r="AR50">
+        <v>9.4</v>
+      </c>
+      <c r="AS50">
+        <v>17.5</v>
+      </c>
+      <c r="AT50">
+        <v>13</v>
+      </c>
+      <c r="AU50">
+        <v>7</v>
+      </c>
+      <c r="AV50">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW50">
+        <v>18</v>
+      </c>
+      <c r="AX50">
+        <v>6.8</v>
+      </c>
+      <c r="AY50">
+        <v>16.5</v>
+      </c>
+      <c r="AZ50">
+        <v>17</v>
+      </c>
+      <c r="BA50">
+        <v>6.8</v>
+      </c>
+      <c r="BB50">
+        <v>7.8</v>
+      </c>
+      <c r="BC50">
+        <v>7.4</v>
+      </c>
+      <c r="BD50">
+        <v>7.4</v>
+      </c>
+      <c r="BE50">
+        <v>7.8</v>
+      </c>
+      <c r="BF50">
+        <v>7.6</v>
+      </c>
+      <c r="BG50">
+        <v>10.5</v>
+      </c>
+      <c r="BH50">
+        <v>1000</v>
+      </c>
+      <c r="BI50">
+        <v>1.87</v>
+      </c>
+      <c r="BJ50">
+        <v>14.5</v>
+      </c>
+      <c r="BK50">
+        <v>1.66</v>
+      </c>
+      <c r="BL50">
+        <v>1000</v>
+      </c>
+      <c r="BM50">
+        <v>1.87</v>
+      </c>
+      <c r="BN50">
+        <v>11</v>
+      </c>
+      <c r="BO50">
+        <v>5.4</v>
+      </c>
+      <c r="BP50">
+        <v>1000</v>
+      </c>
+      <c r="BQ50">
+        <v>1.81</v>
+      </c>
+      <c r="BR50">
+        <v>1000</v>
+      </c>
+      <c r="BS50">
         <v>1.83</v>
       </c>
-      <c r="R50">
-        <v>1.18</v>
-      </c>
-      <c r="S50">
-        <v>2.72</v>
-      </c>
-      <c r="T50">
-        <v>1.01</v>
-      </c>
-      <c r="U50">
-        <v>1.01</v>
-      </c>
-      <c r="V50">
-        <v>1.2</v>
-      </c>
-      <c r="W50">
-        <v>1.83</v>
-      </c>
-      <c r="X50">
+      <c r="BT50">
+        <v>5.9</v>
+      </c>
+      <c r="BU50">
+        <v>3.1</v>
+      </c>
+      <c r="BV50">
         <v>18.5</v>
       </c>
-      <c r="Y50">
-        <v>21</v>
-      </c>
-      <c r="Z50">
-        <v>48</v>
-      </c>
-      <c r="AA50">
-        <v>1000</v>
-      </c>
-      <c r="AB50">
-        <v>11</v>
-      </c>
-      <c r="AC50">
-        <v>11</v>
-      </c>
-      <c r="AD50">
-        <v>25</v>
-      </c>
-      <c r="AE50">
-        <v>85</v>
-      </c>
-      <c r="AF50">
-        <v>15.5</v>
-      </c>
-      <c r="AG50">
-        <v>13.5</v>
-      </c>
-      <c r="AH50">
-        <v>26</v>
-      </c>
-      <c r="AI50">
-        <v>90</v>
-      </c>
-      <c r="AJ50">
-        <v>30</v>
-      </c>
-      <c r="AK50">
-        <v>29</v>
-      </c>
-      <c r="AL50">
-        <v>50</v>
-      </c>
-      <c r="AM50">
-        <v>1000</v>
-      </c>
-      <c r="AN50">
-        <v>1000</v>
-      </c>
-      <c r="AO50">
-        <v>1000</v>
-      </c>
-      <c r="AP50">
-        <v>10</v>
-      </c>
-      <c r="AQ50">
-        <v>11.5</v>
-      </c>
-      <c r="AR50">
-        <v>2.56</v>
-      </c>
-      <c r="AS50">
-        <v>2.7</v>
-      </c>
-      <c r="AT50">
-        <v>2.16</v>
-      </c>
-      <c r="AU50">
-        <v>2.16</v>
-      </c>
-      <c r="AV50">
-        <v>2.44</v>
-      </c>
-      <c r="AW50">
-        <v>2.62</v>
-      </c>
-      <c r="AX50">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY50">
-        <v>2.26</v>
-      </c>
-      <c r="AZ50">
-        <v>2.46</v>
-      </c>
-      <c r="BA50">
-        <v>2.62</v>
-      </c>
-      <c r="BB50">
-        <v>16</v>
-      </c>
-      <c r="BC50">
-        <v>15.5</v>
-      </c>
-      <c r="BD50">
-        <v>2.56</v>
-      </c>
-      <c r="BE50">
-        <v>2.7</v>
-      </c>
-      <c r="BF50">
-        <v>2.7</v>
-      </c>
-      <c r="BG50">
-        <v>2.7</v>
-      </c>
-      <c r="BH50">
-        <v>1000</v>
-      </c>
-      <c r="BI50">
-        <v>1.01</v>
-      </c>
-      <c r="BJ50">
-        <v>1000</v>
-      </c>
-      <c r="BK50">
-        <v>1.01</v>
-      </c>
-      <c r="BL50">
-        <v>1000</v>
-      </c>
-      <c r="BM50">
-        <v>1.01</v>
-      </c>
-      <c r="BN50">
-        <v>1000</v>
-      </c>
-      <c r="BO50">
-        <v>1.01</v>
-      </c>
-      <c r="BP50">
-        <v>1000</v>
-      </c>
-      <c r="BQ50">
-        <v>1.01</v>
-      </c>
-      <c r="BR50">
-        <v>1000</v>
-      </c>
-      <c r="BS50">
-        <v>1.01</v>
-      </c>
-      <c r="BT50">
-        <v>1000</v>
-      </c>
-      <c r="BU50">
-        <v>1.01</v>
-      </c>
-      <c r="BV50">
-        <v>1000</v>
-      </c>
       <c r="BW50">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BX50">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY50">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BZ50">
         <v>0</v>
@@ -13108,7 +13114,249 @@
         <v>0</v>
       </c>
       <c r="CB50" t="s">
-        <v>220</v>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="51" spans="1:80">
+      <c r="A51" t="s">
+        <v>104</v>
+      </c>
+      <c r="B51" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" t="s">
+        <v>121</v>
+      </c>
+      <c r="D51" t="s">
+        <v>171</v>
+      </c>
+      <c r="E51" t="s">
+        <v>221</v>
+      </c>
+      <c r="F51">
+        <v>1.78</v>
+      </c>
+      <c r="G51">
+        <v>2.2</v>
+      </c>
+      <c r="H51">
+        <v>3.85</v>
+      </c>
+      <c r="I51">
+        <v>6.4</v>
+      </c>
+      <c r="J51">
+        <v>2.56</v>
+      </c>
+      <c r="K51">
+        <v>4.6</v>
+      </c>
+      <c r="L51">
+        <v>1.01</v>
+      </c>
+      <c r="M51">
+        <v>1.07</v>
+      </c>
+      <c r="N51">
+        <v>2.8</v>
+      </c>
+      <c r="O51">
+        <v>1.32</v>
+      </c>
+      <c r="P51">
+        <v>1.71</v>
+      </c>
+      <c r="Q51">
+        <v>1.83</v>
+      </c>
+      <c r="R51">
+        <v>1.24</v>
+      </c>
+      <c r="S51">
+        <v>3.2</v>
+      </c>
+      <c r="T51">
+        <v>1.11</v>
+      </c>
+      <c r="U51">
+        <v>1.11</v>
+      </c>
+      <c r="V51">
+        <v>1.2</v>
+      </c>
+      <c r="W51">
+        <v>1.83</v>
+      </c>
+      <c r="X51">
+        <v>1000</v>
+      </c>
+      <c r="Y51">
+        <v>21</v>
+      </c>
+      <c r="Z51">
+        <v>48</v>
+      </c>
+      <c r="AA51">
+        <v>1000</v>
+      </c>
+      <c r="AB51">
+        <v>11</v>
+      </c>
+      <c r="AC51">
+        <v>11</v>
+      </c>
+      <c r="AD51">
+        <v>25</v>
+      </c>
+      <c r="AE51">
+        <v>85</v>
+      </c>
+      <c r="AF51">
+        <v>15.5</v>
+      </c>
+      <c r="AG51">
+        <v>13.5</v>
+      </c>
+      <c r="AH51">
+        <v>26</v>
+      </c>
+      <c r="AI51">
+        <v>90</v>
+      </c>
+      <c r="AJ51">
+        <v>30</v>
+      </c>
+      <c r="AK51">
+        <v>29</v>
+      </c>
+      <c r="AL51">
+        <v>50</v>
+      </c>
+      <c r="AM51">
+        <v>1000</v>
+      </c>
+      <c r="AN51">
+        <v>1000</v>
+      </c>
+      <c r="AO51">
+        <v>1000</v>
+      </c>
+      <c r="AP51">
+        <v>2.36</v>
+      </c>
+      <c r="AQ51">
+        <v>11.5</v>
+      </c>
+      <c r="AR51">
+        <v>2.26</v>
+      </c>
+      <c r="AS51">
+        <v>2.36</v>
+      </c>
+      <c r="AT51">
+        <v>1.95</v>
+      </c>
+      <c r="AU51">
+        <v>1.95</v>
+      </c>
+      <c r="AV51">
+        <v>2.16</v>
+      </c>
+      <c r="AW51">
+        <v>2.3</v>
+      </c>
+      <c r="AX51">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY51">
+        <v>2.02</v>
+      </c>
+      <c r="AZ51">
+        <v>2.16</v>
+      </c>
+      <c r="BA51">
+        <v>2.3</v>
+      </c>
+      <c r="BB51">
+        <v>16</v>
+      </c>
+      <c r="BC51">
+        <v>15.5</v>
+      </c>
+      <c r="BD51">
+        <v>2.26</v>
+      </c>
+      <c r="BE51">
+        <v>2.36</v>
+      </c>
+      <c r="BF51">
+        <v>2.36</v>
+      </c>
+      <c r="BG51">
+        <v>2.36</v>
+      </c>
+      <c r="BH51">
+        <v>1000</v>
+      </c>
+      <c r="BI51">
+        <v>1.04</v>
+      </c>
+      <c r="BJ51">
+        <v>1000</v>
+      </c>
+      <c r="BK51">
+        <v>1.04</v>
+      </c>
+      <c r="BL51">
+        <v>1000</v>
+      </c>
+      <c r="BM51">
+        <v>1.04</v>
+      </c>
+      <c r="BN51">
+        <v>1000</v>
+      </c>
+      <c r="BO51">
+        <v>1.04</v>
+      </c>
+      <c r="BP51">
+        <v>1000</v>
+      </c>
+      <c r="BQ51">
+        <v>1.04</v>
+      </c>
+      <c r="BR51">
+        <v>1000</v>
+      </c>
+      <c r="BS51">
+        <v>1.04</v>
+      </c>
+      <c r="BT51">
+        <v>1000</v>
+      </c>
+      <c r="BU51">
+        <v>1.04</v>
+      </c>
+      <c r="BV51">
+        <v>1000</v>
+      </c>
+      <c r="BW51">
+        <v>1.04</v>
+      </c>
+      <c r="BX51">
+        <v>1000</v>
+      </c>
+      <c r="BY51">
+        <v>1.04</v>
+      </c>
+      <c r="BZ51">
+        <v>0</v>
+      </c>
+      <c r="CA51">
+        <v>0</v>
+      </c>
+      <c r="CB51" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -682,7 +682,7 @@
     <t>Comerciantes Unidos</t>
   </si>
   <si>
-    <t>2026-07-29 20:24:43</t>
+    <t>2026-07-29 22:33:30</t>
   </si>
 </sst>
 </file>
@@ -1276,10 +1276,10 @@
         <v>172</v>
       </c>
       <c r="F2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H2">
         <v>2.6</v>
@@ -1291,7 +1291,7 @@
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
         <v>1.61</v>
@@ -1300,7 +1300,7 @@
         <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O2">
         <v>1.56</v>
@@ -1324,10 +1324,10 @@
         <v>1.77</v>
       </c>
       <c r="V2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X2">
         <v>8.4</v>
@@ -1387,10 +1387,10 @@
         <v>7.6</v>
       </c>
       <c r="AQ2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS2">
         <v>36</v>
@@ -1521,7 +1521,7 @@
         <v>1.7</v>
       </c>
       <c r="G3">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H3">
         <v>6.2</v>
@@ -1530,10 +1530,10 @@
         <v>7.2</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L3">
         <v>1.51</v>
@@ -1545,13 +1545,13 @@
         <v>2.84</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P3">
         <v>1.62</v>
       </c>
       <c r="Q3">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R3">
         <v>1.22</v>
@@ -1560,7 +1560,7 @@
         <v>4.7</v>
       </c>
       <c r="T3">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U3">
         <v>1.7</v>
@@ -1596,7 +1596,7 @@
         <v>160</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AG3">
         <v>13</v>
@@ -1620,7 +1620,7 @@
         <v>260</v>
       </c>
       <c r="AN3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO3">
         <v>270</v>
@@ -1632,13 +1632,13 @@
         <v>12</v>
       </c>
       <c r="AR3">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AS3">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU3">
         <v>7.2</v>
@@ -1647,7 +1647,7 @@
         <v>19.5</v>
       </c>
       <c r="AW3">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX3">
         <v>7.6</v>
@@ -1656,10 +1656,10 @@
         <v>9</v>
       </c>
       <c r="AZ3">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BA3">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BB3">
         <v>15</v>
@@ -1668,16 +1668,16 @@
         <v>19</v>
       </c>
       <c r="BD3">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BE3">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF3">
         <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH3">
         <v>3.05</v>
@@ -1689,13 +1689,13 @@
         <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3">
         <v>4.2</v>
@@ -1704,19 +1704,19 @@
         <v>3.15</v>
       </c>
       <c r="BP3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ3">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BU3">
         <v>5.1</v>
@@ -1725,7 +1725,7 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX3">
         <v>1000</v>
@@ -1737,7 +1737,7 @@
         <v>34</v>
       </c>
       <c r="CA3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="s">
         <v>222</v>
@@ -1775,7 +1775,7 @@
         <v>3.4</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
         <v>1.46</v>
@@ -1796,7 +1796,7 @@
         <v>2.18</v>
       </c>
       <c r="R4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
         <v>4</v>
@@ -1823,7 +1823,7 @@
         <v>14</v>
       </c>
       <c r="AA4">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AB4">
         <v>12.5</v>
@@ -1844,7 +1844,7 @@
         <v>15</v>
       </c>
       <c r="AH4">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AI4">
         <v>44</v>
@@ -1868,7 +1868,7 @@
         <v>23</v>
       </c>
       <c r="AP4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4">
         <v>8.199999999999999</v>
@@ -1889,10 +1889,10 @@
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AX4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY4">
         <v>13.5</v>
@@ -1904,7 +1904,7 @@
         <v>38</v>
       </c>
       <c r="BB4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC4">
         <v>40</v>
@@ -1943,7 +1943,7 @@
         <v>6.8</v>
       </c>
       <c r="BO4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP4">
         <v>32</v>
@@ -2002,22 +2002,22 @@
         <v>175</v>
       </c>
       <c r="F5">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G5">
         <v>1.56</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2044,10 +2044,10 @@
         <v>3.85</v>
       </c>
       <c r="T5">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="V5">
         <v>1.12</v>
@@ -2071,7 +2071,7 @@
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD5">
         <v>38</v>
@@ -2095,7 +2095,7 @@
         <v>15</v>
       </c>
       <c r="AK5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL5">
         <v>60</v>
@@ -2104,7 +2104,7 @@
         <v>240</v>
       </c>
       <c r="AN5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO5">
         <v>290</v>
@@ -2116,13 +2116,13 @@
         <v>15.5</v>
       </c>
       <c r="AR5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS5">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU5">
         <v>8.6</v>
@@ -2131,7 +2131,7 @@
         <v>22</v>
       </c>
       <c r="AW5">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX5">
         <v>7</v>
@@ -2140,10 +2140,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA5">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB5">
         <v>10.5</v>
@@ -2155,13 +2155,13 @@
         <v>34</v>
       </c>
       <c r="BE5">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF5">
         <v>9.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH5">
         <v>3.35</v>
@@ -2244,76 +2244,76 @@
         <v>176</v>
       </c>
       <c r="F6">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G6">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L6">
         <v>1.27</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O6">
         <v>1.19</v>
       </c>
       <c r="P6">
+        <v>2.46</v>
+      </c>
+      <c r="Q6">
+        <v>1.57</v>
+      </c>
+      <c r="R6">
+        <v>1.6</v>
+      </c>
+      <c r="S6">
         <v>2.44</v>
       </c>
-      <c r="Q6">
-        <v>1.56</v>
-      </c>
-      <c r="R6">
-        <v>1.58</v>
-      </c>
-      <c r="S6">
-        <v>2.4</v>
-      </c>
       <c r="T6">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W6">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X6">
         <v>30</v>
       </c>
       <c r="Y6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z6">
         <v>42</v>
       </c>
       <c r="AA6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB6">
         <v>16</v>
       </c>
       <c r="AC6">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
         <v>20</v>
@@ -2322,13 +2322,13 @@
         <v>55</v>
       </c>
       <c r="AF6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI6">
         <v>55</v>
@@ -2343,7 +2343,7 @@
         <v>34</v>
       </c>
       <c r="AM6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN6">
         <v>10.5</v>
@@ -2358,13 +2358,13 @@
         <v>17.5</v>
       </c>
       <c r="AR6">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AS6">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AT6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU6">
         <v>8.6</v>
@@ -2376,10 +2376,10 @@
         <v>34</v>
       </c>
       <c r="AX6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
         <v>13.5</v>
@@ -2391,19 +2391,19 @@
         <v>18.5</v>
       </c>
       <c r="BC6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD6">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE6">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BF6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG6">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH6">
         <v>4.5</v>
@@ -2421,7 +2421,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN6">
         <v>5.2</v>
@@ -2433,10 +2433,10 @@
         <v>13</v>
       </c>
       <c r="BQ6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS6">
         <v>7</v>
@@ -2457,7 +2457,7 @@
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ6">
         <v>16</v>
@@ -2728,19 +2728,19 @@
         <v>178</v>
       </c>
       <c r="F8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G8">
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2985,7 +2985,7 @@
         <v>3.5</v>
       </c>
       <c r="K9">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L9">
         <v>1.45</v>
@@ -3039,7 +3039,7 @@
         <v>7</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9">
         <v>29</v>
@@ -3084,10 +3084,10 @@
         <v>14</v>
       </c>
       <c r="AR9">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AS9">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT9">
         <v>5.9</v>
@@ -3099,7 +3099,7 @@
         <v>20</v>
       </c>
       <c r="AW9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX9">
         <v>8</v>
@@ -3111,7 +3111,7 @@
         <v>21</v>
       </c>
       <c r="BA9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BB9">
         <v>15</v>
@@ -3120,16 +3120,16 @@
         <v>18</v>
       </c>
       <c r="BD9">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE9">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF9">
         <v>11</v>
       </c>
       <c r="BG9">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3159,10 +3159,10 @@
         <v>17</v>
       </c>
       <c r="BQ9">
-        <v>8.800000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="BR9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS9">
         <v>1.75</v>
@@ -3171,13 +3171,13 @@
         <v>13</v>
       </c>
       <c r="BU9">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BX9">
         <v>1000</v>
@@ -3248,16 +3248,16 @@
         <v>1.67</v>
       </c>
       <c r="R10">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S10">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T10">
         <v>1.69</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V10">
         <v>1.2</v>
@@ -3469,7 +3469,7 @@
         <v>3</v>
       </c>
       <c r="K11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3490,16 +3490,16 @@
         <v>2.32</v>
       </c>
       <c r="R11">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S11">
         <v>4.1</v>
       </c>
       <c r="T11">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="V11">
         <v>1.61</v>
@@ -3699,16 +3699,16 @@
         <v>2</v>
       </c>
       <c r="G12">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="H12">
+        <v>2.68</v>
+      </c>
+      <c r="I12">
+        <v>3.9</v>
+      </c>
+      <c r="J12">
         <v>3.05</v>
-      </c>
-      <c r="I12">
-        <v>3.6</v>
-      </c>
-      <c r="J12">
-        <v>3.55</v>
       </c>
       <c r="K12">
         <v>4.8</v>
@@ -3720,22 +3720,22 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>2.44</v>
+        <v>2.06</v>
       </c>
       <c r="O12">
         <v>1.14</v>
       </c>
       <c r="P12">
-        <v>2.44</v>
+        <v>2.04</v>
       </c>
       <c r="Q12">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="R12">
-        <v>1.59</v>
+        <v>1.18</v>
       </c>
       <c r="S12">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3744,10 +3744,10 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W12">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3974,13 +3974,13 @@
         <v>1.63</v>
       </c>
       <c r="R13">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S13">
         <v>2.54</v>
       </c>
       <c r="T13">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="U13">
         <v>2.44</v>
@@ -4189,7 +4189,7 @@
         <v>2.46</v>
       </c>
       <c r="I14">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J14">
         <v>3.3</v>
@@ -4198,7 +4198,7 @@
         <v>3.6</v>
       </c>
       <c r="L14">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M14">
         <v>1.08</v>
@@ -4219,7 +4219,7 @@
         <v>1.32</v>
       </c>
       <c r="S14">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="T14">
         <v>1.78</v>
@@ -4228,7 +4228,7 @@
         <v>2.08</v>
       </c>
       <c r="V14">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W14">
         <v>1.44</v>
@@ -4288,7 +4288,7 @@
         <v>32</v>
       </c>
       <c r="AP14">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AQ14">
         <v>9</v>
@@ -4303,13 +4303,13 @@
         <v>10</v>
       </c>
       <c r="AU14">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV14">
         <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX14">
         <v>18</v>
@@ -4333,13 +4333,13 @@
         <v>29</v>
       </c>
       <c r="BE14">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH14">
         <v>3.3</v>
@@ -4425,13 +4425,13 @@
         <v>1.71</v>
       </c>
       <c r="G15">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="H15">
         <v>5</v>
       </c>
       <c r="I15">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J15">
         <v>3.85</v>
@@ -4458,49 +4458,49 @@
         <v>1.83</v>
       </c>
       <c r="R15">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S15">
         <v>3.1</v>
       </c>
       <c r="T15">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U15">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V15">
         <v>1.2</v>
       </c>
       <c r="W15">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X15">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z15">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA15">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AB15">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG15">
         <v>11.5</v>
@@ -4512,22 +4512,22 @@
         <v>80</v>
       </c>
       <c r="AJ15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK15">
         <v>21</v>
       </c>
       <c r="AL15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM15">
         <v>120</v>
       </c>
       <c r="AN15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO15">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP15">
         <v>12.5</v>
@@ -4536,34 +4536,34 @@
         <v>14.5</v>
       </c>
       <c r="AR15">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS15">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT15">
         <v>7</v>
       </c>
       <c r="AU15">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AV15">
         <v>15.5</v>
       </c>
       <c r="AW15">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="AX15">
         <v>8.4</v>
       </c>
       <c r="AY15">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AZ15">
         <v>15</v>
       </c>
       <c r="BA15">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BB15">
         <v>14</v>
@@ -4572,76 +4572,76 @@
         <v>14</v>
       </c>
       <c r="BD15">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE15">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF15">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG15">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH15">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>222</v>
@@ -4664,7 +4664,7 @@
         <v>186</v>
       </c>
       <c r="F16">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G16">
         <v>3.35</v>
@@ -4673,7 +4673,7 @@
         <v>2.4</v>
       </c>
       <c r="I16">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J16">
         <v>3.25</v>
@@ -4703,7 +4703,7 @@
         <v>1.25</v>
       </c>
       <c r="S16">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T16">
         <v>1.11</v>
@@ -4712,7 +4712,7 @@
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W16">
         <v>1.44</v>
@@ -4921,7 +4921,7 @@
         <v>3.8</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -5107,7 +5107,7 @@
         <v>6.6</v>
       </c>
       <c r="BU17">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BV17">
         <v>18.5</v>
@@ -5313,7 +5313,7 @@
         <v>5.7</v>
       </c>
       <c r="BI18">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ18">
         <v>12</v>
@@ -5635,16 +5635,16 @@
         <v>2.36</v>
       </c>
       <c r="G20">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="H20">
         <v>2.78</v>
       </c>
       <c r="I20">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="J20">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="K20">
         <v>4.2</v>
@@ -5680,10 +5680,10 @@
         <v>2.38</v>
       </c>
       <c r="V20">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="X20">
         <v>22</v>
@@ -5794,64 +5794,64 @@
         <v>16.5</v>
       </c>
       <c r="BH20">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BP20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
         <v>222</v>
@@ -5874,7 +5874,7 @@
         <v>191</v>
       </c>
       <c r="F21">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G21">
         <v>2.32</v>
@@ -5883,7 +5883,7 @@
         <v>3.2</v>
       </c>
       <c r="I21">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J21">
         <v>3.75</v>
@@ -5898,7 +5898,7 @@
         <v>1.04</v>
       </c>
       <c r="N21">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O21">
         <v>1.2</v>
@@ -5913,16 +5913,16 @@
         <v>1.37</v>
       </c>
       <c r="S21">
-        <v>2.26</v>
+        <v>1.7</v>
       </c>
       <c r="T21">
         <v>1.45</v>
       </c>
       <c r="U21">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
         <v>1.75</v>
@@ -5943,7 +5943,7 @@
         <v>18.5</v>
       </c>
       <c r="AC21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD21">
         <v>21</v>
@@ -5982,16 +5982,16 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AQ21">
         <v>10</v>
       </c>
       <c r="AR21">
-        <v>15.5</v>
+        <v>1.87</v>
       </c>
       <c r="AS21">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AT21">
         <v>8</v>
@@ -6003,37 +6003,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW21">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AX21">
         <v>9.6</v>
       </c>
       <c r="AY21">
-        <v>7</v>
+        <v>1.76</v>
       </c>
       <c r="AZ21">
-        <v>9.6</v>
+        <v>1.81</v>
       </c>
       <c r="BA21">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BB21">
         <v>16.5</v>
       </c>
       <c r="BC21">
-        <v>13</v>
+        <v>1.85</v>
       </c>
       <c r="BD21">
         <v>18.5</v>
       </c>
       <c r="BE21">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BF21">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BG21">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BH21">
         <v>5.5</v>
@@ -6116,19 +6116,19 @@
         <v>192</v>
       </c>
       <c r="F22">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G22">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="H22">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I22">
         <v>6.2</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K22">
         <v>4.7</v>
@@ -6140,34 +6140,34 @@
         <v>1.04</v>
       </c>
       <c r="N22">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
         <v>1.21</v>
       </c>
       <c r="P22">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q22">
         <v>1.69</v>
       </c>
       <c r="R22">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="S22">
-        <v>2.46</v>
+        <v>1.69</v>
       </c>
       <c r="T22">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U22">
         <v>2.16</v>
       </c>
       <c r="V22">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W22">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6842,19 +6842,19 @@
         <v>195</v>
       </c>
       <c r="F25">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="G25">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="H25">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="I25">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="J25">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K25">
         <v>3.9</v>
@@ -6866,22 +6866,22 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>3.25</v>
+        <v>1.26</v>
       </c>
       <c r="O25">
         <v>1.01</v>
       </c>
       <c r="P25">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="Q25">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="R25">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S25">
-        <v>2.36</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
         <v>1.11</v>
@@ -6890,10 +6890,10 @@
         <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -7004,64 +7004,64 @@
         <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="s">
         <v>222</v>
@@ -7189,7 +7189,7 @@
         <v>26</v>
       </c>
       <c r="AO26">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP26">
         <v>16.5</v>
@@ -7228,16 +7228,16 @@
         <v>21</v>
       </c>
       <c r="BB26">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC26">
         <v>4.7</v>
       </c>
       <c r="BD26">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE26">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF26">
         <v>15</v>
@@ -7335,7 +7335,7 @@
         <v>2.26</v>
       </c>
       <c r="I27">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J27">
         <v>3.1</v>
@@ -7350,7 +7350,7 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="O27">
         <v>1.26</v>
@@ -7374,13 +7374,13 @@
         <v>1.96</v>
       </c>
       <c r="V27">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W27">
         <v>1.39</v>
       </c>
       <c r="X27">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
         <v>1000</v>
@@ -7434,58 +7434,58 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>11</v>
+        <v>1.16</v>
       </c>
       <c r="AQ27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AR27">
+        <v>1.09</v>
+      </c>
+      <c r="AS27">
+        <v>1.12</v>
+      </c>
+      <c r="AT27">
         <v>1.16</v>
       </c>
-      <c r="AS27">
-        <v>1.2</v>
-      </c>
-      <c r="AT27">
-        <v>1.23</v>
-      </c>
       <c r="AU27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AV27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AW27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AX27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AY27">
         <v>10</v>
       </c>
       <c r="AZ27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="BA27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="BB27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="BC27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="BD27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="BE27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="BF27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="BG27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="BH27">
         <v>4.1</v>
@@ -7739,16 +7739,16 @@
         <v>19</v>
       </c>
       <c r="BK28">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BN28">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO28">
         <v>2.68</v>
@@ -7763,31 +7763,31 @@
         <v>34</v>
       </c>
       <c r="BS28">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BT28">
         <v>25</v>
       </c>
       <c r="BU28">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BZ28">
         <v>13.5</v>
       </c>
       <c r="CA28">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CB28" t="s">
         <v>222</v>
@@ -8235,7 +8235,7 @@
         <v>5.9</v>
       </c>
       <c r="BO30">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BP30">
         <v>15.5</v>
@@ -8327,10 +8327,10 @@
         <v>2.54</v>
       </c>
       <c r="Q31">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R31">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S31">
         <v>1.89</v>
@@ -8387,7 +8387,7 @@
         <v>29</v>
       </c>
       <c r="AK31">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL31">
         <v>36</v>
@@ -8405,7 +8405,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ31">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR31">
         <v>2.24</v>
@@ -8441,7 +8441,7 @@
         <v>13</v>
       </c>
       <c r="BC31">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BD31">
         <v>16.5</v>
@@ -8450,7 +8450,7 @@
         <v>2.24</v>
       </c>
       <c r="BF31">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BG31">
         <v>2.24</v>
@@ -8536,16 +8536,16 @@
         <v>202</v>
       </c>
       <c r="F32">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G32">
         <v>2.78</v>
       </c>
       <c r="H32">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I32">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J32">
         <v>4</v>
@@ -8560,31 +8560,31 @@
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="O32">
         <v>1.14</v>
       </c>
       <c r="P32">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q32">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R32">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S32">
         <v>2.16</v>
       </c>
       <c r="T32">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="U32">
         <v>2.46</v>
       </c>
       <c r="V32">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W32">
         <v>1.56</v>
@@ -8719,19 +8719,19 @@
         <v>8.6</v>
       </c>
       <c r="BO32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP32">
         <v>23</v>
       </c>
       <c r="BQ32">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BR32">
         <v>30</v>
       </c>
       <c r="BS32">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BT32">
         <v>8.6</v>
@@ -8740,7 +8740,7 @@
         <v>4.3</v>
       </c>
       <c r="BV32">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW32">
         <v>2.88</v>
@@ -8749,7 +8749,7 @@
         <v>30</v>
       </c>
       <c r="BY32">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BZ32">
         <v>0</v>
@@ -8787,10 +8787,10 @@
         <v>2.82</v>
       </c>
       <c r="I33">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J33">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K33">
         <v>4.6</v>
@@ -9023,19 +9023,19 @@
         <v>1.26</v>
       </c>
       <c r="G34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H34">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I34">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J34">
         <v>6.6</v>
       </c>
       <c r="K34">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -9062,7 +9062,7 @@
         <v>0</v>
       </c>
       <c r="T34">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U34">
         <v>1.86</v>
@@ -9083,7 +9083,7 @@
         <v>160</v>
       </c>
       <c r="AA34">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="AB34">
         <v>14</v>
@@ -9110,7 +9110,7 @@
         <v>160</v>
       </c>
       <c r="AJ34">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK34">
         <v>15</v>
@@ -9122,22 +9122,22 @@
         <v>170</v>
       </c>
       <c r="AN34">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO34">
         <v>250</v>
       </c>
       <c r="AP34">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ34">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AR34">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AS34">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT34">
         <v>10</v>
@@ -9146,10 +9146,10 @@
         <v>14</v>
       </c>
       <c r="AV34">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AW34">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX34">
         <v>8</v>
@@ -9158,10 +9158,10 @@
         <v>10</v>
       </c>
       <c r="AZ34">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BA34">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB34">
         <v>8.6</v>
@@ -9170,16 +9170,16 @@
         <v>10</v>
       </c>
       <c r="BD34">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE34">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF34">
         <v>3</v>
       </c>
       <c r="BG34">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH34">
         <v>0</v>
@@ -9304,10 +9304,10 @@
         <v>3.55</v>
       </c>
       <c r="T35">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U35">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V35">
         <v>1.21</v>
@@ -9516,7 +9516,7 @@
         <v>2.22</v>
       </c>
       <c r="J36">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K36">
         <v>4.3</v>
@@ -9528,7 +9528,7 @@
         <v>1.04</v>
       </c>
       <c r="N36">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O36">
         <v>1.19</v>
@@ -9549,7 +9549,7 @@
         <v>1.48</v>
       </c>
       <c r="U36">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V36">
         <v>1.81</v>
@@ -9666,22 +9666,22 @@
         <v>8</v>
       </c>
       <c r="BH36">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BI36">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BJ36">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK36">
-        <v>5.4</v>
+        <v>2.38</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BN36">
         <v>10</v>
@@ -9690,34 +9690,34 @@
         <v>4.6</v>
       </c>
       <c r="BP36">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ36">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BR36">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BS36">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BT36">
         <v>7.4</v>
       </c>
       <c r="BU36">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BV36">
         <v>20</v>
       </c>
       <c r="BW36">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BX36">
         <v>34</v>
       </c>
       <c r="BY36">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BZ36">
         <v>0</v>
@@ -9764,7 +9764,7 @@
         <v>3.5</v>
       </c>
       <c r="L37">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M37">
         <v>1.1</v>
@@ -9800,16 +9800,16 @@
         <v>1.79</v>
       </c>
       <c r="X37">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y37">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z37">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA37">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB37">
         <v>9.4</v>
@@ -9818,10 +9818,10 @@
         <v>7.8</v>
       </c>
       <c r="AD37">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE37">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF37">
         <v>15</v>
@@ -9887,7 +9887,7 @@
         <v>17.5</v>
       </c>
       <c r="BA37">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB37">
         <v>21</v>
@@ -9896,16 +9896,16 @@
         <v>20</v>
       </c>
       <c r="BD37">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE37">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF37">
         <v>17</v>
       </c>
       <c r="BG37">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH37">
         <v>3.05</v>
@@ -9997,7 +9997,7 @@
         <v>2.12</v>
       </c>
       <c r="I38">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J38">
         <v>3.1</v>
@@ -10027,7 +10027,7 @@
         <v>1.18</v>
       </c>
       <c r="S38">
-        <v>1.05</v>
+        <v>2.58</v>
       </c>
       <c r="T38">
         <v>1.76</v>
@@ -10036,7 +10036,7 @@
         <v>1.75</v>
       </c>
       <c r="V38">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W38">
         <v>1.31</v>
@@ -10230,19 +10230,19 @@
         <v>209</v>
       </c>
       <c r="F39">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G39">
-        <v>990</v>
+        <v>2.6</v>
       </c>
       <c r="H39">
         <v>1.04</v>
       </c>
       <c r="I39">
-        <v>990</v>
+        <v>3.7</v>
       </c>
       <c r="J39">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="K39">
         <v>950</v>
@@ -10254,22 +10254,22 @@
         <v>1.01</v>
       </c>
       <c r="N39">
-        <v>1.24</v>
+        <v>2.48</v>
       </c>
       <c r="O39">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P39">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q39">
-        <v>1.21</v>
+        <v>1.64</v>
       </c>
       <c r="R39">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>2.42</v>
       </c>
       <c r="T39">
         <v>1.11</v>
@@ -10278,10 +10278,10 @@
         <v>1.11</v>
       </c>
       <c r="V39">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W39">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -10505,7 +10505,7 @@
         <v>1.74</v>
       </c>
       <c r="Q40">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="R40">
         <v>1.25</v>
@@ -10723,7 +10723,7 @@
         <v>2.34</v>
       </c>
       <c r="I41">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J41">
         <v>3.55</v>
@@ -10747,7 +10747,7 @@
         <v>2.14</v>
       </c>
       <c r="Q41">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="R41">
         <v>1.45</v>
@@ -10762,7 +10762,7 @@
         <v>2.32</v>
       </c>
       <c r="V41">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W41">
         <v>1.44</v>
@@ -10822,10 +10822,10 @@
         <v>19</v>
       </c>
       <c r="AP41">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ41">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR41">
         <v>13.5</v>
@@ -10989,7 +10989,7 @@
         <v>2.54</v>
       </c>
       <c r="Q42">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="R42">
         <v>1.5</v>
@@ -11234,7 +11234,7 @@
         <v>1.51</v>
       </c>
       <c r="R43">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S43">
         <v>2.3</v>
@@ -11883,7 +11883,7 @@
         <v>8.6</v>
       </c>
       <c r="BU45">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV45">
         <v>30</v>
@@ -11972,7 +11972,7 @@
         <v>1.11</v>
       </c>
       <c r="V46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W46">
         <v>2.24</v>
@@ -12089,7 +12089,7 @@
         <v>4.7</v>
       </c>
       <c r="BI46">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ46">
         <v>13.5</v>
@@ -12202,16 +12202,16 @@
         <v>1.94</v>
       </c>
       <c r="R47">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="S47">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="T47">
         <v>1.11</v>
       </c>
       <c r="U47">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="V47">
         <v>1.39</v>
@@ -12417,7 +12417,7 @@
         <v>9.6</v>
       </c>
       <c r="I48">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="J48">
         <v>6.8</v>
@@ -12650,7 +12650,7 @@
         <v>219</v>
       </c>
       <c r="F49">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G49">
         <v>6.6</v>
@@ -12659,10 +12659,10 @@
         <v>1.55</v>
       </c>
       <c r="I49">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="J49">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K49">
         <v>5.1</v>
@@ -12683,7 +12683,7 @@
         <v>2.56</v>
       </c>
       <c r="Q49">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R49">
         <v>1.63</v>
@@ -12758,7 +12758,7 @@
         <v>6.4</v>
       </c>
       <c r="AP49">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ49">
         <v>10.5</v>
@@ -12794,22 +12794,22 @@
         <v>22</v>
       </c>
       <c r="BB49">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC49">
         <v>55</v>
       </c>
       <c r="BD49">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE49">
         <v>60</v>
       </c>
       <c r="BF49">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BG49">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH49">
         <v>4.7</v>
@@ -12934,7 +12934,7 @@
         <v>3.7</v>
       </c>
       <c r="T50">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U50">
         <v>1.92</v>
@@ -12970,7 +12970,7 @@
         <v>22</v>
       </c>
       <c r="AF50">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG50">
         <v>21</v>
@@ -13033,7 +13033,7 @@
         <v>17</v>
       </c>
       <c r="BA50">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB50">
         <v>7.8</v>
@@ -13042,13 +13042,13 @@
         <v>7.4</v>
       </c>
       <c r="BD50">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE50">
         <v>7.8</v>
       </c>
       <c r="BF50">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG50">
         <v>10.5</v>
@@ -13143,10 +13143,10 @@
         <v>3.85</v>
       </c>
       <c r="I51">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J51">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="K51">
         <v>4.6</v>
@@ -13173,7 +13173,7 @@
         <v>1.24</v>
       </c>
       <c r="S51">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T51">
         <v>1.11</v>
@@ -13182,7 +13182,7 @@
         <v>1.11</v>
       </c>
       <c r="V51">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W51">
         <v>1.83</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="231">
   <si>
     <t>League</t>
   </si>
@@ -319,18 +319,24 @@
     <t>Hungarian NB I</t>
   </si>
   <si>
+    <t>Irish Division 1</t>
+  </si>
+  <si>
     <t>Irish Premier Division</t>
   </si>
   <si>
-    <t>Irish Division 1</t>
-  </si>
-  <si>
     <t>Scottish Premiership</t>
   </si>
   <si>
     <t>Peruvian Primera Division</t>
   </si>
   <si>
+    <t>Uruguayan Primera Division</t>
+  </si>
+  <si>
+    <t>US MLS</t>
+  </si>
+  <si>
     <t>2026-07-31</t>
   </si>
   <si>
@@ -382,6 +388,12 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>23:30:00</t>
+  </si>
+  <si>
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
@@ -448,12 +460,12 @@
     <t>Valerenga</t>
   </si>
   <si>
+    <t>Roskilde</t>
+  </si>
+  <si>
     <t>Nykobing FC</t>
   </si>
   <si>
-    <t>Roskilde</t>
-  </si>
-  <si>
     <t>AB</t>
   </si>
   <si>
@@ -484,40 +496,43 @@
     <t>Puskas Akademia</t>
   </si>
   <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
     <t>Kriens</t>
   </si>
   <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
     <t>Otelul Galati</t>
   </si>
   <si>
     <t>Lechia Gdansk</t>
   </si>
   <si>
+    <t>LKP Motor Lublin</t>
+  </si>
+  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
-    <t>LKP Motor Lublin</t>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
   </si>
   <si>
     <t>Dundalk</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
+    <t>Drogheda</t>
   </si>
   <si>
     <t>Bodo Glimt</t>
@@ -526,12 +541,15 @@
     <t>Dundee Utd</t>
   </si>
   <si>
-    <t>Drogheda</t>
-  </si>
-  <si>
     <t>CD Los Chankas</t>
   </si>
   <si>
+    <t>Torque</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
@@ -598,12 +616,12 @@
     <t>Ham-Kam</t>
   </si>
   <si>
+    <t>Naestved</t>
+  </si>
+  <si>
     <t>Fremad Amager</t>
   </si>
   <si>
-    <t>Naestved</t>
-  </si>
-  <si>
     <t>Fredericia</t>
   </si>
   <si>
@@ -634,40 +652,43 @@
     <t>Kisvarda</t>
   </si>
   <si>
+    <t>Arda</t>
+  </si>
+  <si>
     <t>Winterthur</t>
   </si>
   <si>
-    <t>Arda</t>
-  </si>
-  <si>
     <t>Dinamo Bucharest</t>
   </si>
   <si>
     <t>Warta Poznan</t>
   </si>
   <si>
+    <t>Jagiellonia Bialystock</t>
+  </si>
+  <si>
     <t>St Polten</t>
   </si>
   <si>
-    <t>Jagiellonia Bialystock</t>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Wexford F.C</t>
+  </si>
+  <si>
+    <t>Kerry FC</t>
+  </si>
+  <si>
+    <t>Longford</t>
   </si>
   <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Wexford F.C</t>
-  </si>
-  <si>
-    <t>Kerry FC</t>
-  </si>
-  <si>
-    <t>Longford</t>
+    <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>Lillestrom</t>
@@ -676,13 +697,16 @@
     <t>Rangers</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
     <t>Comerciantes Unidos</t>
   </si>
   <si>
-    <t>2026-07-29 22:33:30</t>
+    <t>Wanderers (Uru)</t>
+  </si>
+  <si>
+    <t>Toronto FC</t>
+  </si>
+  <si>
+    <t>2026-07-30 00:42:57</t>
   </si>
 </sst>
 </file>
@@ -1014,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB51"/>
+  <dimension ref="A1:CB53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1264,16 +1288,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F2">
         <v>3.35</v>
@@ -1291,7 +1315,7 @@
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
         <v>1.61</v>
@@ -1303,7 +1327,7 @@
         <v>2.66</v>
       </c>
       <c r="O2">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P2">
         <v>1.54</v>
@@ -1312,7 +1336,7 @@
         <v>2.72</v>
       </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S2">
         <v>5.7</v>
@@ -1321,7 +1345,7 @@
         <v>2.18</v>
       </c>
       <c r="U2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V2">
         <v>1.6</v>
@@ -1366,7 +1390,7 @@
         <v>70</v>
       </c>
       <c r="AJ2">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
         <v>55</v>
@@ -1381,7 +1405,7 @@
         <v>75</v>
       </c>
       <c r="AO2">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AP2">
         <v>7.6</v>
@@ -1432,7 +1456,7 @@
         <v>46</v>
       </c>
       <c r="BF2">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BG2">
         <v>36</v>
@@ -1498,7 +1522,7 @@
         <v>12</v>
       </c>
       <c r="CB2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1506,16 +1530,16 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F3">
         <v>1.7</v>
@@ -1542,7 +1566,7 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O3">
         <v>1.47</v>
@@ -1551,7 +1575,7 @@
         <v>1.62</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R3">
         <v>1.22</v>
@@ -1560,7 +1584,7 @@
         <v>4.7</v>
       </c>
       <c r="T3">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U3">
         <v>1.7</v>
@@ -1575,7 +1599,7 @@
         <v>12.5</v>
       </c>
       <c r="Y3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z3">
         <v>65</v>
@@ -1584,13 +1608,13 @@
         <v>270</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE3">
         <v>160</v>
@@ -1608,10 +1632,10 @@
         <v>160</v>
       </c>
       <c r="AJ3">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AK3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL3">
         <v>65</v>
@@ -1620,7 +1644,7 @@
         <v>260</v>
       </c>
       <c r="AN3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO3">
         <v>270</v>
@@ -1632,10 +1656,10 @@
         <v>12</v>
       </c>
       <c r="AR3">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AS3">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT3">
         <v>5.7</v>
@@ -1647,7 +1671,7 @@
         <v>19.5</v>
       </c>
       <c r="AW3">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX3">
         <v>7.6</v>
@@ -1656,10 +1680,10 @@
         <v>9</v>
       </c>
       <c r="AZ3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA3">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB3">
         <v>15</v>
@@ -1668,16 +1692,16 @@
         <v>19</v>
       </c>
       <c r="BD3">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BE3">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF3">
         <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH3">
         <v>3.05</v>
@@ -1740,7 +1764,7 @@
         <v>7.8</v>
       </c>
       <c r="CB3" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1748,22 +1772,22 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F4">
         <v>3.55</v>
       </c>
       <c r="G4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H4">
         <v>2.3</v>
@@ -1772,40 +1796,40 @@
         <v>2.34</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
         <v>3.45</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
         <v>1.3</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V4">
         <v>1.74</v>
@@ -1817,25 +1841,25 @@
         <v>12</v>
       </c>
       <c r="Y4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z4">
         <v>14</v>
       </c>
       <c r="AA4">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AB4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
         <v>11.5</v>
       </c>
       <c r="AE4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF4">
         <v>24</v>
@@ -1844,10 +1868,10 @@
         <v>15</v>
       </c>
       <c r="AH4">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AI4">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="AJ4">
         <v>70</v>
@@ -1901,7 +1925,7 @@
         <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB4">
         <v>32</v>
@@ -1916,49 +1940,49 @@
         <v>40</v>
       </c>
       <c r="BF4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BG4">
         <v>20</v>
       </c>
       <c r="BH4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI4">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ4">
         <v>10</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BN4">
         <v>6.8</v>
       </c>
       <c r="BO4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP4">
         <v>32</v>
       </c>
       <c r="BQ4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU4">
         <v>4</v>
@@ -1967,22 +1991,22 @@
         <v>18</v>
       </c>
       <c r="BW4">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1990,16 +2014,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F5">
         <v>1.5</v>
@@ -2011,7 +2035,7 @@
         <v>7.8</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J5">
         <v>4.2</v>
@@ -2062,7 +2086,7 @@
         <v>23</v>
       </c>
       <c r="Z5">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AA5">
         <v>350</v>
@@ -2074,13 +2098,13 @@
         <v>11</v>
       </c>
       <c r="AD5">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AE5">
         <v>180</v>
       </c>
       <c r="AF5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
@@ -2116,10 +2140,10 @@
         <v>15.5</v>
       </c>
       <c r="AR5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS5">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT5">
         <v>6</v>
@@ -2131,7 +2155,7 @@
         <v>22</v>
       </c>
       <c r="AW5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX5">
         <v>7</v>
@@ -2140,10 +2164,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ5">
-        <v>5.6</v>
+        <v>24</v>
       </c>
       <c r="BA5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB5">
         <v>10.5</v>
@@ -2155,13 +2179,13 @@
         <v>34</v>
       </c>
       <c r="BE5">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF5">
         <v>9.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH5">
         <v>3.35</v>
@@ -2224,7 +2248,7 @@
         <v>7.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2232,19 +2256,19 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F6">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G6">
         <v>1.98</v>
@@ -2259,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L6">
         <v>1.27</v>
@@ -2271,22 +2295,22 @@
         <v>5.3</v>
       </c>
       <c r="O6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P6">
         <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R6">
         <v>1.6</v>
       </c>
       <c r="S6">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T6">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U6">
         <v>2.48</v>
@@ -2304,13 +2328,13 @@
         <v>22</v>
       </c>
       <c r="Z6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA6">
         <v>90</v>
       </c>
       <c r="AB6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AC6">
         <v>10.5</v>
@@ -2355,13 +2379,13 @@
         <v>20</v>
       </c>
       <c r="AQ6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS6">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT6">
         <v>11.5</v>
@@ -2394,16 +2418,16 @@
         <v>15.5</v>
       </c>
       <c r="BD6">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE6">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF6">
         <v>7.6</v>
       </c>
       <c r="BG6">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH6">
         <v>4.5</v>
@@ -2415,7 +2439,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK6">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2466,7 +2490,7 @@
         <v>6.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2474,16 +2498,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F7">
         <v>2.12</v>
@@ -2708,7 +2732,7 @@
         <v>2.68</v>
       </c>
       <c r="CB7" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2716,31 +2740,31 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F8">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G8">
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2764,7 +2788,7 @@
         <v>1.02</v>
       </c>
       <c r="R8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S8">
         <v>1.4</v>
@@ -2950,7 +2974,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2958,16 +2982,16 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="F9">
         <v>1.71</v>
@@ -2985,7 +3009,7 @@
         <v>3.5</v>
       </c>
       <c r="K9">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L9">
         <v>1.45</v>
@@ -3021,7 +3045,7 @@
         <v>1.18</v>
       </c>
       <c r="W9">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X9">
         <v>13</v>
@@ -3141,7 +3165,7 @@
         <v>16</v>
       </c>
       <c r="BK9">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -3162,16 +3186,16 @@
         <v>1.65</v>
       </c>
       <c r="BR9">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BS9">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BT9">
         <v>13</v>
       </c>
       <c r="BU9">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV9">
         <v>1000</v>
@@ -3186,13 +3210,13 @@
         <v>1.79</v>
       </c>
       <c r="BZ9">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CB9" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3200,22 +3224,22 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F10">
         <v>1.71</v>
       </c>
       <c r="G10">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H10">
         <v>4.7</v>
@@ -3299,7 +3323,7 @@
         <v>21</v>
       </c>
       <c r="AI10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ10">
         <v>22</v>
@@ -3362,7 +3386,7 @@
         <v>13</v>
       </c>
       <c r="BD10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE10">
         <v>4.8</v>
@@ -3434,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3442,16 +3466,16 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E11" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F11">
         <v>3.5</v>
@@ -3460,7 +3484,7 @@
         <v>3.7</v>
       </c>
       <c r="H11">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I11">
         <v>2.64</v>
@@ -3469,37 +3493,37 @@
         <v>3</v>
       </c>
       <c r="K11">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N11">
         <v>2.82</v>
       </c>
       <c r="O11">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="P11">
         <v>1.61</v>
       </c>
       <c r="Q11">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R11">
         <v>1.22</v>
       </c>
       <c r="S11">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T11">
         <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
         <v>1.61</v>
@@ -3508,7 +3532,7 @@
         <v>1.37</v>
       </c>
       <c r="X11">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
         <v>9.800000000000001</v>
@@ -3568,79 +3592,79 @@
         <v>7.2</v>
       </c>
       <c r="AR11">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AS11">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AT11">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AU11">
         <v>6</v>
       </c>
       <c r="AV11">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AW11">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AX11">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AY11">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AZ11">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="BA11">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="BB11">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="BC11">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="BD11">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="BE11">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="BF11">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="BG11">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="BH11">
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BJ11">
         <v>14.5</v>
       </c>
       <c r="BK11">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BN11">
         <v>8.6</v>
       </c>
       <c r="BO11">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP11">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BQ11">
         <v>1.71</v>
@@ -3655,19 +3679,19 @@
         <v>7</v>
       </c>
       <c r="BU11">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BV11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW11">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3676,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3684,31 +3708,31 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="H12">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="I12">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="J12">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="K12">
         <v>4.8</v>
@@ -3720,22 +3744,22 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
       <c r="O12">
         <v>1.14</v>
       </c>
       <c r="P12">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="Q12">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="S12">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3744,10 +3768,10 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3918,7 +3942,7 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3926,16 +3950,16 @@
         <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E13" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F13">
         <v>2.5</v>
@@ -3995,7 +4019,7 @@
         <v>27</v>
       </c>
       <c r="Y13">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z13">
         <v>26</v>
@@ -4010,7 +4034,7 @@
         <v>11.5</v>
       </c>
       <c r="AD13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE13">
         <v>34</v>
@@ -4043,7 +4067,7 @@
         <v>19</v>
       </c>
       <c r="AO13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP13">
         <v>16</v>
@@ -4055,7 +4079,7 @@
         <v>15.5</v>
       </c>
       <c r="AS13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AT13">
         <v>10.5</v>
@@ -4079,19 +4103,19 @@
         <v>11</v>
       </c>
       <c r="BA13">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BB13">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BC13">
         <v>18</v>
       </c>
       <c r="BD13">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF13">
         <v>11</v>
@@ -4160,7 +4184,7 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4168,16 +4192,16 @@
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F14">
         <v>2.92</v>
@@ -4198,7 +4222,7 @@
         <v>3.6</v>
       </c>
       <c r="L14">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M14">
         <v>1.08</v>
@@ -4219,7 +4243,7 @@
         <v>1.32</v>
       </c>
       <c r="S14">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T14">
         <v>1.78</v>
@@ -4288,7 +4312,7 @@
         <v>32</v>
       </c>
       <c r="AP14">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ14">
         <v>9</v>
@@ -4303,13 +4327,13 @@
         <v>10</v>
       </c>
       <c r="AU14">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV14">
         <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AX14">
         <v>18</v>
@@ -4324,7 +4348,7 @@
         <v>26</v>
       </c>
       <c r="BB14">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BC14">
         <v>22</v>
@@ -4333,13 +4357,13 @@
         <v>29</v>
       </c>
       <c r="BE14">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG14">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH14">
         <v>3.3</v>
@@ -4363,7 +4387,7 @@
         <v>6.2</v>
       </c>
       <c r="BO14">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BP14">
         <v>25</v>
@@ -4402,7 +4426,7 @@
         <v>10</v>
       </c>
       <c r="CB14" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4410,22 +4434,22 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F15">
         <v>1.71</v>
       </c>
       <c r="G15">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="H15">
         <v>5</v>
@@ -4464,16 +4488,16 @@
         <v>3.1</v>
       </c>
       <c r="T15">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U15">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V15">
         <v>1.2</v>
       </c>
       <c r="W15">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X15">
         <v>19.5</v>
@@ -4503,7 +4527,7 @@
         <v>13</v>
       </c>
       <c r="AG15">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH15">
         <v>23</v>
@@ -4533,118 +4557,118 @@
         <v>12.5</v>
       </c>
       <c r="AQ15">
-        <v>14.5</v>
+        <v>4.4</v>
       </c>
       <c r="AR15">
+        <v>5</v>
+      </c>
+      <c r="AS15">
+        <v>5.4</v>
+      </c>
+      <c r="AT15">
+        <v>7.8</v>
+      </c>
+      <c r="AU15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV15">
         <v>4.5</v>
       </c>
-      <c r="AS15">
-        <v>4.8</v>
-      </c>
-      <c r="AT15">
-        <v>7</v>
-      </c>
-      <c r="AU15">
-        <v>7.2</v>
-      </c>
-      <c r="AV15">
-        <v>15.5</v>
-      </c>
       <c r="AW15">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX15">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY15">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA15">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC15">
         <v>14</v>
       </c>
       <c r="BD15">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE15">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF15">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG15">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BH15">
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="CB15" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4652,19 +4676,19 @@
         <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F16">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="G16">
         <v>3.35</v>
@@ -4673,7 +4697,7 @@
         <v>2.4</v>
       </c>
       <c r="I16">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="J16">
         <v>3.25</v>
@@ -4694,16 +4718,16 @@
         <v>1.32</v>
       </c>
       <c r="P16">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="Q16">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="R16">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S16">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T16">
         <v>1.11</v>
@@ -4712,10 +4736,10 @@
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W16">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X16">
         <v>18.5</v>
@@ -4829,7 +4853,7 @@
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BJ16">
         <v>13.5</v>
@@ -4841,19 +4865,19 @@
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BN16">
         <v>8.800000000000001</v>
       </c>
       <c r="BO16">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP16">
         <v>36</v>
       </c>
       <c r="BQ16">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="BR16">
         <v>1000</v>
@@ -4865,10 +4889,10 @@
         <v>7.6</v>
       </c>
       <c r="BU16">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BV16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW16">
         <v>1.69</v>
@@ -4877,7 +4901,7 @@
         <v>48</v>
       </c>
       <c r="BY16">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BZ16">
         <v>44</v>
@@ -4886,7 +4910,7 @@
         <v>1.73</v>
       </c>
       <c r="CB16" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4894,16 +4918,16 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E17" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F17">
         <v>3.55</v>
@@ -4966,7 +4990,7 @@
         <v>1000</v>
       </c>
       <c r="Z17">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA17">
         <v>1000</v>
@@ -5023,49 +5047,49 @@
         <v>10.5</v>
       </c>
       <c r="AS17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AT17">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AU17">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AV17">
         <v>1.52</v>
       </c>
       <c r="AW17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AX17">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AY17">
         <v>1.41</v>
       </c>
       <c r="AZ17">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BA17">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BB17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BC17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BD17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BE17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BF17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BG17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BH17">
         <v>5.3</v>
@@ -5107,7 +5131,7 @@
         <v>6.6</v>
       </c>
       <c r="BU17">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BV17">
         <v>18.5</v>
@@ -5128,7 +5152,7 @@
         <v>2.86</v>
       </c>
       <c r="CB17" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5136,16 +5160,16 @@
         <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E18" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F18">
         <v>3.9</v>
@@ -5349,7 +5373,7 @@
         <v>6.4</v>
       </c>
       <c r="BU18">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BV18">
         <v>16</v>
@@ -5370,7 +5394,7 @@
         <v>9.6</v>
       </c>
       <c r="CB18" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5378,16 +5402,16 @@
         <v>92</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E19" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F19">
         <v>2.16</v>
@@ -5612,7 +5636,7 @@
         <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5620,37 +5644,37 @@
         <v>92</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E20" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F20">
         <v>2.36</v>
       </c>
       <c r="G20">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="H20">
         <v>2.78</v>
       </c>
       <c r="I20">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J20">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M20">
         <v>1.05</v>
@@ -5680,10 +5704,10 @@
         <v>2.38</v>
       </c>
       <c r="V20">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W20">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="X20">
         <v>22</v>
@@ -5728,7 +5752,7 @@
         <v>29</v>
       </c>
       <c r="AL20">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM20">
         <v>80</v>
@@ -5749,7 +5773,7 @@
         <v>16.5</v>
       </c>
       <c r="AS20">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT20">
         <v>10</v>
@@ -5761,7 +5785,7 @@
         <v>10</v>
       </c>
       <c r="AW20">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX20">
         <v>13.5</v>
@@ -5773,10 +5797,10 @@
         <v>12</v>
       </c>
       <c r="BA20">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB20">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC20">
         <v>18.5</v>
@@ -5785,7 +5809,7 @@
         <v>4.7</v>
       </c>
       <c r="BE20">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF20">
         <v>12</v>
@@ -5797,64 +5821,64 @@
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK20">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO20">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ20">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS20">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU20">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="CB20" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5862,16 +5886,16 @@
         <v>92</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E21" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F21">
         <v>2.14</v>
@@ -5898,7 +5922,7 @@
         <v>1.04</v>
       </c>
       <c r="N21">
-        <v>2.24</v>
+        <v>1.1</v>
       </c>
       <c r="O21">
         <v>1.2</v>
@@ -5910,7 +5934,7 @@
         <v>1.67</v>
       </c>
       <c r="R21">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S21">
         <v>1.7</v>
@@ -5919,7 +5943,7 @@
         <v>1.45</v>
       </c>
       <c r="U21">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V21">
         <v>1.36</v>
@@ -5943,7 +5967,7 @@
         <v>18.5</v>
       </c>
       <c r="AC21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD21">
         <v>21</v>
@@ -5982,16 +6006,16 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AQ21">
         <v>10</v>
       </c>
       <c r="AR21">
-        <v>1.87</v>
+        <v>15.5</v>
       </c>
       <c r="AS21">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AT21">
         <v>8</v>
@@ -6000,46 +6024,46 @@
         <v>5.8</v>
       </c>
       <c r="AV21">
-        <v>8.800000000000001</v>
+        <v>1.79</v>
       </c>
       <c r="AW21">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AX21">
         <v>9.6</v>
       </c>
       <c r="AY21">
-        <v>1.76</v>
+        <v>7</v>
       </c>
       <c r="AZ21">
-        <v>1.81</v>
+        <v>9.6</v>
       </c>
       <c r="BA21">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BB21">
         <v>16.5</v>
       </c>
       <c r="BC21">
-        <v>1.85</v>
+        <v>13</v>
       </c>
       <c r="BD21">
         <v>18.5</v>
       </c>
       <c r="BE21">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BF21">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BG21">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BH21">
         <v>5.5</v>
       </c>
       <c r="BI21">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="BJ21">
         <v>12.5</v>
@@ -6057,7 +6081,7 @@
         <v>7.6</v>
       </c>
       <c r="BO21">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP21">
         <v>21</v>
@@ -6075,7 +6099,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU21">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV21">
         <v>34</v>
@@ -6096,7 +6120,7 @@
         <v>2.64</v>
       </c>
       <c r="CB21" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6104,31 +6128,31 @@
         <v>93</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F22">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G22">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="H22">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I22">
         <v>6.2</v>
       </c>
       <c r="J22">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K22">
         <v>4.7</v>
@@ -6140,22 +6164,22 @@
         <v>1.04</v>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O22">
         <v>1.21</v>
       </c>
       <c r="P22">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q22">
         <v>1.69</v>
       </c>
       <c r="R22">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S22">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="T22">
         <v>1.72</v>
@@ -6167,7 +6191,7 @@
         <v>1.2</v>
       </c>
       <c r="W22">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6338,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6346,16 +6370,16 @@
         <v>94</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E23" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F23">
         <v>1.64</v>
@@ -6364,7 +6388,7 @@
         <v>1.65</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I23">
         <v>5.8</v>
@@ -6373,7 +6397,7 @@
         <v>4.6</v>
       </c>
       <c r="K23">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6382,7 +6406,7 @@
         <v>1.03</v>
       </c>
       <c r="N23">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O23">
         <v>1.16</v>
@@ -6394,16 +6418,16 @@
         <v>1.49</v>
       </c>
       <c r="R23">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S23">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T23">
         <v>1.58</v>
       </c>
       <c r="U23">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V23">
         <v>1.01</v>
@@ -6580,7 +6604,7 @@
         <v>1.04</v>
       </c>
       <c r="CB23" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6588,34 +6612,34 @@
         <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E24" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F24">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G24">
-        <v>990</v>
+        <v>2.52</v>
       </c>
       <c r="H24">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="I24">
-        <v>990</v>
+        <v>3.45</v>
       </c>
       <c r="J24">
-        <v>1.06</v>
+        <v>3.15</v>
       </c>
       <c r="K24">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6624,22 +6648,22 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.26</v>
+        <v>3.1</v>
       </c>
       <c r="O24">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="P24">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q24">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="R24">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S24">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="T24">
         <v>1.11</v>
@@ -6648,10 +6672,10 @@
         <v>1.11</v>
       </c>
       <c r="V24">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6762,67 +6786,67 @@
         <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI24">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
       </c>
       <c r="BK24">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BN24">
         <v>1000</v>
       </c>
       <c r="BO24">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BP24">
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BT24">
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="CB24" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6830,34 +6854,34 @@
         <v>95</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E25" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F25">
-        <v>2.06</v>
+        <v>1.06</v>
       </c>
       <c r="G25">
-        <v>2.82</v>
+        <v>990</v>
       </c>
       <c r="H25">
-        <v>2.72</v>
+        <v>1.06</v>
       </c>
       <c r="I25">
-        <v>3.95</v>
+        <v>990</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="K25">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6875,13 +6899,13 @@
         <v>1.25</v>
       </c>
       <c r="Q25">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
         <v>1.25</v>
       </c>
       <c r="S25">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="T25">
         <v>1.11</v>
@@ -6890,10 +6914,10 @@
         <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="W25">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -7064,7 +7088,7 @@
         <v>1.04</v>
       </c>
       <c r="CB25" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7072,16 +7096,16 @@
         <v>90</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E26" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F26">
         <v>2.96</v>
@@ -7306,7 +7330,7 @@
         <v>1.04</v>
       </c>
       <c r="CB26" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7314,16 +7338,16 @@
         <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E27" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F27">
         <v>3.05</v>
@@ -7344,7 +7368,7 @@
         <v>3.9</v>
       </c>
       <c r="L27">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M27">
         <v>1.01</v>
@@ -7362,10 +7386,10 @@
         <v>1.9</v>
       </c>
       <c r="R27">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S27">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T27">
         <v>1.6</v>
@@ -7488,22 +7512,22 @@
         <v>1.16</v>
       </c>
       <c r="BH27">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="BJ27">
         <v>13</v>
       </c>
       <c r="BK27">
-        <v>2.72</v>
+        <v>1.66</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="BN27">
         <v>8.800000000000001</v>
@@ -7515,40 +7539,40 @@
         <v>36</v>
       </c>
       <c r="BQ27">
-        <v>3.15</v>
+        <v>1.81</v>
       </c>
       <c r="BR27">
         <v>50</v>
       </c>
       <c r="BS27">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="BT27">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU27">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BV27">
         <v>24</v>
       </c>
       <c r="BW27">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="BX27">
         <v>44</v>
       </c>
       <c r="BY27">
-        <v>3.2</v>
+        <v>1.82</v>
       </c>
       <c r="BZ27">
         <v>36</v>
       </c>
       <c r="CA27">
-        <v>3.15</v>
+        <v>1.81</v>
       </c>
       <c r="CB27" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7556,16 +7580,16 @@
         <v>96</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E28" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F28">
         <v>1.23</v>
@@ -7751,7 +7775,7 @@
         <v>5</v>
       </c>
       <c r="BO28">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BP28">
         <v>9.6</v>
@@ -7790,7 +7814,7 @@
         <v>2.4</v>
       </c>
       <c r="CB28" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7798,16 +7822,16 @@
         <v>90</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E29" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F29">
         <v>4.3</v>
@@ -7975,7 +7999,7 @@
         <v>5.3</v>
       </c>
       <c r="BI29">
-        <v>2.84</v>
+        <v>1.98</v>
       </c>
       <c r="BJ29">
         <v>13</v>
@@ -8011,7 +8035,7 @@
         <v>6.4</v>
       </c>
       <c r="BU29">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BV29">
         <v>17</v>
@@ -8032,7 +8056,7 @@
         <v>2.78</v>
       </c>
       <c r="CB29" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8040,16 +8064,16 @@
         <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E30" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F30">
         <v>1.66</v>
@@ -8193,7 +8217,7 @@
         <v>17.5</v>
       </c>
       <c r="BA30">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB30">
         <v>14</v>
@@ -8217,64 +8241,64 @@
         <v>1000</v>
       </c>
       <c r="BI30">
-        <v>2.92</v>
+        <v>1.95</v>
       </c>
       <c r="BJ30">
         <v>13.5</v>
       </c>
       <c r="BK30">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BN30">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO30">
-        <v>3.35</v>
+        <v>1.46</v>
       </c>
       <c r="BP30">
         <v>15.5</v>
       </c>
       <c r="BQ30">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BR30">
         <v>34</v>
       </c>
       <c r="BS30">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BT30">
         <v>12.5</v>
       </c>
       <c r="BU30">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BZ30">
         <v>26</v>
       </c>
       <c r="CA30">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CB30" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8282,16 +8306,16 @@
         <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E31" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F31">
         <v>1.78</v>
@@ -8333,7 +8357,7 @@
         <v>1.5</v>
       </c>
       <c r="S31">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="T31">
         <v>1.11</v>
@@ -8387,7 +8411,7 @@
         <v>29</v>
       </c>
       <c r="AK31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL31">
         <v>36</v>
@@ -8405,13 +8429,13 @@
         <v>2.22</v>
       </c>
       <c r="AQ31">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR31">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AS31">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AT31">
         <v>8.4</v>
@@ -8420,10 +8444,10 @@
         <v>7</v>
       </c>
       <c r="AV31">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW31">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AX31">
         <v>8.800000000000001</v>
@@ -8435,25 +8459,25 @@
         <v>10.5</v>
       </c>
       <c r="BA31">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BB31">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC31">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD31">
         <v>16.5</v>
       </c>
       <c r="BE31">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BF31">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG31">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BH31">
         <v>6</v>
@@ -8465,13 +8489,13 @@
         <v>12.5</v>
       </c>
       <c r="BK31">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BN31">
         <v>6.6</v>
@@ -8480,22 +8504,22 @@
         <v>3.4</v>
       </c>
       <c r="BP31">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ31">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BR31">
         <v>29</v>
       </c>
       <c r="BS31">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BT31">
         <v>11</v>
       </c>
       <c r="BU31">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV31">
         <v>44</v>
@@ -8504,10 +8528,10 @@
         <v>3</v>
       </c>
       <c r="BX31">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY31">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BZ31">
         <v>0</v>
@@ -8516,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8524,16 +8548,16 @@
         <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D32" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E32" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F32">
         <v>2.46</v>
@@ -8572,7 +8596,7 @@
         <v>1.47</v>
       </c>
       <c r="R32">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="S32">
         <v>2.16</v>
@@ -8701,7 +8725,7 @@
         <v>6.4</v>
       </c>
       <c r="BI32">
-        <v>3.35</v>
+        <v>2.16</v>
       </c>
       <c r="BJ32">
         <v>11</v>
@@ -8737,7 +8761,7 @@
         <v>8.6</v>
       </c>
       <c r="BU32">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV32">
         <v>23</v>
@@ -8758,7 +8782,7 @@
         <v>0</v>
       </c>
       <c r="CB32" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8766,22 +8790,22 @@
         <v>98</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D33" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E33" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F33">
         <v>2.24</v>
       </c>
       <c r="G33">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H33">
         <v>2.82</v>
@@ -9000,7 +9024,7 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -9008,16 +9032,16 @@
         <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E34" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F34">
         <v>1.26</v>
@@ -9035,7 +9059,7 @@
         <v>6.6</v>
       </c>
       <c r="K34">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -9050,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q34">
         <v>1.44</v>
@@ -9242,7 +9266,7 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9250,19 +9274,19 @@
         <v>100</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C35" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D35" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E35" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F35">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G35">
         <v>1.93</v>
@@ -9277,7 +9301,7 @@
         <v>3.6</v>
       </c>
       <c r="K35">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L35">
         <v>1.32</v>
@@ -9325,16 +9349,16 @@
         <v>48</v>
       </c>
       <c r="AA35">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB35">
         <v>8.800000000000001</v>
       </c>
       <c r="AC35">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD35">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE35">
         <v>75</v>
@@ -9361,7 +9385,7 @@
         <v>48</v>
       </c>
       <c r="AM35">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN35">
         <v>14</v>
@@ -9376,13 +9400,13 @@
         <v>12</v>
       </c>
       <c r="AR35">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS35">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT35">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU35">
         <v>6.4</v>
@@ -9391,7 +9415,7 @@
         <v>14.5</v>
       </c>
       <c r="AW35">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX35">
         <v>8</v>
@@ -9403,7 +9427,7 @@
         <v>14.5</v>
       </c>
       <c r="BA35">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB35">
         <v>14.5</v>
@@ -9412,16 +9436,16 @@
         <v>14.5</v>
       </c>
       <c r="BD35">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE35">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF35">
         <v>9.6</v>
       </c>
       <c r="BG35">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9484,491 +9508,491 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D36" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E36" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F36">
-        <v>3.35</v>
+        <v>2.24</v>
       </c>
       <c r="G36">
+        <v>2.28</v>
+      </c>
+      <c r="H36">
         <v>3.8</v>
       </c>
-      <c r="H36">
-        <v>2.02</v>
-      </c>
       <c r="I36">
+        <v>3.85</v>
+      </c>
+      <c r="J36">
+        <v>3.3</v>
+      </c>
+      <c r="K36">
+        <v>3.6</v>
+      </c>
+      <c r="L36">
+        <v>1.42</v>
+      </c>
+      <c r="M36">
+        <v>1.1</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="O36">
+        <v>1.43</v>
+      </c>
+      <c r="P36">
+        <v>1.69</v>
+      </c>
+      <c r="Q36">
         <v>2.22</v>
       </c>
-      <c r="J36">
-        <v>3.9</v>
-      </c>
-      <c r="K36">
-        <v>4.3</v>
-      </c>
-      <c r="L36">
-        <v>1.01</v>
-      </c>
-      <c r="M36">
-        <v>1.04</v>
-      </c>
-      <c r="N36">
-        <v>3.4</v>
-      </c>
-      <c r="O36">
-        <v>1.19</v>
-      </c>
-      <c r="P36">
-        <v>2.5</v>
-      </c>
-      <c r="Q36">
-        <v>1.63</v>
-      </c>
       <c r="R36">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="S36">
-        <v>2.28</v>
+        <v>4.2</v>
       </c>
       <c r="T36">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="U36">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="V36">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="W36">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="X36">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y36">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z36">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AA36">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="AB36">
-        <v>25</v>
+        <v>9.4</v>
       </c>
       <c r="AC36">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD36">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AE36">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AF36">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AG36">
+        <v>13</v>
+      </c>
+      <c r="AH36">
+        <v>24</v>
+      </c>
+      <c r="AI36">
+        <v>75</v>
+      </c>
+      <c r="AJ36">
+        <v>34</v>
+      </c>
+      <c r="AK36">
+        <v>32</v>
+      </c>
+      <c r="AL36">
+        <v>55</v>
+      </c>
+      <c r="AM36">
+        <v>160</v>
+      </c>
+      <c r="AN36">
+        <v>26</v>
+      </c>
+      <c r="AO36">
+        <v>80</v>
+      </c>
+      <c r="AP36">
+        <v>9.6</v>
+      </c>
+      <c r="AQ36">
+        <v>9.6</v>
+      </c>
+      <c r="AR36">
         <v>21</v>
       </c>
-      <c r="AH36">
-        <v>22</v>
-      </c>
-      <c r="AI36">
-        <v>40</v>
-      </c>
-      <c r="AJ36">
-        <v>1000</v>
-      </c>
-      <c r="AK36">
-        <v>1000</v>
-      </c>
-      <c r="AL36">
-        <v>1000</v>
-      </c>
-      <c r="AM36">
-        <v>1000</v>
-      </c>
-      <c r="AN36">
-        <v>1000</v>
-      </c>
-      <c r="AO36">
-        <v>15.5</v>
-      </c>
-      <c r="AP36">
-        <v>2.2</v>
-      </c>
-      <c r="AQ36">
+      <c r="AS36">
+        <v>5.6</v>
+      </c>
+      <c r="AT36">
+        <v>7</v>
+      </c>
+      <c r="AU36">
+        <v>6.6</v>
+      </c>
+      <c r="AV36">
+        <v>14.5</v>
+      </c>
+      <c r="AW36">
+        <v>5.5</v>
+      </c>
+      <c r="AX36">
+        <v>11</v>
+      </c>
+      <c r="AY36">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ36">
+        <v>17.5</v>
+      </c>
+      <c r="BA36">
+        <v>5.5</v>
+      </c>
+      <c r="BB36">
+        <v>21</v>
+      </c>
+      <c r="BC36">
+        <v>20</v>
+      </c>
+      <c r="BD36">
+        <v>5.4</v>
+      </c>
+      <c r="BE36">
+        <v>5.8</v>
+      </c>
+      <c r="BF36">
+        <v>17</v>
+      </c>
+      <c r="BG36">
+        <v>5.5</v>
+      </c>
+      <c r="BH36">
+        <v>3.05</v>
+      </c>
+      <c r="BI36">
+        <v>2.54</v>
+      </c>
+      <c r="BJ36">
+        <v>10.5</v>
+      </c>
+      <c r="BK36">
+        <v>6.2</v>
+      </c>
+      <c r="BL36">
+        <v>1000</v>
+      </c>
+      <c r="BM36">
+        <v>14</v>
+      </c>
+      <c r="BN36">
+        <v>4.8</v>
+      </c>
+      <c r="BO36">
+        <v>3.85</v>
+      </c>
+      <c r="BP36">
+        <v>17</v>
+      </c>
+      <c r="BQ36">
         <v>8</v>
       </c>
-      <c r="AR36">
-        <v>9.6</v>
-      </c>
-      <c r="AS36">
-        <v>15.5</v>
-      </c>
-      <c r="AT36">
+      <c r="BR36">
+        <v>1000</v>
+      </c>
+      <c r="BS36">
+        <v>10.5</v>
+      </c>
+      <c r="BT36">
+        <v>7.2</v>
+      </c>
+      <c r="BU36">
+        <v>5.6</v>
+      </c>
+      <c r="BV36">
+        <v>1000</v>
+      </c>
+      <c r="BW36">
         <v>11</v>
       </c>
-      <c r="AU36">
-        <v>6.2</v>
-      </c>
-      <c r="AV36">
-        <v>7</v>
-      </c>
-      <c r="AW36">
+      <c r="BX36">
+        <v>1000</v>
+      </c>
+      <c r="BY36">
         <v>12</v>
       </c>
-      <c r="AX36">
-        <v>16.5</v>
-      </c>
-      <c r="AY36">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ36">
-        <v>9.6</v>
-      </c>
-      <c r="BA36">
-        <v>16.5</v>
-      </c>
-      <c r="BB36">
-        <v>2.2</v>
-      </c>
-      <c r="BC36">
-        <v>2.2</v>
-      </c>
-      <c r="BD36">
-        <v>2.2</v>
-      </c>
-      <c r="BE36">
-        <v>2.2</v>
-      </c>
-      <c r="BF36">
-        <v>2.2</v>
-      </c>
-      <c r="BG36">
-        <v>8</v>
-      </c>
-      <c r="BH36">
-        <v>5.5</v>
-      </c>
-      <c r="BI36">
-        <v>2.9</v>
-      </c>
-      <c r="BJ36">
-        <v>13</v>
-      </c>
-      <c r="BK36">
-        <v>2.38</v>
-      </c>
-      <c r="BL36">
-        <v>1000</v>
-      </c>
-      <c r="BM36">
-        <v>2.92</v>
-      </c>
-      <c r="BN36">
-        <v>10</v>
-      </c>
-      <c r="BO36">
-        <v>4.6</v>
-      </c>
-      <c r="BP36">
-        <v>40</v>
-      </c>
-      <c r="BQ36">
-        <v>2.72</v>
-      </c>
-      <c r="BR36">
-        <v>48</v>
-      </c>
-      <c r="BS36">
-        <v>2.76</v>
-      </c>
-      <c r="BT36">
-        <v>7.4</v>
-      </c>
-      <c r="BU36">
-        <v>3.55</v>
-      </c>
-      <c r="BV36">
-        <v>20</v>
-      </c>
-      <c r="BW36">
-        <v>2.54</v>
-      </c>
-      <c r="BX36">
-        <v>34</v>
-      </c>
-      <c r="BY36">
-        <v>2.68</v>
-      </c>
       <c r="BZ36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA36">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="CB36" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="37" spans="1:80">
       <c r="A37" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C37" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E37" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F37">
+        <v>3.35</v>
+      </c>
+      <c r="G37">
+        <v>3.8</v>
+      </c>
+      <c r="H37">
+        <v>2.02</v>
+      </c>
+      <c r="I37">
+        <v>2.22</v>
+      </c>
+      <c r="J37">
+        <v>3.9</v>
+      </c>
+      <c r="K37">
+        <v>4.3</v>
+      </c>
+      <c r="L37">
+        <v>1.01</v>
+      </c>
+      <c r="M37">
+        <v>1.04</v>
+      </c>
+      <c r="N37">
+        <v>3.35</v>
+      </c>
+      <c r="O37">
+        <v>1.19</v>
+      </c>
+      <c r="P37">
+        <v>2.5</v>
+      </c>
+      <c r="Q37">
+        <v>1.63</v>
+      </c>
+      <c r="R37">
+        <v>1.44</v>
+      </c>
+      <c r="S37">
+        <v>2.28</v>
+      </c>
+      <c r="T37">
+        <v>1.48</v>
+      </c>
+      <c r="U37">
+        <v>2.12</v>
+      </c>
+      <c r="V37">
+        <v>1.81</v>
+      </c>
+      <c r="W37">
+        <v>1.35</v>
+      </c>
+      <c r="X37">
+        <v>1000</v>
+      </c>
+      <c r="Y37">
+        <v>18.5</v>
+      </c>
+      <c r="Z37">
+        <v>22</v>
+      </c>
+      <c r="AA37">
+        <v>36</v>
+      </c>
+      <c r="AB37">
+        <v>25</v>
+      </c>
+      <c r="AC37">
+        <v>13.5</v>
+      </c>
+      <c r="AD37">
+        <v>15.5</v>
+      </c>
+      <c r="AE37">
+        <v>29</v>
+      </c>
+      <c r="AF37">
+        <v>40</v>
+      </c>
+      <c r="AG37">
+        <v>21</v>
+      </c>
+      <c r="AH37">
+        <v>22</v>
+      </c>
+      <c r="AI37">
+        <v>40</v>
+      </c>
+      <c r="AJ37">
+        <v>1000</v>
+      </c>
+      <c r="AK37">
+        <v>1000</v>
+      </c>
+      <c r="AL37">
+        <v>1000</v>
+      </c>
+      <c r="AM37">
+        <v>1000</v>
+      </c>
+      <c r="AN37">
+        <v>1000</v>
+      </c>
+      <c r="AO37">
+        <v>15.5</v>
+      </c>
+      <c r="AP37">
         <v>2.2</v>
       </c>
-      <c r="G37">
-        <v>2.28</v>
-      </c>
-      <c r="H37">
-        <v>3.8</v>
-      </c>
-      <c r="I37">
-        <v>3.85</v>
-      </c>
-      <c r="J37">
-        <v>3.3</v>
-      </c>
-      <c r="K37">
-        <v>3.5</v>
-      </c>
-      <c r="L37">
-        <v>1.48</v>
-      </c>
-      <c r="M37">
-        <v>1.1</v>
-      </c>
-      <c r="N37">
-        <v>3</v>
-      </c>
-      <c r="O37">
-        <v>1.42</v>
-      </c>
-      <c r="P37">
-        <v>1.69</v>
-      </c>
-      <c r="Q37">
-        <v>2.22</v>
-      </c>
-      <c r="R37">
-        <v>1.26</v>
-      </c>
-      <c r="S37">
-        <v>4.2</v>
-      </c>
-      <c r="T37">
-        <v>1.92</v>
-      </c>
-      <c r="U37">
-        <v>1.91</v>
-      </c>
-      <c r="V37">
-        <v>1.35</v>
-      </c>
-      <c r="W37">
-        <v>1.79</v>
-      </c>
-      <c r="X37">
+      <c r="AQ37">
+        <v>8</v>
+      </c>
+      <c r="AR37">
+        <v>9.6</v>
+      </c>
+      <c r="AS37">
+        <v>15.5</v>
+      </c>
+      <c r="AT37">
+        <v>11</v>
+      </c>
+      <c r="AU37">
+        <v>6.2</v>
+      </c>
+      <c r="AV37">
+        <v>7</v>
+      </c>
+      <c r="AW37">
+        <v>12</v>
+      </c>
+      <c r="AX37">
+        <v>16.5</v>
+      </c>
+      <c r="AY37">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ37">
+        <v>9.6</v>
+      </c>
+      <c r="BA37">
+        <v>16.5</v>
+      </c>
+      <c r="BB37">
+        <v>2.2</v>
+      </c>
+      <c r="BC37">
+        <v>2.2</v>
+      </c>
+      <c r="BD37">
+        <v>2.2</v>
+      </c>
+      <c r="BE37">
+        <v>2.2</v>
+      </c>
+      <c r="BF37">
+        <v>2.2</v>
+      </c>
+      <c r="BG37">
+        <v>8</v>
+      </c>
+      <c r="BH37">
+        <v>5.8</v>
+      </c>
+      <c r="BI37">
+        <v>1.93</v>
+      </c>
+      <c r="BJ37">
         <v>12.5</v>
       </c>
-      <c r="Y37">
-        <v>14</v>
-      </c>
-      <c r="Z37">
-        <v>32</v>
-      </c>
-      <c r="AA37">
-        <v>90</v>
-      </c>
-      <c r="AB37">
-        <v>9.4</v>
-      </c>
-      <c r="AC37">
-        <v>7.8</v>
-      </c>
-      <c r="AD37">
-        <v>19</v>
-      </c>
-      <c r="AE37">
-        <v>65</v>
-      </c>
-      <c r="AF37">
-        <v>15</v>
-      </c>
-      <c r="AG37">
-        <v>13</v>
-      </c>
-      <c r="AH37">
-        <v>24</v>
-      </c>
-      <c r="AI37">
-        <v>75</v>
-      </c>
-      <c r="AJ37">
+      <c r="BK37">
+        <v>5.4</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>2.88</v>
+      </c>
+      <c r="BN37">
+        <v>10</v>
+      </c>
+      <c r="BO37">
+        <v>4.6</v>
+      </c>
+      <c r="BP37">
+        <v>38</v>
+      </c>
+      <c r="BQ37">
+        <v>2.7</v>
+      </c>
+      <c r="BR37">
+        <v>46</v>
+      </c>
+      <c r="BS37">
+        <v>2.72</v>
+      </c>
+      <c r="BT37">
+        <v>7.4</v>
+      </c>
+      <c r="BU37">
+        <v>3.75</v>
+      </c>
+      <c r="BV37">
+        <v>20</v>
+      </c>
+      <c r="BW37">
+        <v>2.52</v>
+      </c>
+      <c r="BX37">
         <v>34</v>
       </c>
-      <c r="AK37">
-        <v>32</v>
-      </c>
-      <c r="AL37">
-        <v>55</v>
-      </c>
-      <c r="AM37">
-        <v>160</v>
-      </c>
-      <c r="AN37">
-        <v>26</v>
-      </c>
-      <c r="AO37">
-        <v>80</v>
-      </c>
-      <c r="AP37">
-        <v>9.6</v>
-      </c>
-      <c r="AQ37">
-        <v>9.6</v>
-      </c>
-      <c r="AR37">
-        <v>21</v>
-      </c>
-      <c r="AS37">
-        <v>5.5</v>
-      </c>
-      <c r="AT37">
-        <v>7</v>
-      </c>
-      <c r="AU37">
-        <v>6.6</v>
-      </c>
-      <c r="AV37">
-        <v>14.5</v>
-      </c>
-      <c r="AW37">
-        <v>5.4</v>
-      </c>
-      <c r="AX37">
-        <v>11</v>
-      </c>
-      <c r="AY37">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ37">
-        <v>17.5</v>
-      </c>
-      <c r="BA37">
-        <v>5.5</v>
-      </c>
-      <c r="BB37">
-        <v>21</v>
-      </c>
-      <c r="BC37">
-        <v>20</v>
-      </c>
-      <c r="BD37">
-        <v>5.3</v>
-      </c>
-      <c r="BE37">
-        <v>5.7</v>
-      </c>
-      <c r="BF37">
-        <v>17</v>
-      </c>
-      <c r="BG37">
-        <v>5.5</v>
-      </c>
-      <c r="BH37">
-        <v>3.05</v>
-      </c>
-      <c r="BI37">
-        <v>2.54</v>
-      </c>
-      <c r="BJ37">
-        <v>10.5</v>
-      </c>
-      <c r="BK37">
-        <v>6.2</v>
-      </c>
-      <c r="BL37">
-        <v>1000</v>
-      </c>
-      <c r="BM37">
-        <v>14</v>
-      </c>
-      <c r="BN37">
-        <v>4.8</v>
-      </c>
-      <c r="BO37">
-        <v>3.85</v>
-      </c>
-      <c r="BP37">
-        <v>17</v>
-      </c>
-      <c r="BQ37">
-        <v>8</v>
-      </c>
-      <c r="BR37">
-        <v>1000</v>
-      </c>
-      <c r="BS37">
-        <v>10.5</v>
-      </c>
-      <c r="BT37">
-        <v>7.2</v>
-      </c>
-      <c r="BU37">
-        <v>5.6</v>
-      </c>
-      <c r="BV37">
-        <v>1000</v>
-      </c>
-      <c r="BW37">
-        <v>11</v>
-      </c>
-      <c r="BX37">
-        <v>1000</v>
-      </c>
       <c r="BY37">
-        <v>12</v>
+        <v>2.66</v>
       </c>
       <c r="BZ37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA37">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB37" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -9976,16 +10000,16 @@
         <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C38" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D38" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E38" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F38">
         <v>3.65</v>
@@ -9994,7 +10018,7 @@
         <v>4.2</v>
       </c>
       <c r="H38">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I38">
         <v>2.36</v>
@@ -10003,13 +10027,13 @@
         <v>3.1</v>
       </c>
       <c r="K38">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L38">
         <v>1.01</v>
       </c>
       <c r="M38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N38">
         <v>2.86</v>
@@ -10027,7 +10051,7 @@
         <v>1.18</v>
       </c>
       <c r="S38">
-        <v>2.58</v>
+        <v>3.7</v>
       </c>
       <c r="T38">
         <v>1.76</v>
@@ -10210,7 +10234,7 @@
         <v>1.04</v>
       </c>
       <c r="CB38" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10218,70 +10242,70 @@
         <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D39" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E39" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>2.72</v>
       </c>
       <c r="G39">
+        <v>2.94</v>
+      </c>
+      <c r="H39">
+        <v>2.4</v>
+      </c>
+      <c r="I39">
+        <v>2.66</v>
+      </c>
+      <c r="J39">
+        <v>3.7</v>
+      </c>
+      <c r="K39">
+        <v>4.1</v>
+      </c>
+      <c r="L39">
+        <v>1.01</v>
+      </c>
+      <c r="M39">
+        <v>1.01</v>
+      </c>
+      <c r="N39">
         <v>2.6</v>
-      </c>
-      <c r="H39">
-        <v>1.04</v>
-      </c>
-      <c r="I39">
-        <v>3.7</v>
-      </c>
-      <c r="J39">
-        <v>3.55</v>
-      </c>
-      <c r="K39">
-        <v>950</v>
-      </c>
-      <c r="L39">
-        <v>1.01</v>
-      </c>
-      <c r="M39">
-        <v>1.01</v>
-      </c>
-      <c r="N39">
-        <v>2.48</v>
       </c>
       <c r="O39">
         <v>1.22</v>
       </c>
       <c r="P39">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q39">
         <v>1.64</v>
       </c>
       <c r="R39">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S39">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="T39">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="U39">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="V39">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="W39">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -10452,491 +10476,491 @@
         <v>0</v>
       </c>
       <c r="CB39" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D40" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E40" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F40">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="G40">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="H40">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I40">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="J40">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="K40">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L40">
         <v>1.01</v>
       </c>
       <c r="M40">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N40">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="O40">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="P40">
-        <v>1.74</v>
+        <v>2.14</v>
       </c>
       <c r="Q40">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="R40">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S40">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="T40">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="U40">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V40">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W40">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="X40">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y40">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z40">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA40">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB40">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC40">
         <v>10.5</v>
       </c>
       <c r="AD40">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AE40">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AF40">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AG40">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AH40">
-        <v>950</v>
+        <v>18.5</v>
       </c>
       <c r="AI40">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ40">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK40">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL40">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM40">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN40">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO40">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP40">
-        <v>1.89</v>
+        <v>16</v>
       </c>
       <c r="AQ40">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR40">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AS40">
-        <v>1.89</v>
+        <v>4.3</v>
       </c>
       <c r="AT40">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AU40">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AV40">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW40">
         <v>18.5</v>
       </c>
       <c r="AX40">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AY40">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AZ40">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA40">
-        <v>1.89</v>
+        <v>4.3</v>
       </c>
       <c r="BB40">
-        <v>1.89</v>
+        <v>4.5</v>
       </c>
       <c r="BC40">
-        <v>1.89</v>
+        <v>4.3</v>
       </c>
       <c r="BD40">
-        <v>1.89</v>
+        <v>4.4</v>
       </c>
       <c r="BE40">
-        <v>1.89</v>
+        <v>4.6</v>
       </c>
       <c r="BF40">
-        <v>1.89</v>
+        <v>17.5</v>
       </c>
       <c r="BG40">
-        <v>1.89</v>
+        <v>12.5</v>
       </c>
       <c r="BH40">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI40">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="BJ40">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK40">
-        <v>2.66</v>
+        <v>1.69</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="BN40">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BO40">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP40">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BQ40">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="BR40">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS40">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="BT40">
         <v>7.6</v>
       </c>
       <c r="BU40">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BV40">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BW40">
-        <v>2.92</v>
+        <v>1.8</v>
       </c>
       <c r="BX40">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BY40">
-        <v>3.05</v>
+        <v>1.85</v>
       </c>
       <c r="BZ40">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="CA40">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="CB40" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D41" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E41" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F41">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="G41">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="H41">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I41">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="J41">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="K41">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="L41">
         <v>1.01</v>
       </c>
       <c r="M41">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N41">
-        <v>4.3</v>
+        <v>2.74</v>
       </c>
       <c r="O41">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="P41">
-        <v>2.14</v>
+        <v>1.74</v>
       </c>
       <c r="Q41">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="R41">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="S41">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="T41">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="U41">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="V41">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W41">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="X41">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y41">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z41">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA41">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB41">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC41">
         <v>10.5</v>
       </c>
       <c r="AD41">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AE41">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AF41">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AG41">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AH41">
-        <v>18.5</v>
+        <v>950</v>
       </c>
       <c r="AI41">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ41">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK41">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL41">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM41">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN41">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO41">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP41">
-        <v>16</v>
+        <v>1.89</v>
       </c>
       <c r="AQ41">
-        <v>9.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="AR41">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS41">
-        <v>4.3</v>
+        <v>1.89</v>
       </c>
       <c r="AT41">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AU41">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="AV41">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AW41">
         <v>18.5</v>
       </c>
       <c r="AX41">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AY41">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AZ41">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA41">
-        <v>4.3</v>
+        <v>1.89</v>
       </c>
       <c r="BB41">
-        <v>4.5</v>
+        <v>1.89</v>
       </c>
       <c r="BC41">
-        <v>4.3</v>
+        <v>1.89</v>
       </c>
       <c r="BD41">
-        <v>4.4</v>
+        <v>1.89</v>
       </c>
       <c r="BE41">
-        <v>4.6</v>
+        <v>1.89</v>
       </c>
       <c r="BF41">
-        <v>17.5</v>
+        <v>1.89</v>
       </c>
       <c r="BG41">
-        <v>12.5</v>
+        <v>1.89</v>
       </c>
       <c r="BH41">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI41">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="BJ41">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK41">
-        <v>1.69</v>
+        <v>2.66</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="BN41">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO41">
         <v>4.3</v>
       </c>
       <c r="BP41">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BQ41">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="BR41">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS41">
-        <v>1.87</v>
+        <v>3.1</v>
       </c>
       <c r="BT41">
         <v>7.6</v>
       </c>
       <c r="BU41">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BV41">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BW41">
-        <v>1.8</v>
+        <v>2.92</v>
       </c>
       <c r="BX41">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BY41">
-        <v>1.85</v>
+        <v>3.05</v>
       </c>
       <c r="BZ41">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CA41">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="CB41" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:80">
@@ -10944,178 +10968,178 @@
         <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D42" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E42" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F42">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G42">
-        <v>1.57</v>
+        <v>990</v>
       </c>
       <c r="H42">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="I42">
-        <v>8</v>
+        <v>1.42</v>
       </c>
       <c r="J42">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="K42">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="L42">
         <v>1.01</v>
       </c>
       <c r="M42">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N42">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="O42">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P42">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="Q42">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="R42">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S42">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="T42">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="U42">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="V42">
-        <v>1.15</v>
+        <v>3.4</v>
       </c>
       <c r="W42">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="X42">
         <v>1000</v>
       </c>
       <c r="Y42">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z42">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA42">
         <v>1000</v>
       </c>
       <c r="AB42">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC42">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AD42">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE42">
         <v>1000</v>
       </c>
       <c r="AF42">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG42">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH42">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI42">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ42">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK42">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL42">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM42">
         <v>1000</v>
       </c>
       <c r="AN42">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO42">
         <v>1000</v>
       </c>
       <c r="AP42">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="AQ42">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR42">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="AS42">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="AT42">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU42">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV42">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW42">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="AX42">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY42">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ42">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA42">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BB42">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC42">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BD42">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BE42">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BF42">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BG42">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11178,66 +11202,66 @@
         <v>0</v>
       </c>
       <c r="CB42" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="43" spans="1:80">
       <c r="A43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B43" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C43" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D43" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E43" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F43">
-        <v>8.800000000000001</v>
+        <v>2.86</v>
       </c>
       <c r="G43">
-        <v>990</v>
+        <v>3.35</v>
       </c>
       <c r="H43">
-        <v>1.3</v>
+        <v>2.32</v>
       </c>
       <c r="I43">
-        <v>1.42</v>
+        <v>2.62</v>
       </c>
       <c r="J43">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K43">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="L43">
         <v>1.01</v>
       </c>
       <c r="M43">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N43">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="O43">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="P43">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="Q43">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="R43">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="S43">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="T43">
         <v>1.11</v>
@@ -11246,172 +11270,172 @@
         <v>1.11</v>
       </c>
       <c r="V43">
-        <v>3.4</v>
+        <v>1.61</v>
       </c>
       <c r="W43">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X43">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y43">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z43">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA43">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB43">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC43">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD43">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE43">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF43">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG43">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH43">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI43">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ43">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK43">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL43">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM43">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN43">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO43">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP43">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ43">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR43">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS43">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT43">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU43">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV43">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW43">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AX43">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY43">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ43">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA43">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB43">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC43">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD43">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE43">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF43">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG43">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH43">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI43">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BJ43">
         <v>1000</v>
       </c>
       <c r="BK43">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BN43">
         <v>1000</v>
       </c>
       <c r="BO43">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BP43">
         <v>1000</v>
       </c>
       <c r="BQ43">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BR43">
         <v>1000</v>
       </c>
       <c r="BS43">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BT43">
         <v>1000</v>
       </c>
       <c r="BU43">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BV43">
         <v>1000</v>
       </c>
       <c r="BW43">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BX43">
         <v>1000</v>
       </c>
       <c r="BY43">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BZ43">
         <v>0</v>
@@ -11420,42 +11444,42 @@
         <v>0</v>
       </c>
       <c r="CB43" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="1:80">
       <c r="A44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C44" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D44" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E44" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F44">
-        <v>2.78</v>
+        <v>2.28</v>
       </c>
       <c r="G44">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="H44">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="I44">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="J44">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K44">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="L44">
         <v>1.01</v>
@@ -11464,22 +11488,22 @@
         <v>1.01</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O44">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="P44">
         <v>2</v>
       </c>
       <c r="Q44">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="R44">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S44">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="T44">
         <v>1.11</v>
@@ -11488,10 +11512,10 @@
         <v>1.11</v>
       </c>
       <c r="V44">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="W44">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="X44">
         <v>1000</v>
@@ -11602,58 +11626,58 @@
         <v>1.01</v>
       </c>
       <c r="BH44">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BI44">
-        <v>2.9</v>
+        <v>1.97</v>
       </c>
       <c r="BJ44">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK44">
-        <v>1.29</v>
+        <v>2.52</v>
       </c>
       <c r="BL44">
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>1.29</v>
+        <v>3.15</v>
       </c>
       <c r="BN44">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO44">
-        <v>1.29</v>
+        <v>3.95</v>
       </c>
       <c r="BP44">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ44">
-        <v>1.29</v>
+        <v>2.8</v>
       </c>
       <c r="BR44">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS44">
-        <v>1.29</v>
+        <v>2.92</v>
       </c>
       <c r="BT44">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU44">
-        <v>1.29</v>
+        <v>4.3</v>
       </c>
       <c r="BV44">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW44">
-        <v>1.29</v>
+        <v>2.88</v>
       </c>
       <c r="BX44">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY44">
-        <v>1.29</v>
+        <v>2.96</v>
       </c>
       <c r="BZ44">
         <v>0</v>
@@ -11662,42 +11686,42 @@
         <v>0</v>
       </c>
       <c r="CB44" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="45" spans="1:80">
       <c r="A45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C45" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E45" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F45">
-        <v>2.28</v>
+        <v>1.49</v>
       </c>
       <c r="G45">
-        <v>2.96</v>
+        <v>1.79</v>
       </c>
       <c r="H45">
-        <v>2.52</v>
+        <v>4.5</v>
       </c>
       <c r="I45">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J45">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="K45">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="L45">
         <v>1.01</v>
@@ -11706,22 +11730,22 @@
         <v>1.01</v>
       </c>
       <c r="N45">
-        <v>3.9</v>
+        <v>2.18</v>
       </c>
       <c r="O45">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P45">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q45">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="R45">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S45">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="T45">
         <v>1.11</v>
@@ -11730,10 +11754,10 @@
         <v>1.11</v>
       </c>
       <c r="V45">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="W45">
-        <v>1.51</v>
+        <v>2.26</v>
       </c>
       <c r="X45">
         <v>1000</v>
@@ -11844,58 +11868,58 @@
         <v>1.01</v>
       </c>
       <c r="BH45">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BI45">
+        <v>2.98</v>
+      </c>
+      <c r="BJ45">
+        <v>13.5</v>
+      </c>
+      <c r="BK45">
+        <v>2.8</v>
+      </c>
+      <c r="BL45">
+        <v>1000</v>
+      </c>
+      <c r="BM45">
+        <v>3.5</v>
+      </c>
+      <c r="BN45">
+        <v>5.8</v>
+      </c>
+      <c r="BO45">
+        <v>3.05</v>
+      </c>
+      <c r="BP45">
+        <v>15</v>
+      </c>
+      <c r="BQ45">
+        <v>2.86</v>
+      </c>
+      <c r="BR45">
+        <v>32</v>
+      </c>
+      <c r="BS45">
+        <v>3.15</v>
+      </c>
+      <c r="BT45">
+        <v>12.5</v>
+      </c>
+      <c r="BU45">
         <v>2.76</v>
       </c>
-      <c r="BJ45">
-        <v>12</v>
-      </c>
-      <c r="BK45">
-        <v>2.52</v>
-      </c>
-      <c r="BL45">
-        <v>1000</v>
-      </c>
-      <c r="BM45">
-        <v>3.15</v>
-      </c>
-      <c r="BN45">
-        <v>7.6</v>
-      </c>
-      <c r="BO45">
-        <v>3.85</v>
-      </c>
-      <c r="BP45">
-        <v>24</v>
-      </c>
-      <c r="BQ45">
-        <v>2.8</v>
-      </c>
-      <c r="BR45">
-        <v>36</v>
-      </c>
-      <c r="BS45">
-        <v>2.92</v>
-      </c>
-      <c r="BT45">
-        <v>8.6</v>
-      </c>
-      <c r="BU45">
-        <v>4.5</v>
-      </c>
       <c r="BV45">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW45">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="BX45">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY45">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="BZ45">
         <v>0</v>
@@ -11904,240 +11928,240 @@
         <v>0</v>
       </c>
       <c r="CB45" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" spans="1:80">
       <c r="A46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D46" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E46" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F46">
-        <v>1.51</v>
+        <v>2.44</v>
       </c>
       <c r="G46">
-        <v>1.8</v>
+        <v>2.68</v>
       </c>
       <c r="H46">
-        <v>4.5</v>
+        <v>2.94</v>
       </c>
       <c r="I46">
+        <v>3.3</v>
+      </c>
+      <c r="J46">
+        <v>3.3</v>
+      </c>
+      <c r="K46">
+        <v>3.7</v>
+      </c>
+      <c r="L46">
+        <v>1.01</v>
+      </c>
+      <c r="M46">
+        <v>1.07</v>
+      </c>
+      <c r="N46">
+        <v>3.55</v>
+      </c>
+      <c r="O46">
+        <v>1.33</v>
+      </c>
+      <c r="P46">
+        <v>1.88</v>
+      </c>
+      <c r="Q46">
+        <v>1.97</v>
+      </c>
+      <c r="R46">
+        <v>1.36</v>
+      </c>
+      <c r="S46">
+        <v>3.5</v>
+      </c>
+      <c r="T46">
+        <v>1.75</v>
+      </c>
+      <c r="U46">
+        <v>2.12</v>
+      </c>
+      <c r="V46">
+        <v>1.44</v>
+      </c>
+      <c r="W46">
+        <v>1.59</v>
+      </c>
+      <c r="X46">
+        <v>14</v>
+      </c>
+      <c r="Y46">
+        <v>14</v>
+      </c>
+      <c r="Z46">
+        <v>24</v>
+      </c>
+      <c r="AA46">
+        <v>55</v>
+      </c>
+      <c r="AB46">
+        <v>12.5</v>
+      </c>
+      <c r="AC46">
+        <v>8</v>
+      </c>
+      <c r="AD46">
+        <v>15.5</v>
+      </c>
+      <c r="AE46">
+        <v>42</v>
+      </c>
+      <c r="AF46">
+        <v>19.5</v>
+      </c>
+      <c r="AG46">
+        <v>14</v>
+      </c>
+      <c r="AH46">
+        <v>17.5</v>
+      </c>
+      <c r="AI46">
+        <v>55</v>
+      </c>
+      <c r="AJ46">
+        <v>38</v>
+      </c>
+      <c r="AK46">
+        <v>29</v>
+      </c>
+      <c r="AL46">
+        <v>48</v>
+      </c>
+      <c r="AM46">
+        <v>110</v>
+      </c>
+      <c r="AN46">
+        <v>27</v>
+      </c>
+      <c r="AO46">
+        <v>38</v>
+      </c>
+      <c r="AP46">
+        <v>10.5</v>
+      </c>
+      <c r="AQ46">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR46">
+        <v>16</v>
+      </c>
+      <c r="AS46">
+        <v>5.8</v>
+      </c>
+      <c r="AT46">
         <v>8.199999999999999</v>
       </c>
-      <c r="J46">
-        <v>3.75</v>
-      </c>
-      <c r="K46">
-        <v>8.6</v>
-      </c>
-      <c r="L46">
-        <v>1.01</v>
-      </c>
-      <c r="M46">
-        <v>1.01</v>
-      </c>
-      <c r="N46">
-        <v>2.18</v>
-      </c>
-      <c r="O46">
-        <v>1.25</v>
-      </c>
-      <c r="P46">
-        <v>1.91</v>
-      </c>
-      <c r="Q46">
-        <v>1.63</v>
-      </c>
-      <c r="R46">
-        <v>1.34</v>
-      </c>
-      <c r="S46">
-        <v>2.58</v>
-      </c>
-      <c r="T46">
-        <v>1.11</v>
-      </c>
-      <c r="U46">
-        <v>1.11</v>
-      </c>
-      <c r="V46">
-        <v>1.14</v>
-      </c>
-      <c r="W46">
-        <v>2.24</v>
-      </c>
-      <c r="X46">
-        <v>1000</v>
-      </c>
-      <c r="Y46">
-        <v>1000</v>
-      </c>
-      <c r="Z46">
-        <v>1000</v>
-      </c>
-      <c r="AA46">
-        <v>1000</v>
-      </c>
-      <c r="AB46">
-        <v>1000</v>
-      </c>
-      <c r="AC46">
-        <v>1000</v>
-      </c>
-      <c r="AD46">
-        <v>1000</v>
-      </c>
-      <c r="AE46">
-        <v>1000</v>
-      </c>
-      <c r="AF46">
-        <v>1000</v>
-      </c>
-      <c r="AG46">
-        <v>1000</v>
-      </c>
-      <c r="AH46">
-        <v>1000</v>
-      </c>
-      <c r="AI46">
-        <v>1000</v>
-      </c>
-      <c r="AJ46">
-        <v>1000</v>
-      </c>
-      <c r="AK46">
-        <v>1000</v>
-      </c>
-      <c r="AL46">
-        <v>1000</v>
-      </c>
-      <c r="AM46">
-        <v>1000</v>
-      </c>
-      <c r="AN46">
-        <v>1000</v>
-      </c>
-      <c r="AO46">
-        <v>1000</v>
-      </c>
-      <c r="AP46">
-        <v>1.01</v>
-      </c>
-      <c r="AQ46">
-        <v>1.01</v>
-      </c>
-      <c r="AR46">
-        <v>1.01</v>
-      </c>
-      <c r="AS46">
-        <v>1.01</v>
-      </c>
-      <c r="AT46">
-        <v>1.01</v>
-      </c>
       <c r="AU46">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV46">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW46">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX46">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY46">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ46">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA46">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB46">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BC46">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD46">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BE46">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF46">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG46">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH46">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BI46">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="BJ46">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK46">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="BL46">
         <v>1000</v>
       </c>
       <c r="BM46">
-        <v>3.35</v>
+        <v>1.33</v>
       </c>
       <c r="BN46">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO46">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="BP46">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ46">
-        <v>2.76</v>
+        <v>1.33</v>
       </c>
       <c r="BR46">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS46">
-        <v>3.05</v>
+        <v>1.33</v>
       </c>
       <c r="BT46">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU46">
-        <v>2.66</v>
+        <v>1.33</v>
       </c>
       <c r="BV46">
         <v>1000</v>
       </c>
       <c r="BW46">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="BX46">
         <v>1000</v>
       </c>
       <c r="BY46">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="BZ46">
         <v>0</v>
@@ -12146,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="CB46" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:80">
@@ -12154,232 +12178,232 @@
         <v>102</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C47" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D47" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E47" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F47">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="G47">
-        <v>2.66</v>
+        <v>1.57</v>
       </c>
       <c r="H47">
-        <v>2.92</v>
+        <v>6.6</v>
       </c>
       <c r="I47">
-        <v>3.55</v>
+        <v>8</v>
       </c>
       <c r="J47">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="K47">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="L47">
         <v>1.01</v>
       </c>
       <c r="M47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N47">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="O47">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="P47">
-        <v>1.83</v>
+        <v>2.52</v>
       </c>
       <c r="Q47">
-        <v>1.94</v>
+        <v>1.47</v>
       </c>
       <c r="R47">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="S47">
-        <v>2.82</v>
+        <v>2.18</v>
       </c>
       <c r="T47">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="U47">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="V47">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="W47">
-        <v>1.6</v>
+        <v>2.76</v>
       </c>
       <c r="X47">
         <v>1000</v>
       </c>
       <c r="Y47">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z47">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA47">
         <v>1000</v>
       </c>
       <c r="AB47">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC47">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD47">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE47">
         <v>1000</v>
       </c>
       <c r="AF47">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG47">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH47">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI47">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ47">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK47">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL47">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM47">
         <v>1000</v>
       </c>
       <c r="AN47">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO47">
         <v>1000</v>
       </c>
       <c r="AP47">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AQ47">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR47">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AS47">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AT47">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU47">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV47">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AW47">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AX47">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY47">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ47">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA47">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BB47">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BC47">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BD47">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BE47">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BF47">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG47">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BH47">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI47">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BJ47">
         <v>1000</v>
       </c>
       <c r="BK47">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BL47">
         <v>1000</v>
       </c>
       <c r="BM47">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BN47">
         <v>1000</v>
       </c>
       <c r="BO47">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BP47">
         <v>1000</v>
       </c>
       <c r="BQ47">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BR47">
         <v>1000</v>
       </c>
       <c r="BS47">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BT47">
         <v>1000</v>
       </c>
       <c r="BU47">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BV47">
         <v>1000</v>
       </c>
       <c r="BW47">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BX47">
         <v>1000</v>
       </c>
       <c r="BY47">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BZ47">
         <v>0</v>
@@ -12388,724 +12412,724 @@
         <v>0</v>
       </c>
       <c r="CB47" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="48" spans="1:80">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C48" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D48" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E48" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F48">
-        <v>1.28</v>
+        <v>4.7</v>
       </c>
       <c r="G48">
-        <v>1.31</v>
+        <v>5.2</v>
       </c>
       <c r="H48">
+        <v>1.9</v>
+      </c>
+      <c r="I48">
+        <v>1.99</v>
+      </c>
+      <c r="J48">
+        <v>3.45</v>
+      </c>
+      <c r="K48">
+        <v>3.7</v>
+      </c>
+      <c r="L48">
+        <v>1.35</v>
+      </c>
+      <c r="M48">
+        <v>1.08</v>
+      </c>
+      <c r="N48">
+        <v>3.4</v>
+      </c>
+      <c r="O48">
+        <v>1.35</v>
+      </c>
+      <c r="P48">
+        <v>1.81</v>
+      </c>
+      <c r="Q48">
+        <v>2</v>
+      </c>
+      <c r="R48">
+        <v>1.3</v>
+      </c>
+      <c r="S48">
+        <v>3.7</v>
+      </c>
+      <c r="T48">
+        <v>1.86</v>
+      </c>
+      <c r="U48">
+        <v>1.95</v>
+      </c>
+      <c r="V48">
+        <v>2</v>
+      </c>
+      <c r="W48">
+        <v>1.23</v>
+      </c>
+      <c r="X48">
+        <v>15.5</v>
+      </c>
+      <c r="Y48">
+        <v>8.6</v>
+      </c>
+      <c r="Z48">
+        <v>12</v>
+      </c>
+      <c r="AA48">
+        <v>22</v>
+      </c>
+      <c r="AB48">
+        <v>16.5</v>
+      </c>
+      <c r="AC48">
+        <v>8.6</v>
+      </c>
+      <c r="AD48">
+        <v>11</v>
+      </c>
+      <c r="AE48">
+        <v>22</v>
+      </c>
+      <c r="AF48">
+        <v>38</v>
+      </c>
+      <c r="AG48">
+        <v>21</v>
+      </c>
+      <c r="AH48">
+        <v>21</v>
+      </c>
+      <c r="AI48">
+        <v>42</v>
+      </c>
+      <c r="AJ48">
+        <v>150</v>
+      </c>
+      <c r="AK48">
+        <v>75</v>
+      </c>
+      <c r="AL48">
+        <v>80</v>
+      </c>
+      <c r="AM48">
+        <v>150</v>
+      </c>
+      <c r="AN48">
+        <v>110</v>
+      </c>
+      <c r="AO48">
+        <v>15.5</v>
+      </c>
+      <c r="AP48">
         <v>9.6</v>
       </c>
-      <c r="I48">
-        <v>12.5</v>
-      </c>
-      <c r="J48">
+      <c r="AQ48">
+        <v>7</v>
+      </c>
+      <c r="AR48">
+        <v>9.4</v>
+      </c>
+      <c r="AS48">
+        <v>17.5</v>
+      </c>
+      <c r="AT48">
+        <v>13</v>
+      </c>
+      <c r="AU48">
+        <v>7</v>
+      </c>
+      <c r="AV48">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW48">
+        <v>18</v>
+      </c>
+      <c r="AX48">
         <v>6.8</v>
       </c>
-      <c r="K48">
+      <c r="AY48">
+        <v>16.5</v>
+      </c>
+      <c r="AZ48">
+        <v>17</v>
+      </c>
+      <c r="BA48">
+        <v>7</v>
+      </c>
+      <c r="BB48">
+        <v>7.8</v>
+      </c>
+      <c r="BC48">
+        <v>7.4</v>
+      </c>
+      <c r="BD48">
         <v>7.6</v>
       </c>
-      <c r="L48">
-        <v>1.01</v>
-      </c>
-      <c r="M48">
-        <v>1.01</v>
-      </c>
-      <c r="N48">
-        <v>7.4</v>
-      </c>
-      <c r="O48">
-        <v>1.1</v>
-      </c>
-      <c r="P48">
-        <v>3.65</v>
-      </c>
-      <c r="Q48">
-        <v>1.34</v>
-      </c>
-      <c r="R48">
-        <v>2.04</v>
-      </c>
-      <c r="S48">
-        <v>1.8</v>
-      </c>
-      <c r="T48">
+      <c r="BE48">
+        <v>7.8</v>
+      </c>
+      <c r="BF48">
+        <v>7.8</v>
+      </c>
+      <c r="BG48">
+        <v>10.5</v>
+      </c>
+      <c r="BH48">
+        <v>1000</v>
+      </c>
+      <c r="BI48">
+        <v>1.87</v>
+      </c>
+      <c r="BJ48">
+        <v>14.5</v>
+      </c>
+      <c r="BK48">
+        <v>1.66</v>
+      </c>
+      <c r="BL48">
+        <v>1000</v>
+      </c>
+      <c r="BM48">
+        <v>1.87</v>
+      </c>
+      <c r="BN48">
+        <v>11</v>
+      </c>
+      <c r="BO48">
+        <v>5.4</v>
+      </c>
+      <c r="BP48">
+        <v>1000</v>
+      </c>
+      <c r="BQ48">
+        <v>1.81</v>
+      </c>
+      <c r="BR48">
+        <v>1000</v>
+      </c>
+      <c r="BS48">
+        <v>1.83</v>
+      </c>
+      <c r="BT48">
+        <v>5.9</v>
+      </c>
+      <c r="BU48">
+        <v>3.2</v>
+      </c>
+      <c r="BV48">
+        <v>18.5</v>
+      </c>
+      <c r="BW48">
         <v>1.7</v>
       </c>
-      <c r="U48">
-        <v>2.2</v>
-      </c>
-      <c r="V48">
-        <v>1.09</v>
-      </c>
-      <c r="W48">
-        <v>4.1</v>
-      </c>
-      <c r="X48">
-        <v>950</v>
-      </c>
-      <c r="Y48">
-        <v>950</v>
-      </c>
-      <c r="Z48">
-        <v>140</v>
-      </c>
-      <c r="AA48">
-        <v>390</v>
-      </c>
-      <c r="AB48">
-        <v>17.5</v>
-      </c>
-      <c r="AC48">
-        <v>18.5</v>
-      </c>
-      <c r="AD48">
-        <v>55</v>
-      </c>
-      <c r="AE48">
-        <v>150</v>
-      </c>
-      <c r="AF48">
-        <v>13</v>
-      </c>
-      <c r="AG48">
-        <v>13.5</v>
-      </c>
-      <c r="AH48">
-        <v>26</v>
-      </c>
-      <c r="AI48">
-        <v>110</v>
-      </c>
-      <c r="AJ48">
-        <v>13</v>
-      </c>
-      <c r="AK48">
-        <v>14</v>
-      </c>
-      <c r="AL48">
-        <v>38</v>
-      </c>
-      <c r="AM48">
-        <v>110</v>
-      </c>
-      <c r="AN48">
-        <v>3.25</v>
-      </c>
-      <c r="AO48">
-        <v>120</v>
-      </c>
-      <c r="AP48">
-        <v>7.8</v>
-      </c>
-      <c r="AQ48">
-        <v>8</v>
-      </c>
-      <c r="AR48">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS48">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT48">
-        <v>14</v>
-      </c>
-      <c r="AU48">
-        <v>15</v>
-      </c>
-      <c r="AV48">
-        <v>30</v>
-      </c>
-      <c r="AW48">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX48">
-        <v>10</v>
-      </c>
-      <c r="AY48">
-        <v>10.5</v>
-      </c>
-      <c r="AZ48">
-        <v>20</v>
-      </c>
-      <c r="BA48">
-        <v>8.6</v>
-      </c>
-      <c r="BB48">
-        <v>10</v>
-      </c>
-      <c r="BC48">
-        <v>11</v>
-      </c>
-      <c r="BD48">
-        <v>19</v>
-      </c>
-      <c r="BE48">
-        <v>8.6</v>
-      </c>
-      <c r="BF48">
-        <v>2.84</v>
-      </c>
-      <c r="BG48">
-        <v>8.6</v>
-      </c>
-      <c r="BH48">
-        <v>1000</v>
-      </c>
-      <c r="BI48">
-        <v>1.04</v>
-      </c>
-      <c r="BJ48">
-        <v>1000</v>
-      </c>
-      <c r="BK48">
-        <v>1.04</v>
-      </c>
-      <c r="BL48">
-        <v>1000</v>
-      </c>
-      <c r="BM48">
-        <v>1.04</v>
-      </c>
-      <c r="BN48">
-        <v>1000</v>
-      </c>
-      <c r="BO48">
-        <v>1.04</v>
-      </c>
-      <c r="BP48">
-        <v>1000</v>
-      </c>
-      <c r="BQ48">
-        <v>1.04</v>
-      </c>
-      <c r="BR48">
-        <v>1000</v>
-      </c>
-      <c r="BS48">
-        <v>1.04</v>
-      </c>
-      <c r="BT48">
-        <v>1000</v>
-      </c>
-      <c r="BU48">
-        <v>1.04</v>
-      </c>
-      <c r="BV48">
-        <v>1000</v>
-      </c>
-      <c r="BW48">
-        <v>1.04</v>
-      </c>
       <c r="BX48">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY48">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="BZ48">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA48">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB48" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:80">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C49" t="s">
+        <v>122</v>
+      </c>
+      <c r="D49" t="s">
+        <v>173</v>
+      </c>
+      <c r="E49" t="s">
+        <v>225</v>
+      </c>
+      <c r="F49">
+        <v>1.28</v>
+      </c>
+      <c r="G49">
+        <v>1.31</v>
+      </c>
+      <c r="H49">
+        <v>10</v>
+      </c>
+      <c r="I49">
+        <v>12.5</v>
+      </c>
+      <c r="J49">
+        <v>6.8</v>
+      </c>
+      <c r="K49">
+        <v>7.6</v>
+      </c>
+      <c r="L49">
+        <v>1.01</v>
+      </c>
+      <c r="M49">
+        <v>1.01</v>
+      </c>
+      <c r="N49">
+        <v>7.4</v>
+      </c>
+      <c r="O49">
+        <v>1.1</v>
+      </c>
+      <c r="P49">
+        <v>3.65</v>
+      </c>
+      <c r="Q49">
+        <v>1.34</v>
+      </c>
+      <c r="R49">
+        <v>2.04</v>
+      </c>
+      <c r="S49">
+        <v>1.8</v>
+      </c>
+      <c r="T49">
+        <v>1.7</v>
+      </c>
+      <c r="U49">
+        <v>2.2</v>
+      </c>
+      <c r="V49">
+        <v>1.09</v>
+      </c>
+      <c r="W49">
+        <v>4.1</v>
+      </c>
+      <c r="X49">
+        <v>950</v>
+      </c>
+      <c r="Y49">
+        <v>950</v>
+      </c>
+      <c r="Z49">
+        <v>140</v>
+      </c>
+      <c r="AA49">
+        <v>390</v>
+      </c>
+      <c r="AB49">
+        <v>17.5</v>
+      </c>
+      <c r="AC49">
+        <v>18.5</v>
+      </c>
+      <c r="AD49">
+        <v>55</v>
+      </c>
+      <c r="AE49">
+        <v>150</v>
+      </c>
+      <c r="AF49">
+        <v>13</v>
+      </c>
+      <c r="AG49">
+        <v>13.5</v>
+      </c>
+      <c r="AH49">
+        <v>26</v>
+      </c>
+      <c r="AI49">
+        <v>110</v>
+      </c>
+      <c r="AJ49">
+        <v>13</v>
+      </c>
+      <c r="AK49">
+        <v>14</v>
+      </c>
+      <c r="AL49">
+        <v>38</v>
+      </c>
+      <c r="AM49">
+        <v>110</v>
+      </c>
+      <c r="AN49">
+        <v>3.25</v>
+      </c>
+      <c r="AO49">
         <v>120</v>
       </c>
-      <c r="D49" t="s">
-        <v>169</v>
-      </c>
-      <c r="E49" t="s">
-        <v>219</v>
-      </c>
-      <c r="F49">
-        <v>5.8</v>
-      </c>
-      <c r="G49">
-        <v>6.6</v>
-      </c>
-      <c r="H49">
-        <v>1.55</v>
-      </c>
-      <c r="I49">
-        <v>1.61</v>
-      </c>
-      <c r="J49">
-        <v>4.8</v>
-      </c>
-      <c r="K49">
-        <v>5.1</v>
-      </c>
-      <c r="L49">
-        <v>1.26</v>
-      </c>
-      <c r="M49">
-        <v>1.03</v>
-      </c>
-      <c r="N49">
-        <v>5.6</v>
-      </c>
-      <c r="O49">
-        <v>1.18</v>
-      </c>
-      <c r="P49">
-        <v>2.56</v>
-      </c>
-      <c r="Q49">
-        <v>1.53</v>
-      </c>
-      <c r="R49">
-        <v>1.63</v>
-      </c>
-      <c r="S49">
-        <v>2.3</v>
-      </c>
-      <c r="T49">
-        <v>1.65</v>
-      </c>
-      <c r="U49">
-        <v>2.26</v>
-      </c>
-      <c r="V49">
-        <v>2.62</v>
-      </c>
-      <c r="W49">
-        <v>1.18</v>
-      </c>
-      <c r="X49">
-        <v>34</v>
-      </c>
-      <c r="Y49">
-        <v>13</v>
-      </c>
-      <c r="Z49">
-        <v>12</v>
-      </c>
-      <c r="AA49">
+      <c r="AP49">
+        <v>7.8</v>
+      </c>
+      <c r="AQ49">
+        <v>8</v>
+      </c>
+      <c r="AR49">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS49">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT49">
+        <v>14</v>
+      </c>
+      <c r="AU49">
+        <v>15</v>
+      </c>
+      <c r="AV49">
+        <v>30</v>
+      </c>
+      <c r="AW49">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX49">
+        <v>10</v>
+      </c>
+      <c r="AY49">
+        <v>10.5</v>
+      </c>
+      <c r="AZ49">
+        <v>20</v>
+      </c>
+      <c r="BA49">
+        <v>8.6</v>
+      </c>
+      <c r="BB49">
+        <v>10</v>
+      </c>
+      <c r="BC49">
+        <v>11</v>
+      </c>
+      <c r="BD49">
         <v>19</v>
       </c>
-      <c r="AB49">
-        <v>34</v>
-      </c>
-      <c r="AC49">
-        <v>12</v>
-      </c>
-      <c r="AD49">
-        <v>11.5</v>
-      </c>
-      <c r="AE49">
-        <v>15.5</v>
-      </c>
-      <c r="AF49">
-        <v>60</v>
-      </c>
-      <c r="AG49">
-        <v>24</v>
-      </c>
-      <c r="AH49">
-        <v>21</v>
-      </c>
-      <c r="AI49">
-        <v>27</v>
-      </c>
-      <c r="AJ49">
-        <v>170</v>
-      </c>
-      <c r="AK49">
-        <v>70</v>
-      </c>
-      <c r="AL49">
-        <v>65</v>
-      </c>
-      <c r="AM49">
-        <v>80</v>
-      </c>
-      <c r="AN49">
-        <v>60</v>
-      </c>
-      <c r="AO49">
-        <v>6.4</v>
-      </c>
-      <c r="AP49">
-        <v>7</v>
-      </c>
-      <c r="AQ49">
-        <v>10.5</v>
-      </c>
-      <c r="AR49">
-        <v>10</v>
-      </c>
-      <c r="AS49">
-        <v>14</v>
-      </c>
-      <c r="AT49">
-        <v>23</v>
-      </c>
-      <c r="AU49">
-        <v>10</v>
-      </c>
-      <c r="AV49">
-        <v>9</v>
-      </c>
-      <c r="AW49">
-        <v>13</v>
-      </c>
-      <c r="AX49">
-        <v>44</v>
-      </c>
-      <c r="AY49">
-        <v>20</v>
-      </c>
-      <c r="AZ49">
-        <v>16</v>
-      </c>
-      <c r="BA49">
-        <v>22</v>
-      </c>
-      <c r="BB49">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC49">
-        <v>55</v>
-      </c>
-      <c r="BD49">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE49">
-        <v>60</v>
+        <v>8.6</v>
       </c>
       <c r="BF49">
-        <v>40</v>
+        <v>2.84</v>
       </c>
       <c r="BG49">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH49">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI49">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BJ49">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK49">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL49">
         <v>1000</v>
       </c>
       <c r="BM49">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN49">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO49">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP49">
         <v>1000</v>
       </c>
       <c r="BQ49">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR49">
         <v>1000</v>
       </c>
       <c r="BS49">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT49">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU49">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV49">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BW49">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX49">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BY49">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ49">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA49">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB49" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50" spans="1:80">
       <c r="A50" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C50" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D50" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E50" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F50">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="G50">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="H50">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="I50">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="J50">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="K50">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="L50">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="M50">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="N50">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="O50">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="P50">
-        <v>1.8</v>
+        <v>2.56</v>
       </c>
       <c r="Q50">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="R50">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="S50">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="T50">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="U50">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="V50">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="W50">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X50">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="Y50">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="Z50">
         <v>12</v>
       </c>
       <c r="AA50">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AB50">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="AC50">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AD50">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE50">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AF50">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AG50">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AH50">
         <v>21</v>
       </c>
       <c r="AI50">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AJ50">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AK50">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL50">
+        <v>65</v>
+      </c>
+      <c r="AM50">
         <v>80</v>
       </c>
-      <c r="AM50">
-        <v>150</v>
-      </c>
       <c r="AN50">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AO50">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="AP50">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AQ50">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AR50">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AS50">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AT50">
+        <v>23</v>
+      </c>
+      <c r="AU50">
+        <v>10</v>
+      </c>
+      <c r="AV50">
+        <v>9</v>
+      </c>
+      <c r="AW50">
         <v>13</v>
       </c>
-      <c r="AU50">
-        <v>7</v>
-      </c>
-      <c r="AV50">
+      <c r="AX50">
+        <v>44</v>
+      </c>
+      <c r="AY50">
+        <v>20</v>
+      </c>
+      <c r="AZ50">
+        <v>16</v>
+      </c>
+      <c r="BA50">
+        <v>22</v>
+      </c>
+      <c r="BB50">
         <v>8.800000000000001</v>
       </c>
-      <c r="AW50">
-        <v>18</v>
-      </c>
-      <c r="AX50">
-        <v>6.8</v>
-      </c>
-      <c r="AY50">
-        <v>16.5</v>
-      </c>
-      <c r="AZ50">
-        <v>17</v>
-      </c>
-      <c r="BA50">
-        <v>7</v>
-      </c>
-      <c r="BB50">
-        <v>7.8</v>
-      </c>
       <c r="BC50">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="BD50">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE50">
-        <v>7.8</v>
+        <v>60</v>
       </c>
       <c r="BF50">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="BG50">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH50">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI50">
-        <v>1.87</v>
+        <v>3.55</v>
       </c>
       <c r="BJ50">
-        <v>14.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK50">
-        <v>1.66</v>
+        <v>5.2</v>
       </c>
       <c r="BL50">
         <v>1000</v>
       </c>
       <c r="BM50">
-        <v>1.87</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN50">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BO50">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP50">
         <v>1000</v>
       </c>
       <c r="BQ50">
-        <v>1.81</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR50">
         <v>1000</v>
       </c>
       <c r="BS50">
-        <v>1.83</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT50">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="BU50">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BV50">
-        <v>18.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW50">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="BX50">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="BY50">
-        <v>1.79</v>
+        <v>7.2</v>
       </c>
       <c r="BZ50">
         <v>0</v>
@@ -13114,7 +13138,7 @@
         <v>0</v>
       </c>
       <c r="CB50" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="51" spans="1:80">
@@ -13122,34 +13146,34 @@
         <v>104</v>
       </c>
       <c r="B51" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D51" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E51" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F51">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="G51">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H51">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I51">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J51">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K51">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="L51">
         <v>1.01</v>
@@ -13158,22 +13182,22 @@
         <v>1.07</v>
       </c>
       <c r="N51">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="O51">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P51">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q51">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="R51">
         <v>1.24</v>
       </c>
       <c r="S51">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="T51">
         <v>1.11</v>
@@ -13182,10 +13206,10 @@
         <v>1.11</v>
       </c>
       <c r="V51">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W51">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -13209,7 +13233,7 @@
         <v>25</v>
       </c>
       <c r="AE51">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF51">
         <v>15.5</v>
@@ -13245,7 +13269,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ51">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR51">
         <v>2.26</v>
@@ -13272,13 +13296,13 @@
         <v>2.02</v>
       </c>
       <c r="AZ51">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BA51">
         <v>2.3</v>
       </c>
       <c r="BB51">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC51">
         <v>15.5</v>
@@ -13356,7 +13380,491 @@
         <v>0</v>
       </c>
       <c r="CB51" t="s">
-        <v>222</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="1:80">
+      <c r="A52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" t="s">
+        <v>124</v>
+      </c>
+      <c r="D52" t="s">
+        <v>176</v>
+      </c>
+      <c r="E52" t="s">
+        <v>228</v>
+      </c>
+      <c r="F52">
+        <v>1.92</v>
+      </c>
+      <c r="G52">
+        <v>2.1</v>
+      </c>
+      <c r="H52">
+        <v>4.2</v>
+      </c>
+      <c r="I52">
+        <v>5</v>
+      </c>
+      <c r="J52">
+        <v>3.4</v>
+      </c>
+      <c r="K52">
+        <v>3.7</v>
+      </c>
+      <c r="L52">
+        <v>1.35</v>
+      </c>
+      <c r="M52">
+        <v>1.08</v>
+      </c>
+      <c r="N52">
+        <v>3.2</v>
+      </c>
+      <c r="O52">
+        <v>1.37</v>
+      </c>
+      <c r="P52">
+        <v>1.74</v>
+      </c>
+      <c r="Q52">
+        <v>2.1</v>
+      </c>
+      <c r="R52">
+        <v>1.28</v>
+      </c>
+      <c r="S52">
+        <v>3.9</v>
+      </c>
+      <c r="T52">
+        <v>1.89</v>
+      </c>
+      <c r="U52">
+        <v>1.92</v>
+      </c>
+      <c r="V52">
+        <v>1.25</v>
+      </c>
+      <c r="W52">
+        <v>1.91</v>
+      </c>
+      <c r="X52">
+        <v>15</v>
+      </c>
+      <c r="Y52">
+        <v>17</v>
+      </c>
+      <c r="Z52">
+        <v>34</v>
+      </c>
+      <c r="AA52">
+        <v>130</v>
+      </c>
+      <c r="AB52">
+        <v>9.6</v>
+      </c>
+      <c r="AC52">
+        <v>9.4</v>
+      </c>
+      <c r="AD52">
+        <v>23</v>
+      </c>
+      <c r="AE52">
+        <v>70</v>
+      </c>
+      <c r="AF52">
+        <v>13.5</v>
+      </c>
+      <c r="AG52">
+        <v>12.5</v>
+      </c>
+      <c r="AH52">
+        <v>25</v>
+      </c>
+      <c r="AI52">
+        <v>90</v>
+      </c>
+      <c r="AJ52">
+        <v>29</v>
+      </c>
+      <c r="AK52">
+        <v>28</v>
+      </c>
+      <c r="AL52">
+        <v>55</v>
+      </c>
+      <c r="AM52">
+        <v>160</v>
+      </c>
+      <c r="AN52">
+        <v>21</v>
+      </c>
+      <c r="AO52">
+        <v>85</v>
+      </c>
+      <c r="AP52">
+        <v>9</v>
+      </c>
+      <c r="AQ52">
+        <v>10.5</v>
+      </c>
+      <c r="AR52">
+        <v>4.3</v>
+      </c>
+      <c r="AS52">
+        <v>4.8</v>
+      </c>
+      <c r="AT52">
+        <v>6</v>
+      </c>
+      <c r="AU52">
+        <v>6</v>
+      </c>
+      <c r="AV52">
+        <v>13.5</v>
+      </c>
+      <c r="AW52">
+        <v>4.6</v>
+      </c>
+      <c r="AX52">
+        <v>8.6</v>
+      </c>
+      <c r="AY52">
+        <v>7.8</v>
+      </c>
+      <c r="AZ52">
+        <v>14.5</v>
+      </c>
+      <c r="BA52">
+        <v>4.7</v>
+      </c>
+      <c r="BB52">
+        <v>17</v>
+      </c>
+      <c r="BC52">
+        <v>16.5</v>
+      </c>
+      <c r="BD52">
+        <v>4.5</v>
+      </c>
+      <c r="BE52">
+        <v>4.8</v>
+      </c>
+      <c r="BF52">
+        <v>12.5</v>
+      </c>
+      <c r="BG52">
+        <v>4.7</v>
+      </c>
+      <c r="BH52">
+        <v>1000</v>
+      </c>
+      <c r="BI52">
+        <v>1.78</v>
+      </c>
+      <c r="BJ52">
+        <v>15</v>
+      </c>
+      <c r="BK52">
+        <v>1.59</v>
+      </c>
+      <c r="BL52">
+        <v>1000</v>
+      </c>
+      <c r="BM52">
+        <v>1.78</v>
+      </c>
+      <c r="BN52">
+        <v>6.4</v>
+      </c>
+      <c r="BO52">
+        <v>3.1</v>
+      </c>
+      <c r="BP52">
+        <v>21</v>
+      </c>
+      <c r="BQ52">
+        <v>1.64</v>
+      </c>
+      <c r="BR52">
+        <v>46</v>
+      </c>
+      <c r="BS52">
+        <v>1.71</v>
+      </c>
+      <c r="BT52">
+        <v>11</v>
+      </c>
+      <c r="BU52">
+        <v>4.9</v>
+      </c>
+      <c r="BV52">
+        <v>1000</v>
+      </c>
+      <c r="BW52">
+        <v>1.72</v>
+      </c>
+      <c r="BX52">
+        <v>1000</v>
+      </c>
+      <c r="BY52">
+        <v>1.74</v>
+      </c>
+      <c r="BZ52">
+        <v>44</v>
+      </c>
+      <c r="CA52">
+        <v>1.71</v>
+      </c>
+      <c r="CB52" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="53" spans="1:80">
+      <c r="A53" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53" t="s">
+        <v>125</v>
+      </c>
+      <c r="D53" t="s">
+        <v>177</v>
+      </c>
+      <c r="E53" t="s">
+        <v>229</v>
+      </c>
+      <c r="F53">
+        <v>1.7</v>
+      </c>
+      <c r="G53">
+        <v>1.71</v>
+      </c>
+      <c r="H53">
+        <v>5.3</v>
+      </c>
+      <c r="I53">
+        <v>5.7</v>
+      </c>
+      <c r="J53">
+        <v>4.2</v>
+      </c>
+      <c r="K53">
+        <v>4.4</v>
+      </c>
+      <c r="L53">
+        <v>1.35</v>
+      </c>
+      <c r="M53">
+        <v>1.05</v>
+      </c>
+      <c r="N53">
+        <v>4.4</v>
+      </c>
+      <c r="O53">
+        <v>1.26</v>
+      </c>
+      <c r="P53">
+        <v>2.16</v>
+      </c>
+      <c r="Q53">
+        <v>1.79</v>
+      </c>
+      <c r="R53">
+        <v>1.45</v>
+      </c>
+      <c r="S53">
+        <v>3.05</v>
+      </c>
+      <c r="T53">
+        <v>1.79</v>
+      </c>
+      <c r="U53">
+        <v>2.1</v>
+      </c>
+      <c r="V53">
+        <v>1.21</v>
+      </c>
+      <c r="W53">
+        <v>2.38</v>
+      </c>
+      <c r="X53">
+        <v>19</v>
+      </c>
+      <c r="Y53">
+        <v>21</v>
+      </c>
+      <c r="Z53">
+        <v>100</v>
+      </c>
+      <c r="AA53">
+        <v>160</v>
+      </c>
+      <c r="AB53">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC53">
+        <v>10</v>
+      </c>
+      <c r="AD53">
+        <v>21</v>
+      </c>
+      <c r="AE53">
+        <v>1000</v>
+      </c>
+      <c r="AF53">
+        <v>11</v>
+      </c>
+      <c r="AG53">
+        <v>10</v>
+      </c>
+      <c r="AH53">
+        <v>20</v>
+      </c>
+      <c r="AI53">
+        <v>70</v>
+      </c>
+      <c r="AJ53">
+        <v>17</v>
+      </c>
+      <c r="AK53">
+        <v>17</v>
+      </c>
+      <c r="AL53">
+        <v>65</v>
+      </c>
+      <c r="AM53">
+        <v>1000</v>
+      </c>
+      <c r="AN53">
+        <v>9</v>
+      </c>
+      <c r="AO53">
+        <v>1000</v>
+      </c>
+      <c r="AP53">
+        <v>16.5</v>
+      </c>
+      <c r="AQ53">
+        <v>18</v>
+      </c>
+      <c r="AR53">
+        <v>36</v>
+      </c>
+      <c r="AS53">
+        <v>42</v>
+      </c>
+      <c r="AT53">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU53">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV53">
+        <v>18</v>
+      </c>
+      <c r="AW53">
+        <v>55</v>
+      </c>
+      <c r="AX53">
+        <v>9.6</v>
+      </c>
+      <c r="AY53">
+        <v>9</v>
+      </c>
+      <c r="AZ53">
+        <v>17.5</v>
+      </c>
+      <c r="BA53">
+        <v>55</v>
+      </c>
+      <c r="BB53">
+        <v>15</v>
+      </c>
+      <c r="BC53">
+        <v>15</v>
+      </c>
+      <c r="BD53">
+        <v>28</v>
+      </c>
+      <c r="BE53">
+        <v>38</v>
+      </c>
+      <c r="BF53">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG53">
+        <v>34</v>
+      </c>
+      <c r="BH53">
+        <v>1000</v>
+      </c>
+      <c r="BI53">
+        <v>1.91</v>
+      </c>
+      <c r="BJ53">
+        <v>14.5</v>
+      </c>
+      <c r="BK53">
+        <v>1.69</v>
+      </c>
+      <c r="BL53">
+        <v>1000</v>
+      </c>
+      <c r="BM53">
+        <v>1.91</v>
+      </c>
+      <c r="BN53">
+        <v>6</v>
+      </c>
+      <c r="BO53">
+        <v>3.1</v>
+      </c>
+      <c r="BP53">
+        <v>16</v>
+      </c>
+      <c r="BQ53">
+        <v>1.71</v>
+      </c>
+      <c r="BR53">
+        <v>34</v>
+      </c>
+      <c r="BS53">
+        <v>1.81</v>
+      </c>
+      <c r="BT53">
+        <v>12.5</v>
+      </c>
+      <c r="BU53">
+        <v>1.66</v>
+      </c>
+      <c r="BV53">
+        <v>1000</v>
+      </c>
+      <c r="BW53">
+        <v>1.85</v>
+      </c>
+      <c r="BX53">
+        <v>1000</v>
+      </c>
+      <c r="BY53">
+        <v>1.86</v>
+      </c>
+      <c r="BZ53">
+        <v>26</v>
+      </c>
+      <c r="CA53">
+        <v>1.78</v>
+      </c>
+      <c r="CB53" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -706,7 +706,7 @@
     <t>Toronto FC</t>
   </si>
   <si>
-    <t>2026-07-30 00:42:57</t>
+    <t>2026-07-30 02:52:20</t>
   </si>
 </sst>
 </file>
@@ -1315,28 +1315,28 @@
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M2">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N2">
         <v>2.66</v>
       </c>
       <c r="O2">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P2">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="R2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
         <v>5.7</v>
@@ -1345,7 +1345,7 @@
         <v>2.18</v>
       </c>
       <c r="U2">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V2">
         <v>1.6</v>
@@ -1354,13 +1354,13 @@
         <v>1.4</v>
       </c>
       <c r="X2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Y2">
         <v>7.8</v>
       </c>
       <c r="Z2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA2">
         <v>42</v>
@@ -1372,7 +1372,7 @@
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE2">
         <v>38</v>
@@ -1390,7 +1390,7 @@
         <v>70</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK2">
         <v>55</v>
@@ -1414,7 +1414,7 @@
         <v>7.2</v>
       </c>
       <c r="AR2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS2">
         <v>36</v>
@@ -1429,7 +1429,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX2">
         <v>18.5</v>
@@ -1444,7 +1444,7 @@
         <v>60</v>
       </c>
       <c r="BB2">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BC2">
         <v>46</v>
@@ -1456,7 +1456,7 @@
         <v>46</v>
       </c>
       <c r="BF2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BG2">
         <v>36</v>
@@ -1465,37 +1465,37 @@
         <v>2.64</v>
       </c>
       <c r="BI2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2.24</v>
+        <v>16</v>
       </c>
       <c r="BN2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BQ2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR2">
         <v>60</v>
       </c>
       <c r="BS2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT2">
         <v>5.3</v>
@@ -1504,22 +1504,22 @@
         <v>4</v>
       </c>
       <c r="BV2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
         <v>55</v>
       </c>
       <c r="CA2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CB2" t="s">
         <v>230</v>
@@ -1542,58 +1542,58 @@
         <v>179</v>
       </c>
       <c r="F3">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G3">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H3">
         <v>6.2</v>
       </c>
       <c r="I3">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J3">
         <v>3.65</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q3">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T3">
         <v>2.24</v>
       </c>
       <c r="U3">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V3">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W3">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X3">
         <v>12.5</v>
@@ -1608,7 +1608,7 @@
         <v>270</v>
       </c>
       <c r="AB3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC3">
         <v>9.199999999999999</v>
@@ -1656,22 +1656,22 @@
         <v>12</v>
       </c>
       <c r="AR3">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT3">
         <v>5.7</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV3">
         <v>19.5</v>
       </c>
       <c r="AW3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX3">
         <v>7.6</v>
@@ -1680,10 +1680,10 @@
         <v>9</v>
       </c>
       <c r="AZ3">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BA3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB3">
         <v>15</v>
@@ -1692,76 +1692,76 @@
         <v>19</v>
       </c>
       <c r="BD3">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE3">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF3">
         <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH3">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI3">
         <v>2.38</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK3">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP3">
         <v>13</v>
       </c>
       <c r="BQ3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3">
         <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
         <v>230</v>
@@ -1796,7 +1796,7 @@
         <v>2.34</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4">
         <v>3.45</v>
@@ -1808,7 +1808,7 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
         <v>1.4</v>
@@ -1817,16 +1817,16 @@
         <v>1.78</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T4">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U4">
         <v>2.02</v>
@@ -1844,7 +1844,7 @@
         <v>9</v>
       </c>
       <c r="Z4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA4">
         <v>32</v>
@@ -1871,7 +1871,7 @@
         <v>19.5</v>
       </c>
       <c r="AI4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ4">
         <v>70</v>
@@ -1913,13 +1913,13 @@
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX4">
         <v>21</v>
       </c>
       <c r="AY4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ4">
         <v>17.5</v>
@@ -1928,7 +1928,7 @@
         <v>40</v>
       </c>
       <c r="BB4">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BC4">
         <v>40</v>
@@ -1940,7 +1940,7 @@
         <v>40</v>
       </c>
       <c r="BF4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BG4">
         <v>20</v>
@@ -1955,7 +1955,7 @@
         <v>10</v>
       </c>
       <c r="BK4">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1967,7 +1967,7 @@
         <v>6.8</v>
       </c>
       <c r="BO4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP4">
         <v>32</v>
@@ -1985,7 +1985,7 @@
         <v>5</v>
       </c>
       <c r="BU4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BV4">
         <v>18</v>
@@ -2026,7 +2026,7 @@
         <v>181</v>
       </c>
       <c r="F5">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="G5">
         <v>1.56</v>
@@ -2035,16 +2035,16 @@
         <v>7.8</v>
       </c>
       <c r="I5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
         <v>4.2</v>
       </c>
       <c r="K5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -2053,28 +2053,28 @@
         <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q5">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T5">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="V5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W5">
         <v>2.78</v>
@@ -2128,7 +2128,7 @@
         <v>240</v>
       </c>
       <c r="AN5">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO5">
         <v>290</v>
@@ -2140,10 +2140,10 @@
         <v>15.5</v>
       </c>
       <c r="AR5">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS5">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT5">
         <v>6</v>
@@ -2155,7 +2155,7 @@
         <v>22</v>
       </c>
       <c r="AW5">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX5">
         <v>7</v>
@@ -2164,10 +2164,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ5">
-        <v>24</v>
+        <v>6.2</v>
       </c>
       <c r="BA5">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB5">
         <v>10.5</v>
@@ -2179,13 +2179,13 @@
         <v>34</v>
       </c>
       <c r="BE5">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF5">
         <v>9.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH5">
         <v>3.35</v>
@@ -2203,49 +2203,49 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO5">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP5">
         <v>11</v>
       </c>
       <c r="BQ5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR5">
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5">
         <v>11.5</v>
       </c>
       <c r="BU5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ5">
         <v>24</v>
       </c>
       <c r="CA5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="s">
         <v>230</v>
@@ -2268,10 +2268,10 @@
         <v>182</v>
       </c>
       <c r="F6">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G6">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H6">
         <v>3.9</v>
@@ -2280,10 +2280,10 @@
         <v>4.3</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K6">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L6">
         <v>1.27</v>
@@ -2301,7 +2301,7 @@
         <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R6">
         <v>1.6</v>
@@ -2313,16 +2313,16 @@
         <v>1.58</v>
       </c>
       <c r="U6">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V6">
         <v>1.3</v>
       </c>
       <c r="W6">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y6">
         <v>22</v>
@@ -2421,7 +2421,7 @@
         <v>6</v>
       </c>
       <c r="BE6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF6">
         <v>7.6</v>
@@ -2430,64 +2430,64 @@
         <v>6</v>
       </c>
       <c r="BH6">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>230</v>
@@ -2510,79 +2510,79 @@
         <v>183</v>
       </c>
       <c r="F7">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="G7">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="H7">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="I7">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="K7">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="O7">
         <v>1.25</v>
       </c>
       <c r="P7">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="Q7">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S7">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T7">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W7">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="X7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
         <v>21</v>
       </c>
       <c r="Z7">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
         <v>1000</v>
@@ -2594,7 +2594,7 @@
         <v>16</v>
       </c>
       <c r="AH7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
         <v>1000</v>
@@ -2603,10 +2603,10 @@
         <v>40</v>
       </c>
       <c r="AK7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
         <v>1000</v>
@@ -2618,61 +2618,61 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>1.27</v>
       </c>
       <c r="AQ7">
-        <v>9.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="AR7">
-        <v>15.5</v>
+        <v>1.27</v>
       </c>
       <c r="AS7">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="AT7">
-        <v>7</v>
+        <v>1.27</v>
       </c>
       <c r="AU7">
-        <v>1.81</v>
+        <v>1.27</v>
       </c>
       <c r="AV7">
-        <v>1.92</v>
+        <v>1.27</v>
       </c>
       <c r="AW7">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="AX7">
-        <v>9.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="AY7">
-        <v>1.87</v>
+        <v>1.18</v>
       </c>
       <c r="AZ7">
-        <v>10</v>
+        <v>1.27</v>
       </c>
       <c r="BA7">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="BB7">
-        <v>16.5</v>
+        <v>1.23</v>
       </c>
       <c r="BC7">
-        <v>14</v>
+        <v>1.22</v>
       </c>
       <c r="BD7">
-        <v>2.02</v>
+        <v>1.27</v>
       </c>
       <c r="BE7">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="BF7">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="BG7">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="BH7">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BI7">
         <v>2.56</v>
@@ -2681,55 +2681,55 @@
         <v>13</v>
       </c>
       <c r="BK7">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="BN7">
         <v>7.4</v>
       </c>
       <c r="BO7">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BP7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ7">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="BR7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS7">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="BT7">
         <v>9.800000000000001</v>
       </c>
       <c r="BU7">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="BV7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW7">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="BX7">
         <v>50</v>
       </c>
       <c r="BY7">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="BZ7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CA7">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="CB7" t="s">
         <v>230</v>
@@ -2752,19 +2752,19 @@
         <v>184</v>
       </c>
       <c r="F8">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G8">
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2994,10 +2994,10 @@
         <v>185</v>
       </c>
       <c r="F9">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="G9">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H9">
         <v>5.7</v>
@@ -3006,13 +3006,13 @@
         <v>6.6</v>
       </c>
       <c r="J9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
         <v>3.8</v>
       </c>
       <c r="L9">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M9">
         <v>1.09</v>
@@ -3045,7 +3045,7 @@
         <v>1.18</v>
       </c>
       <c r="W9">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="X9">
         <v>13</v>
@@ -3159,7 +3159,7 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="BJ9">
         <v>16</v>
@@ -3171,10 +3171,10 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="BN9">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO9">
         <v>2.88</v>
@@ -3183,37 +3183,37 @@
         <v>17</v>
       </c>
       <c r="BQ9">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BR9">
         <v>48</v>
       </c>
       <c r="BS9">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BT9">
         <v>13</v>
       </c>
       <c r="BU9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
+        <v>1.77</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
         <v>1.78</v>
       </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
-        <v>1.79</v>
-      </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CB9" t="s">
         <v>230</v>
@@ -3236,22 +3236,22 @@
         <v>186</v>
       </c>
       <c r="F10">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G10">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="H10">
         <v>4.7</v>
       </c>
       <c r="I10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>4.1</v>
       </c>
       <c r="K10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L10">
         <v>1.28</v>
@@ -3260,34 +3260,34 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O10">
         <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
       </c>
       <c r="R10">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S10">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T10">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U10">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V10">
         <v>1.2</v>
       </c>
       <c r="W10">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X10">
         <v>24</v>
@@ -3311,10 +3311,10 @@
         <v>23</v>
       </c>
       <c r="AE10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG10">
         <v>12</v>
@@ -3326,118 +3326,118 @@
         <v>60</v>
       </c>
       <c r="AJ10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM10">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN10">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AO10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP10">
+        <v>16</v>
+      </c>
+      <c r="AQ10">
+        <v>16.5</v>
+      </c>
+      <c r="AR10">
+        <v>5</v>
+      </c>
+      <c r="AS10">
+        <v>5.4</v>
+      </c>
+      <c r="AT10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU10">
+        <v>7.8</v>
+      </c>
+      <c r="AV10">
         <v>15.5</v>
       </c>
-      <c r="AQ10">
-        <v>16</v>
-      </c>
-      <c r="AR10">
-        <v>4.6</v>
-      </c>
-      <c r="AS10">
-        <v>4.9</v>
-      </c>
-      <c r="AT10">
-        <v>8.4</v>
-      </c>
-      <c r="AU10">
-        <v>7.6</v>
-      </c>
-      <c r="AV10">
-        <v>15</v>
-      </c>
       <c r="AW10">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX10">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY10">
         <v>8</v>
       </c>
       <c r="AZ10">
+        <v>14</v>
+      </c>
+      <c r="BA10">
+        <v>5.1</v>
+      </c>
+      <c r="BB10">
         <v>13.5</v>
       </c>
-      <c r="BA10">
-        <v>4.7</v>
-      </c>
-      <c r="BB10">
-        <v>14</v>
-      </c>
       <c r="BC10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD10">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE10">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF10">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG10">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH10">
         <v>4.1</v>
       </c>
       <c r="BI10">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ10">
         <v>9.6</v>
       </c>
       <c r="BK10">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO10">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT10">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BU10">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV10">
         <v>1000</v>
@@ -3449,7 +3449,7 @@
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3484,7 +3484,7 @@
         <v>3.7</v>
       </c>
       <c r="H11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I11">
         <v>2.64</v>
@@ -3502,7 +3502,7 @@
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O11">
         <v>1.47</v>
@@ -3514,16 +3514,16 @@
         <v>2.36</v>
       </c>
       <c r="R11">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S11">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="V11">
         <v>1.61</v>
@@ -3532,112 +3532,112 @@
         <v>1.37</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y11">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC11">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP11">
-        <v>1.29</v>
+        <v>8.6</v>
       </c>
       <c r="AQ11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR11">
-        <v>1.29</v>
+        <v>13</v>
       </c>
       <c r="AS11">
-        <v>1.29</v>
+        <v>5.4</v>
       </c>
       <c r="AT11">
-        <v>1.29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV11">
-        <v>1.29</v>
+        <v>10</v>
       </c>
       <c r="AW11">
-        <v>1.29</v>
+        <v>5.2</v>
       </c>
       <c r="AX11">
-        <v>1.29</v>
+        <v>19</v>
       </c>
       <c r="AY11">
-        <v>1.29</v>
+        <v>12.5</v>
       </c>
       <c r="AZ11">
-        <v>1.29</v>
+        <v>16.5</v>
       </c>
       <c r="BA11">
-        <v>1.29</v>
+        <v>5.6</v>
       </c>
       <c r="BB11">
-        <v>1.29</v>
+        <v>5.7</v>
       </c>
       <c r="BC11">
-        <v>1.29</v>
+        <v>5.5</v>
       </c>
       <c r="BD11">
-        <v>1.29</v>
+        <v>5.7</v>
       </c>
       <c r="BE11">
-        <v>1.29</v>
+        <v>5.9</v>
       </c>
       <c r="BF11">
-        <v>1.29</v>
+        <v>5.6</v>
       </c>
       <c r="BG11">
-        <v>1.29</v>
+        <v>5.2</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3723,16 +3723,16 @@
         <v>2</v>
       </c>
       <c r="G12">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I12">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="J12">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K12">
         <v>4.8</v>
@@ -3756,10 +3756,10 @@
         <v>1.43</v>
       </c>
       <c r="R12">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S12">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3768,7 +3768,7 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W12">
         <v>1.79</v>
@@ -3786,13 +3786,13 @@
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC12">
         <v>1000</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE12">
         <v>1000</v>
@@ -3801,10 +3801,10 @@
         <v>1000</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI12">
         <v>1000</v>
@@ -3816,7 +3816,7 @@
         <v>1000</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM12">
         <v>1000</v>
@@ -3828,58 +3828,58 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3986,22 +3986,22 @@
         <v>1.04</v>
       </c>
       <c r="N13">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="O13">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P13">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q13">
         <v>1.63</v>
       </c>
       <c r="R13">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S13">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="T13">
         <v>1.57</v>
@@ -4016,7 +4016,7 @@
         <v>1.56</v>
       </c>
       <c r="X13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y13">
         <v>18.5</v>
@@ -4025,7 +4025,7 @@
         <v>26</v>
       </c>
       <c r="AA13">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB13">
         <v>18</v>
@@ -4064,7 +4064,7 @@
         <v>75</v>
       </c>
       <c r="AN13">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO13">
         <v>21</v>
@@ -4103,16 +4103,16 @@
         <v>11</v>
       </c>
       <c r="BA13">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB13">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC13">
         <v>18</v>
       </c>
       <c r="BD13">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE13">
         <v>4.1</v>
@@ -4204,175 +4204,175 @@
         <v>190</v>
       </c>
       <c r="F14">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="G14">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="H14">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="I14">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="J14">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="K14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L14">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M14">
         <v>1.08</v>
       </c>
       <c r="N14">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O14">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P14">
         <v>1.84</v>
       </c>
       <c r="Q14">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="R14">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S14">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="T14">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U14">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V14">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W14">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y14">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AA14">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD14">
+        <v>12</v>
+      </c>
+      <c r="AE14">
+        <v>29</v>
+      </c>
+      <c r="AF14">
+        <v>23</v>
+      </c>
+      <c r="AG14">
         <v>14.5</v>
       </c>
-      <c r="AE14">
-        <v>36</v>
-      </c>
-      <c r="AF14">
-        <v>26</v>
-      </c>
-      <c r="AG14">
-        <v>16.5</v>
-      </c>
       <c r="AH14">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI14">
         <v>55</v>
       </c>
       <c r="AJ14">
+        <v>70</v>
+      </c>
+      <c r="AK14">
+        <v>48</v>
+      </c>
+      <c r="AL14">
         <v>65</v>
       </c>
-      <c r="AK14">
-        <v>44</v>
-      </c>
-      <c r="AL14">
-        <v>60</v>
-      </c>
       <c r="AM14">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AO14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP14">
+        <v>5.2</v>
+      </c>
+      <c r="AQ14">
+        <v>4.4</v>
+      </c>
+      <c r="AR14">
+        <v>5.3</v>
+      </c>
+      <c r="AS14">
+        <v>6.6</v>
+      </c>
+      <c r="AT14">
+        <v>4.7</v>
+      </c>
+      <c r="AU14">
+        <v>5</v>
+      </c>
+      <c r="AV14">
+        <v>4.7</v>
+      </c>
+      <c r="AW14">
+        <v>6.2</v>
+      </c>
+      <c r="AX14">
+        <v>5.9</v>
+      </c>
+      <c r="AY14">
+        <v>5.1</v>
+      </c>
+      <c r="AZ14">
+        <v>5.5</v>
+      </c>
+      <c r="BA14">
+        <v>6.8</v>
+      </c>
+      <c r="BB14">
+        <v>7</v>
+      </c>
+      <c r="BC14">
+        <v>6.8</v>
+      </c>
+      <c r="BD14">
+        <v>7</v>
+      </c>
+      <c r="BE14">
+        <v>7.4</v>
+      </c>
+      <c r="BF14">
+        <v>6.8</v>
+      </c>
+      <c r="BG14">
+        <v>6.2</v>
+      </c>
+      <c r="BH14">
+        <v>3.25</v>
+      </c>
+      <c r="BI14">
+        <v>2.66</v>
+      </c>
+      <c r="BJ14">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AQ14">
-        <v>9</v>
-      </c>
-      <c r="AR14">
-        <v>14.5</v>
-      </c>
-      <c r="AS14">
-        <v>23</v>
-      </c>
-      <c r="AT14">
-        <v>10</v>
-      </c>
-      <c r="AU14">
-        <v>5.9</v>
-      </c>
-      <c r="AV14">
-        <v>10.5</v>
-      </c>
-      <c r="AW14">
-        <v>18</v>
-      </c>
-      <c r="AX14">
-        <v>18</v>
-      </c>
-      <c r="AY14">
-        <v>11.5</v>
-      </c>
-      <c r="AZ14">
-        <v>15.5</v>
-      </c>
-      <c r="BA14">
-        <v>26</v>
-      </c>
-      <c r="BB14">
-        <v>32</v>
-      </c>
-      <c r="BC14">
-        <v>22</v>
-      </c>
-      <c r="BD14">
-        <v>29</v>
-      </c>
-      <c r="BE14">
-        <v>4.4</v>
-      </c>
-      <c r="BF14">
-        <v>21</v>
-      </c>
-      <c r="BG14">
-        <v>15.5</v>
-      </c>
-      <c r="BH14">
-        <v>3.3</v>
-      </c>
-      <c r="BI14">
-        <v>2.98</v>
-      </c>
-      <c r="BJ14">
-        <v>9.6</v>
       </c>
       <c r="BK14">
         <v>5.9</v>
@@ -4381,49 +4381,49 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>13.5</v>
+        <v>2.62</v>
       </c>
       <c r="BN14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO14">
+        <v>4.5</v>
+      </c>
+      <c r="BP14">
+        <v>26</v>
+      </c>
+      <c r="BQ14">
+        <v>2.42</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>2.5</v>
+      </c>
+      <c r="BT14">
         <v>5.4</v>
       </c>
-      <c r="BP14">
-        <v>25</v>
-      </c>
-      <c r="BQ14">
-        <v>9.4</v>
-      </c>
-      <c r="BR14">
-        <v>38</v>
-      </c>
-      <c r="BS14">
-        <v>10.5</v>
-      </c>
-      <c r="BT14">
-        <v>5.6</v>
-      </c>
       <c r="BU14">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BV14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW14">
-        <v>8.6</v>
+        <v>2.36</v>
       </c>
       <c r="BX14">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>10</v>
+        <v>2.48</v>
       </c>
       <c r="BZ14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CA14">
-        <v>10</v>
+        <v>2.46</v>
       </c>
       <c r="CB14" t="s">
         <v>230</v>
@@ -4446,76 +4446,76 @@
         <v>191</v>
       </c>
       <c r="F15">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G15">
         <v>1.82</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="I15">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J15">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M15">
         <v>1.06</v>
       </c>
       <c r="N15">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O15">
         <v>1.29</v>
       </c>
       <c r="P15">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q15">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R15">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S15">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T15">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="U15">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V15">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W15">
         <v>2.2</v>
       </c>
       <c r="X15">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z15">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA15">
         <v>150</v>
       </c>
       <c r="AB15">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC15">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15">
         <v>24</v>
@@ -4527,7 +4527,7 @@
         <v>13</v>
       </c>
       <c r="AG15">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH15">
         <v>23</v>
@@ -4542,7 +4542,7 @@
         <v>21</v>
       </c>
       <c r="AL15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM15">
         <v>120</v>
@@ -4554,118 +4554,118 @@
         <v>90</v>
       </c>
       <c r="AP15">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="AQ15">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AR15">
+        <v>5.2</v>
+      </c>
+      <c r="AS15">
+        <v>5.5</v>
+      </c>
+      <c r="AT15">
+        <v>3.55</v>
+      </c>
+      <c r="AU15">
+        <v>3.55</v>
+      </c>
+      <c r="AV15">
+        <v>4.6</v>
+      </c>
+      <c r="AW15">
+        <v>5.4</v>
+      </c>
+      <c r="AX15">
+        <v>4</v>
+      </c>
+      <c r="AY15">
+        <v>3.85</v>
+      </c>
+      <c r="AZ15">
+        <v>4.6</v>
+      </c>
+      <c r="BA15">
+        <v>5.4</v>
+      </c>
+      <c r="BB15">
+        <v>4.6</v>
+      </c>
+      <c r="BC15">
+        <v>4.5</v>
+      </c>
+      <c r="BD15">
         <v>5</v>
       </c>
-      <c r="AS15">
+      <c r="BE15">
+        <v>5.5</v>
+      </c>
+      <c r="BF15">
+        <v>3.95</v>
+      </c>
+      <c r="BG15">
         <v>5.4</v>
       </c>
-      <c r="AT15">
-        <v>7.8</v>
-      </c>
-      <c r="AU15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV15">
+      <c r="BH15">
+        <v>3.65</v>
+      </c>
+      <c r="BI15">
+        <v>2.94</v>
+      </c>
+      <c r="BJ15">
+        <v>10</v>
+      </c>
+      <c r="BK15">
+        <v>6</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>2.86</v>
+      </c>
+      <c r="BN15">
         <v>4.5</v>
       </c>
-      <c r="AW15">
-        <v>5.2</v>
-      </c>
-      <c r="AX15">
-        <v>9.6</v>
-      </c>
-      <c r="AY15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ15">
-        <v>17</v>
-      </c>
-      <c r="BA15">
-        <v>5.2</v>
-      </c>
-      <c r="BB15">
-        <v>16</v>
-      </c>
-      <c r="BC15">
-        <v>14</v>
-      </c>
-      <c r="BD15">
-        <v>4.9</v>
-      </c>
-      <c r="BE15">
-        <v>5.3</v>
-      </c>
-      <c r="BF15">
-        <v>9.4</v>
-      </c>
-      <c r="BG15">
-        <v>5.3</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.93</v>
-      </c>
-      <c r="BJ15">
-        <v>13.5</v>
-      </c>
-      <c r="BK15">
-        <v>1.69</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.93</v>
-      </c>
-      <c r="BN15">
-        <v>5.9</v>
-      </c>
       <c r="BO15">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BQ15">
-        <v>1.74</v>
+        <v>6.6</v>
       </c>
       <c r="BR15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.84</v>
+        <v>2.64</v>
       </c>
       <c r="BT15">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BU15">
-        <v>1.66</v>
+        <v>5.4</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.87</v>
+        <v>3.3</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.88</v>
+        <v>3.3</v>
       </c>
       <c r="BZ15">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.81</v>
+        <v>2.58</v>
       </c>
       <c r="CB15" t="s">
         <v>230</v>
@@ -4688,10 +4688,10 @@
         <v>192</v>
       </c>
       <c r="F16">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="G16">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H16">
         <v>2.4</v>
@@ -4700,154 +4700,154 @@
         <v>2.66</v>
       </c>
       <c r="J16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K16">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N16">
         <v>3.6</v>
       </c>
       <c r="O16">
+        <v>1.34</v>
+      </c>
+      <c r="P16">
+        <v>1.84</v>
+      </c>
+      <c r="Q16">
+        <v>1.97</v>
+      </c>
+      <c r="R16">
         <v>1.32</v>
       </c>
-      <c r="P16">
-        <v>1.72</v>
-      </c>
-      <c r="Q16">
-        <v>1.93</v>
-      </c>
-      <c r="R16">
-        <v>1.24</v>
-      </c>
       <c r="S16">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V16">
         <v>1.61</v>
       </c>
       <c r="W16">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X16">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y16">
+        <v>11</v>
+      </c>
+      <c r="Z16">
+        <v>17.5</v>
+      </c>
+      <c r="AA16">
+        <v>38</v>
+      </c>
+      <c r="AB16">
+        <v>12.5</v>
+      </c>
+      <c r="AC16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD16">
+        <v>12.5</v>
+      </c>
+      <c r="AE16">
+        <v>30</v>
+      </c>
+      <c r="AF16">
+        <v>23</v>
+      </c>
+      <c r="AG16">
         <v>14.5</v>
       </c>
-      <c r="Z16">
-        <v>23</v>
-      </c>
-      <c r="AA16">
+      <c r="AH16">
+        <v>18</v>
+      </c>
+      <c r="AI16">
+        <v>44</v>
+      </c>
+      <c r="AJ16">
+        <v>55</v>
+      </c>
+      <c r="AK16">
+        <v>38</v>
+      </c>
+      <c r="AL16">
         <v>50</v>
       </c>
-      <c r="AB16">
-        <v>16.5</v>
-      </c>
-      <c r="AC16">
-        <v>10.5</v>
-      </c>
-      <c r="AD16">
-        <v>16.5</v>
-      </c>
-      <c r="AE16">
-        <v>40</v>
-      </c>
-      <c r="AF16">
-        <v>30</v>
-      </c>
-      <c r="AG16">
-        <v>19</v>
-      </c>
-      <c r="AH16">
+      <c r="AM16">
+        <v>120</v>
+      </c>
+      <c r="AN16">
+        <v>36</v>
+      </c>
+      <c r="AO16">
         <v>25</v>
       </c>
-      <c r="AI16">
-        <v>60</v>
-      </c>
-      <c r="AJ16">
-        <v>75</v>
-      </c>
-      <c r="AK16">
-        <v>50</v>
-      </c>
-      <c r="AL16">
-        <v>65</v>
-      </c>
-      <c r="AM16">
-        <v>1000</v>
-      </c>
-      <c r="AN16">
-        <v>1000</v>
-      </c>
-      <c r="AO16">
-        <v>1000</v>
-      </c>
       <c r="AP16">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="AQ16">
-        <v>2.22</v>
+        <v>4.9</v>
       </c>
       <c r="AR16">
-        <v>11.5</v>
+        <v>5.9</v>
       </c>
       <c r="AS16">
-        <v>2.48</v>
+        <v>7.2</v>
       </c>
       <c r="AT16">
-        <v>2.26</v>
+        <v>5.2</v>
       </c>
       <c r="AU16">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="AV16">
-        <v>2.26</v>
+        <v>5.2</v>
       </c>
       <c r="AW16">
-        <v>19.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX16">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="AY16">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="AZ16">
-        <v>2.36</v>
+        <v>6</v>
       </c>
       <c r="BA16">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="BB16">
-        <v>2.52</v>
+        <v>7.6</v>
       </c>
       <c r="BC16">
-        <v>23</v>
+        <v>7.2</v>
       </c>
       <c r="BD16">
-        <v>2.52</v>
+        <v>7.6</v>
       </c>
       <c r="BE16">
-        <v>2.62</v>
+        <v>8.4</v>
       </c>
       <c r="BF16">
-        <v>2.62</v>
+        <v>7.2</v>
       </c>
       <c r="BG16">
-        <v>2.62</v>
+        <v>6.6</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4859,7 +4859,7 @@
         <v>13.5</v>
       </c>
       <c r="BK16">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BL16">
         <v>1000</v>
@@ -4871,10 +4871,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BO16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ16">
         <v>1.71</v>
@@ -4889,7 +4889,7 @@
         <v>7.6</v>
       </c>
       <c r="BU16">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BV16">
         <v>29</v>
@@ -4907,7 +4907,7 @@
         <v>44</v>
       </c>
       <c r="CA16">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CB16" t="s">
         <v>230</v>
@@ -4933,13 +4933,13 @@
         <v>3.55</v>
       </c>
       <c r="G17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H17">
         <v>1.99</v>
       </c>
       <c r="I17">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J17">
         <v>3.8</v>
@@ -4978,10 +4978,10 @@
         <v>2.1</v>
       </c>
       <c r="V17">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="W17">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4990,7 +4990,7 @@
         <v>1000</v>
       </c>
       <c r="Z17">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA17">
         <v>1000</v>
@@ -5008,10 +5008,10 @@
         <v>1000</v>
       </c>
       <c r="AF17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG17">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH17">
         <v>20</v>
@@ -5038,10 +5038,10 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AQ17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AR17">
         <v>10.5</v>
@@ -5056,7 +5056,7 @@
         <v>1.35</v>
       </c>
       <c r="AV17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AW17">
         <v>1.53</v>
@@ -5172,22 +5172,22 @@
         <v>194</v>
       </c>
       <c r="F18">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H18">
         <v>1.79</v>
       </c>
       <c r="I18">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="J18">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5196,7 +5196,7 @@
         <v>1.03</v>
       </c>
       <c r="N18">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>1.16</v>
@@ -5217,10 +5217,10 @@
         <v>1.48</v>
       </c>
       <c r="U18">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="V18">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W18">
         <v>1.27</v>
@@ -5417,13 +5417,13 @@
         <v>2.16</v>
       </c>
       <c r="G19">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H19">
         <v>3.15</v>
       </c>
       <c r="I19">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J19">
         <v>3.8</v>
@@ -5462,10 +5462,10 @@
         <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5656,16 +5656,16 @@
         <v>196</v>
       </c>
       <c r="F20">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="G20">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="H20">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="I20">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J20">
         <v>3.75</v>
@@ -5683,31 +5683,31 @@
         <v>4.5</v>
       </c>
       <c r="O20">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P20">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="Q20">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R20">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S20">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="T20">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U20">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V20">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="X20">
         <v>22</v>
@@ -5773,7 +5773,7 @@
         <v>16.5</v>
       </c>
       <c r="AS20">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT20">
         <v>10</v>
@@ -5785,7 +5785,7 @@
         <v>10</v>
       </c>
       <c r="AW20">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX20">
         <v>13.5</v>
@@ -5800,16 +5800,16 @@
         <v>4.8</v>
       </c>
       <c r="BB20">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC20">
         <v>18.5</v>
       </c>
       <c r="BD20">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BE20">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF20">
         <v>12</v>
@@ -5901,31 +5901,31 @@
         <v>2.14</v>
       </c>
       <c r="G21">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="H21">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="I21">
+        <v>3.55</v>
+      </c>
+      <c r="J21">
+        <v>3.65</v>
+      </c>
+      <c r="K21">
         <v>4.1</v>
       </c>
-      <c r="J21">
-        <v>3.75</v>
-      </c>
-      <c r="K21">
-        <v>4.2</v>
-      </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N21">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="O21">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P21">
         <v>2.24</v>
@@ -5934,130 +5934,130 @@
         <v>1.67</v>
       </c>
       <c r="R21">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S21">
+        <v>2.52</v>
+      </c>
+      <c r="T21">
+        <v>1.61</v>
+      </c>
+      <c r="U21">
+        <v>2.36</v>
+      </c>
+      <c r="V21">
+        <v>1.39</v>
+      </c>
+      <c r="W21">
         <v>1.7</v>
       </c>
-      <c r="T21">
-        <v>1.45</v>
-      </c>
-      <c r="U21">
-        <v>2.06</v>
-      </c>
-      <c r="V21">
-        <v>1.36</v>
-      </c>
-      <c r="W21">
-        <v>1.75</v>
-      </c>
       <c r="X21">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y21">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="Z21">
+        <v>32</v>
+      </c>
+      <c r="AA21">
+        <v>70</v>
+      </c>
+      <c r="AB21">
+        <v>15</v>
+      </c>
+      <c r="AC21">
+        <v>11</v>
+      </c>
+      <c r="AD21">
+        <v>17.5</v>
+      </c>
+      <c r="AE21">
+        <v>42</v>
+      </c>
+      <c r="AF21">
+        <v>19.5</v>
+      </c>
+      <c r="AG21">
+        <v>14</v>
+      </c>
+      <c r="AH21">
+        <v>19.5</v>
+      </c>
+      <c r="AI21">
+        <v>48</v>
+      </c>
+      <c r="AJ21">
+        <v>36</v>
+      </c>
+      <c r="AK21">
+        <v>27</v>
+      </c>
+      <c r="AL21">
         <v>38</v>
       </c>
-      <c r="AA21">
-        <v>1000</v>
-      </c>
-      <c r="AB21">
-        <v>18.5</v>
-      </c>
-      <c r="AC21">
-        <v>13.5</v>
-      </c>
-      <c r="AD21">
-        <v>21</v>
-      </c>
-      <c r="AE21">
-        <v>50</v>
-      </c>
-      <c r="AF21">
-        <v>23</v>
-      </c>
-      <c r="AG21">
-        <v>17</v>
-      </c>
-      <c r="AH21">
-        <v>23</v>
-      </c>
-      <c r="AI21">
-        <v>1000</v>
-      </c>
-      <c r="AJ21">
-        <v>40</v>
-      </c>
-      <c r="AK21">
-        <v>30</v>
-      </c>
-      <c r="AL21">
-        <v>46</v>
-      </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP21">
-        <v>1.95</v>
+        <v>3.65</v>
       </c>
       <c r="AQ21">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="AR21">
-        <v>15.5</v>
+        <v>3.8</v>
       </c>
       <c r="AS21">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="AT21">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="AU21">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="AV21">
-        <v>1.79</v>
+        <v>3.45</v>
       </c>
       <c r="AW21">
-        <v>1.88</v>
+        <v>3.9</v>
       </c>
       <c r="AX21">
-        <v>9.6</v>
+        <v>3.5</v>
       </c>
       <c r="AY21">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="AZ21">
-        <v>9.6</v>
+        <v>3.5</v>
       </c>
       <c r="BA21">
-        <v>1.96</v>
+        <v>3.95</v>
       </c>
       <c r="BB21">
-        <v>16.5</v>
+        <v>3.85</v>
       </c>
       <c r="BC21">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="BD21">
-        <v>18.5</v>
+        <v>3.85</v>
       </c>
       <c r="BE21">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="BF21">
-        <v>1.96</v>
+        <v>3.4</v>
       </c>
       <c r="BG21">
-        <v>1.96</v>
+        <v>3.8</v>
       </c>
       <c r="BH21">
         <v>5.5</v>
@@ -6143,43 +6143,43 @@
         <v>1.68</v>
       </c>
       <c r="G22">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H22">
         <v>4.8</v>
       </c>
       <c r="I22">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J22">
         <v>4</v>
       </c>
       <c r="K22">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N22">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="O22">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P22">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q22">
         <v>1.69</v>
       </c>
       <c r="R22">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S22">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="T22">
         <v>1.72</v>
@@ -6188,172 +6188,172 @@
         <v>2.16</v>
       </c>
       <c r="V22">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W22">
         <v>2.2</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP22">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AQ22">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AR22">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AS22">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AT22">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AW22">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AX22">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY22">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ22">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA22">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB22">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BC22">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD22">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE22">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI22">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK22">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO22">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ22">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS22">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU22">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ22">
         <v>0</v>
@@ -6385,16 +6385,16 @@
         <v>1.64</v>
       </c>
       <c r="G23">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H23">
         <v>5.3</v>
       </c>
       <c r="I23">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K23">
         <v>4.8</v>
@@ -6412,22 +6412,22 @@
         <v>1.16</v>
       </c>
       <c r="P23">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q23">
         <v>1.49</v>
       </c>
       <c r="R23">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S23">
         <v>2.2</v>
       </c>
       <c r="T23">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U23">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
         <v>1.01</v>
@@ -6484,22 +6484,22 @@
         <v>75</v>
       </c>
       <c r="AN23">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO23">
         <v>48</v>
       </c>
       <c r="AP23">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ23">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AR23">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AS23">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT23">
         <v>12</v>
@@ -6508,10 +6508,10 @@
         <v>10</v>
       </c>
       <c r="AV23">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AW23">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX23">
         <v>11.5</v>
@@ -6520,10 +6520,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ23">
-        <v>3.9</v>
+        <v>14.5</v>
       </c>
       <c r="BA23">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB23">
         <v>15.5</v>
@@ -6532,16 +6532,16 @@
         <v>13.5</v>
       </c>
       <c r="BD23">
-        <v>4.1</v>
+        <v>17.5</v>
       </c>
       <c r="BE23">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF23">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BG23">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6624,58 +6624,58 @@
         <v>200</v>
       </c>
       <c r="F24">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="G24">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="H24">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="I24">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="J24">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K24">
-        <v>3.85</v>
+        <v>7.4</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M24">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N24">
         <v>3.1</v>
       </c>
       <c r="O24">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="P24">
         <v>1.81</v>
       </c>
       <c r="Q24">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R24">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S24">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="T24">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="U24">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W24">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6786,64 +6786,64 @@
         <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BI24">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
       </c>
       <c r="BK24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BN24">
         <v>1000</v>
       </c>
       <c r="BO24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BP24">
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BT24">
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="CB24" t="s">
         <v>230</v>
@@ -6866,19 +6866,19 @@
         <v>201</v>
       </c>
       <c r="F25">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="G25">
         <v>990</v>
       </c>
       <c r="H25">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="I25">
         <v>990</v>
       </c>
       <c r="J25">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="K25">
         <v>950</v>
@@ -7108,22 +7108,22 @@
         <v>202</v>
       </c>
       <c r="F26">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G26">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H26">
         <v>2.24</v>
       </c>
       <c r="I26">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="J26">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K26">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7138,10 +7138,10 @@
         <v>1.21</v>
       </c>
       <c r="P26">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q26">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R26">
         <v>1.53</v>
@@ -7153,16 +7153,16 @@
         <v>1.58</v>
       </c>
       <c r="U26">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V26">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W26">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X26">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y26">
         <v>15</v>
@@ -7171,7 +7171,7 @@
         <v>19</v>
       </c>
       <c r="AA26">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB26">
         <v>18</v>
@@ -7180,7 +7180,7 @@
         <v>11.5</v>
       </c>
       <c r="AD26">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE26">
         <v>27</v>
@@ -7252,16 +7252,16 @@
         <v>21</v>
       </c>
       <c r="BB26">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC26">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BD26">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE26">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF26">
         <v>15</v>
@@ -7350,58 +7350,58 @@
         <v>203</v>
       </c>
       <c r="F27">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="H27">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="I27">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="J27">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="K27">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="L27">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M27">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N27">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O27">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P27">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="Q27">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R27">
         <v>1.31</v>
       </c>
       <c r="S27">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="T27">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="U27">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="V27">
         <v>1.64</v>
       </c>
       <c r="W27">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7410,10 +7410,10 @@
         <v>1000</v>
       </c>
       <c r="Z27">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
         <v>1000</v>
@@ -7431,7 +7431,7 @@
         <v>1000</v>
       </c>
       <c r="AG27">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
         <v>1000</v>
@@ -7458,118 +7458,118 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AR27">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AT27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AU27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AV27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AX27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AY27">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BA27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BB27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BC27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BD27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BE27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BF27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI27">
-        <v>1.9</v>
+        <v>2.66</v>
       </c>
       <c r="BJ27">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK27">
-        <v>1.66</v>
+        <v>5.1</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="BN27">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BO27">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP27">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BQ27">
-        <v>1.81</v>
+        <v>7.6</v>
       </c>
       <c r="BR27">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BS27">
-        <v>1.83</v>
+        <v>8.4</v>
       </c>
       <c r="BT27">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BU27">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV27">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BW27">
-        <v>1.76</v>
+        <v>6.6</v>
       </c>
       <c r="BX27">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BY27">
-        <v>1.82</v>
+        <v>8</v>
       </c>
       <c r="BZ27">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="CA27">
-        <v>1.81</v>
+        <v>7.6</v>
       </c>
       <c r="CB27" t="s">
         <v>230</v>
@@ -7616,7 +7616,7 @@
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O28">
         <v>1.18</v>
@@ -7637,7 +7637,7 @@
         <v>2.16</v>
       </c>
       <c r="U28">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V28">
         <v>1.05</v>
@@ -7667,13 +7667,13 @@
         <v>70</v>
       </c>
       <c r="AE28">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AF28">
         <v>8.6</v>
       </c>
       <c r="AG28">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH28">
         <v>44</v>
@@ -7682,7 +7682,7 @@
         <v>240</v>
       </c>
       <c r="AJ28">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AK28">
         <v>15</v>
@@ -7691,25 +7691,25 @@
         <v>55</v>
       </c>
       <c r="AM28">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN28">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO28">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="AP28">
         <v>19.5</v>
       </c>
       <c r="AQ28">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AR28">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS28">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT28">
         <v>7.2</v>
@@ -7718,10 +7718,10 @@
         <v>13.5</v>
       </c>
       <c r="AV28">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AW28">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX28">
         <v>6.8</v>
@@ -7730,10 +7730,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ28">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BA28">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB28">
         <v>6.8</v>
@@ -7742,34 +7742,34 @@
         <v>12</v>
       </c>
       <c r="BD28">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE28">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF28">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BG28">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH28">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="BJ28">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BK28">
-        <v>2.54</v>
+        <v>1.83</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="BN28">
         <v>5</v>
@@ -7781,37 +7781,37 @@
         <v>9.6</v>
       </c>
       <c r="BQ28">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BR28">
         <v>34</v>
       </c>
       <c r="BS28">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="BT28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BU28">
-        <v>2.62</v>
+        <v>1.86</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="BZ28">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA28">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="CB28" t="s">
         <v>230</v>
@@ -7837,13 +7837,13 @@
         <v>4.3</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H29">
         <v>1.77</v>
       </c>
       <c r="I29">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J29">
         <v>3.95</v>
@@ -7852,7 +7852,7 @@
         <v>4.4</v>
       </c>
       <c r="L29">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M29">
         <v>1.05</v>
@@ -7885,7 +7885,7 @@
         <v>2.12</v>
       </c>
       <c r="W29">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X29">
         <v>24</v>
@@ -7933,10 +7933,10 @@
         <v>55</v>
       </c>
       <c r="AM29">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN29">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO29">
         <v>9.800000000000001</v>
@@ -7966,7 +7966,7 @@
         <v>13.5</v>
       </c>
       <c r="AX29">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY29">
         <v>14</v>
@@ -7981,7 +7981,7 @@
         <v>7.6</v>
       </c>
       <c r="BC29">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD29">
         <v>38</v>
@@ -7996,64 +7996,64 @@
         <v>7.4</v>
       </c>
       <c r="BH29">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BI29">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="BJ29">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="BK29">
-        <v>2.54</v>
+        <v>5.1</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>3.15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN29">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BO29">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BP29">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BQ29">
-        <v>2.96</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS29">
-        <v>2.98</v>
+        <v>8.6</v>
       </c>
       <c r="BT29">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BU29">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="BV29">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="BW29">
-        <v>2.66</v>
+        <v>5.8</v>
       </c>
       <c r="BX29">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BY29">
-        <v>2.88</v>
+        <v>7.4</v>
       </c>
       <c r="BZ29">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="CA29">
-        <v>2.78</v>
+        <v>6.8</v>
       </c>
       <c r="CB29" t="s">
         <v>230</v>
@@ -8079,10 +8079,10 @@
         <v>1.66</v>
       </c>
       <c r="G30">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H30">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I30">
         <v>5.9</v>
@@ -8109,7 +8109,7 @@
         <v>2.1</v>
       </c>
       <c r="Q30">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R30">
         <v>1.43</v>
@@ -8118,13 +8118,13 @@
         <v>3</v>
       </c>
       <c r="T30">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U30">
         <v>2.08</v>
       </c>
       <c r="V30">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W30">
         <v>2.36</v>
@@ -8136,7 +8136,7 @@
         <v>24</v>
       </c>
       <c r="Z30">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AA30">
         <v>160</v>
@@ -8178,7 +8178,7 @@
         <v>120</v>
       </c>
       <c r="AN30">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AO30">
         <v>95</v>
@@ -8190,10 +8190,10 @@
         <v>15.5</v>
       </c>
       <c r="AR30">
-        <v>30</v>
+        <v>9.4</v>
       </c>
       <c r="AS30">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AT30">
         <v>8</v>
@@ -8205,7 +8205,7 @@
         <v>16.5</v>
       </c>
       <c r="AW30">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX30">
         <v>9.4</v>
@@ -8217,10 +8217,10 @@
         <v>17.5</v>
       </c>
       <c r="BA30">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BB30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC30">
         <v>15</v>
@@ -8229,13 +8229,13 @@
         <v>24</v>
       </c>
       <c r="BE30">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BF30">
         <v>8.199999999999999</v>
       </c>
       <c r="BG30">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8247,7 +8247,7 @@
         <v>13.5</v>
       </c>
       <c r="BK30">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="BL30">
         <v>1000</v>
@@ -8256,7 +8256,7 @@
         <v>1.95</v>
       </c>
       <c r="BN30">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO30">
         <v>1.46</v>
@@ -8265,7 +8265,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ30">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BR30">
         <v>34</v>
@@ -8292,10 +8292,10 @@
         <v>1.9</v>
       </c>
       <c r="BZ30">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CA30">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CB30" t="s">
         <v>230</v>
@@ -8321,19 +8321,19 @@
         <v>1.78</v>
       </c>
       <c r="G31">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H31">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I31">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J31">
         <v>4.2</v>
       </c>
       <c r="K31">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8342,64 +8342,64 @@
         <v>1.03</v>
       </c>
       <c r="N31">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="O31">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P31">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="Q31">
         <v>1.55</v>
       </c>
       <c r="R31">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S31">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T31">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="U31">
-        <v>1.11</v>
+        <v>2.46</v>
       </c>
       <c r="V31">
         <v>1.27</v>
       </c>
       <c r="W31">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X31">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y31">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA31">
         <v>1000</v>
       </c>
       <c r="AB31">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC31">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AD31">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE31">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF31">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AG31">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH31">
         <v>23</v>
@@ -8408,76 +8408,76 @@
         <v>1000</v>
       </c>
       <c r="AJ31">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK31">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AL31">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AM31">
         <v>1000</v>
       </c>
       <c r="AN31">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AO31">
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>2.22</v>
+        <v>20</v>
       </c>
       <c r="AQ31">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AR31">
-        <v>2.22</v>
+        <v>4.2</v>
       </c>
       <c r="AS31">
-        <v>2.22</v>
+        <v>4.6</v>
       </c>
       <c r="AT31">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AU31">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AV31">
         <v>12</v>
       </c>
       <c r="AW31">
-        <v>2.22</v>
+        <v>4.3</v>
       </c>
       <c r="AX31">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AY31">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="AZ31">
         <v>10.5</v>
       </c>
       <c r="BA31">
-        <v>2.22</v>
+        <v>4.6</v>
       </c>
       <c r="BB31">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC31">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BD31">
-        <v>16.5</v>
+        <v>3.95</v>
       </c>
       <c r="BE31">
-        <v>2.22</v>
+        <v>4.6</v>
       </c>
       <c r="BF31">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BG31">
-        <v>2.22</v>
+        <v>4.6</v>
       </c>
       <c r="BH31">
         <v>6</v>
@@ -8489,13 +8489,13 @@
         <v>12.5</v>
       </c>
       <c r="BK31">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BN31">
         <v>6.6</v>
@@ -8504,7 +8504,7 @@
         <v>3.4</v>
       </c>
       <c r="BP31">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ31">
         <v>2.7</v>
@@ -8531,7 +8531,7 @@
         <v>48</v>
       </c>
       <c r="BY31">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BZ31">
         <v>0</v>
@@ -8584,13 +8584,13 @@
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O32">
         <v>1.14</v>
       </c>
       <c r="P32">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q32">
         <v>1.47</v>
@@ -8644,10 +8644,10 @@
         <v>1000</v>
       </c>
       <c r="AH32">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI32">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ32">
         <v>1000</v>
@@ -8710,7 +8710,7 @@
         <v>1.13</v>
       </c>
       <c r="BD32">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BE32">
         <v>1.13</v>
@@ -8725,7 +8725,7 @@
         <v>6.4</v>
       </c>
       <c r="BI32">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ32">
         <v>11</v>
@@ -8737,25 +8737,25 @@
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BN32">
         <v>8.6</v>
       </c>
       <c r="BO32">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP32">
         <v>23</v>
       </c>
       <c r="BQ32">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BR32">
         <v>30</v>
       </c>
       <c r="BS32">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BT32">
         <v>8.6</v>
@@ -8764,16 +8764,16 @@
         <v>4.5</v>
       </c>
       <c r="BV32">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW32">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BX32">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY32">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BZ32">
         <v>0</v>
@@ -8826,16 +8826,16 @@
         <v>1.02</v>
       </c>
       <c r="N33">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O33">
         <v>1.14</v>
       </c>
       <c r="P33">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q33">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="R33">
         <v>1.61</v>
@@ -8844,10 +8844,10 @@
         <v>2.18</v>
       </c>
       <c r="T33">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="U33">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V33">
         <v>1.41</v>
@@ -9047,10 +9047,10 @@
         <v>1.26</v>
       </c>
       <c r="G34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="I34">
         <v>17</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="Q34">
         <v>1.44</v>
@@ -9086,10 +9086,10 @@
         <v>0</v>
       </c>
       <c r="T34">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U34">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V34">
         <v>0</v>
@@ -9122,7 +9122,7 @@
         <v>230</v>
       </c>
       <c r="AF34">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG34">
         <v>14</v>
@@ -9137,7 +9137,7 @@
         <v>12</v>
       </c>
       <c r="AK34">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL34">
         <v>42</v>
@@ -9146,64 +9146,64 @@
         <v>170</v>
       </c>
       <c r="AN34">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AO34">
         <v>250</v>
       </c>
       <c r="AP34">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AQ34">
+        <v>4.7</v>
+      </c>
+      <c r="AR34">
+        <v>5</v>
+      </c>
+      <c r="AS34">
         <v>5.1</v>
       </c>
-      <c r="AR34">
-        <v>5.4</v>
-      </c>
-      <c r="AS34">
-        <v>5.5</v>
-      </c>
       <c r="AT34">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU34">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV34">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AW34">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AX34">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY34">
         <v>10</v>
       </c>
       <c r="AZ34">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BA34">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BB34">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="BC34">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BD34">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE34">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BF34">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BG34">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BH34">
         <v>0</v>
@@ -9289,10 +9289,10 @@
         <v>1.78</v>
       </c>
       <c r="G35">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H35">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I35">
         <v>5.7</v>
@@ -9325,7 +9325,7 @@
         <v>1.32</v>
       </c>
       <c r="S35">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T35">
         <v>1.86</v>
@@ -9406,10 +9406,10 @@
         <v>5.7</v>
       </c>
       <c r="AT35">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AU35">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV35">
         <v>14.5</v>
@@ -9531,76 +9531,76 @@
         <v>2.24</v>
       </c>
       <c r="G36">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="H36">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="I36">
         <v>3.85</v>
       </c>
       <c r="J36">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K36">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L36">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M36">
         <v>1.1</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O36">
         <v>1.43</v>
       </c>
       <c r="P36">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Q36">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R36">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S36">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T36">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U36">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V36">
         <v>1.35</v>
       </c>
       <c r="W36">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X36">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y36">
         <v>13.5</v>
       </c>
       <c r="Z36">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA36">
         <v>90</v>
       </c>
       <c r="AB36">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC36">
         <v>7.8</v>
       </c>
       <c r="AD36">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE36">
         <v>65</v>
@@ -9633,121 +9633,121 @@
         <v>26</v>
       </c>
       <c r="AO36">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP36">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="AQ36">
-        <v>9.6</v>
+        <v>4.3</v>
       </c>
       <c r="AR36">
-        <v>21</v>
+        <v>5.2</v>
       </c>
       <c r="AS36">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT36">
         <v>7</v>
       </c>
       <c r="AU36">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="AV36">
-        <v>14.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW36">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX36">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="AY36">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ36">
-        <v>17.5</v>
+        <v>5</v>
       </c>
       <c r="BA36">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB36">
-        <v>21</v>
+        <v>5.3</v>
       </c>
       <c r="BC36">
-        <v>20</v>
+        <v>5.3</v>
       </c>
       <c r="BD36">
+        <v>5.7</v>
+      </c>
+      <c r="BE36">
+        <v>6</v>
+      </c>
+      <c r="BF36">
+        <v>19.5</v>
+      </c>
+      <c r="BG36">
+        <v>5.8</v>
+      </c>
+      <c r="BH36">
+        <v>3</v>
+      </c>
+      <c r="BI36">
+        <v>2.48</v>
+      </c>
+      <c r="BJ36">
+        <v>11</v>
+      </c>
+      <c r="BK36">
+        <v>6</v>
+      </c>
+      <c r="BL36">
+        <v>1000</v>
+      </c>
+      <c r="BM36">
+        <v>12</v>
+      </c>
+      <c r="BN36">
+        <v>5</v>
+      </c>
+      <c r="BO36">
+        <v>3.95</v>
+      </c>
+      <c r="BP36">
+        <v>18.5</v>
+      </c>
+      <c r="BQ36">
+        <v>7.6</v>
+      </c>
+      <c r="BR36">
+        <v>1000</v>
+      </c>
+      <c r="BS36">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT36">
+        <v>7</v>
+      </c>
+      <c r="BU36">
         <v>5.4</v>
       </c>
-      <c r="BE36">
-        <v>5.8</v>
-      </c>
-      <c r="BF36">
-        <v>17</v>
-      </c>
-      <c r="BG36">
-        <v>5.5</v>
-      </c>
-      <c r="BH36">
-        <v>3.05</v>
-      </c>
-      <c r="BI36">
-        <v>2.54</v>
-      </c>
-      <c r="BJ36">
+      <c r="BV36">
+        <v>1000</v>
+      </c>
+      <c r="BW36">
+        <v>9.6</v>
+      </c>
+      <c r="BX36">
+        <v>1000</v>
+      </c>
+      <c r="BY36">
         <v>10.5</v>
       </c>
-      <c r="BK36">
-        <v>6.2</v>
-      </c>
-      <c r="BL36">
-        <v>1000</v>
-      </c>
-      <c r="BM36">
-        <v>14</v>
-      </c>
-      <c r="BN36">
-        <v>4.8</v>
-      </c>
-      <c r="BO36">
-        <v>3.85</v>
-      </c>
-      <c r="BP36">
-        <v>17</v>
-      </c>
-      <c r="BQ36">
-        <v>8</v>
-      </c>
-      <c r="BR36">
-        <v>1000</v>
-      </c>
-      <c r="BS36">
-        <v>10.5</v>
-      </c>
-      <c r="BT36">
-        <v>7.2</v>
-      </c>
-      <c r="BU36">
-        <v>5.6</v>
-      </c>
-      <c r="BV36">
-        <v>1000</v>
-      </c>
-      <c r="BW36">
-        <v>11</v>
-      </c>
-      <c r="BX36">
-        <v>1000</v>
-      </c>
-      <c r="BY36">
-        <v>12</v>
-      </c>
       <c r="BZ36">
         <v>1000</v>
       </c>
       <c r="CA36">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB36" t="s">
         <v>230</v>
@@ -9770,22 +9770,22 @@
         <v>213</v>
       </c>
       <c r="F37">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G37">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="H37">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I37">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J37">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K37">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -9794,148 +9794,148 @@
         <v>1.04</v>
       </c>
       <c r="N37">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="O37">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P37">
         <v>2.5</v>
       </c>
       <c r="Q37">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R37">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S37">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="T37">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="U37">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="V37">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="W37">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X37">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y37">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z37">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AA37">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AB37">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AC37">
+        <v>9.6</v>
+      </c>
+      <c r="AD37">
+        <v>11.5</v>
+      </c>
+      <c r="AE37">
+        <v>21</v>
+      </c>
+      <c r="AF37">
+        <v>29</v>
+      </c>
+      <c r="AG37">
+        <v>15.5</v>
+      </c>
+      <c r="AH37">
+        <v>16.5</v>
+      </c>
+      <c r="AI37">
+        <v>30</v>
+      </c>
+      <c r="AJ37">
+        <v>80</v>
+      </c>
+      <c r="AK37">
+        <v>48</v>
+      </c>
+      <c r="AL37">
+        <v>50</v>
+      </c>
+      <c r="AM37">
+        <v>85</v>
+      </c>
+      <c r="AN37">
+        <v>30</v>
+      </c>
+      <c r="AO37">
+        <v>11.5</v>
+      </c>
+      <c r="AP37">
+        <v>15</v>
+      </c>
+      <c r="AQ37">
+        <v>10.5</v>
+      </c>
+      <c r="AR37">
+        <v>13</v>
+      </c>
+      <c r="AS37">
+        <v>21</v>
+      </c>
+      <c r="AT37">
+        <v>15</v>
+      </c>
+      <c r="AU37">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV37">
+        <v>9.6</v>
+      </c>
+      <c r="AW37">
+        <v>17</v>
+      </c>
+      <c r="AX37">
+        <v>20</v>
+      </c>
+      <c r="AY37">
         <v>13.5</v>
       </c>
-      <c r="AD37">
-        <v>15.5</v>
-      </c>
-      <c r="AE37">
-        <v>29</v>
-      </c>
-      <c r="AF37">
-        <v>40</v>
-      </c>
-      <c r="AG37">
-        <v>21</v>
-      </c>
-      <c r="AH37">
-        <v>22</v>
-      </c>
-      <c r="AI37">
-        <v>40</v>
-      </c>
-      <c r="AJ37">
-        <v>1000</v>
-      </c>
-      <c r="AK37">
-        <v>1000</v>
-      </c>
-      <c r="AL37">
-        <v>1000</v>
-      </c>
-      <c r="AM37">
-        <v>1000</v>
-      </c>
-      <c r="AN37">
-        <v>1000</v>
-      </c>
-      <c r="AO37">
-        <v>15.5</v>
-      </c>
-      <c r="AP37">
-        <v>2.2</v>
-      </c>
-      <c r="AQ37">
-        <v>8</v>
-      </c>
-      <c r="AR37">
-        <v>9.6</v>
-      </c>
-      <c r="AS37">
-        <v>15.5</v>
-      </c>
-      <c r="AT37">
-        <v>11</v>
-      </c>
-      <c r="AU37">
-        <v>6.2</v>
-      </c>
-      <c r="AV37">
-        <v>7</v>
-      </c>
-      <c r="AW37">
-        <v>12</v>
-      </c>
-      <c r="AX37">
-        <v>16.5</v>
-      </c>
-      <c r="AY37">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ37">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="BA37">
         <v>16.5</v>
       </c>
       <c r="BB37">
-        <v>2.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC37">
-        <v>2.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD37">
-        <v>2.2</v>
+        <v>30</v>
       </c>
       <c r="BE37">
-        <v>2.2</v>
+        <v>9</v>
       </c>
       <c r="BF37">
-        <v>2.2</v>
+        <v>20</v>
       </c>
       <c r="BG37">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH37">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BI37">
-        <v>1.93</v>
+        <v>2.78</v>
       </c>
       <c r="BJ37">
         <v>12.5</v>
@@ -9947,7 +9947,7 @@
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BN37">
         <v>10</v>
@@ -9956,34 +9956,34 @@
         <v>4.6</v>
       </c>
       <c r="BP37">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ37">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BR37">
         <v>46</v>
       </c>
       <c r="BS37">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BT37">
         <v>7.4</v>
       </c>
       <c r="BU37">
-        <v>3.75</v>
+        <v>2.08</v>
       </c>
       <c r="BV37">
         <v>20</v>
       </c>
       <c r="BW37">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BX37">
         <v>34</v>
       </c>
       <c r="BY37">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BZ37">
         <v>0</v>
@@ -10018,13 +10018,13 @@
         <v>4.2</v>
       </c>
       <c r="H38">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I38">
         <v>2.36</v>
       </c>
       <c r="J38">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K38">
         <v>3.4</v>
@@ -10036,7 +10036,7 @@
         <v>1.09</v>
       </c>
       <c r="N38">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="O38">
         <v>1.42</v>
@@ -10048,16 +10048,16 @@
         <v>2.22</v>
       </c>
       <c r="R38">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S38">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T38">
         <v>1.76</v>
       </c>
       <c r="U38">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V38">
         <v>1.73</v>
@@ -10066,112 +10066,112 @@
         <v>1.31</v>
       </c>
       <c r="X38">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y38">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z38">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA38">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB38">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC38">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AD38">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE38">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF38">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG38">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AH38">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI38">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ38">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK38">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL38">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM38">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN38">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO38">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP38">
-        <v>1.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ38">
-        <v>1.35</v>
+        <v>7</v>
       </c>
       <c r="AR38">
-        <v>1.35</v>
+        <v>11</v>
       </c>
       <c r="AS38">
-        <v>1.31</v>
+        <v>5.8</v>
       </c>
       <c r="AT38">
-        <v>1.35</v>
+        <v>10</v>
       </c>
       <c r="AU38">
-        <v>1.17</v>
+        <v>6.4</v>
       </c>
       <c r="AV38">
-        <v>1.35</v>
+        <v>9.6</v>
       </c>
       <c r="AW38">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX38">
-        <v>19</v>
+        <v>5.7</v>
       </c>
       <c r="AY38">
-        <v>1.27</v>
+        <v>14</v>
       </c>
       <c r="AZ38">
-        <v>1.35</v>
+        <v>17</v>
       </c>
       <c r="BA38">
-        <v>1.35</v>
+        <v>6.2</v>
       </c>
       <c r="BB38">
-        <v>1.35</v>
+        <v>6.4</v>
       </c>
       <c r="BC38">
-        <v>1.35</v>
+        <v>6.2</v>
       </c>
       <c r="BD38">
-        <v>1.33</v>
+        <v>6.4</v>
       </c>
       <c r="BE38">
-        <v>1.35</v>
+        <v>6.6</v>
       </c>
       <c r="BF38">
-        <v>1.35</v>
+        <v>6.4</v>
       </c>
       <c r="BG38">
-        <v>1.35</v>
+        <v>18</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10254,166 +10254,166 @@
         <v>215</v>
       </c>
       <c r="F39">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="G39">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="H39">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="I39">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="J39">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K39">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L39">
         <v>1.01</v>
       </c>
       <c r="M39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N39">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O39">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P39">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q39">
+        <v>1.66</v>
+      </c>
+      <c r="R39">
+        <v>1.5</v>
+      </c>
+      <c r="S39">
+        <v>2.48</v>
+      </c>
+      <c r="T39">
+        <v>1.6</v>
+      </c>
+      <c r="U39">
+        <v>2.36</v>
+      </c>
+      <c r="V39">
         <v>1.64</v>
       </c>
-      <c r="R39">
+      <c r="W39">
         <v>1.45</v>
       </c>
-      <c r="S39">
-        <v>2</v>
-      </c>
-      <c r="T39">
-        <v>1.53</v>
-      </c>
-      <c r="U39">
-        <v>2.2</v>
-      </c>
-      <c r="V39">
-        <v>1.6</v>
-      </c>
-      <c r="W39">
-        <v>1.51</v>
-      </c>
       <c r="X39">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y39">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z39">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA39">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB39">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC39">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD39">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE39">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF39">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG39">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH39">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI39">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ39">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK39">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL39">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM39">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN39">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO39">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP39">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR39">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS39">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT39">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU39">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV39">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW39">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX39">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY39">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AZ39">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA39">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB39">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BC39">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD39">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE39">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF39">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG39">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH39">
         <v>1000</v>
@@ -10499,7 +10499,7 @@
         <v>2.9</v>
       </c>
       <c r="G40">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H40">
         <v>2.36</v>
@@ -10526,28 +10526,28 @@
         <v>1.24</v>
       </c>
       <c r="P40">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q40">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="R40">
         <v>1.45</v>
       </c>
       <c r="S40">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T40">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U40">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V40">
         <v>1.65</v>
       </c>
       <c r="W40">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X40">
         <v>22</v>
@@ -10580,7 +10580,7 @@
         <v>15.5</v>
       </c>
       <c r="AH40">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI40">
         <v>40</v>
@@ -10601,25 +10601,25 @@
         <v>27</v>
       </c>
       <c r="AO40">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AP40">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ40">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR40">
         <v>13.5</v>
       </c>
       <c r="AS40">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT40">
         <v>11</v>
       </c>
       <c r="AU40">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV40">
         <v>9.199999999999999</v>
@@ -10628,7 +10628,7 @@
         <v>18.5</v>
       </c>
       <c r="AX40">
-        <v>17</v>
+        <v>4.1</v>
       </c>
       <c r="AY40">
         <v>10</v>
@@ -10637,7 +10637,7 @@
         <v>12</v>
       </c>
       <c r="BA40">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB40">
         <v>4.5</v>
@@ -10652,7 +10652,7 @@
         <v>4.6</v>
       </c>
       <c r="BF40">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG40">
         <v>12.5</v>
@@ -10741,7 +10741,7 @@
         <v>3.05</v>
       </c>
       <c r="G41">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H41">
         <v>2.38</v>
@@ -10771,7 +10771,7 @@
         <v>1.74</v>
       </c>
       <c r="Q41">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="R41">
         <v>1.25</v>
@@ -10780,16 +10780,16 @@
         <v>3.35</v>
       </c>
       <c r="T41">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="U41">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="V41">
         <v>1.59</v>
       </c>
       <c r="W41">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="X41">
         <v>1000</v>
@@ -10819,7 +10819,7 @@
         <v>32</v>
       </c>
       <c r="AG41">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH41">
         <v>950</v>
@@ -10846,7 +10846,7 @@
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AQ41">
         <v>5.9</v>
@@ -10855,7 +10855,7 @@
         <v>9.6</v>
       </c>
       <c r="AS41">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AT41">
         <v>7</v>
@@ -10873,31 +10873,31 @@
         <v>13.5</v>
       </c>
       <c r="AY41">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ41">
         <v>11.5</v>
       </c>
       <c r="BA41">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="BB41">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="BC41">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="BD41">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="BE41">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="BF41">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="BG41">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="BH41">
         <v>3.8</v>
@@ -10980,22 +10980,22 @@
         <v>218</v>
       </c>
       <c r="F42">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="G42">
-        <v>990</v>
+        <v>12</v>
       </c>
       <c r="H42">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="I42">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="J42">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="L42">
         <v>1.01</v>
@@ -11004,142 +11004,142 @@
         <v>1.01</v>
       </c>
       <c r="N42">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="O42">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P42">
         <v>2.46</v>
       </c>
       <c r="Q42">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="R42">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="S42">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T42">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U42">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V42">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="W42">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X42">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y42">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z42">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA42">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AB42">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AC42">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD42">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE42">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AF42">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AG42">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AH42">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI42">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ42">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AK42">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AL42">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM42">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN42">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AO42">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AP42">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ42">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR42">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS42">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AT42">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU42">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AV42">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW42">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX42">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY42">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ42">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA42">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB42">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC42">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD42">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE42">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF42">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG42">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11225,7 +11225,7 @@
         <v>2.86</v>
       </c>
       <c r="G43">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H43">
         <v>2.32</v>
@@ -11234,40 +11234,40 @@
         <v>2.62</v>
       </c>
       <c r="J43">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K43">
+        <v>3.95</v>
+      </c>
+      <c r="L43">
+        <v>1.01</v>
+      </c>
+      <c r="M43">
+        <v>1.05</v>
+      </c>
+      <c r="N43">
         <v>4</v>
       </c>
-      <c r="L43">
-        <v>1.01</v>
-      </c>
-      <c r="M43">
-        <v>1.06</v>
-      </c>
-      <c r="N43">
-        <v>3.45</v>
-      </c>
       <c r="O43">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P43">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q43">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R43">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S43">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="T43">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="U43">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V43">
         <v>1.61</v>
@@ -11282,13 +11282,13 @@
         <v>14</v>
       </c>
       <c r="Z43">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AA43">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB43">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AC43">
         <v>9.800000000000001</v>
@@ -11306,16 +11306,16 @@
         <v>15.5</v>
       </c>
       <c r="AH43">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI43">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ43">
         <v>60</v>
       </c>
       <c r="AK43">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL43">
         <v>48</v>
@@ -11327,10 +11327,10 @@
         <v>32</v>
       </c>
       <c r="AO43">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP43">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ43">
         <v>9.199999999999999</v>
@@ -11339,7 +11339,7 @@
         <v>13</v>
       </c>
       <c r="AS43">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT43">
         <v>10.5</v>
@@ -11354,34 +11354,34 @@
         <v>19</v>
       </c>
       <c r="AX43">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY43">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ43">
         <v>12.5</v>
       </c>
       <c r="BA43">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB43">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC43">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD43">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE43">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BF43">
         <v>20</v>
       </c>
       <c r="BG43">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH43">
         <v>4.6</v>
@@ -11464,220 +11464,220 @@
         <v>220</v>
       </c>
       <c r="F44">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="G44">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="H44">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="I44">
+        <v>3.15</v>
+      </c>
+      <c r="J44">
         <v>3.6</v>
       </c>
-      <c r="J44">
-        <v>3.15</v>
-      </c>
       <c r="K44">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="L44">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M44">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N44">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O44">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P44">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="Q44">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="R44">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="S44">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="T44">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="U44">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="V44">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W44">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="X44">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y44">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z44">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA44">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB44">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC44">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD44">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE44">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF44">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG44">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH44">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI44">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ44">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK44">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL44">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM44">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN44">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO44">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP44">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ44">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR44">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS44">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AT44">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU44">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV44">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW44">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX44">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY44">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ44">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA44">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB44">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BC44">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD44">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE44">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF44">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG44">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH44">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI44">
-        <v>1.97</v>
+        <v>3.4</v>
       </c>
       <c r="BJ44">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK44">
-        <v>2.52</v>
+        <v>5.8</v>
       </c>
       <c r="BL44">
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>3.15</v>
+        <v>8.6</v>
       </c>
       <c r="BN44">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BO44">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="BP44">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="BQ44">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR44">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BS44">
-        <v>2.92</v>
+        <v>7</v>
       </c>
       <c r="BT44">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BU44">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BV44">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BW44">
-        <v>2.88</v>
+        <v>6.6</v>
       </c>
       <c r="BX44">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BY44">
-        <v>2.96</v>
+        <v>7.2</v>
       </c>
       <c r="BZ44">
         <v>0</v>
@@ -11730,13 +11730,13 @@
         <v>1.01</v>
       </c>
       <c r="N45">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O45">
         <v>1.25</v>
       </c>
       <c r="P45">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="Q45">
         <v>1.63</v>
@@ -11877,7 +11877,7 @@
         <v>13.5</v>
       </c>
       <c r="BK45">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BL45">
         <v>1000</v>
@@ -11889,13 +11889,13 @@
         <v>5.8</v>
       </c>
       <c r="BO45">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BP45">
         <v>15</v>
       </c>
       <c r="BQ45">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BR45">
         <v>32</v>
@@ -11904,7 +11904,7 @@
         <v>3.15</v>
       </c>
       <c r="BT45">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BU45">
         <v>2.76</v>
@@ -11913,7 +11913,7 @@
         <v>1000</v>
       </c>
       <c r="BW45">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BX45">
         <v>1000</v>
@@ -11954,7 +11954,7 @@
         <v>2.68</v>
       </c>
       <c r="H46">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="I46">
         <v>3.3</v>
@@ -11984,13 +11984,13 @@
         <v>1.97</v>
       </c>
       <c r="R46">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S46">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T46">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U46">
         <v>2.12</v>
@@ -12080,7 +12080,7 @@
         <v>5.6</v>
       </c>
       <c r="AX46">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY46">
         <v>9.199999999999999</v>
@@ -12193,19 +12193,19 @@
         <v>1.5</v>
       </c>
       <c r="G47">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="H47">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I47">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J47">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K47">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L47">
         <v>1.01</v>
@@ -12214,142 +12214,142 @@
         <v>1.04</v>
       </c>
       <c r="N47">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="O47">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P47">
         <v>2.52</v>
       </c>
       <c r="Q47">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="R47">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S47">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="T47">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="U47">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="V47">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W47">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="X47">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y47">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="Z47">
         <v>90</v>
       </c>
       <c r="AA47">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB47">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AC47">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AD47">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AE47">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF47">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AG47">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH47">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AI47">
         <v>100</v>
       </c>
       <c r="AJ47">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AK47">
+        <v>15.5</v>
+      </c>
+      <c r="AL47">
+        <v>32</v>
+      </c>
+      <c r="AM47">
+        <v>120</v>
+      </c>
+      <c r="AN47">
+        <v>5.7</v>
+      </c>
+      <c r="AO47">
+        <v>120</v>
+      </c>
+      <c r="AP47">
         <v>21</v>
-      </c>
-      <c r="AL47">
-        <v>44</v>
-      </c>
-      <c r="AM47">
-        <v>1000</v>
-      </c>
-      <c r="AN47">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO47">
-        <v>1000</v>
-      </c>
-      <c r="AP47">
-        <v>2.48</v>
       </c>
       <c r="AQ47">
         <v>17.5</v>
       </c>
       <c r="AR47">
-        <v>2.42</v>
+        <v>8</v>
       </c>
       <c r="AS47">
-        <v>2.48</v>
+        <v>8.6</v>
       </c>
       <c r="AT47">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AU47">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AV47">
         <v>16</v>
       </c>
       <c r="AW47">
-        <v>2.48</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX47">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AY47">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ47">
+        <v>17.5</v>
+      </c>
+      <c r="BA47">
+        <v>8</v>
+      </c>
+      <c r="BB47">
+        <v>11.5</v>
+      </c>
+      <c r="BC47">
         <v>12.5</v>
       </c>
-      <c r="BA47">
-        <v>2.42</v>
-      </c>
-      <c r="BB47">
+      <c r="BD47">
+        <v>20</v>
+      </c>
+      <c r="BE47">
         <v>8.4</v>
       </c>
-      <c r="BC47">
-        <v>10</v>
-      </c>
-      <c r="BD47">
-        <v>2.36</v>
-      </c>
-      <c r="BE47">
-        <v>2.48</v>
-      </c>
       <c r="BF47">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="BG47">
-        <v>2.48</v>
+        <v>8.4</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12432,16 +12432,16 @@
         <v>224</v>
       </c>
       <c r="F48">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G48">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="H48">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I48">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="J48">
         <v>3.45</v>
@@ -12450,22 +12450,22 @@
         <v>3.7</v>
       </c>
       <c r="L48">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M48">
         <v>1.08</v>
       </c>
       <c r="N48">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O48">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P48">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q48">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R48">
         <v>1.3</v>
@@ -12480,7 +12480,7 @@
         <v>1.95</v>
       </c>
       <c r="V48">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="W48">
         <v>1.23</v>
@@ -12495,13 +12495,13 @@
         <v>12</v>
       </c>
       <c r="AA48">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB48">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AC48">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD48">
         <v>11</v>
@@ -12510,7 +12510,7 @@
         <v>22</v>
       </c>
       <c r="AF48">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG48">
         <v>21</v>
@@ -12522,19 +12522,19 @@
         <v>42</v>
       </c>
       <c r="AJ48">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AK48">
         <v>75</v>
       </c>
       <c r="AL48">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AM48">
         <v>150</v>
       </c>
       <c r="AN48">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO48">
         <v>15.5</v>
@@ -12564,7 +12564,7 @@
         <v>18</v>
       </c>
       <c r="AX48">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY48">
         <v>16.5</v>
@@ -12573,79 +12573,79 @@
         <v>17</v>
       </c>
       <c r="BA48">
+        <v>6.4</v>
+      </c>
+      <c r="BB48">
+        <v>7.2</v>
+      </c>
+      <c r="BC48">
         <v>7</v>
       </c>
-      <c r="BB48">
-        <v>7.8</v>
-      </c>
-      <c r="BC48">
-        <v>7.4</v>
-      </c>
       <c r="BD48">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BE48">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF48">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BG48">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH48">
         <v>1000</v>
       </c>
       <c r="BI48">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="BJ48">
         <v>14.5</v>
       </c>
       <c r="BK48">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BL48">
         <v>1000</v>
       </c>
       <c r="BM48">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="BN48">
         <v>11</v>
       </c>
       <c r="BO48">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP48">
         <v>1000</v>
       </c>
       <c r="BQ48">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="BR48">
         <v>1000</v>
       </c>
       <c r="BS48">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="BT48">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU48">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BV48">
         <v>18.5</v>
       </c>
       <c r="BW48">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="BX48">
         <v>42</v>
       </c>
       <c r="BY48">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BZ48">
         <v>0</v>
@@ -12680,13 +12680,13 @@
         <v>1.31</v>
       </c>
       <c r="H49">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I49">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J49">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="K49">
         <v>7.6</v>
@@ -12713,10 +12713,10 @@
         <v>2.04</v>
       </c>
       <c r="S49">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="T49">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U49">
         <v>2.2</v>
@@ -12740,7 +12740,7 @@
         <v>390</v>
       </c>
       <c r="AB49">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC49">
         <v>18.5</v>
@@ -12752,10 +12752,10 @@
         <v>150</v>
       </c>
       <c r="AF49">
+        <v>12.5</v>
+      </c>
+      <c r="AG49">
         <v>13</v>
-      </c>
-      <c r="AG49">
-        <v>13.5</v>
       </c>
       <c r="AH49">
         <v>26</v>
@@ -12764,7 +12764,7 @@
         <v>110</v>
       </c>
       <c r="AJ49">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK49">
         <v>14</v>
@@ -12782,16 +12782,16 @@
         <v>120</v>
       </c>
       <c r="AP49">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ49">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR49">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS49">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT49">
         <v>14</v>
@@ -12803,7 +12803,7 @@
         <v>30</v>
       </c>
       <c r="AW49">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX49">
         <v>10</v>
@@ -12815,7 +12815,7 @@
         <v>20</v>
       </c>
       <c r="BA49">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB49">
         <v>10</v>
@@ -12827,13 +12827,13 @@
         <v>19</v>
       </c>
       <c r="BE49">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF49">
         <v>2.84</v>
       </c>
       <c r="BG49">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -12922,10 +12922,10 @@
         <v>6.6</v>
       </c>
       <c r="H50">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I50">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="J50">
         <v>4.8</v>
@@ -12955,7 +12955,7 @@
         <v>1.63</v>
       </c>
       <c r="S50">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T50">
         <v>1.65</v>
@@ -12964,13 +12964,13 @@
         <v>2.26</v>
       </c>
       <c r="V50">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="W50">
         <v>1.18</v>
       </c>
       <c r="X50">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Y50">
         <v>13</v>
@@ -13042,7 +13042,7 @@
         <v>10</v>
       </c>
       <c r="AV50">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW50">
         <v>13</v>
@@ -13054,7 +13054,7 @@
         <v>20</v>
       </c>
       <c r="AZ50">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA50">
         <v>22</v>
@@ -13158,37 +13158,37 @@
         <v>227</v>
       </c>
       <c r="F51">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G51">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H51">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I51">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J51">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K51">
         <v>3.65</v>
       </c>
       <c r="L51">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M51">
         <v>1.07</v>
       </c>
       <c r="N51">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="O51">
         <v>1.34</v>
       </c>
       <c r="P51">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="Q51">
         <v>1.96</v>
@@ -13197,7 +13197,7 @@
         <v>1.24</v>
       </c>
       <c r="S51">
-        <v>3.55</v>
+        <v>1.05</v>
       </c>
       <c r="T51">
         <v>1.11</v>
@@ -13206,10 +13206,10 @@
         <v>1.11</v>
       </c>
       <c r="V51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W51">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -13224,100 +13224,100 @@
         <v>1000</v>
       </c>
       <c r="AB51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC51">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD51">
         <v>25</v>
       </c>
       <c r="AE51">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF51">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG51">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH51">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI51">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ51">
         <v>30</v>
       </c>
       <c r="AK51">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL51">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM51">
         <v>1000</v>
       </c>
       <c r="AN51">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO51">
         <v>1000</v>
       </c>
       <c r="AP51">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AQ51">
-        <v>11</v>
+        <v>2.1</v>
       </c>
       <c r="AR51">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AS51">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AT51">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AU51">
         <v>1.95</v>
       </c>
       <c r="AV51">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AW51">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AX51">
-        <v>8.800000000000001</v>
+        <v>2.04</v>
       </c>
       <c r="AY51">
         <v>2.02</v>
       </c>
       <c r="AZ51">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BA51">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BB51">
-        <v>16.5</v>
+        <v>2.16</v>
       </c>
       <c r="BC51">
-        <v>15.5</v>
+        <v>2.16</v>
       </c>
       <c r="BD51">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="BE51">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BF51">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="BG51">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BH51">
         <v>1000</v>
@@ -13406,10 +13406,10 @@
         <v>2.1</v>
       </c>
       <c r="H52">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I52">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J52">
         <v>3.4</v>
@@ -13475,10 +13475,10 @@
         <v>23</v>
       </c>
       <c r="AE52">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF52">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG52">
         <v>12.5</v>
@@ -13487,7 +13487,7 @@
         <v>25</v>
       </c>
       <c r="AI52">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ52">
         <v>29</v>
@@ -13514,52 +13514,52 @@
         <v>10.5</v>
       </c>
       <c r="AR52">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS52">
+        <v>5</v>
+      </c>
+      <c r="AT52">
+        <v>7</v>
+      </c>
+      <c r="AU52">
+        <v>6.8</v>
+      </c>
+      <c r="AV52">
+        <v>13</v>
+      </c>
+      <c r="AW52">
         <v>4.8</v>
       </c>
-      <c r="AT52">
-        <v>6</v>
-      </c>
-      <c r="AU52">
-        <v>6</v>
-      </c>
-      <c r="AV52">
-        <v>13.5</v>
-      </c>
-      <c r="AW52">
-        <v>4.6</v>
-      </c>
       <c r="AX52">
-        <v>8.6</v>
+        <v>3.65</v>
       </c>
       <c r="AY52">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ52">
         <v>14.5</v>
       </c>
       <c r="BA52">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB52">
-        <v>17</v>
+        <v>4.3</v>
       </c>
       <c r="BC52">
         <v>16.5</v>
       </c>
       <c r="BD52">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE52">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF52">
         <v>12.5</v>
       </c>
       <c r="BG52">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH52">
         <v>1000</v>
@@ -13645,13 +13645,13 @@
         <v>1.7</v>
       </c>
       <c r="G53">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H53">
         <v>5.3</v>
       </c>
       <c r="I53">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J53">
         <v>4.2</v>
@@ -13702,10 +13702,10 @@
         <v>21</v>
       </c>
       <c r="Z53">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AA53">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB53">
         <v>9.800000000000001</v>
@@ -13714,7 +13714,7 @@
         <v>10</v>
       </c>
       <c r="AD53">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE53">
         <v>1000</v>
@@ -13762,7 +13762,7 @@
         <v>42</v>
       </c>
       <c r="AT53">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU53">
         <v>8.800000000000001</v>
@@ -13801,7 +13801,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG53">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BH53">
         <v>1000</v>
@@ -13828,7 +13828,7 @@
         <v>3.1</v>
       </c>
       <c r="BP53">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ53">
         <v>1.71</v>
@@ -13849,13 +13849,13 @@
         <v>1000</v>
       </c>
       <c r="BW53">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BX53">
         <v>1000</v>
       </c>
       <c r="BY53">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BZ53">
         <v>26</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -706,7 +706,7 @@
     <t>Toronto FC</t>
   </si>
   <si>
-    <t>2026-07-30 02:52:20</t>
+    <t>2026-07-30 05:02:17</t>
   </si>
 </sst>
 </file>
@@ -1300,7 +1300,7 @@
         <v>178</v>
       </c>
       <c r="F2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G2">
         <v>3.45</v>
@@ -1315,31 +1315,31 @@
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
         <v>1.62</v>
       </c>
       <c r="M2">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O2">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q2">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T2">
         <v>2.18</v>
@@ -1354,13 +1354,13 @@
         <v>1.4</v>
       </c>
       <c r="X2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Y2">
         <v>7.8</v>
       </c>
       <c r="Z2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA2">
         <v>42</v>
@@ -1372,7 +1372,7 @@
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE2">
         <v>38</v>
@@ -1414,7 +1414,7 @@
         <v>7.2</v>
       </c>
       <c r="AR2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS2">
         <v>36</v>
@@ -1465,19 +1465,19 @@
         <v>2.64</v>
       </c>
       <c r="BI2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BN2">
         <v>6.4</v>
@@ -1501,10 +1501,10 @@
         <v>5.3</v>
       </c>
       <c r="BU2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW2">
         <v>10</v>
@@ -1513,13 +1513,13 @@
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ2">
         <v>55</v>
       </c>
       <c r="CA2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB2" t="s">
         <v>230</v>
@@ -1542,7 +1542,7 @@
         <v>179</v>
       </c>
       <c r="F3">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G3">
         <v>1.75</v>
@@ -1551,19 +1551,19 @@
         <v>6.2</v>
       </c>
       <c r="I3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
         <v>3.65</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
         <v>1.53</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
         <v>3</v>
@@ -1572,10 +1572,10 @@
         <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q3">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R3">
         <v>1.23</v>
@@ -1584,7 +1584,7 @@
         <v>5</v>
       </c>
       <c r="T3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U3">
         <v>1.68</v>
@@ -1725,7 +1725,7 @@
         <v>4.1</v>
       </c>
       <c r="BO3">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BP3">
         <v>13</v>
@@ -1734,7 +1734,7 @@
         <v>6</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS3">
         <v>8.800000000000001</v>
@@ -1790,10 +1790,10 @@
         <v>3.6</v>
       </c>
       <c r="H4">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J4">
         <v>3.4</v>
@@ -1808,22 +1808,22 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
         <v>2.22</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
         <v>1.92</v>
@@ -1832,7 +1832,7 @@
         <v>2.02</v>
       </c>
       <c r="V4">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W4">
         <v>1.38</v>
@@ -1844,7 +1844,7 @@
         <v>9</v>
       </c>
       <c r="Z4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA4">
         <v>32</v>
@@ -1859,7 +1859,7 @@
         <v>11.5</v>
       </c>
       <c r="AE4">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AF4">
         <v>24</v>
@@ -1874,7 +1874,7 @@
         <v>150</v>
       </c>
       <c r="AJ4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
         <v>46</v>
@@ -1889,7 +1889,7 @@
         <v>50</v>
       </c>
       <c r="AO4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
@@ -1913,7 +1913,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AX4">
         <v>21</v>
@@ -2035,16 +2035,16 @@
         <v>7.8</v>
       </c>
       <c r="I5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J5">
         <v>4.2</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -2059,16 +2059,16 @@
         <v>1.81</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R5">
         <v>1.3</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
         <v>1.74</v>
@@ -2119,7 +2119,7 @@
         <v>15</v>
       </c>
       <c r="AK5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL5">
         <v>60</v>
@@ -2140,10 +2140,10 @@
         <v>15.5</v>
       </c>
       <c r="AR5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT5">
         <v>6</v>
@@ -2155,19 +2155,19 @@
         <v>22</v>
       </c>
       <c r="AW5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX5">
         <v>7</v>
       </c>
       <c r="AY5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB5">
         <v>10.5</v>
@@ -2179,13 +2179,13 @@
         <v>34</v>
       </c>
       <c r="BE5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF5">
         <v>9.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH5">
         <v>3.35</v>
@@ -2271,10 +2271,10 @@
         <v>1.86</v>
       </c>
       <c r="G6">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I6">
         <v>4.3</v>
@@ -2289,7 +2289,7 @@
         <v>1.27</v>
       </c>
       <c r="M6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
         <v>5.3</v>
@@ -2298,16 +2298,16 @@
         <v>1.2</v>
       </c>
       <c r="P6">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q6">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R6">
         <v>1.6</v>
       </c>
       <c r="S6">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="T6">
         <v>1.58</v>
@@ -2319,7 +2319,7 @@
         <v>1.3</v>
       </c>
       <c r="W6">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X6">
         <v>29</v>
@@ -2421,10 +2421,10 @@
         <v>6</v>
       </c>
       <c r="BE6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG6">
         <v>6</v>
@@ -2439,7 +2439,7 @@
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2451,7 +2451,7 @@
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP6">
         <v>1000</v>
@@ -2510,22 +2510,22 @@
         <v>183</v>
       </c>
       <c r="F7">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="G7">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="H7">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="I7">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="J7">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2534,142 +2534,142 @@
         <v>1.06</v>
       </c>
       <c r="N7">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="O7">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P7">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="Q7">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="R7">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S7">
         <v>2.84</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V7">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y7">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF7">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AG7">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ7">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AK7">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP7">
-        <v>1.27</v>
+        <v>5.7</v>
       </c>
       <c r="AQ7">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR7">
-        <v>1.27</v>
+        <v>6</v>
       </c>
       <c r="AS7">
-        <v>1.27</v>
+        <v>7</v>
       </c>
       <c r="AT7">
-        <v>1.27</v>
+        <v>4.6</v>
       </c>
       <c r="AU7">
-        <v>1.27</v>
+        <v>4.1</v>
       </c>
       <c r="AV7">
-        <v>1.27</v>
+        <v>5.1</v>
       </c>
       <c r="AW7">
-        <v>1.27</v>
+        <v>6.6</v>
       </c>
       <c r="AX7">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="AY7">
-        <v>1.18</v>
+        <v>4.6</v>
       </c>
       <c r="AZ7">
-        <v>1.27</v>
+        <v>5.3</v>
       </c>
       <c r="BA7">
-        <v>1.27</v>
+        <v>6.8</v>
       </c>
       <c r="BB7">
-        <v>1.23</v>
+        <v>6</v>
       </c>
       <c r="BC7">
-        <v>1.22</v>
+        <v>5.8</v>
       </c>
       <c r="BD7">
-        <v>1.27</v>
+        <v>6.4</v>
       </c>
       <c r="BE7">
-        <v>1.27</v>
+        <v>7.2</v>
       </c>
       <c r="BF7">
-        <v>1.27</v>
+        <v>5.5</v>
       </c>
       <c r="BG7">
-        <v>1.27</v>
+        <v>6.4</v>
       </c>
       <c r="BH7">
         <v>4.5</v>
@@ -2752,19 +2752,19 @@
         <v>184</v>
       </c>
       <c r="F8">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G8">
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2773,19 +2773,19 @@
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
         <v>1.1</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="P8">
         <v>1.08</v>
       </c>
       <c r="Q8">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="R8">
         <v>1.08</v>
@@ -2800,7 +2800,7 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="W8">
         <v>1.02</v>
@@ -3003,7 +3003,7 @@
         <v>5.7</v>
       </c>
       <c r="I9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J9">
         <v>3.55</v>
@@ -3201,7 +3201,7 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BX9">
         <v>1000</v>
@@ -3242,7 +3242,7 @@
         <v>1.77</v>
       </c>
       <c r="H10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I10">
         <v>6</v>
@@ -3251,7 +3251,7 @@
         <v>4.1</v>
       </c>
       <c r="K10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L10">
         <v>1.28</v>
@@ -3281,7 +3281,7 @@
         <v>1.71</v>
       </c>
       <c r="U10">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
         <v>1.2</v>
@@ -3481,7 +3481,7 @@
         <v>3.5</v>
       </c>
       <c r="G11">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H11">
         <v>2.46</v>
@@ -3496,7 +3496,7 @@
         <v>3.1</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M11">
         <v>1.11</v>
@@ -3511,19 +3511,19 @@
         <v>1.61</v>
       </c>
       <c r="Q11">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R11">
         <v>1.23</v>
       </c>
       <c r="S11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T11">
         <v>1.92</v>
       </c>
       <c r="U11">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V11">
         <v>1.61</v>
@@ -3541,7 +3541,7 @@
         <v>18</v>
       </c>
       <c r="AA11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB11">
         <v>12</v>
@@ -3607,7 +3607,7 @@
         <v>10</v>
       </c>
       <c r="AW11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX11">
         <v>19</v>
@@ -3637,61 +3637,61 @@
         <v>5.6</v>
       </c>
       <c r="BG11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI11">
-        <v>1.78</v>
+        <v>2.44</v>
       </c>
       <c r="BJ11">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK11">
-        <v>1.59</v>
+        <v>5.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.78</v>
+        <v>10</v>
       </c>
       <c r="BN11">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BO11">
+        <v>4.9</v>
+      </c>
+      <c r="BP11">
+        <v>32</v>
+      </c>
+      <c r="BQ11">
+        <v>8</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT11">
+        <v>5.5</v>
+      </c>
+      <c r="BU11">
         <v>4.5</v>
       </c>
-      <c r="BP11">
-        <v>40</v>
-      </c>
-      <c r="BQ11">
-        <v>1.71</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>1.73</v>
-      </c>
-      <c r="BT11">
-        <v>7</v>
-      </c>
-      <c r="BU11">
-        <v>3.85</v>
-      </c>
       <c r="BV11">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BW11">
-        <v>1.68</v>
+        <v>7.2</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.73</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3723,223 +3723,223 @@
         <v>2</v>
       </c>
       <c r="G12">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="H12">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="I12">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="K12">
         <v>4.8</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
-        <v>2.62</v>
+        <v>5.2</v>
       </c>
       <c r="O12">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P12">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="Q12">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="R12">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="S12">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="T12">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB12">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD12">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG12">
+        <v>12.5</v>
+      </c>
+      <c r="AH12">
+        <v>15.5</v>
+      </c>
+      <c r="AI12">
+        <v>38</v>
+      </c>
+      <c r="AJ12">
+        <v>32</v>
+      </c>
+      <c r="AK12">
+        <v>23</v>
+      </c>
+      <c r="AL12">
+        <v>26</v>
+      </c>
+      <c r="AM12">
+        <v>60</v>
+      </c>
+      <c r="AN12">
+        <v>10.5</v>
+      </c>
+      <c r="AO12">
+        <v>21</v>
+      </c>
+      <c r="AP12">
+        <v>5.1</v>
+      </c>
+      <c r="AQ12">
+        <v>4.8</v>
+      </c>
+      <c r="AR12">
+        <v>5.1</v>
+      </c>
+      <c r="AS12">
+        <v>5.5</v>
+      </c>
+      <c r="AT12">
+        <v>4.4</v>
+      </c>
+      <c r="AU12">
+        <v>4</v>
+      </c>
+      <c r="AV12">
+        <v>4.3</v>
+      </c>
+      <c r="AW12">
+        <v>5.1</v>
+      </c>
+      <c r="AX12">
+        <v>4.6</v>
+      </c>
+      <c r="AY12">
+        <v>4</v>
+      </c>
+      <c r="AZ12">
+        <v>4.3</v>
+      </c>
+      <c r="BA12">
+        <v>5.2</v>
+      </c>
+      <c r="BB12">
+        <v>5</v>
+      </c>
+      <c r="BC12">
+        <v>4.7</v>
+      </c>
+      <c r="BD12">
+        <v>4.8</v>
+      </c>
+      <c r="BE12">
+        <v>5.4</v>
+      </c>
+      <c r="BF12">
+        <v>3.8</v>
+      </c>
+      <c r="BG12">
+        <v>4.6</v>
+      </c>
+      <c r="BH12">
+        <v>5</v>
+      </c>
+      <c r="BI12">
+        <v>3.35</v>
+      </c>
+      <c r="BJ12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK12">
+        <v>4.7</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN12">
+        <v>5.8</v>
+      </c>
+      <c r="BO12">
+        <v>3.7</v>
+      </c>
+      <c r="BP12">
         <v>14</v>
       </c>
-      <c r="AH12">
-        <v>17.5</v>
-      </c>
-      <c r="AI12">
-        <v>1000</v>
-      </c>
-      <c r="AJ12">
-        <v>1000</v>
-      </c>
-      <c r="AK12">
-        <v>1000</v>
-      </c>
-      <c r="AL12">
-        <v>30</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>1000</v>
-      </c>
-      <c r="AO12">
-        <v>1000</v>
-      </c>
-      <c r="AP12">
-        <v>1.37</v>
-      </c>
-      <c r="AQ12">
-        <v>1.37</v>
-      </c>
-      <c r="AR12">
-        <v>1.37</v>
-      </c>
-      <c r="AS12">
-        <v>1.37</v>
-      </c>
-      <c r="AT12">
-        <v>1.28</v>
-      </c>
-      <c r="AU12">
-        <v>1.37</v>
-      </c>
-      <c r="AV12">
-        <v>1.27</v>
-      </c>
-      <c r="AW12">
-        <v>1.37</v>
-      </c>
-      <c r="AX12">
-        <v>1.37</v>
-      </c>
-      <c r="AY12">
-        <v>1.25</v>
-      </c>
-      <c r="AZ12">
-        <v>1.27</v>
-      </c>
-      <c r="BA12">
-        <v>1.37</v>
-      </c>
-      <c r="BB12">
-        <v>1.37</v>
-      </c>
-      <c r="BC12">
-        <v>1.37</v>
-      </c>
-      <c r="BD12">
-        <v>1.31</v>
-      </c>
-      <c r="BE12">
-        <v>1.37</v>
-      </c>
-      <c r="BF12">
-        <v>1.37</v>
-      </c>
-      <c r="BG12">
-        <v>1.37</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.04</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.04</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.04</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>1.04</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="CB12" t="s">
         <v>230</v>
@@ -3971,7 +3971,7 @@
         <v>2.64</v>
       </c>
       <c r="I13">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="J13">
         <v>3.65</v>
@@ -3986,34 +3986,34 @@
         <v>1.04</v>
       </c>
       <c r="N13">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="O13">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P13">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q13">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R13">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="S13">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="T13">
         <v>1.57</v>
       </c>
       <c r="U13">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V13">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W13">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X13">
         <v>26</v>
@@ -4207,7 +4207,7 @@
         <v>3.05</v>
       </c>
       <c r="G14">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H14">
         <v>2.38</v>
@@ -4216,7 +4216,7 @@
         <v>2.62</v>
       </c>
       <c r="J14">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K14">
         <v>3.65</v>
@@ -4234,7 +4234,7 @@
         <v>1.36</v>
       </c>
       <c r="P14">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q14">
         <v>1.89</v>
@@ -4255,7 +4255,7 @@
         <v>1.61</v>
       </c>
       <c r="W14">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X14">
         <v>15.5</v>
@@ -4449,22 +4449,22 @@
         <v>1.72</v>
       </c>
       <c r="G15">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H15">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I15">
         <v>5.7</v>
       </c>
       <c r="J15">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M15">
         <v>1.06</v>
@@ -4611,7 +4611,7 @@
         <v>3.65</v>
       </c>
       <c r="BI15">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ15">
         <v>10</v>
@@ -4647,19 +4647,19 @@
         <v>8.6</v>
       </c>
       <c r="BU15">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
@@ -4688,13 +4688,13 @@
         <v>192</v>
       </c>
       <c r="F16">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G16">
         <v>3.3</v>
       </c>
       <c r="H16">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I16">
         <v>2.66</v>
@@ -4706,7 +4706,7 @@
         <v>3.65</v>
       </c>
       <c r="L16">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M16">
         <v>1.07</v>
@@ -4721,7 +4721,7 @@
         <v>1.84</v>
       </c>
       <c r="Q16">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="R16">
         <v>1.32</v>
@@ -4730,10 +4730,10 @@
         <v>3.55</v>
       </c>
       <c r="T16">
-        <v>1.12</v>
+        <v>1.76</v>
       </c>
       <c r="U16">
-        <v>1.12</v>
+        <v>2.1</v>
       </c>
       <c r="V16">
         <v>1.61</v>
@@ -4802,7 +4802,7 @@
         <v>4.9</v>
       </c>
       <c r="AR16">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="AS16">
         <v>7.2</v>
@@ -4811,7 +4811,7 @@
         <v>5.2</v>
       </c>
       <c r="AU16">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AV16">
         <v>5.2</v>
@@ -4823,7 +4823,7 @@
         <v>6.4</v>
       </c>
       <c r="AY16">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AZ16">
         <v>6</v>
@@ -4832,7 +4832,7 @@
         <v>7.4</v>
       </c>
       <c r="BB16">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BC16">
         <v>7.2</v>
@@ -4847,67 +4847,67 @@
         <v>7.2</v>
       </c>
       <c r="BG16">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI16">
-        <v>1.79</v>
+        <v>2.66</v>
       </c>
       <c r="BJ16">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BK16">
-        <v>1.58</v>
+        <v>5.1</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.79</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN16">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BO16">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP16">
+        <v>26</v>
+      </c>
+      <c r="BQ16">
+        <v>7.4</v>
+      </c>
+      <c r="BR16">
         <v>38</v>
       </c>
-      <c r="BQ16">
-        <v>1.71</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
       <c r="BS16">
-        <v>1.74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT16">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU16">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BV16">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="BW16">
-        <v>1.69</v>
+        <v>6.8</v>
       </c>
       <c r="BX16">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BY16">
-        <v>1.73</v>
+        <v>8</v>
       </c>
       <c r="BZ16">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="CA16">
-        <v>1.72</v>
+        <v>7.8</v>
       </c>
       <c r="CB16" t="s">
         <v>230</v>
@@ -4951,7 +4951,7 @@
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
         <v>3.05</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="AG17">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AH17">
         <v>20</v>
@@ -5038,10 +5038,10 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AQ17">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AR17">
         <v>10.5</v>
@@ -5056,13 +5056,13 @@
         <v>1.35</v>
       </c>
       <c r="AV17">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AW17">
         <v>1.53</v>
       </c>
       <c r="AX17">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AY17">
         <v>1.41</v>
@@ -5196,7 +5196,7 @@
         <v>1.03</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O18">
         <v>1.16</v>
@@ -5429,19 +5429,19 @@
         <v>3.8</v>
       </c>
       <c r="K19">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N19">
-        <v>2.96</v>
+        <v>4.7</v>
       </c>
       <c r="O19">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P19">
         <v>2.26</v>
@@ -5450,16 +5450,16 @@
         <v>1.67</v>
       </c>
       <c r="R19">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S19">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="T19">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U19">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
         <v>1.4</v>
@@ -5468,112 +5468,112 @@
         <v>1.74</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5674,7 +5674,7 @@
         <v>4.1</v>
       </c>
       <c r="L20">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="M20">
         <v>1.05</v>
@@ -5689,7 +5689,7 @@
         <v>2.16</v>
       </c>
       <c r="Q20">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R20">
         <v>1.47</v>
@@ -5818,64 +5818,64 @@
         <v>16.5</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI20">
-        <v>1.95</v>
+        <v>3.15</v>
       </c>
       <c r="BJ20">
+        <v>9</v>
+      </c>
+      <c r="BK20">
+        <v>5.5</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
         <v>12.5</v>
       </c>
-      <c r="BK20">
-        <v>1.69</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.95</v>
-      </c>
       <c r="BN20">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="BO20">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BP20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="BR20">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.86</v>
+        <v>9.6</v>
       </c>
       <c r="BT20">
+        <v>6.2</v>
+      </c>
+      <c r="BU20">
+        <v>4.9</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
         <v>8.6</v>
       </c>
-      <c r="BU20">
-        <v>4.5</v>
-      </c>
-      <c r="BV20">
-        <v>29</v>
-      </c>
-      <c r="BW20">
-        <v>1.83</v>
-      </c>
       <c r="BX20">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.87</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ20">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="CA20">
-        <v>1.83</v>
+        <v>8.6</v>
       </c>
       <c r="CB20" t="s">
         <v>230</v>
@@ -5901,7 +5901,7 @@
         <v>2.14</v>
       </c>
       <c r="G21">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H21">
         <v>3.05</v>
@@ -5937,7 +5937,7 @@
         <v>1.48</v>
       </c>
       <c r="S21">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="T21">
         <v>1.61</v>
@@ -5949,7 +5949,7 @@
         <v>1.39</v>
       </c>
       <c r="W21">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X21">
         <v>24</v>
@@ -6149,7 +6149,7 @@
         <v>4.8</v>
       </c>
       <c r="I22">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -6158,7 +6158,7 @@
         <v>4.6</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M22">
         <v>1.05</v>
@@ -6191,7 +6191,7 @@
         <v>1.21</v>
       </c>
       <c r="W22">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X22">
         <v>23</v>
@@ -6388,19 +6388,19 @@
         <v>1.66</v>
       </c>
       <c r="H23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J23">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K23">
         <v>4.8</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M23">
         <v>1.03</v>
@@ -6418,13 +6418,13 @@
         <v>1.49</v>
       </c>
       <c r="R23">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S23">
         <v>2.2</v>
       </c>
       <c r="T23">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U23">
         <v>2.5</v>
@@ -6472,10 +6472,10 @@
         <v>60</v>
       </c>
       <c r="AJ23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK23">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL23">
         <v>30</v>
@@ -6484,22 +6484,22 @@
         <v>75</v>
       </c>
       <c r="AN23">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO23">
         <v>48</v>
       </c>
       <c r="AP23">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ23">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR23">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS23">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT23">
         <v>12</v>
@@ -6508,10 +6508,10 @@
         <v>10</v>
       </c>
       <c r="AV23">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AW23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX23">
         <v>11.5</v>
@@ -6523,7 +6523,7 @@
         <v>14.5</v>
       </c>
       <c r="BA23">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB23">
         <v>15.5</v>
@@ -6535,73 +6535,73 @@
         <v>17.5</v>
       </c>
       <c r="BE23">
+        <v>5</v>
+      </c>
+      <c r="BF23">
+        <v>5.4</v>
+      </c>
+      <c r="BG23">
+        <v>4.9</v>
+      </c>
+      <c r="BH23">
         <v>4.8</v>
       </c>
-      <c r="BF23">
-        <v>5.5</v>
-      </c>
-      <c r="BG23">
-        <v>4.7</v>
-      </c>
-      <c r="BH23">
-        <v>1000</v>
-      </c>
       <c r="BI23">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU23">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA23">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB23" t="s">
         <v>230</v>
@@ -6624,22 +6624,22 @@
         <v>200</v>
       </c>
       <c r="F24">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="G24">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="H24">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="I24">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K24">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="L24">
         <v>1.32</v>
@@ -6648,22 +6648,22 @@
         <v>1.06</v>
       </c>
       <c r="N24">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O24">
-        <v>1.06</v>
+        <v>1.29</v>
       </c>
       <c r="P24">
+        <v>1.98</v>
+      </c>
+      <c r="Q24">
         <v>1.81</v>
-      </c>
-      <c r="Q24">
-        <v>1.8</v>
       </c>
       <c r="R24">
         <v>1.38</v>
       </c>
       <c r="S24">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="T24">
         <v>1.7</v>
@@ -6672,178 +6672,178 @@
         <v>2.18</v>
       </c>
       <c r="V24">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH24">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BI24">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK24">
-        <v>1.34</v>
+        <v>5.5</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO24">
-        <v>1.34</v>
+        <v>3.85</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ24">
-        <v>1.34</v>
+        <v>7.4</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS24">
-        <v>1.34</v>
+        <v>7.2</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU24">
-        <v>1.34</v>
+        <v>4.4</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW24">
-        <v>1.34</v>
+        <v>6.8</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY24">
-        <v>1.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA24">
-        <v>1.34</v>
+        <v>6.8</v>
       </c>
       <c r="CB24" t="s">
         <v>230</v>
@@ -6872,7 +6872,7 @@
         <v>990</v>
       </c>
       <c r="H25">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I25">
         <v>990</v>
@@ -7111,13 +7111,13 @@
         <v>3</v>
       </c>
       <c r="G26">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H26">
         <v>2.24</v>
       </c>
       <c r="I26">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J26">
         <v>3.85</v>
@@ -7129,7 +7129,7 @@
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N26">
         <v>5</v>
@@ -7156,7 +7156,7 @@
         <v>2.5</v>
       </c>
       <c r="V26">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W26">
         <v>1.44</v>
@@ -7353,169 +7353,169 @@
         <v>3</v>
       </c>
       <c r="G27">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H27">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I27">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="J27">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="K27">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="L27">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N27">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="O27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P27">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="Q27">
         <v>1.89</v>
       </c>
       <c r="R27">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S27">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T27">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="U27">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="V27">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W27">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y27">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB27">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC27">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD27">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG27">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP27">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ27">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR27">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS27">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT27">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU27">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AV27">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX27">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AY27">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AZ27">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB27">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF27">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG27">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH27">
         <v>3.55</v>
       </c>
       <c r="BI27">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="BJ27">
         <v>9.800000000000001</v>
@@ -7592,58 +7592,58 @@
         <v>204</v>
       </c>
       <c r="F28">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="G28">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="H28">
         <v>14.5</v>
       </c>
       <c r="I28">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J28">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="K28">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L28">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M28">
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P28">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="Q28">
         <v>1.55</v>
       </c>
       <c r="R28">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="S28">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="T28">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="U28">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="V28">
         <v>1.05</v>
       </c>
       <c r="W28">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="X28">
         <v>34</v>
@@ -7667,10 +7667,10 @@
         <v>70</v>
       </c>
       <c r="AE28">
-        <v>330</v>
+        <v>410</v>
       </c>
       <c r="AF28">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AG28">
         <v>14</v>
@@ -7682,7 +7682,7 @@
         <v>240</v>
       </c>
       <c r="AJ28">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK28">
         <v>15</v>
@@ -7694,46 +7694,46 @@
         <v>240</v>
       </c>
       <c r="AN28">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AO28">
-        <v>460</v>
+        <v>580</v>
       </c>
       <c r="AP28">
         <v>19.5</v>
       </c>
       <c r="AQ28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR28">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS28">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AT28">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU28">
         <v>13.5</v>
       </c>
       <c r="AV28">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AW28">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX28">
         <v>6.8</v>
       </c>
       <c r="AY28">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ28">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BA28">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB28">
         <v>6.8</v>
@@ -7742,16 +7742,16 @@
         <v>12</v>
       </c>
       <c r="BD28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE28">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF28">
         <v>3.3</v>
       </c>
       <c r="BG28">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7763,7 +7763,7 @@
         <v>20</v>
       </c>
       <c r="BK28">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BL28">
         <v>1000</v>
@@ -7778,7 +7778,7 @@
         <v>2.72</v>
       </c>
       <c r="BP28">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ28">
         <v>4.5</v>
@@ -7787,13 +7787,13 @@
         <v>34</v>
       </c>
       <c r="BS28">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BT28">
         <v>24</v>
       </c>
       <c r="BU28">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BV28">
         <v>1000</v>
@@ -7811,7 +7811,7 @@
         <v>13</v>
       </c>
       <c r="CA28">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CB28" t="s">
         <v>230</v>
@@ -7843,7 +7843,7 @@
         <v>1.77</v>
       </c>
       <c r="I29">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J29">
         <v>3.95</v>
@@ -7882,7 +7882,7 @@
         <v>2.26</v>
       </c>
       <c r="V29">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="W29">
         <v>1.26</v>
@@ -7999,7 +7999,7 @@
         <v>4.1</v>
       </c>
       <c r="BI29">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BJ29">
         <v>9.6</v>
@@ -8035,7 +8035,7 @@
         <v>4.9</v>
       </c>
       <c r="BU29">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BV29">
         <v>12.5</v>
@@ -8076,22 +8076,22 @@
         <v>206</v>
       </c>
       <c r="F30">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G30">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H30">
         <v>5.2</v>
       </c>
       <c r="I30">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J30">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K30">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L30">
         <v>1.31</v>
@@ -8124,10 +8124,10 @@
         <v>2.08</v>
       </c>
       <c r="V30">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W30">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="X30">
         <v>21</v>
@@ -8136,7 +8136,7 @@
         <v>24</v>
       </c>
       <c r="Z30">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA30">
         <v>160</v>
@@ -8145,7 +8145,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC30">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD30">
         <v>25</v>
@@ -8190,10 +8190,10 @@
         <v>15.5</v>
       </c>
       <c r="AR30">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AS30">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT30">
         <v>8</v>
@@ -8202,10 +8202,10 @@
         <v>8.6</v>
       </c>
       <c r="AV30">
-        <v>16.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW30">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX30">
         <v>9.4</v>
@@ -8217,7 +8217,7 @@
         <v>17.5</v>
       </c>
       <c r="BA30">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB30">
         <v>15</v>
@@ -8229,13 +8229,13 @@
         <v>24</v>
       </c>
       <c r="BE30">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF30">
         <v>8.199999999999999</v>
       </c>
       <c r="BG30">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8318,7 +8318,7 @@
         <v>207</v>
       </c>
       <c r="F31">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G31">
         <v>1.88</v>
@@ -8336,16 +8336,16 @@
         <v>4.8</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M31">
         <v>1.03</v>
       </c>
       <c r="N31">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O31">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P31">
         <v>2.58</v>
@@ -8354,10 +8354,10 @@
         <v>1.55</v>
       </c>
       <c r="R31">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S31">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="T31">
         <v>1.58</v>
@@ -8375,163 +8375,163 @@
         <v>32</v>
       </c>
       <c r="Y31">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Z31">
         <v>44</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB31">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC31">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD31">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE31">
         <v>55</v>
       </c>
       <c r="AF31">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG31">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH31">
+        <v>19</v>
+      </c>
+      <c r="AI31">
+        <v>55</v>
+      </c>
+      <c r="AJ31">
         <v>23</v>
       </c>
-      <c r="AI31">
-        <v>1000</v>
-      </c>
-      <c r="AJ31">
-        <v>28</v>
-      </c>
       <c r="AK31">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AL31">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN31">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AO31">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP31">
         <v>20</v>
       </c>
       <c r="AQ31">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AR31">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS31">
+        <v>4.8</v>
+      </c>
+      <c r="AT31">
+        <v>10</v>
+      </c>
+      <c r="AU31">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV31">
+        <v>14</v>
+      </c>
+      <c r="AW31">
         <v>4.6</v>
       </c>
-      <c r="AT31">
-        <v>11.5</v>
-      </c>
-      <c r="AU31">
-        <v>9.4</v>
-      </c>
-      <c r="AV31">
-        <v>12</v>
-      </c>
-      <c r="AW31">
-        <v>4.3</v>
-      </c>
       <c r="AX31">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AY31">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ31">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA31">
         <v>4.6</v>
       </c>
       <c r="BB31">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BC31">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD31">
-        <v>3.95</v>
+        <v>19.5</v>
       </c>
       <c r="BE31">
+        <v>4.8</v>
+      </c>
+      <c r="BF31">
+        <v>5.9</v>
+      </c>
+      <c r="BG31">
+        <v>4.5</v>
+      </c>
+      <c r="BH31">
         <v>4.6</v>
       </c>
-      <c r="BF31">
-        <v>6.6</v>
-      </c>
-      <c r="BG31">
-        <v>4.6</v>
-      </c>
-      <c r="BH31">
-        <v>6</v>
-      </c>
       <c r="BI31">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="BJ31">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BK31">
-        <v>2.56</v>
+        <v>5.4</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>3.1</v>
+        <v>11.5</v>
       </c>
       <c r="BN31">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="BO31">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="BP31">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BQ31">
-        <v>2.7</v>
+        <v>6.2</v>
       </c>
       <c r="BR31">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BS31">
-        <v>2.92</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT31">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BU31">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV31">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BW31">
-        <v>3</v>
+        <v>9.4</v>
       </c>
       <c r="BX31">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BY31">
-        <v>3</v>
+        <v>9.6</v>
       </c>
       <c r="BZ31">
         <v>0</v>
@@ -8563,49 +8563,49 @@
         <v>2.46</v>
       </c>
       <c r="G32">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H32">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I32">
         <v>2.8</v>
       </c>
       <c r="J32">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K32">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L32">
         <v>1.01</v>
       </c>
       <c r="M32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N32">
-        <v>2.68</v>
+        <v>5.5</v>
       </c>
       <c r="O32">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P32">
         <v>2.68</v>
       </c>
       <c r="Q32">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R32">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S32">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T32">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="U32">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="V32">
         <v>1.55</v>
@@ -8614,112 +8614,112 @@
         <v>1.56</v>
       </c>
       <c r="X32">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y32">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z32">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA32">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB32">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC32">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD32">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE32">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF32">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG32">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH32">
+        <v>17</v>
+      </c>
+      <c r="AI32">
+        <v>34</v>
+      </c>
+      <c r="AJ32">
+        <v>44</v>
+      </c>
+      <c r="AK32">
+        <v>28</v>
+      </c>
+      <c r="AL32">
+        <v>32</v>
+      </c>
+      <c r="AM32">
+        <v>60</v>
+      </c>
+      <c r="AN32">
+        <v>14.5</v>
+      </c>
+      <c r="AO32">
+        <v>15</v>
+      </c>
+      <c r="AP32">
+        <v>4.3</v>
+      </c>
+      <c r="AQ32">
+        <v>14</v>
+      </c>
+      <c r="AR32">
+        <v>17</v>
+      </c>
+      <c r="AS32">
+        <v>4.4</v>
+      </c>
+      <c r="AT32">
+        <v>14</v>
+      </c>
+      <c r="AU32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV32">
+        <v>10</v>
+      </c>
+      <c r="AW32">
         <v>18</v>
       </c>
-      <c r="AI32">
-        <v>36</v>
-      </c>
-      <c r="AJ32">
-        <v>1000</v>
-      </c>
-      <c r="AK32">
-        <v>1000</v>
-      </c>
-      <c r="AL32">
-        <v>34</v>
-      </c>
-      <c r="AM32">
-        <v>1000</v>
-      </c>
-      <c r="AN32">
-        <v>1000</v>
-      </c>
-      <c r="AO32">
-        <v>1000</v>
-      </c>
-      <c r="AP32">
-        <v>1.13</v>
-      </c>
-      <c r="AQ32">
-        <v>1.13</v>
-      </c>
-      <c r="AR32">
-        <v>1.13</v>
-      </c>
-      <c r="AS32">
-        <v>1.13</v>
-      </c>
-      <c r="AT32">
-        <v>1.13</v>
-      </c>
-      <c r="AU32">
-        <v>1.13</v>
-      </c>
-      <c r="AV32">
-        <v>1.13</v>
-      </c>
-      <c r="AW32">
-        <v>1.13</v>
-      </c>
       <c r="AX32">
-        <v>1.13</v>
+        <v>17</v>
       </c>
       <c r="AY32">
-        <v>1.13</v>
+        <v>10</v>
       </c>
       <c r="AZ32">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA32">
-        <v>1.1</v>
+        <v>21</v>
       </c>
       <c r="BB32">
-        <v>1.13</v>
+        <v>4.4</v>
       </c>
       <c r="BC32">
-        <v>1.13</v>
+        <v>18</v>
       </c>
       <c r="BD32">
-        <v>1.09</v>
+        <v>21</v>
       </c>
       <c r="BE32">
-        <v>1.13</v>
+        <v>4.5</v>
       </c>
       <c r="BF32">
-        <v>1.13</v>
+        <v>9.6</v>
       </c>
       <c r="BG32">
-        <v>1.13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH32">
         <v>6.4</v>
@@ -8835,10 +8835,10 @@
         <v>2.5</v>
       </c>
       <c r="Q33">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="R33">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S33">
         <v>2.18</v>
@@ -9053,7 +9053,7 @@
         <v>12.5</v>
       </c>
       <c r="I34">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J34">
         <v>6.6</v>
@@ -9089,7 +9089,7 @@
         <v>1.94</v>
       </c>
       <c r="U34">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V34">
         <v>0</v>
@@ -9164,10 +9164,10 @@
         <v>5.1</v>
       </c>
       <c r="AT34">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU34">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV34">
         <v>4.7</v>
@@ -9176,7 +9176,7 @@
         <v>5</v>
       </c>
       <c r="AX34">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="AY34">
         <v>10</v>
@@ -9188,7 +9188,7 @@
         <v>5</v>
       </c>
       <c r="BB34">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC34">
         <v>11.5</v>
@@ -9200,7 +9200,7 @@
         <v>5</v>
       </c>
       <c r="BF34">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="BG34">
         <v>5</v>
@@ -9292,7 +9292,7 @@
         <v>1.94</v>
       </c>
       <c r="H35">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I35">
         <v>5.7</v>
@@ -9304,7 +9304,7 @@
         <v>3.8</v>
       </c>
       <c r="L35">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M35">
         <v>1.07</v>
@@ -9325,7 +9325,7 @@
         <v>1.32</v>
       </c>
       <c r="S35">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T35">
         <v>1.86</v>
@@ -9406,34 +9406,34 @@
         <v>5.7</v>
       </c>
       <c r="AT35">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AU35">
         <v>6.2</v>
       </c>
       <c r="AV35">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AW35">
         <v>5.5</v>
       </c>
       <c r="AX35">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AY35">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ35">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA35">
         <v>5.5</v>
       </c>
       <c r="BB35">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BC35">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BD35">
         <v>5.3</v>
@@ -9442,64 +9442,64 @@
         <v>5.7</v>
       </c>
       <c r="BF35">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BG35">
         <v>5.6</v>
       </c>
       <c r="BH35">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI35">
-        <v>1.82</v>
+        <v>2.68</v>
       </c>
       <c r="BJ35">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BK35">
-        <v>1.62</v>
+        <v>5.3</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>1.82</v>
+        <v>9.6</v>
       </c>
       <c r="BN35">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BO35">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="BP35">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ35">
-        <v>1.66</v>
+        <v>9.4</v>
       </c>
       <c r="BR35">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BS35">
-        <v>1.75</v>
+        <v>7.6</v>
       </c>
       <c r="BT35">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU35">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BV35">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW35">
-        <v>1.77</v>
+        <v>8.4</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>1.78</v>
+        <v>8.6</v>
       </c>
       <c r="BZ35">
         <v>0</v>
@@ -9531,16 +9531,16 @@
         <v>2.24</v>
       </c>
       <c r="G36">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H36">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I36">
         <v>3.85</v>
       </c>
       <c r="J36">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K36">
         <v>3.5</v>
@@ -9555,13 +9555,13 @@
         <v>2.92</v>
       </c>
       <c r="O36">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P36">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q36">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R36">
         <v>1.25</v>
@@ -9570,7 +9570,7 @@
         <v>4.4</v>
       </c>
       <c r="T36">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U36">
         <v>1.9</v>
@@ -9579,7 +9579,7 @@
         <v>1.35</v>
       </c>
       <c r="W36">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X36">
         <v>12</v>
@@ -9633,13 +9633,13 @@
         <v>26</v>
       </c>
       <c r="AO36">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP36">
         <v>4.1</v>
       </c>
       <c r="AQ36">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="AR36">
         <v>5.2</v>
@@ -9648,19 +9648,19 @@
         <v>5.9</v>
       </c>
       <c r="AT36">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="AU36">
         <v>3.5</v>
       </c>
       <c r="AV36">
-        <v>4.7</v>
+        <v>14</v>
       </c>
       <c r="AW36">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AX36">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY36">
         <v>9.800000000000001</v>
@@ -9672,7 +9672,7 @@
         <v>5.8</v>
       </c>
       <c r="BB36">
-        <v>5.3</v>
+        <v>26</v>
       </c>
       <c r="BC36">
         <v>5.3</v>
@@ -9690,7 +9690,7 @@
         <v>5.8</v>
       </c>
       <c r="BH36">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI36">
         <v>2.48</v>
@@ -9699,31 +9699,31 @@
         <v>11</v>
       </c>
       <c r="BK36">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN36">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO36">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BP36">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR36">
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT36">
         <v>7</v>
@@ -9735,19 +9735,19 @@
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
+        <v>11.5</v>
+      </c>
+      <c r="BZ36">
+        <v>1000</v>
+      </c>
+      <c r="CA36">
         <v>10.5</v>
-      </c>
-      <c r="BZ36">
-        <v>1000</v>
-      </c>
-      <c r="CA36">
-        <v>9.800000000000001</v>
       </c>
       <c r="CB36" t="s">
         <v>230</v>
@@ -9773,13 +9773,13 @@
         <v>3.45</v>
       </c>
       <c r="G37">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H37">
         <v>2</v>
       </c>
       <c r="I37">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J37">
         <v>3.75</v>
@@ -9806,7 +9806,7 @@
         <v>1.65</v>
       </c>
       <c r="R37">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S37">
         <v>2.66</v>
@@ -9815,13 +9815,13 @@
         <v>1.61</v>
       </c>
       <c r="U37">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V37">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W37">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X37">
         <v>25</v>
@@ -10012,7 +10012,7 @@
         <v>214</v>
       </c>
       <c r="F38">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G38">
         <v>4.2</v>
@@ -10054,10 +10054,10 @@
         <v>4.2</v>
       </c>
       <c r="T38">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="U38">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="V38">
         <v>1.73</v>
@@ -10254,88 +10254,88 @@
         <v>215</v>
       </c>
       <c r="F39">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="G39">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H39">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="I39">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="J39">
         <v>3.8</v>
       </c>
       <c r="K39">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L39">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M39">
         <v>1.04</v>
       </c>
       <c r="N39">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O39">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P39">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q39">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R39">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S39">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="T39">
         <v>1.6</v>
       </c>
       <c r="U39">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V39">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W39">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X39">
         <v>24</v>
       </c>
       <c r="Y39">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z39">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA39">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB39">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC39">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD39">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE39">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF39">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG39">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH39">
         <v>17</v>
@@ -10344,10 +10344,10 @@
         <v>34</v>
       </c>
       <c r="AJ39">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK39">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL39">
         <v>38</v>
@@ -10356,118 +10356,118 @@
         <v>75</v>
       </c>
       <c r="AN39">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO39">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP39">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ39">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR39">
+        <v>4.8</v>
+      </c>
+      <c r="AS39">
+        <v>5.6</v>
+      </c>
+      <c r="AT39">
         <v>4.7</v>
       </c>
-      <c r="AS39">
-        <v>5.4</v>
-      </c>
-      <c r="AT39">
-        <v>4.5</v>
-      </c>
       <c r="AU39">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AV39">
         <v>4.3</v>
       </c>
       <c r="AW39">
+        <v>5.2</v>
+      </c>
+      <c r="AX39">
         <v>5.1</v>
-      </c>
-      <c r="AX39">
-        <v>5</v>
       </c>
       <c r="AY39">
         <v>4.5</v>
       </c>
       <c r="AZ39">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA39">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB39">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BC39">
         <v>5.3</v>
       </c>
       <c r="BD39">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE39">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF39">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG39">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH39">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI39">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BJ39">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK39">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BN39">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO39">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP39">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ39">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR39">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS39">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT39">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU39">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV39">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW39">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX39">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY39">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ39">
         <v>0</v>
@@ -10496,16 +10496,16 @@
         <v>216</v>
       </c>
       <c r="F40">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G40">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H40">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I40">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J40">
         <v>3.55</v>
@@ -10514,13 +10514,13 @@
         <v>3.8</v>
       </c>
       <c r="L40">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M40">
         <v>1.05</v>
       </c>
       <c r="N40">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O40">
         <v>1.24</v>
@@ -10529,16 +10529,16 @@
         <v>2.16</v>
       </c>
       <c r="Q40">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="R40">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S40">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="T40">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U40">
         <v>2.34</v>
@@ -10619,7 +10619,7 @@
         <v>11</v>
       </c>
       <c r="AU40">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV40">
         <v>9.199999999999999</v>
@@ -10652,64 +10652,64 @@
         <v>4.6</v>
       </c>
       <c r="BF40">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG40">
         <v>12.5</v>
       </c>
       <c r="BH40">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI40">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="BJ40">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BK40">
-        <v>1.69</v>
+        <v>5.4</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.95</v>
+        <v>11.5</v>
       </c>
       <c r="BN40">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO40">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BP40">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>1.83</v>
+        <v>8.4</v>
       </c>
       <c r="BR40">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS40">
-        <v>1.87</v>
+        <v>9.6</v>
       </c>
       <c r="BT40">
+        <v>5.7</v>
+      </c>
+      <c r="BU40">
+        <v>4.6</v>
+      </c>
+      <c r="BV40">
+        <v>1000</v>
+      </c>
+      <c r="BW40">
         <v>7.6</v>
       </c>
-      <c r="BU40">
-        <v>3.85</v>
-      </c>
-      <c r="BV40">
-        <v>24</v>
-      </c>
-      <c r="BW40">
-        <v>1.8</v>
-      </c>
       <c r="BX40">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY40">
-        <v>1.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ40">
         <v>0</v>
@@ -10741,223 +10741,223 @@
         <v>3.05</v>
       </c>
       <c r="G41">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H41">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I41">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J41">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K41">
         <v>3.6</v>
       </c>
       <c r="L41">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M41">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N41">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="O41">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P41">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q41">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="R41">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S41">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="T41">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="U41">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="V41">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W41">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X41">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y41">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z41">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AA41">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB41">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AC41">
+        <v>8</v>
+      </c>
+      <c r="AD41">
+        <v>12.5</v>
+      </c>
+      <c r="AE41">
+        <v>32</v>
+      </c>
+      <c r="AF41">
+        <v>24</v>
+      </c>
+      <c r="AG41">
+        <v>15</v>
+      </c>
+      <c r="AH41">
+        <v>19.5</v>
+      </c>
+      <c r="AI41">
+        <v>48</v>
+      </c>
+      <c r="AJ41">
+        <v>65</v>
+      </c>
+      <c r="AK41">
+        <v>44</v>
+      </c>
+      <c r="AL41">
+        <v>60</v>
+      </c>
+      <c r="AM41">
+        <v>140</v>
+      </c>
+      <c r="AN41">
+        <v>46</v>
+      </c>
+      <c r="AO41">
+        <v>28</v>
+      </c>
+      <c r="AP41">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ41">
+        <v>8</v>
+      </c>
+      <c r="AR41">
+        <v>13</v>
+      </c>
+      <c r="AS41">
+        <v>6.6</v>
+      </c>
+      <c r="AT41">
+        <v>9.6</v>
+      </c>
+      <c r="AU41">
+        <v>6.4</v>
+      </c>
+      <c r="AV41">
+        <v>10</v>
+      </c>
+      <c r="AW41">
+        <v>6.4</v>
+      </c>
+      <c r="AX41">
+        <v>18.5</v>
+      </c>
+      <c r="AY41">
+        <v>12</v>
+      </c>
+      <c r="AZ41">
+        <v>15.5</v>
+      </c>
+      <c r="BA41">
+        <v>6.8</v>
+      </c>
+      <c r="BB41">
+        <v>7.2</v>
+      </c>
+      <c r="BC41">
+        <v>6.8</v>
+      </c>
+      <c r="BD41">
+        <v>38</v>
+      </c>
+      <c r="BE41">
+        <v>7.6</v>
+      </c>
+      <c r="BF41">
+        <v>30</v>
+      </c>
+      <c r="BG41">
+        <v>19</v>
+      </c>
+      <c r="BH41">
+        <v>3.25</v>
+      </c>
+      <c r="BI41">
+        <v>2.78</v>
+      </c>
+      <c r="BJ41">
         <v>10.5</v>
       </c>
-      <c r="AD41">
-        <v>17.5</v>
-      </c>
-      <c r="AE41">
-        <v>46</v>
-      </c>
-      <c r="AF41">
-        <v>32</v>
-      </c>
-      <c r="AG41">
+      <c r="BK41">
+        <v>7.4</v>
+      </c>
+      <c r="BL41">
+        <v>1000</v>
+      </c>
+      <c r="BM41">
+        <v>9.4</v>
+      </c>
+      <c r="BN41">
+        <v>6.6</v>
+      </c>
+      <c r="BO41">
+        <v>4.8</v>
+      </c>
+      <c r="BP41">
+        <v>1000</v>
+      </c>
+      <c r="BQ41">
+        <v>7.4</v>
+      </c>
+      <c r="BR41">
+        <v>1000</v>
+      </c>
+      <c r="BS41">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT41">
+        <v>5.5</v>
+      </c>
+      <c r="BU41">
+        <v>4</v>
+      </c>
+      <c r="BV41">
         <v>21</v>
       </c>
-      <c r="AH41">
-        <v>950</v>
-      </c>
-      <c r="AI41">
-        <v>1000</v>
-      </c>
-      <c r="AJ41">
-        <v>1000</v>
-      </c>
-      <c r="AK41">
-        <v>1000</v>
-      </c>
-      <c r="AL41">
-        <v>1000</v>
-      </c>
-      <c r="AM41">
-        <v>1000</v>
-      </c>
-      <c r="AN41">
-        <v>1000</v>
-      </c>
-      <c r="AO41">
-        <v>1000</v>
-      </c>
-      <c r="AP41">
-        <v>1.88</v>
-      </c>
-      <c r="AQ41">
-        <v>5.9</v>
-      </c>
-      <c r="AR41">
-        <v>9.6</v>
-      </c>
-      <c r="AS41">
-        <v>1.88</v>
-      </c>
-      <c r="AT41">
-        <v>7</v>
-      </c>
-      <c r="AU41">
-        <v>4.9</v>
-      </c>
-      <c r="AV41">
-        <v>7.4</v>
-      </c>
-      <c r="AW41">
-        <v>18.5</v>
-      </c>
-      <c r="AX41">
-        <v>13.5</v>
-      </c>
-      <c r="AY41">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ41">
-        <v>11.5</v>
-      </c>
-      <c r="BA41">
-        <v>1.88</v>
-      </c>
-      <c r="BB41">
-        <v>1.88</v>
-      </c>
-      <c r="BC41">
-        <v>1.88</v>
-      </c>
-      <c r="BD41">
-        <v>1.88</v>
-      </c>
-      <c r="BE41">
-        <v>1.88</v>
-      </c>
-      <c r="BF41">
-        <v>1.88</v>
-      </c>
-      <c r="BG41">
-        <v>1.88</v>
-      </c>
-      <c r="BH41">
-        <v>3.8</v>
-      </c>
-      <c r="BI41">
-        <v>2.5</v>
-      </c>
-      <c r="BJ41">
-        <v>14.5</v>
-      </c>
-      <c r="BK41">
-        <v>2.66</v>
-      </c>
-      <c r="BL41">
-        <v>1000</v>
-      </c>
-      <c r="BM41">
-        <v>3.2</v>
-      </c>
-      <c r="BN41">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO41">
-        <v>4.3</v>
-      </c>
-      <c r="BP41">
-        <v>40</v>
-      </c>
-      <c r="BQ41">
-        <v>3</v>
-      </c>
-      <c r="BR41">
-        <v>1000</v>
-      </c>
-      <c r="BS41">
-        <v>3.1</v>
-      </c>
-      <c r="BT41">
-        <v>7.6</v>
-      </c>
-      <c r="BU41">
-        <v>3.65</v>
-      </c>
-      <c r="BV41">
-        <v>29</v>
-      </c>
       <c r="BW41">
-        <v>2.92</v>
+        <v>6.8</v>
       </c>
       <c r="BX41">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY41">
-        <v>3.05</v>
+        <v>8</v>
       </c>
       <c r="BZ41">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA41">
-        <v>3.05</v>
+        <v>7.8</v>
       </c>
       <c r="CB41" t="s">
         <v>230</v>
@@ -10986,7 +10986,7 @@
         <v>12</v>
       </c>
       <c r="H42">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I42">
         <v>1.4</v>
@@ -10998,19 +10998,19 @@
         <v>6.6</v>
       </c>
       <c r="L42">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M42">
         <v>1.01</v>
       </c>
       <c r="N42">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O42">
         <v>1.16</v>
       </c>
       <c r="P42">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q42">
         <v>1.54</v>
@@ -11019,10 +11019,10 @@
         <v>1.59</v>
       </c>
       <c r="S42">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T42">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U42">
         <v>1.9</v>
@@ -11085,10 +11085,10 @@
         <v>200</v>
       </c>
       <c r="AO42">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AP42">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="AQ42">
         <v>8</v>
@@ -11097,103 +11097,103 @@
         <v>7.2</v>
       </c>
       <c r="AS42">
-        <v>3.75</v>
+        <v>8.6</v>
       </c>
       <c r="AT42">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU42">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AV42">
-        <v>3.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW42">
         <v>11</v>
       </c>
       <c r="AX42">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AY42">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ42">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BA42">
         <v>4.7</v>
       </c>
       <c r="BB42">
+        <v>5.3</v>
+      </c>
+      <c r="BC42">
         <v>5.2</v>
       </c>
-      <c r="BC42">
-        <v>5.1</v>
-      </c>
       <c r="BD42">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE42">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF42">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG42">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="BH42">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI42">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BJ42">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK42">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN42">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BO42">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BP42">
         <v>1000</v>
       </c>
       <c r="BQ42">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BR42">
         <v>1000</v>
       </c>
       <c r="BS42">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT42">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BU42">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BV42">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BW42">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX42">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY42">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ42">
         <v>0</v>
@@ -11222,7 +11222,7 @@
         <v>219</v>
       </c>
       <c r="F43">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="G43">
         <v>3.4</v>
@@ -11231,10 +11231,10 @@
         <v>2.32</v>
       </c>
       <c r="I43">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J43">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K43">
         <v>3.95</v>
@@ -11252,16 +11252,16 @@
         <v>1.27</v>
       </c>
       <c r="P43">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q43">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R43">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S43">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T43">
         <v>1.65</v>
@@ -11270,7 +11270,7 @@
         <v>2.24</v>
       </c>
       <c r="V43">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W43">
         <v>1.42</v>
@@ -11282,10 +11282,10 @@
         <v>14</v>
       </c>
       <c r="Z43">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA43">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AB43">
         <v>14.5</v>
@@ -11336,52 +11336,52 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR43">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS43">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT43">
         <v>10.5</v>
       </c>
       <c r="AU43">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV43">
         <v>9</v>
       </c>
       <c r="AW43">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX43">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY43">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ43">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA43">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB43">
+        <v>5.5</v>
+      </c>
+      <c r="BC43">
+        <v>5.2</v>
+      </c>
+      <c r="BD43">
         <v>5.4</v>
       </c>
-      <c r="BC43">
-        <v>5.1</v>
-      </c>
-      <c r="BD43">
-        <v>5.3</v>
-      </c>
       <c r="BE43">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF43">
         <v>20</v>
       </c>
       <c r="BG43">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH43">
         <v>4.6</v>
@@ -11464,22 +11464,22 @@
         <v>220</v>
       </c>
       <c r="F44">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G44">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H44">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="I44">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J44">
         <v>3.6</v>
       </c>
       <c r="K44">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L44">
         <v>1.28</v>
@@ -11497,25 +11497,25 @@
         <v>2.16</v>
       </c>
       <c r="Q44">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R44">
         <v>1.46</v>
       </c>
       <c r="S44">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T44">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U44">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V44">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W44">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X44">
         <v>24</v>
@@ -11524,7 +11524,7 @@
         <v>15.5</v>
       </c>
       <c r="Z44">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AA44">
         <v>55</v>
@@ -11533,16 +11533,16 @@
         <v>14</v>
       </c>
       <c r="AC44">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AD44">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE44">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF44">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG44">
         <v>12.5</v>
@@ -11563,13 +11563,13 @@
         <v>34</v>
       </c>
       <c r="AM44">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN44">
         <v>20</v>
       </c>
       <c r="AO44">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP44">
         <v>14</v>
@@ -11578,19 +11578,19 @@
         <v>10.5</v>
       </c>
       <c r="AR44">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS44">
-        <v>30</v>
+        <v>5.1</v>
       </c>
       <c r="AT44">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU44">
         <v>6.6</v>
       </c>
       <c r="AV44">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW44">
         <v>21</v>
@@ -11599,37 +11599,37 @@
         <v>13.5</v>
       </c>
       <c r="AY44">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ44">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA44">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="BB44">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC44">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD44">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BE44">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF44">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BG44">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BH44">
         <v>4.1</v>
       </c>
       <c r="BI44">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BJ44">
         <v>9.199999999999999</v>
@@ -11641,43 +11641,43 @@
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN44">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO44">
         <v>4.9</v>
       </c>
       <c r="BP44">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ44">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR44">
         <v>28</v>
       </c>
       <c r="BS44">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT44">
         <v>6.6</v>
       </c>
       <c r="BU44">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV44">
         <v>22</v>
       </c>
       <c r="BW44">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX44">
         <v>32</v>
       </c>
       <c r="BY44">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ44">
         <v>0</v>
@@ -11706,220 +11706,220 @@
         <v>221</v>
       </c>
       <c r="F45">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="G45">
+        <v>1.76</v>
+      </c>
+      <c r="H45">
+        <v>5.3</v>
+      </c>
+      <c r="I45">
+        <v>7.2</v>
+      </c>
+      <c r="J45">
+        <v>4</v>
+      </c>
+      <c r="K45">
+        <v>4.6</v>
+      </c>
+      <c r="L45">
+        <v>1.29</v>
+      </c>
+      <c r="M45">
+        <v>1.05</v>
+      </c>
+      <c r="N45">
+        <v>4.1</v>
+      </c>
+      <c r="O45">
+        <v>1.26</v>
+      </c>
+      <c r="P45">
+        <v>2.1</v>
+      </c>
+      <c r="Q45">
+        <v>1.75</v>
+      </c>
+      <c r="R45">
+        <v>1.42</v>
+      </c>
+      <c r="S45">
+        <v>2.92</v>
+      </c>
+      <c r="T45">
         <v>1.79</v>
       </c>
-      <c r="H45">
+      <c r="U45">
+        <v>2.08</v>
+      </c>
+      <c r="V45">
+        <v>1.18</v>
+      </c>
+      <c r="W45">
+        <v>2.3</v>
+      </c>
+      <c r="X45">
+        <v>22</v>
+      </c>
+      <c r="Y45">
+        <v>26</v>
+      </c>
+      <c r="Z45">
+        <v>60</v>
+      </c>
+      <c r="AA45">
+        <v>170</v>
+      </c>
+      <c r="AB45">
+        <v>11.5</v>
+      </c>
+      <c r="AC45">
+        <v>12</v>
+      </c>
+      <c r="AD45">
+        <v>27</v>
+      </c>
+      <c r="AE45">
+        <v>90</v>
+      </c>
+      <c r="AF45">
+        <v>13</v>
+      </c>
+      <c r="AG45">
+        <v>12.5</v>
+      </c>
+      <c r="AH45">
+        <v>24</v>
+      </c>
+      <c r="AI45">
+        <v>85</v>
+      </c>
+      <c r="AJ45">
+        <v>21</v>
+      </c>
+      <c r="AK45">
+        <v>21</v>
+      </c>
+      <c r="AL45">
+        <v>40</v>
+      </c>
+      <c r="AM45">
+        <v>120</v>
+      </c>
+      <c r="AN45">
+        <v>11</v>
+      </c>
+      <c r="AO45">
+        <v>100</v>
+      </c>
+      <c r="AP45">
+        <v>13</v>
+      </c>
+      <c r="AQ45">
+        <v>15</v>
+      </c>
+      <c r="AR45">
+        <v>3.95</v>
+      </c>
+      <c r="AS45">
+        <v>4.1</v>
+      </c>
+      <c r="AT45">
+        <v>7</v>
+      </c>
+      <c r="AU45">
+        <v>7.2</v>
+      </c>
+      <c r="AV45">
+        <v>15.5</v>
+      </c>
+      <c r="AW45">
+        <v>4</v>
+      </c>
+      <c r="AX45">
+        <v>8</v>
+      </c>
+      <c r="AY45">
+        <v>7.4</v>
+      </c>
+      <c r="AZ45">
+        <v>14.5</v>
+      </c>
+      <c r="BA45">
+        <v>4</v>
+      </c>
+      <c r="BB45">
+        <v>12</v>
+      </c>
+      <c r="BC45">
+        <v>12.5</v>
+      </c>
+      <c r="BD45">
+        <v>3.8</v>
+      </c>
+      <c r="BE45">
+        <v>4.1</v>
+      </c>
+      <c r="BF45">
+        <v>6.6</v>
+      </c>
+      <c r="BG45">
+        <v>4</v>
+      </c>
+      <c r="BH45">
+        <v>3.9</v>
+      </c>
+      <c r="BI45">
+        <v>3.3</v>
+      </c>
+      <c r="BJ45">
+        <v>10.5</v>
+      </c>
+      <c r="BK45">
+        <v>5.3</v>
+      </c>
+      <c r="BL45">
+        <v>1000</v>
+      </c>
+      <c r="BM45">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN45">
         <v>4.5</v>
       </c>
-      <c r="I45">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J45">
-        <v>3.85</v>
-      </c>
-      <c r="K45">
+      <c r="BO45">
+        <v>3.8</v>
+      </c>
+      <c r="BP45">
+        <v>11.5</v>
+      </c>
+      <c r="BQ45">
+        <v>5.5</v>
+      </c>
+      <c r="BR45">
+        <v>1000</v>
+      </c>
+      <c r="BS45">
+        <v>7.4</v>
+      </c>
+      <c r="BT45">
         <v>9.4</v>
       </c>
-      <c r="L45">
-        <v>1.01</v>
-      </c>
-      <c r="M45">
-        <v>1.01</v>
-      </c>
-      <c r="N45">
-        <v>2.2</v>
-      </c>
-      <c r="O45">
-        <v>1.25</v>
-      </c>
-      <c r="P45">
-        <v>1.81</v>
-      </c>
-      <c r="Q45">
-        <v>1.63</v>
-      </c>
-      <c r="R45">
-        <v>1.34</v>
-      </c>
-      <c r="S45">
-        <v>2.58</v>
-      </c>
-      <c r="T45">
-        <v>1.11</v>
-      </c>
-      <c r="U45">
-        <v>1.11</v>
-      </c>
-      <c r="V45">
-        <v>1.14</v>
-      </c>
-      <c r="W45">
-        <v>2.26</v>
-      </c>
-      <c r="X45">
-        <v>1000</v>
-      </c>
-      <c r="Y45">
-        <v>1000</v>
-      </c>
-      <c r="Z45">
-        <v>1000</v>
-      </c>
-      <c r="AA45">
-        <v>1000</v>
-      </c>
-      <c r="AB45">
-        <v>1000</v>
-      </c>
-      <c r="AC45">
-        <v>1000</v>
-      </c>
-      <c r="AD45">
-        <v>1000</v>
-      </c>
-      <c r="AE45">
-        <v>1000</v>
-      </c>
-      <c r="AF45">
-        <v>1000</v>
-      </c>
-      <c r="AG45">
-        <v>1000</v>
-      </c>
-      <c r="AH45">
-        <v>1000</v>
-      </c>
-      <c r="AI45">
-        <v>1000</v>
-      </c>
-      <c r="AJ45">
-        <v>1000</v>
-      </c>
-      <c r="AK45">
-        <v>1000</v>
-      </c>
-      <c r="AL45">
-        <v>1000</v>
-      </c>
-      <c r="AM45">
-        <v>1000</v>
-      </c>
-      <c r="AN45">
-        <v>1000</v>
-      </c>
-      <c r="AO45">
-        <v>1000</v>
-      </c>
-      <c r="AP45">
-        <v>1.01</v>
-      </c>
-      <c r="AQ45">
-        <v>1.01</v>
-      </c>
-      <c r="AR45">
-        <v>1.01</v>
-      </c>
-      <c r="AS45">
-        <v>1.01</v>
-      </c>
-      <c r="AT45">
-        <v>1.01</v>
-      </c>
-      <c r="AU45">
-        <v>1.01</v>
-      </c>
-      <c r="AV45">
-        <v>1.01</v>
-      </c>
-      <c r="AW45">
-        <v>1.01</v>
-      </c>
-      <c r="AX45">
-        <v>1.01</v>
-      </c>
-      <c r="AY45">
-        <v>1.01</v>
-      </c>
-      <c r="AZ45">
-        <v>1.01</v>
-      </c>
-      <c r="BA45">
-        <v>1.01</v>
-      </c>
-      <c r="BB45">
-        <v>1.01</v>
-      </c>
-      <c r="BC45">
-        <v>1.01</v>
-      </c>
-      <c r="BD45">
-        <v>1.01</v>
-      </c>
-      <c r="BE45">
-        <v>1.01</v>
-      </c>
-      <c r="BF45">
-        <v>1.01</v>
-      </c>
-      <c r="BG45">
-        <v>1.01</v>
-      </c>
-      <c r="BH45">
-        <v>4.5</v>
-      </c>
-      <c r="BI45">
-        <v>2.98</v>
-      </c>
-      <c r="BJ45">
-        <v>13.5</v>
-      </c>
-      <c r="BK45">
-        <v>2.78</v>
-      </c>
-      <c r="BL45">
-        <v>1000</v>
-      </c>
-      <c r="BM45">
-        <v>3.5</v>
-      </c>
-      <c r="BN45">
-        <v>5.8</v>
-      </c>
-      <c r="BO45">
-        <v>3.1</v>
-      </c>
-      <c r="BP45">
-        <v>15</v>
-      </c>
-      <c r="BQ45">
-        <v>2.84</v>
-      </c>
-      <c r="BR45">
-        <v>32</v>
-      </c>
-      <c r="BS45">
-        <v>3.15</v>
-      </c>
-      <c r="BT45">
-        <v>13</v>
-      </c>
       <c r="BU45">
-        <v>2.76</v>
+        <v>5</v>
       </c>
       <c r="BV45">
         <v>1000</v>
       </c>
       <c r="BW45">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="BX45">
         <v>1000</v>
       </c>
       <c r="BY45">
-        <v>3.35</v>
+        <v>9</v>
       </c>
       <c r="BZ45">
         <v>0</v>
@@ -11948,43 +11948,43 @@
         <v>222</v>
       </c>
       <c r="F46">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G46">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="H46">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I46">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J46">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K46">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L46">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M46">
         <v>1.07</v>
       </c>
       <c r="N46">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O46">
         <v>1.33</v>
       </c>
       <c r="P46">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q46">
         <v>1.97</v>
       </c>
       <c r="R46">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S46">
         <v>3.45</v>
@@ -11993,13 +11993,13 @@
         <v>1.74</v>
       </c>
       <c r="U46">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V46">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W46">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X46">
         <v>14</v>
@@ -12011,7 +12011,7 @@
         <v>24</v>
       </c>
       <c r="AA46">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB46">
         <v>12.5</v>
@@ -12023,7 +12023,7 @@
         <v>15.5</v>
       </c>
       <c r="AE46">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF46">
         <v>19.5</v>
@@ -12038,7 +12038,7 @@
         <v>55</v>
       </c>
       <c r="AJ46">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK46">
         <v>29</v>
@@ -12053,7 +12053,7 @@
         <v>27</v>
       </c>
       <c r="AO46">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP46">
         <v>10.5</v>
@@ -12062,13 +12062,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR46">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS46">
         <v>5.8</v>
       </c>
       <c r="AT46">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU46">
         <v>6.2</v>
@@ -12089,79 +12089,79 @@
         <v>13</v>
       </c>
       <c r="BA46">
+        <v>5.9</v>
+      </c>
+      <c r="BB46">
+        <v>5.7</v>
+      </c>
+      <c r="BC46">
+        <v>5.3</v>
+      </c>
+      <c r="BD46">
         <v>5.8</v>
-      </c>
-      <c r="BB46">
-        <v>5.6</v>
-      </c>
-      <c r="BC46">
-        <v>21</v>
-      </c>
-      <c r="BD46">
-        <v>5.7</v>
       </c>
       <c r="BE46">
         <v>6.2</v>
       </c>
       <c r="BF46">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG46">
+        <v>5.5</v>
+      </c>
+      <c r="BH46">
+        <v>3.4</v>
+      </c>
+      <c r="BI46">
+        <v>3.05</v>
+      </c>
+      <c r="BJ46">
+        <v>9.6</v>
+      </c>
+      <c r="BK46">
+        <v>5.8</v>
+      </c>
+      <c r="BL46">
+        <v>1000</v>
+      </c>
+      <c r="BM46">
+        <v>13</v>
+      </c>
+      <c r="BN46">
         <v>5.6</v>
       </c>
-      <c r="BH46">
-        <v>4.1</v>
-      </c>
-      <c r="BI46">
-        <v>2.66</v>
-      </c>
-      <c r="BJ46">
-        <v>1000</v>
-      </c>
-      <c r="BK46">
-        <v>1.33</v>
-      </c>
-      <c r="BL46">
-        <v>1000</v>
-      </c>
-      <c r="BM46">
-        <v>1.33</v>
-      </c>
-      <c r="BN46">
-        <v>1000</v>
-      </c>
       <c r="BO46">
-        <v>1.33</v>
+        <v>4.4</v>
       </c>
       <c r="BP46">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ46">
-        <v>1.33</v>
+        <v>8.4</v>
       </c>
       <c r="BR46">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS46">
-        <v>1.33</v>
+        <v>10</v>
       </c>
       <c r="BT46">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU46">
-        <v>1.33</v>
+        <v>4.8</v>
       </c>
       <c r="BV46">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW46">
-        <v>1.33</v>
+        <v>9</v>
       </c>
       <c r="BX46">
         <v>1000</v>
       </c>
       <c r="BY46">
-        <v>1.33</v>
+        <v>10</v>
       </c>
       <c r="BZ46">
         <v>0</v>
@@ -12190,16 +12190,16 @@
         <v>223</v>
       </c>
       <c r="F47">
+        <v>1.43</v>
+      </c>
+      <c r="G47">
         <v>1.5</v>
-      </c>
-      <c r="G47">
-        <v>1.53</v>
       </c>
       <c r="H47">
         <v>7</v>
       </c>
       <c r="I47">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J47">
         <v>4.9</v>
@@ -12220,28 +12220,28 @@
         <v>1.18</v>
       </c>
       <c r="P47">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q47">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R47">
         <v>1.6</v>
       </c>
       <c r="S47">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T47">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U47">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V47">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W47">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="X47">
         <v>32</v>
@@ -12292,7 +12292,7 @@
         <v>120</v>
       </c>
       <c r="AN47">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AO47">
         <v>120</v>
@@ -12304,10 +12304,10 @@
         <v>17.5</v>
       </c>
       <c r="AR47">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS47">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT47">
         <v>9.4</v>
@@ -12319,7 +12319,7 @@
         <v>16</v>
       </c>
       <c r="AW47">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX47">
         <v>9</v>
@@ -12331,7 +12331,7 @@
         <v>17.5</v>
       </c>
       <c r="BA47">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB47">
         <v>11.5</v>
@@ -12343,13 +12343,13 @@
         <v>20</v>
       </c>
       <c r="BE47">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF47">
         <v>4.8</v>
       </c>
       <c r="BG47">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12432,16 +12432,16 @@
         <v>224</v>
       </c>
       <c r="F48">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="G48">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="H48">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="I48">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="J48">
         <v>3.45</v>
@@ -12459,10 +12459,10 @@
         <v>3.35</v>
       </c>
       <c r="O48">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P48">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q48">
         <v>2.02</v>
@@ -12480,10 +12480,10 @@
         <v>1.95</v>
       </c>
       <c r="V48">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W48">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X48">
         <v>15.5</v>
@@ -12528,7 +12528,7 @@
         <v>75</v>
       </c>
       <c r="AL48">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AM48">
         <v>150</v>
@@ -12588,7 +12588,7 @@
         <v>7.2</v>
       </c>
       <c r="BF48">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG48">
         <v>11</v>
@@ -12615,13 +12615,13 @@
         <v>11</v>
       </c>
       <c r="BO48">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP48">
         <v>1000</v>
       </c>
       <c r="BQ48">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BR48">
         <v>1000</v>
@@ -12630,22 +12630,22 @@
         <v>1.82</v>
       </c>
       <c r="BT48">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU48">
         <v>3.3</v>
       </c>
       <c r="BV48">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BW48">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BX48">
         <v>42</v>
       </c>
       <c r="BY48">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BZ48">
         <v>0</v>
@@ -12686,19 +12686,19 @@
         <v>12</v>
       </c>
       <c r="J49">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K49">
         <v>7.6</v>
       </c>
       <c r="L49">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M49">
         <v>1.01</v>
       </c>
       <c r="N49">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="O49">
         <v>1.1</v>
@@ -12707,25 +12707,25 @@
         <v>3.65</v>
       </c>
       <c r="Q49">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="R49">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="S49">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="T49">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U49">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V49">
         <v>1.09</v>
       </c>
       <c r="W49">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X49">
         <v>950</v>
@@ -12752,10 +12752,10 @@
         <v>150</v>
       </c>
       <c r="AF49">
+        <v>12</v>
+      </c>
+      <c r="AG49">
         <v>12.5</v>
-      </c>
-      <c r="AG49">
-        <v>13</v>
       </c>
       <c r="AH49">
         <v>26</v>
@@ -12776,22 +12776,22 @@
         <v>110</v>
       </c>
       <c r="AN49">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AO49">
         <v>120</v>
       </c>
       <c r="AP49">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ49">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR49">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS49">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT49">
         <v>14</v>
@@ -12803,97 +12803,97 @@
         <v>30</v>
       </c>
       <c r="AW49">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX49">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY49">
         <v>10.5</v>
       </c>
       <c r="AZ49">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA49">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB49">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC49">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD49">
         <v>19</v>
       </c>
       <c r="BE49">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF49">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="BG49">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH49">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI49">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BJ49">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK49">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL49">
         <v>1000</v>
       </c>
       <c r="BM49">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN49">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO49">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP49">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BQ49">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BR49">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS49">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT49">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU49">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BV49">
         <v>1000</v>
       </c>
       <c r="BW49">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX49">
         <v>1000</v>
       </c>
       <c r="BY49">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ49">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="CA49">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB49" t="s">
         <v>230</v>
@@ -12916,16 +12916,16 @@
         <v>226</v>
       </c>
       <c r="F50">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="G50">
         <v>6.6</v>
       </c>
       <c r="H50">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="I50">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="J50">
         <v>4.8</v>
@@ -12952,7 +12952,7 @@
         <v>1.53</v>
       </c>
       <c r="R50">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S50">
         <v>2.32</v>
@@ -12961,10 +12961,10 @@
         <v>1.65</v>
       </c>
       <c r="U50">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V50">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="W50">
         <v>1.18</v>
@@ -13024,7 +13024,7 @@
         <v>6.4</v>
       </c>
       <c r="AP50">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AQ50">
         <v>10.5</v>
@@ -13054,7 +13054,7 @@
         <v>20</v>
       </c>
       <c r="AZ50">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA50">
         <v>22</v>
@@ -13084,37 +13084,37 @@
         <v>3.55</v>
       </c>
       <c r="BJ50">
+        <v>9.6</v>
+      </c>
+      <c r="BK50">
+        <v>5.5</v>
+      </c>
+      <c r="BL50">
+        <v>1000</v>
+      </c>
+      <c r="BM50">
+        <v>11</v>
+      </c>
+      <c r="BN50">
         <v>9.800000000000001</v>
       </c>
-      <c r="BK50">
-        <v>5.2</v>
-      </c>
-      <c r="BL50">
-        <v>1000</v>
-      </c>
-      <c r="BM50">
+      <c r="BO50">
+        <v>5.5</v>
+      </c>
+      <c r="BP50">
+        <v>1000</v>
+      </c>
+      <c r="BQ50">
+        <v>10</v>
+      </c>
+      <c r="BR50">
+        <v>1000</v>
+      </c>
+      <c r="BS50">
         <v>9.800000000000001</v>
       </c>
-      <c r="BN50">
-        <v>10</v>
-      </c>
-      <c r="BO50">
-        <v>5.2</v>
-      </c>
-      <c r="BP50">
-        <v>1000</v>
-      </c>
-      <c r="BQ50">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR50">
-        <v>1000</v>
-      </c>
-      <c r="BS50">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BT50">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU50">
         <v>3.5</v>
@@ -13123,13 +13123,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BW50">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BX50">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BY50">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BZ50">
         <v>0</v>
@@ -13158,22 +13158,22 @@
         <v>227</v>
       </c>
       <c r="F51">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="G51">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="H51">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I51">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="J51">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K51">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="L51">
         <v>1.41</v>
@@ -13182,7 +13182,7 @@
         <v>1.07</v>
       </c>
       <c r="N51">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="O51">
         <v>1.34</v>
@@ -13191,187 +13191,187 @@
         <v>1.79</v>
       </c>
       <c r="Q51">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="R51">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="S51">
-        <v>1.05</v>
+        <v>3.25</v>
       </c>
       <c r="T51">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U51">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V51">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W51">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="X51">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y51">
+        <v>16</v>
+      </c>
+      <c r="Z51">
+        <v>36</v>
+      </c>
+      <c r="AA51">
+        <v>120</v>
+      </c>
+      <c r="AB51">
+        <v>9</v>
+      </c>
+      <c r="AC51">
+        <v>8.6</v>
+      </c>
+      <c r="AD51">
+        <v>19</v>
+      </c>
+      <c r="AE51">
+        <v>65</v>
+      </c>
+      <c r="AF51">
+        <v>12.5</v>
+      </c>
+      <c r="AG51">
+        <v>11</v>
+      </c>
+      <c r="AH51">
         <v>21</v>
       </c>
-      <c r="Z51">
-        <v>48</v>
-      </c>
-      <c r="AA51">
-        <v>1000</v>
-      </c>
-      <c r="AB51">
-        <v>12</v>
-      </c>
-      <c r="AC51">
-        <v>11.5</v>
-      </c>
-      <c r="AD51">
-        <v>25</v>
-      </c>
-      <c r="AE51">
-        <v>1000</v>
-      </c>
-      <c r="AF51">
+      <c r="AI51">
+        <v>70</v>
+      </c>
+      <c r="AJ51">
+        <v>24</v>
+      </c>
+      <c r="AK51">
+        <v>23</v>
+      </c>
+      <c r="AL51">
+        <v>42</v>
+      </c>
+      <c r="AM51">
+        <v>130</v>
+      </c>
+      <c r="AN51">
         <v>16</v>
       </c>
-      <c r="AG51">
+      <c r="AO51">
+        <v>85</v>
+      </c>
+      <c r="AP51">
+        <v>5.5</v>
+      </c>
+      <c r="AQ51">
+        <v>5.5</v>
+      </c>
+      <c r="AR51">
+        <v>6.8</v>
+      </c>
+      <c r="AS51">
+        <v>8</v>
+      </c>
+      <c r="AT51">
+        <v>4.3</v>
+      </c>
+      <c r="AU51">
+        <v>4.3</v>
+      </c>
+      <c r="AV51">
+        <v>5.9</v>
+      </c>
+      <c r="AW51">
+        <v>7.6</v>
+      </c>
+      <c r="AX51">
+        <v>5</v>
+      </c>
+      <c r="AY51">
+        <v>4.8</v>
+      </c>
+      <c r="AZ51">
+        <v>6</v>
+      </c>
+      <c r="BA51">
+        <v>7.6</v>
+      </c>
+      <c r="BB51">
+        <v>6.2</v>
+      </c>
+      <c r="BC51">
+        <v>6.2</v>
+      </c>
+      <c r="BD51">
+        <v>7</v>
+      </c>
+      <c r="BE51">
+        <v>8</v>
+      </c>
+      <c r="BF51">
+        <v>5.5</v>
+      </c>
+      <c r="BG51">
+        <v>7.6</v>
+      </c>
+      <c r="BH51">
+        <v>3.45</v>
+      </c>
+      <c r="BI51">
+        <v>2.74</v>
+      </c>
+      <c r="BJ51">
+        <v>10.5</v>
+      </c>
+      <c r="BK51">
+        <v>5.1</v>
+      </c>
+      <c r="BL51">
+        <v>1000</v>
+      </c>
+      <c r="BM51">
+        <v>2.52</v>
+      </c>
+      <c r="BN51">
+        <v>4.8</v>
+      </c>
+      <c r="BO51">
+        <v>3.25</v>
+      </c>
+      <c r="BP51">
         <v>14.5</v>
       </c>
-      <c r="AH51">
-        <v>950</v>
-      </c>
-      <c r="AI51">
-        <v>95</v>
-      </c>
-      <c r="AJ51">
-        <v>30</v>
-      </c>
-      <c r="AK51">
-        <v>30</v>
-      </c>
-      <c r="AL51">
-        <v>1000</v>
-      </c>
-      <c r="AM51">
-        <v>1000</v>
-      </c>
-      <c r="AN51">
-        <v>20</v>
-      </c>
-      <c r="AO51">
-        <v>1000</v>
-      </c>
-      <c r="AP51">
-        <v>2.34</v>
-      </c>
-      <c r="AQ51">
-        <v>2.1</v>
-      </c>
-      <c r="AR51">
-        <v>2.22</v>
-      </c>
-      <c r="AS51">
-        <v>2.34</v>
-      </c>
-      <c r="AT51">
-        <v>1.96</v>
-      </c>
-      <c r="AU51">
-        <v>1.95</v>
-      </c>
-      <c r="AV51">
-        <v>2.14</v>
-      </c>
-      <c r="AW51">
-        <v>2.34</v>
-      </c>
-      <c r="AX51">
-        <v>2.04</v>
-      </c>
-      <c r="AY51">
-        <v>2.02</v>
-      </c>
-      <c r="AZ51">
-        <v>2.16</v>
-      </c>
-      <c r="BA51">
-        <v>2.28</v>
-      </c>
-      <c r="BB51">
-        <v>2.16</v>
-      </c>
-      <c r="BC51">
-        <v>2.16</v>
-      </c>
-      <c r="BD51">
-        <v>2.34</v>
-      </c>
-      <c r="BE51">
-        <v>2.34</v>
-      </c>
-      <c r="BF51">
-        <v>2.1</v>
-      </c>
-      <c r="BG51">
-        <v>2.34</v>
-      </c>
-      <c r="BH51">
-        <v>1000</v>
-      </c>
-      <c r="BI51">
-        <v>1.04</v>
-      </c>
-      <c r="BJ51">
-        <v>1000</v>
-      </c>
-      <c r="BK51">
-        <v>1.04</v>
-      </c>
-      <c r="BL51">
-        <v>1000</v>
-      </c>
-      <c r="BM51">
-        <v>1.04</v>
-      </c>
-      <c r="BN51">
-        <v>1000</v>
-      </c>
-      <c r="BO51">
-        <v>1.04</v>
-      </c>
-      <c r="BP51">
-        <v>1000</v>
-      </c>
       <c r="BQ51">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR51">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS51">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BT51">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU51">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV51">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW51">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BX51">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY51">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BZ51">
         <v>0</v>
@@ -13406,19 +13406,19 @@
         <v>2.1</v>
       </c>
       <c r="H52">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I52">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J52">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K52">
         <v>3.7</v>
       </c>
       <c r="L52">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="M52">
         <v>1.08</v>
@@ -13532,7 +13532,7 @@
         <v>4.8</v>
       </c>
       <c r="AX52">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="AY52">
         <v>9</v>
@@ -13544,7 +13544,7 @@
         <v>4.8</v>
       </c>
       <c r="BB52">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="BC52">
         <v>16.5</v>
@@ -13562,64 +13562,64 @@
         <v>4.9</v>
       </c>
       <c r="BH52">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI52">
-        <v>1.78</v>
+        <v>2.56</v>
       </c>
       <c r="BJ52">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BK52">
-        <v>1.59</v>
+        <v>5.5</v>
       </c>
       <c r="BL52">
         <v>1000</v>
       </c>
       <c r="BM52">
-        <v>1.78</v>
+        <v>10</v>
       </c>
       <c r="BN52">
+        <v>4.7</v>
+      </c>
+      <c r="BO52">
+        <v>3.55</v>
+      </c>
+      <c r="BP52">
+        <v>15.5</v>
+      </c>
+      <c r="BQ52">
         <v>6.4</v>
       </c>
-      <c r="BO52">
-        <v>3.1</v>
-      </c>
-      <c r="BP52">
-        <v>21</v>
-      </c>
-      <c r="BQ52">
-        <v>1.64</v>
-      </c>
       <c r="BR52">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS52">
-        <v>1.71</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT52">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BU52">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV52">
         <v>1000</v>
       </c>
       <c r="BW52">
-        <v>1.72</v>
+        <v>8.6</v>
       </c>
       <c r="BX52">
         <v>1000</v>
       </c>
       <c r="BY52">
-        <v>1.74</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ52">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="CA52">
-        <v>1.71</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB52" t="s">
         <v>230</v>
@@ -13648,13 +13648,13 @@
         <v>1.72</v>
       </c>
       <c r="H53">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I53">
         <v>5.8</v>
       </c>
       <c r="J53">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K53">
         <v>4.4</v>
@@ -13675,10 +13675,10 @@
         <v>2.16</v>
       </c>
       <c r="Q53">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R53">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S53">
         <v>3.05</v>
@@ -13702,22 +13702,22 @@
         <v>21</v>
       </c>
       <c r="Z53">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AA53">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB53">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC53">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD53">
         <v>22</v>
       </c>
       <c r="AE53">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF53">
         <v>11</v>
@@ -13729,31 +13729,31 @@
         <v>20</v>
       </c>
       <c r="AI53">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ53">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK53">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL53">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AM53">
         <v>1000</v>
       </c>
       <c r="AN53">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO53">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP53">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ53">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR53">
         <v>36</v>
@@ -13765,10 +13765,10 @@
         <v>8.6</v>
       </c>
       <c r="AU53">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV53">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW53">
         <v>55</v>
@@ -13777,7 +13777,7 @@
         <v>9.6</v>
       </c>
       <c r="AY53">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ53">
         <v>17.5</v>
@@ -13798,7 +13798,7 @@
         <v>38</v>
       </c>
       <c r="BF53">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG53">
         <v>46</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -865,7 +865,7 @@
     <t>Toronto FC</t>
   </si>
   <si>
-    <t>2026-07-30 13:50:57</t>
+    <t>2026-07-30 16:05:48</t>
   </si>
 </sst>
 </file>
@@ -1459,19 +1459,19 @@
         <v>212</v>
       </c>
       <c r="F2">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H2">
+        <v>2.46</v>
+      </c>
+      <c r="I2">
         <v>2.5</v>
       </c>
-      <c r="I2">
-        <v>2.54</v>
-      </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K2">
         <v>3.15</v>
@@ -1483,49 +1483,49 @@
         <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O2">
         <v>1.52</v>
       </c>
       <c r="P2">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q2">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R2">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V2">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W2">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X2">
         <v>9</v>
       </c>
       <c r="Y2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
         <v>7</v>
@@ -1534,7 +1534,7 @@
         <v>12.5</v>
       </c>
       <c r="AE2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF2">
         <v>22</v>
@@ -1549,7 +1549,7 @@
         <v>60</v>
       </c>
       <c r="AJ2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK2">
         <v>55</v>
@@ -1567,7 +1567,7 @@
         <v>36</v>
       </c>
       <c r="AP2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2">
         <v>7.4</v>
@@ -1579,7 +1579,7 @@
         <v>32</v>
       </c>
       <c r="AT2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
@@ -1615,7 +1615,7 @@
         <v>46</v>
       </c>
       <c r="BF2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BG2">
         <v>30</v>
@@ -1624,19 +1624,19 @@
         <v>2.8</v>
       </c>
       <c r="BI2">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BN2">
         <v>6.4</v>
@@ -1648,37 +1648,37 @@
         <v>32</v>
       </c>
       <c r="BQ2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BR2">
         <v>55</v>
       </c>
       <c r="BS2">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BT2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU2">
         <v>4</v>
       </c>
       <c r="BV2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX2">
         <v>42</v>
       </c>
       <c r="BY2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ2">
         <v>44</v>
       </c>
       <c r="CA2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB2" t="s">
         <v>283</v>
@@ -1701,22 +1701,22 @@
         <v>213</v>
       </c>
       <c r="F3">
+        <v>1.65</v>
+      </c>
+      <c r="G3">
         <v>1.66</v>
-      </c>
-      <c r="G3">
-        <v>1.67</v>
       </c>
       <c r="H3">
         <v>6.8</v>
       </c>
       <c r="I3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
         <v>3.85</v>
       </c>
       <c r="K3">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>1.52</v>
@@ -1725,22 +1725,22 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R3">
         <v>1.25</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T3">
         <v>2.28</v>
@@ -1749,25 +1749,25 @@
         <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X3">
         <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z3">
         <v>55</v>
       </c>
       <c r="AA3">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AB3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC3">
         <v>8.800000000000001</v>
@@ -1803,7 +1803,7 @@
         <v>220</v>
       </c>
       <c r="AN3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO3">
         <v>230</v>
@@ -1827,7 +1827,7 @@
         <v>8</v>
       </c>
       <c r="AV3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW3">
         <v>70</v>
@@ -1845,19 +1845,19 @@
         <v>80</v>
       </c>
       <c r="BB3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE3">
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG3">
         <v>48</v>
@@ -1866,7 +1866,7 @@
         <v>3.05</v>
       </c>
       <c r="BI3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3">
         <v>12.5</v>
@@ -1878,7 +1878,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN3">
         <v>4.1</v>
@@ -1887,7 +1887,7 @@
         <v>3.45</v>
       </c>
       <c r="BP3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ3">
         <v>7.8</v>
@@ -1896,31 +1896,31 @@
         <v>36</v>
       </c>
       <c r="BS3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT3">
         <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV3">
         <v>75</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>90</v>
       </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="s">
         <v>283</v>
@@ -1946,13 +1946,13 @@
         <v>3.55</v>
       </c>
       <c r="G4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J4">
         <v>3.3</v>
@@ -1961,22 +1961,22 @@
         <v>3.35</v>
       </c>
       <c r="L4">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O4">
         <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1991,10 +1991,10 @@
         <v>1.96</v>
       </c>
       <c r="V4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W4">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X4">
         <v>10.5</v>
@@ -2009,7 +2009,7 @@
         <v>32</v>
       </c>
       <c r="AB4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC4">
         <v>7.2</v>
@@ -2021,16 +2021,16 @@
         <v>29</v>
       </c>
       <c r="AF4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG4">
         <v>15</v>
       </c>
       <c r="AH4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ4">
         <v>70</v>
@@ -2042,7 +2042,7 @@
         <v>65</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN4">
         <v>60</v>
@@ -2060,7 +2060,7 @@
         <v>12.5</v>
       </c>
       <c r="AS4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT4">
         <v>10.5</v>
@@ -2072,7 +2072,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX4">
         <v>21</v>
@@ -2081,10 +2081,10 @@
         <v>13.5</v>
       </c>
       <c r="AZ4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB4">
         <v>60</v>
@@ -2096,7 +2096,7 @@
         <v>50</v>
       </c>
       <c r="BE4">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BF4">
         <v>50</v>
@@ -2108,7 +2108,7 @@
         <v>2.94</v>
       </c>
       <c r="BI4">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
@@ -2150,7 +2150,7 @@
         <v>19</v>
       </c>
       <c r="BW4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX4">
         <v>38</v>
@@ -2185,16 +2185,16 @@
         <v>215</v>
       </c>
       <c r="F5">
+        <v>1.56</v>
+      </c>
+      <c r="G5">
         <v>1.59</v>
       </c>
-      <c r="G5">
-        <v>1.62</v>
-      </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -2212,16 +2212,16 @@
         <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q5">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
         <v>4.2</v>
@@ -2230,13 +2230,13 @@
         <v>2.18</v>
       </c>
       <c r="U5">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V5">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W5">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="X5">
         <v>12.5</v>
@@ -2245,58 +2245,58 @@
         <v>21</v>
       </c>
       <c r="Z5">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AA5">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="AB5">
         <v>6.8</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AE5">
         <v>170</v>
       </c>
       <c r="AF5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI5">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AJ5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL5">
         <v>50</v>
       </c>
       <c r="AM5">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AN5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO5">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="AP5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR5">
         <v>46</v>
@@ -2311,7 +2311,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW5">
         <v>11</v>
@@ -2323,16 +2323,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA5">
         <v>11</v>
       </c>
       <c r="BB5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD5">
         <v>34</v>
@@ -2341,28 +2341,28 @@
         <v>11</v>
       </c>
       <c r="BF5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH5">
         <v>3.25</v>
       </c>
       <c r="BI5">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5">
+        <v>12</v>
+      </c>
+      <c r="BK5">
+        <v>6.2</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
         <v>12.5</v>
-      </c>
-      <c r="BK5">
-        <v>6.6</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>13</v>
       </c>
       <c r="BN5">
         <v>3.9</v>
@@ -2371,7 +2371,7 @@
         <v>3.35</v>
       </c>
       <c r="BP5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BQ5">
         <v>6</v>
@@ -2380,31 +2380,31 @@
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU5">
         <v>6.2</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="s">
         <v>283</v>
@@ -2427,7 +2427,7 @@
         <v>216</v>
       </c>
       <c r="F6">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G6">
         <v>1.92</v>
@@ -2445,7 +2445,7 @@
         <v>4.5</v>
       </c>
       <c r="L6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M6">
         <v>1.03</v>
@@ -2454,25 +2454,25 @@
         <v>5.7</v>
       </c>
       <c r="O6">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P6">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="Q6">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R6">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S6">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T6">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U6">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="V6">
         <v>1.31</v>
@@ -2505,7 +2505,7 @@
         <v>48</v>
       </c>
       <c r="AF6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG6">
         <v>11</v>
@@ -2541,7 +2541,7 @@
         <v>17.5</v>
       </c>
       <c r="AR6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AS6">
         <v>34</v>
@@ -2577,13 +2577,13 @@
         <v>15</v>
       </c>
       <c r="BD6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE6">
         <v>32</v>
       </c>
       <c r="BF6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG6">
         <v>20</v>
@@ -2669,19 +2669,19 @@
         <v>217</v>
       </c>
       <c r="F7">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="G7">
-        <v>990</v>
+        <v>3.35</v>
       </c>
       <c r="H7">
-        <v>1.03</v>
+        <v>1.87</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2693,19 +2693,19 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O7">
         <v>1.29</v>
       </c>
       <c r="P7">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="Q7">
         <v>1.29</v>
       </c>
       <c r="R7">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="S7">
         <v>1.29</v>
@@ -2717,10 +2717,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -3094,7 +3094,7 @@
         <v>5.2</v>
       </c>
       <c r="BO8">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BP8">
         <v>16</v>
@@ -3159,16 +3159,16 @@
         <v>2.84</v>
       </c>
       <c r="H9">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="I9">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J9">
         <v>3.35</v>
       </c>
       <c r="K9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -3186,10 +3186,10 @@
         <v>1.93</v>
       </c>
       <c r="Q9">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R9">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S9">
         <v>2.76</v>
@@ -3395,19 +3395,19 @@
         <v>220</v>
       </c>
       <c r="F10">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G10">
         <v>2.9</v>
       </c>
       <c r="H10">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I10">
         <v>3.3</v>
       </c>
       <c r="J10">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="K10">
         <v>3.5</v>
@@ -3422,7 +3422,7 @@
         <v>2.9</v>
       </c>
       <c r="O10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P10">
         <v>1.65</v>
@@ -3440,7 +3440,7 @@
         <v>1.94</v>
       </c>
       <c r="U10">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V10">
         <v>1.44</v>
@@ -3515,7 +3515,7 @@
         <v>5.5</v>
       </c>
       <c r="AT10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU10">
         <v>5.7</v>
@@ -3649,7 +3649,7 @@
         <v>6.6</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K11">
         <v>3.95</v>
@@ -3667,10 +3667,10 @@
         <v>1.43</v>
       </c>
       <c r="P11">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q11">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R11">
         <v>1.25</v>
@@ -3882,19 +3882,19 @@
         <v>1.67</v>
       </c>
       <c r="G12">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H12">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I12">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L12">
         <v>1.29</v>
@@ -3915,7 +3915,7 @@
         <v>1.7</v>
       </c>
       <c r="R12">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S12">
         <v>2.76</v>
@@ -3924,22 +3924,22 @@
         <v>1.74</v>
       </c>
       <c r="U12">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V12">
         <v>1.21</v>
       </c>
       <c r="W12">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X12">
         <v>23</v>
       </c>
       <c r="Y12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z12">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA12">
         <v>140</v>
@@ -3951,7 +3951,7 @@
         <v>11.5</v>
       </c>
       <c r="AD12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE12">
         <v>65</v>
@@ -3969,7 +3969,7 @@
         <v>65</v>
       </c>
       <c r="AJ12">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AK12">
         <v>19.5</v>
@@ -3984,7 +3984,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO12">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP12">
         <v>15</v>
@@ -3993,34 +3993,34 @@
         <v>16</v>
       </c>
       <c r="AR12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AS12">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT12">
         <v>8</v>
       </c>
       <c r="AU12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
         <v>15.5</v>
       </c>
       <c r="AW12">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX12">
         <v>8.800000000000001</v>
       </c>
       <c r="AY12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ12">
         <v>14</v>
       </c>
       <c r="BA12">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB12">
         <v>13</v>
@@ -4029,22 +4029,22 @@
         <v>13</v>
       </c>
       <c r="BD12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE12">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF12">
         <v>6.6</v>
       </c>
       <c r="BG12">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BH12">
         <v>3.95</v>
       </c>
       <c r="BI12">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BJ12">
         <v>9.6</v>
@@ -4232,7 +4232,7 @@
         <v>5.3</v>
       </c>
       <c r="AQ13">
-        <v>18.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR13">
         <v>5.2</v>
@@ -4244,10 +4244,10 @@
         <v>4.6</v>
       </c>
       <c r="AU13">
-        <v>8.4</v>
+        <v>4.1</v>
       </c>
       <c r="AV13">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="AW13">
         <v>5.3</v>
@@ -4256,10 +4256,10 @@
         <v>4.7</v>
       </c>
       <c r="AY13">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="AZ13">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="BA13">
         <v>5.3</v>
@@ -4271,7 +4271,7 @@
         <v>4.8</v>
       </c>
       <c r="BD13">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="BE13">
         <v>5.5</v>
@@ -4280,7 +4280,7 @@
         <v>3.8</v>
       </c>
       <c r="BG13">
-        <v>15.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH13">
         <v>5</v>
@@ -4366,19 +4366,19 @@
         <v>2.36</v>
       </c>
       <c r="G14">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H14">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I14">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J14">
+        <v>3.65</v>
+      </c>
+      <c r="K14">
         <v>3.9</v>
-      </c>
-      <c r="K14">
-        <v>3.95</v>
       </c>
       <c r="L14">
         <v>1.26</v>
@@ -4390,7 +4390,7 @@
         <v>5</v>
       </c>
       <c r="O14">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P14">
         <v>2.36</v>
@@ -4411,10 +4411,10 @@
         <v>2.52</v>
       </c>
       <c r="V14">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W14">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="X14">
         <v>21</v>
@@ -4614,7 +4614,7 @@
         <v>2.48</v>
       </c>
       <c r="I15">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J15">
         <v>3.1</v>
@@ -4635,7 +4635,7 @@
         <v>1.44</v>
       </c>
       <c r="P15">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q15">
         <v>2.36</v>
@@ -4856,7 +4856,7 @@
         <v>3.05</v>
       </c>
       <c r="I16">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J16">
         <v>3.15</v>
@@ -4877,13 +4877,13 @@
         <v>1.35</v>
       </c>
       <c r="P16">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q16">
         <v>2.14</v>
       </c>
       <c r="R16">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S16">
         <v>3.7</v>
@@ -4895,7 +4895,7 @@
         <v>2</v>
       </c>
       <c r="V16">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
         <v>1.6</v>
@@ -4964,7 +4964,7 @@
         <v>15.5</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AT16">
         <v>7</v>
@@ -4976,7 +4976,7 @@
         <v>10</v>
       </c>
       <c r="AW16">
-        <v>30</v>
+        <v>4.3</v>
       </c>
       <c r="AX16">
         <v>11.5</v>
@@ -4988,25 +4988,25 @@
         <v>13.5</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF16">
         <v>20</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH16">
         <v>3.7</v>
@@ -5089,7 +5089,7 @@
         <v>227</v>
       </c>
       <c r="F17">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G17">
         <v>1.81</v>
@@ -5212,7 +5212,7 @@
         <v>8</v>
       </c>
       <c r="AU17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV17">
         <v>5.1</v>
@@ -5337,7 +5337,7 @@
         <v>3.25</v>
       </c>
       <c r="H18">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I18">
         <v>2.68</v>
@@ -5361,10 +5361,10 @@
         <v>1.35</v>
       </c>
       <c r="P18">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q18">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R18">
         <v>1.33</v>
@@ -5451,13 +5451,13 @@
         <v>7.2</v>
       </c>
       <c r="AT18">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AU18">
         <v>4.2</v>
       </c>
       <c r="AV18">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AW18">
         <v>6.8</v>
@@ -5469,7 +5469,7 @@
         <v>10</v>
       </c>
       <c r="AZ18">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="BA18">
         <v>18.5</v>
@@ -5597,7 +5597,7 @@
         <v>1.08</v>
       </c>
       <c r="N19">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O19">
         <v>1.35</v>
@@ -5621,7 +5621,7 @@
         <v>2.08</v>
       </c>
       <c r="V19">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W19">
         <v>1.45</v>
@@ -5702,7 +5702,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW19">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX19">
         <v>15</v>
@@ -5711,10 +5711,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="BA19">
-        <v>25</v>
+        <v>7.2</v>
       </c>
       <c r="BB19">
         <v>7.2</v>
@@ -5833,7 +5833,7 @@
         <v>4.4</v>
       </c>
       <c r="L20">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="M20">
         <v>1.05</v>
@@ -6338,7 +6338,7 @@
         <v>1.51</v>
       </c>
       <c r="S22">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T22">
         <v>1.61</v>
@@ -6544,13 +6544,13 @@
         <v>2.46</v>
       </c>
       <c r="G23">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H23">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I23">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J23">
         <v>3.7</v>
@@ -6571,7 +6571,7 @@
         <v>1.24</v>
       </c>
       <c r="P23">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q23">
         <v>1.71</v>
@@ -6580,19 +6580,19 @@
         <v>1.49</v>
       </c>
       <c r="S23">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T23">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U23">
         <v>2.42</v>
       </c>
       <c r="V23">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X23">
         <v>22</v>
@@ -6795,7 +6795,7 @@
         <v>3.85</v>
       </c>
       <c r="J24">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K24">
         <v>4.2</v>
@@ -6807,13 +6807,13 @@
         <v>1.04</v>
       </c>
       <c r="N24">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O24">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P24">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q24">
         <v>1.66</v>
@@ -6948,7 +6948,7 @@
         <v>4.1</v>
       </c>
       <c r="BI24">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ24">
         <v>9</v>
@@ -7025,22 +7025,22 @@
         <v>235</v>
       </c>
       <c r="F25">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="G25">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="H25">
-        <v>3.35</v>
+        <v>5.9</v>
       </c>
       <c r="I25">
-        <v>150</v>
+        <v>990</v>
       </c>
       <c r="J25">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="K25">
-        <v>110</v>
+        <v>12.5</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -7049,34 +7049,34 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="O25">
         <v>1.14</v>
       </c>
       <c r="P25">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="Q25">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="R25">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="S25">
         <v>2.04</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W25">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -7276,13 +7276,13 @@
         <v>5.4</v>
       </c>
       <c r="I26">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K26">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L26">
         <v>1.25</v>
@@ -7300,7 +7300,7 @@
         <v>2.82</v>
       </c>
       <c r="Q26">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R26">
         <v>1.75</v>
@@ -7312,7 +7312,7 @@
         <v>1.59</v>
       </c>
       <c r="U26">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V26">
         <v>1.01</v>
@@ -7333,7 +7333,7 @@
         <v>130</v>
       </c>
       <c r="AB26">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC26">
         <v>14</v>
@@ -7351,7 +7351,7 @@
         <v>13</v>
       </c>
       <c r="AH26">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI26">
         <v>60</v>
@@ -7375,16 +7375,16 @@
         <v>48</v>
       </c>
       <c r="AP26">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AQ26">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AR26">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AS26">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT26">
         <v>12</v>
@@ -7393,10 +7393,10 @@
         <v>10</v>
       </c>
       <c r="AV26">
-        <v>4.7</v>
+        <v>18.5</v>
       </c>
       <c r="AW26">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX26">
         <v>11.5</v>
@@ -7408,7 +7408,7 @@
         <v>15</v>
       </c>
       <c r="BA26">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BB26">
         <v>15.5</v>
@@ -7420,13 +7420,13 @@
         <v>17.5</v>
       </c>
       <c r="BE26">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF26">
         <v>5.3</v>
       </c>
       <c r="BG26">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH26">
         <v>4.8</v>
@@ -7435,7 +7435,7 @@
         <v>4.3</v>
       </c>
       <c r="BJ26">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BK26">
         <v>5.6</v>
@@ -7444,7 +7444,7 @@
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN26">
         <v>4.8</v>
@@ -7456,37 +7456,37 @@
         <v>10.5</v>
       </c>
       <c r="BQ26">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT26">
         <v>9.4</v>
       </c>
       <c r="BU26">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ26">
         <v>12</v>
       </c>
       <c r="CA26">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB26" t="s">
         <v>283</v>
@@ -7509,19 +7509,19 @@
         <v>237</v>
       </c>
       <c r="F27">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="G27">
-        <v>990</v>
+        <v>3.2</v>
       </c>
       <c r="H27">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="I27">
-        <v>990</v>
+        <v>3.65</v>
       </c>
       <c r="J27">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="K27">
         <v>950</v>
@@ -7533,13 +7533,13 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>1.26</v>
+        <v>3.15</v>
       </c>
       <c r="O27">
         <v>1.02</v>
       </c>
       <c r="P27">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q27">
         <v>2.1</v>
@@ -7557,10 +7557,10 @@
         <v>1.11</v>
       </c>
       <c r="V27">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7763,10 +7763,10 @@
         <v>990</v>
       </c>
       <c r="J28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K28">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7775,7 +7775,7 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O28">
         <v>1.22</v>
@@ -7993,13 +7993,13 @@
         <v>239</v>
       </c>
       <c r="F29">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="G29">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H29">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="I29">
         <v>23</v>
@@ -8020,7 +8020,7 @@
         <v>6</v>
       </c>
       <c r="O29">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P29">
         <v>2.68</v>
@@ -8029,7 +8029,7 @@
         <v>1.55</v>
       </c>
       <c r="R29">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S29">
         <v>2.26</v>
@@ -8038,16 +8038,16 @@
         <v>2.2</v>
       </c>
       <c r="U29">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V29">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W29">
         <v>4.9</v>
       </c>
       <c r="X29">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y29">
         <v>60</v>
@@ -8083,7 +8083,7 @@
         <v>260</v>
       </c>
       <c r="AJ29">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AK29">
         <v>15</v>
@@ -8098,31 +8098,31 @@
         <v>4.2</v>
       </c>
       <c r="AO29">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="AP29">
         <v>19.5</v>
       </c>
       <c r="AQ29">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="AR29">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS29">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT29">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU29">
         <v>13.5</v>
       </c>
       <c r="AV29">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="AW29">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AX29">
         <v>6.8</v>
@@ -8131,28 +8131,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ29">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BA29">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB29">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC29">
         <v>12</v>
       </c>
       <c r="BD29">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE29">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF29">
         <v>3</v>
       </c>
       <c r="BG29">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8241,16 +8241,16 @@
         <v>4.9</v>
       </c>
       <c r="H30">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I30">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="J30">
         <v>4</v>
       </c>
       <c r="K30">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L30">
         <v>1.28</v>
@@ -8268,7 +8268,7 @@
         <v>2.24</v>
       </c>
       <c r="Q30">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R30">
         <v>1.49</v>
@@ -8283,7 +8283,7 @@
         <v>2.26</v>
       </c>
       <c r="V30">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W30">
         <v>1.26</v>
@@ -8400,7 +8400,7 @@
         <v>4.2</v>
       </c>
       <c r="BI30">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BJ30">
         <v>9.6</v>
@@ -8498,7 +8498,7 @@
         <v>1.01</v>
       </c>
       <c r="M31">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N31">
         <v>5</v>
@@ -8513,7 +8513,7 @@
         <v>1.63</v>
       </c>
       <c r="R31">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S31">
         <v>2.54</v>
@@ -8719,7 +8719,7 @@
         <v>242</v>
       </c>
       <c r="F32">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G32">
         <v>3.6</v>
@@ -8734,34 +8734,34 @@
         <v>3.35</v>
       </c>
       <c r="K32">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L32">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M32">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N32">
         <v>3.7</v>
       </c>
       <c r="O32">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P32">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q32">
         <v>1.89</v>
       </c>
       <c r="R32">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S32">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T32">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U32">
         <v>2.14</v>
@@ -8851,13 +8851,13 @@
         <v>5.5</v>
       </c>
       <c r="AX32">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY32">
         <v>4.7</v>
       </c>
       <c r="AZ32">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="BA32">
         <v>5.9</v>
@@ -8881,16 +8881,16 @@
         <v>5.1</v>
       </c>
       <c r="BH32">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI32">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BJ32">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK32">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL32">
         <v>1000</v>
@@ -8935,7 +8935,7 @@
         <v>8</v>
       </c>
       <c r="BZ32">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA32">
         <v>7.6</v>
@@ -8961,7 +8961,7 @@
         <v>243</v>
       </c>
       <c r="F33">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G33">
         <v>1.81</v>
@@ -8988,7 +8988,7 @@
         <v>4.5</v>
       </c>
       <c r="O33">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P33">
         <v>2.24</v>
@@ -9006,7 +9006,7 @@
         <v>1.72</v>
       </c>
       <c r="U33">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V33">
         <v>1.21</v>
@@ -9081,7 +9081,7 @@
         <v>7.6</v>
       </c>
       <c r="AT33">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU33">
         <v>8.199999999999999</v>
@@ -9099,7 +9099,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ33">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA33">
         <v>7.2</v>
@@ -9206,61 +9206,61 @@
         <v>2.52</v>
       </c>
       <c r="G34">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H34">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I34">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K34">
         <v>3.95</v>
       </c>
       <c r="L34">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M34">
         <v>1.06</v>
       </c>
       <c r="N34">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O34">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P34">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q34">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="R34">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S34">
         <v>2.96</v>
       </c>
       <c r="T34">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U34">
         <v>2.22</v>
       </c>
       <c r="V34">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X34">
         <v>18.5</v>
       </c>
       <c r="Y34">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z34">
         <v>21</v>
@@ -9275,13 +9275,13 @@
         <v>8.6</v>
       </c>
       <c r="AD34">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE34">
         <v>32</v>
       </c>
       <c r="AF34">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG34">
         <v>13</v>
@@ -9293,10 +9293,10 @@
         <v>40</v>
       </c>
       <c r="AJ34">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK34">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL34">
         <v>40</v>
@@ -9305,124 +9305,124 @@
         <v>100</v>
       </c>
       <c r="AN34">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO34">
         <v>24</v>
       </c>
       <c r="AP34">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ34">
         <v>5.2</v>
       </c>
       <c r="AR34">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AS34">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT34">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="AU34">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AV34">
         <v>5.2</v>
       </c>
       <c r="AW34">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="AX34">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AY34">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="AZ34">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="BA34">
         <v>7</v>
       </c>
       <c r="BB34">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC34">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BD34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BE34">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF34">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG34">
-        <v>6.4</v>
+        <v>18.5</v>
       </c>
       <c r="BH34">
         <v>3.8</v>
       </c>
       <c r="BI34">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ34">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK34">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN34">
         <v>6.2</v>
       </c>
       <c r="BO34">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="BP34">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ34">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR34">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS34">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT34">
         <v>6.2</v>
       </c>
       <c r="BU34">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BV34">
         <v>21</v>
       </c>
       <c r="BW34">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX34">
         <v>32</v>
       </c>
       <c r="BY34">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ34">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA34">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB34" t="s">
         <v>283</v>
@@ -9445,7 +9445,7 @@
         <v>245</v>
       </c>
       <c r="F35">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G35">
         <v>2.5</v>
@@ -9454,7 +9454,7 @@
         <v>2.8</v>
       </c>
       <c r="I35">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J35">
         <v>3.9</v>
@@ -9478,25 +9478,25 @@
         <v>2.62</v>
       </c>
       <c r="Q35">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R35">
         <v>1.65</v>
       </c>
       <c r="S35">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T35">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U35">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W35">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X35">
         <v>34</v>
@@ -9687,25 +9687,25 @@
         <v>246</v>
       </c>
       <c r="F36">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G36">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H36">
         <v>2.42</v>
       </c>
       <c r="I36">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J36">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K36">
         <v>4.6</v>
       </c>
       <c r="L36">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M36">
         <v>1.03</v>
@@ -9732,13 +9732,13 @@
         <v>1.47</v>
       </c>
       <c r="U36">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V36">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W36">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X36">
         <v>34</v>
@@ -9858,13 +9858,13 @@
         <v>8.6</v>
       </c>
       <c r="BK36">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN36">
         <v>6.6</v>
@@ -9876,13 +9876,13 @@
         <v>18</v>
       </c>
       <c r="BQ36">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR36">
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT36">
         <v>6.4</v>
@@ -9891,7 +9891,7 @@
         <v>4.9</v>
       </c>
       <c r="BV36">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW36">
         <v>6.8</v>
@@ -9900,7 +9900,7 @@
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ36">
         <v>0</v>
@@ -9929,28 +9929,28 @@
         <v>247</v>
       </c>
       <c r="F37">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G37">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="H37">
         <v>5.3</v>
       </c>
       <c r="I37">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J37">
         <v>4</v>
       </c>
       <c r="K37">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L37">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M37">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N37">
         <v>4.2</v>
@@ -9962,7 +9962,7 @@
         <v>2.1</v>
       </c>
       <c r="Q37">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R37">
         <v>1.43</v>
@@ -9971,7 +9971,7 @@
         <v>3</v>
       </c>
       <c r="T37">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U37">
         <v>2.06</v>
@@ -9980,10 +9980,10 @@
         <v>1.2</v>
       </c>
       <c r="W37">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="X37">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y37">
         <v>24</v>
@@ -9995,7 +9995,7 @@
         <v>150</v>
       </c>
       <c r="AB37">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC37">
         <v>9.6</v>
@@ -10010,7 +10010,7 @@
         <v>11</v>
       </c>
       <c r="AG37">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH37">
         <v>24</v>
@@ -10043,10 +10043,10 @@
         <v>15.5</v>
       </c>
       <c r="AR37">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS37">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT37">
         <v>8</v>
@@ -10055,10 +10055,10 @@
         <v>8.6</v>
       </c>
       <c r="AV37">
-        <v>18.5</v>
+        <v>7.4</v>
       </c>
       <c r="AW37">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX37">
         <v>9.4</v>
@@ -10070,7 +10070,7 @@
         <v>17.5</v>
       </c>
       <c r="BA37">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB37">
         <v>15</v>
@@ -10082,49 +10082,49 @@
         <v>24</v>
       </c>
       <c r="BE37">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF37">
         <v>8.199999999999999</v>
       </c>
       <c r="BG37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BH37">
         <v>3.75</v>
       </c>
       <c r="BI37">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ37">
         <v>10</v>
       </c>
       <c r="BK37">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN37">
         <v>4.4</v>
       </c>
       <c r="BO37">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP37">
         <v>11</v>
       </c>
       <c r="BQ37">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR37">
         <v>1000</v>
       </c>
       <c r="BS37">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT37">
         <v>9</v>
@@ -10142,10 +10142,10 @@
         <v>70</v>
       </c>
       <c r="BY37">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ37">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="CA37">
         <v>8.6</v>
@@ -10171,22 +10171,22 @@
         <v>248</v>
       </c>
       <c r="F38">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="G38">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H38">
         <v>4.1</v>
       </c>
       <c r="I38">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J38">
         <v>4.2</v>
       </c>
       <c r="K38">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L38">
         <v>1.24</v>
@@ -10201,13 +10201,13 @@
         <v>1.16</v>
       </c>
       <c r="P38">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q38">
         <v>1.55</v>
       </c>
       <c r="R38">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S38">
         <v>2.34</v>
@@ -10216,10 +10216,10 @@
         <v>1.58</v>
       </c>
       <c r="U38">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V38">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W38">
         <v>2.12</v>
@@ -10306,7 +10306,7 @@
         <v>10.5</v>
       </c>
       <c r="AY38">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ38">
         <v>12.5</v>
@@ -10428,7 +10428,7 @@
         <v>6.6</v>
       </c>
       <c r="K39">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10443,7 +10443,7 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="Q39">
         <v>1.45</v>
@@ -10455,10 +10455,10 @@
         <v>0</v>
       </c>
       <c r="T39">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U39">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -10533,10 +10533,10 @@
         <v>5.1</v>
       </c>
       <c r="AT39">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="AU39">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AV39">
         <v>4.7</v>
@@ -10548,7 +10548,7 @@
         <v>3.4</v>
       </c>
       <c r="AY39">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="AZ39">
         <v>4.5</v>
@@ -10560,10 +10560,10 @@
         <v>8.4</v>
       </c>
       <c r="BC39">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="BD39">
-        <v>4.6</v>
+        <v>29</v>
       </c>
       <c r="BE39">
         <v>5</v>
@@ -10655,7 +10655,7 @@
         <v>250</v>
       </c>
       <c r="F40">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G40">
         <v>1.9</v>
@@ -10664,10 +10664,10 @@
         <v>4.7</v>
       </c>
       <c r="I40">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J40">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K40">
         <v>3.8</v>
@@ -10679,16 +10679,16 @@
         <v>1.07</v>
       </c>
       <c r="N40">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O40">
         <v>1.33</v>
       </c>
       <c r="P40">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q40">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="R40">
         <v>1.32</v>
@@ -10697,7 +10697,7 @@
         <v>3.55</v>
       </c>
       <c r="T40">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="U40">
         <v>1.96</v>
@@ -10817,7 +10817,7 @@
         <v>6.2</v>
       </c>
       <c r="BH40">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI40">
         <v>2.68</v>
@@ -10826,13 +10826,13 @@
         <v>11</v>
       </c>
       <c r="BK40">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN40">
         <v>4.6</v>
@@ -10844,31 +10844,31 @@
         <v>13.5</v>
       </c>
       <c r="BQ40">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR40">
         <v>30</v>
       </c>
       <c r="BS40">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT40">
         <v>8.800000000000001</v>
       </c>
       <c r="BU40">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV40">
         <v>46</v>
       </c>
       <c r="BW40">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX40">
+        <v>1000</v>
+      </c>
+      <c r="BY40">
         <v>8.4</v>
-      </c>
-      <c r="BX40">
-        <v>1000</v>
-      </c>
-      <c r="BY40">
-        <v>8.6</v>
       </c>
       <c r="BZ40">
         <v>0</v>
@@ -10900,13 +10900,13 @@
         <v>2.22</v>
       </c>
       <c r="G41">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H41">
         <v>3.65</v>
       </c>
       <c r="I41">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J41">
         <v>3.15</v>
@@ -10915,22 +10915,22 @@
         <v>3.45</v>
       </c>
       <c r="L41">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M41">
         <v>1.1</v>
       </c>
       <c r="N41">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O41">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P41">
         <v>1.67</v>
       </c>
       <c r="Q41">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R41">
         <v>1.25</v>
@@ -10939,10 +10939,10 @@
         <v>4.3</v>
       </c>
       <c r="T41">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U41">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V41">
         <v>1.35</v>
@@ -11002,19 +11002,19 @@
         <v>28</v>
       </c>
       <c r="AO41">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP41">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ41">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR41">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AS41">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT41">
         <v>7.2</v>
@@ -11026,55 +11026,55 @@
         <v>14</v>
       </c>
       <c r="AW41">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX41">
         <v>11.5</v>
       </c>
       <c r="AY41">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ41">
-        <v>17.5</v>
+        <v>5.5</v>
       </c>
       <c r="BA41">
         <v>6.6</v>
       </c>
       <c r="BB41">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BC41">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BD41">
         <v>6.4</v>
       </c>
       <c r="BE41">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF41">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG41">
         <v>6.6</v>
       </c>
       <c r="BH41">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI41">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ41">
         <v>10.5</v>
       </c>
       <c r="BK41">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN41">
         <v>4.9</v>
@@ -11083,19 +11083,19 @@
         <v>3.9</v>
       </c>
       <c r="BP41">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ41">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR41">
         <v>1000</v>
       </c>
       <c r="BS41">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT41">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU41">
         <v>5.5</v>
@@ -11104,19 +11104,19 @@
         <v>1000</v>
       </c>
       <c r="BW41">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX41">
         <v>1000</v>
       </c>
       <c r="BY41">
+        <v>12.5</v>
+      </c>
+      <c r="BZ41">
+        <v>1000</v>
+      </c>
+      <c r="CA41">
         <v>11.5</v>
-      </c>
-      <c r="BZ41">
-        <v>1000</v>
-      </c>
-      <c r="CA41">
-        <v>10.5</v>
       </c>
       <c r="CB41" t="s">
         <v>283</v>
@@ -11148,7 +11148,7 @@
         <v>2.02</v>
       </c>
       <c r="I42">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="J42">
         <v>3.85</v>
@@ -11175,19 +11175,19 @@
         <v>1.65</v>
       </c>
       <c r="R42">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S42">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T42">
         <v>1.6</v>
       </c>
       <c r="U42">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V42">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="W42">
         <v>1.35</v>
@@ -11202,7 +11202,7 @@
         <v>15.5</v>
       </c>
       <c r="AA42">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB42">
         <v>18</v>
@@ -11244,7 +11244,7 @@
         <v>29</v>
       </c>
       <c r="AO42">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP42">
         <v>15</v>
@@ -11283,16 +11283,16 @@
         <v>16.5</v>
       </c>
       <c r="BB42">
+        <v>9.6</v>
+      </c>
+      <c r="BC42">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BC42">
-        <v>8.6</v>
       </c>
       <c r="BD42">
         <v>30</v>
       </c>
       <c r="BE42">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF42">
         <v>20</v>
@@ -11304,19 +11304,19 @@
         <v>4.2</v>
       </c>
       <c r="BI42">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="BJ42">
         <v>9</v>
       </c>
       <c r="BK42">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN42">
         <v>7.4</v>
@@ -11325,19 +11325,19 @@
         <v>5.4</v>
       </c>
       <c r="BP42">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ42">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR42">
         <v>48</v>
       </c>
       <c r="BS42">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT42">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU42">
         <v>4.6</v>
@@ -11346,13 +11346,13 @@
         <v>14</v>
       </c>
       <c r="BW42">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX42">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY42">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ42">
         <v>0</v>
@@ -11399,13 +11399,13 @@
         <v>3.55</v>
       </c>
       <c r="L43">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="M43">
         <v>1.09</v>
       </c>
       <c r="N43">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O43">
         <v>1.38</v>
@@ -11423,10 +11423,10 @@
         <v>3.95</v>
       </c>
       <c r="T43">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U43">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V43">
         <v>1.6</v>
@@ -11543,40 +11543,40 @@
         <v>6.6</v>
       </c>
       <c r="BH43">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI43">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ43">
         <v>10.5</v>
       </c>
       <c r="BK43">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN43">
         <v>6.6</v>
       </c>
       <c r="BO43">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP43">
         <v>29</v>
       </c>
       <c r="BQ43">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR43">
         <v>1000</v>
       </c>
       <c r="BS43">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT43">
         <v>5.5</v>
@@ -11588,19 +11588,19 @@
         <v>21</v>
       </c>
       <c r="BW43">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX43">
         <v>1000</v>
       </c>
       <c r="BY43">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ43">
         <v>1000</v>
       </c>
       <c r="CA43">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CB43" t="s">
         <v>283</v>
@@ -11623,10 +11623,10 @@
         <v>254</v>
       </c>
       <c r="F44">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G44">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H44">
         <v>2.4</v>
@@ -11635,10 +11635,10 @@
         <v>2.56</v>
       </c>
       <c r="J44">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K44">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L44">
         <v>1.34</v>
@@ -11653,7 +11653,7 @@
         <v>1.25</v>
       </c>
       <c r="P44">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q44">
         <v>1.73</v>
@@ -11662,19 +11662,19 @@
         <v>1.46</v>
       </c>
       <c r="S44">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T44">
         <v>1.63</v>
       </c>
       <c r="U44">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V44">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W44">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X44">
         <v>21</v>
@@ -11794,13 +11794,13 @@
         <v>9</v>
       </c>
       <c r="BK44">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL44">
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN44">
         <v>6.4</v>
@@ -11812,7 +11812,7 @@
         <v>1000</v>
       </c>
       <c r="BQ44">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR44">
         <v>1000</v>
@@ -11830,13 +11830,13 @@
         <v>1000</v>
       </c>
       <c r="BW44">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX44">
         <v>1000</v>
       </c>
       <c r="BY44">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ44">
         <v>0</v>
@@ -11871,37 +11871,37 @@
         <v>3.15</v>
       </c>
       <c r="H45">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="I45">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="J45">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K45">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L45">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M45">
         <v>1.04</v>
       </c>
       <c r="N45">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O45">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P45">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q45">
         <v>1.66</v>
       </c>
       <c r="R45">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S45">
         <v>2.64</v>
@@ -11913,7 +11913,7 @@
         <v>2.4</v>
       </c>
       <c r="V45">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W45">
         <v>1.46</v>
@@ -11922,10 +11922,10 @@
         <v>21</v>
       </c>
       <c r="Y45">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z45">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA45">
         <v>32</v>
@@ -11937,13 +11937,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD45">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE45">
         <v>23</v>
       </c>
       <c r="AF45">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG45">
         <v>14</v>
@@ -11958,7 +11958,7 @@
         <v>48</v>
       </c>
       <c r="AK45">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL45">
         <v>38</v>
@@ -11970,10 +11970,10 @@
         <v>23</v>
       </c>
       <c r="AO45">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP45">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ45">
         <v>12</v>
@@ -11988,10 +11988,10 @@
         <v>13.5</v>
       </c>
       <c r="AU45">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV45">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW45">
         <v>19</v>
@@ -12003,7 +12003,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ45">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA45">
         <v>24</v>
@@ -12012,25 +12012,25 @@
         <v>40</v>
       </c>
       <c r="BC45">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="BD45">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE45">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BF45">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG45">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH45">
         <v>4.2</v>
       </c>
       <c r="BI45">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="BJ45">
         <v>9.199999999999999</v>
@@ -12048,7 +12048,7 @@
         <v>6.8</v>
       </c>
       <c r="BO45">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BP45">
         <v>23</v>
@@ -12107,28 +12107,28 @@
         <v>256</v>
       </c>
       <c r="F46">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G46">
         <v>4.2</v>
       </c>
       <c r="H46">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I46">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J46">
         <v>3.25</v>
       </c>
       <c r="K46">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L46">
         <v>1.48</v>
       </c>
       <c r="M46">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N46">
         <v>2.98</v>
@@ -12140,7 +12140,7 @@
         <v>1.76</v>
       </c>
       <c r="Q46">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R46">
         <v>1.25</v>
@@ -12149,13 +12149,13 @@
         <v>4.2</v>
       </c>
       <c r="T46">
+        <v>1.93</v>
+      </c>
+      <c r="U46">
         <v>1.91</v>
       </c>
-      <c r="U46">
-        <v>1.9</v>
-      </c>
       <c r="V46">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W46">
         <v>1.31</v>
@@ -12272,10 +12272,10 @@
         <v>3.05</v>
       </c>
       <c r="BI46">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ46">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK46">
         <v>5.8</v>
@@ -12284,7 +12284,7 @@
         <v>1000</v>
       </c>
       <c r="BM46">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN46">
         <v>7.2</v>
@@ -12296,13 +12296,13 @@
         <v>36</v>
       </c>
       <c r="BQ46">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR46">
         <v>55</v>
       </c>
       <c r="BS46">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT46">
         <v>5</v>
@@ -12314,19 +12314,19 @@
         <v>18</v>
       </c>
       <c r="BW46">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX46">
         <v>36</v>
       </c>
       <c r="BY46">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ46">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA46">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB46" t="s">
         <v>283</v>
@@ -12349,7 +12349,7 @@
         <v>257</v>
       </c>
       <c r="F47">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="G47">
         <v>990</v>
@@ -12361,7 +12361,7 @@
         <v>8</v>
       </c>
       <c r="J47">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="K47">
         <v>950</v>
@@ -12370,7 +12370,7 @@
         <v>1.01</v>
       </c>
       <c r="M47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N47">
         <v>1.26</v>
@@ -12591,19 +12591,19 @@
         <v>258</v>
       </c>
       <c r="F48">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="G48">
         <v>4.4</v>
       </c>
       <c r="H48">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="I48">
         <v>990</v>
       </c>
       <c r="J48">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="K48">
         <v>950</v>
@@ -12612,25 +12612,25 @@
         <v>1.01</v>
       </c>
       <c r="M48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N48">
         <v>1.25</v>
       </c>
       <c r="O48">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P48">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q48">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="R48">
         <v>1.18</v>
       </c>
       <c r="S48">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T48">
         <v>1.11</v>
@@ -12639,10 +12639,10 @@
         <v>1.11</v>
       </c>
       <c r="V48">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W48">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X48">
         <v>1000</v>
@@ -12836,28 +12836,28 @@
         <v>1.22</v>
       </c>
       <c r="G49">
-        <v>220</v>
+        <v>990</v>
       </c>
       <c r="H49">
+        <v>1.03</v>
+      </c>
+      <c r="I49">
+        <v>990</v>
+      </c>
+      <c r="J49">
+        <v>1.1</v>
+      </c>
+      <c r="K49">
+        <v>500</v>
+      </c>
+      <c r="L49">
+        <v>1.01</v>
+      </c>
+      <c r="M49">
         <v>1.02</v>
       </c>
-      <c r="I49">
-        <v>1000</v>
-      </c>
-      <c r="J49">
-        <v>1.02</v>
-      </c>
-      <c r="K49">
-        <v>110</v>
-      </c>
-      <c r="L49">
-        <v>1.01</v>
-      </c>
-      <c r="M49">
-        <v>1.01</v>
-      </c>
       <c r="N49">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O49">
         <v>1.17</v>
@@ -12872,19 +12872,19 @@
         <v>1.18</v>
       </c>
       <c r="S49">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="T49">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U49">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X49">
         <v>1000</v>
@@ -13081,10 +13081,10 @@
         <v>1.49</v>
       </c>
       <c r="H50">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I50">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J50">
         <v>4.9</v>
@@ -13105,7 +13105,7 @@
         <v>1.19</v>
       </c>
       <c r="P50">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q50">
         <v>1.55</v>
@@ -13114,13 +13114,13 @@
         <v>1.62</v>
       </c>
       <c r="S50">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T50">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U50">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V50">
         <v>1.14</v>
@@ -13240,22 +13240,22 @@
         <v>4.7</v>
       </c>
       <c r="BI50">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ50">
         <v>10.5</v>
       </c>
       <c r="BK50">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL50">
         <v>1000</v>
       </c>
       <c r="BM50">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN50">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO50">
         <v>3.35</v>
@@ -13264,31 +13264,31 @@
         <v>9</v>
       </c>
       <c r="BQ50">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR50">
         <v>21</v>
       </c>
       <c r="BS50">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BT50">
         <v>11.5</v>
       </c>
       <c r="BU50">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV50">
         <v>60</v>
       </c>
       <c r="BW50">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX50">
         <v>55</v>
       </c>
       <c r="BY50">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ50">
         <v>0</v>
@@ -13317,58 +13317,58 @@
         <v>261</v>
       </c>
       <c r="F51">
+        <v>1.03</v>
+      </c>
+      <c r="G51">
+        <v>990</v>
+      </c>
+      <c r="H51">
+        <v>1.03</v>
+      </c>
+      <c r="I51">
+        <v>990</v>
+      </c>
+      <c r="J51">
+        <v>1.04</v>
+      </c>
+      <c r="K51">
+        <v>500</v>
+      </c>
+      <c r="L51">
+        <v>1.01</v>
+      </c>
+      <c r="M51">
         <v>1.02</v>
       </c>
-      <c r="G51">
-        <v>110</v>
-      </c>
-      <c r="H51">
-        <v>1.02</v>
-      </c>
-      <c r="I51">
-        <v>110</v>
-      </c>
-      <c r="J51">
-        <v>1.02</v>
-      </c>
-      <c r="K51">
-        <v>110</v>
-      </c>
-      <c r="L51">
-        <v>1.01</v>
-      </c>
-      <c r="M51">
-        <v>1.01</v>
-      </c>
       <c r="N51">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O51">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P51">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q51">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="R51">
         <v>1.18</v>
       </c>
       <c r="S51">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T51">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U51">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V51">
         <v>1.01</v>
       </c>
       <c r="W51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -13574,7 +13574,7 @@
         <v>4</v>
       </c>
       <c r="K52">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L52">
         <v>1.29</v>
@@ -13589,19 +13589,19 @@
         <v>1.25</v>
       </c>
       <c r="P52">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q52">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R52">
         <v>1.45</v>
       </c>
       <c r="S52">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T52">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="U52">
         <v>2.14</v>
@@ -13610,7 +13610,7 @@
         <v>1.19</v>
       </c>
       <c r="W52">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X52">
         <v>23</v>
@@ -13804,13 +13804,13 @@
         <v>2.46</v>
       </c>
       <c r="G53">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H53">
         <v>2.9</v>
       </c>
       <c r="I53">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J53">
         <v>3.3</v>
@@ -13819,7 +13819,7 @@
         <v>3.7</v>
       </c>
       <c r="L53">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M53">
         <v>1.07</v>
@@ -13834,7 +13834,7 @@
         <v>1.89</v>
       </c>
       <c r="Q53">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R53">
         <v>1.34</v>
@@ -13843,7 +13843,7 @@
         <v>3.5</v>
       </c>
       <c r="T53">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U53">
         <v>2.14</v>
@@ -14043,13 +14043,13 @@
         <v>264</v>
       </c>
       <c r="F54">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G54">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H54">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I54">
         <v>3.15</v>
@@ -14058,7 +14058,7 @@
         <v>3.6</v>
       </c>
       <c r="K54">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L54">
         <v>1.28</v>
@@ -14070,37 +14070,37 @@
         <v>4.4</v>
       </c>
       <c r="O54">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P54">
         <v>2.18</v>
       </c>
       <c r="Q54">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R54">
         <v>1.47</v>
       </c>
       <c r="S54">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T54">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U54">
         <v>2.36</v>
       </c>
       <c r="V54">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W54">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X54">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y54">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z54">
         <v>27</v>
@@ -14121,13 +14121,13 @@
         <v>32</v>
       </c>
       <c r="AF54">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG54">
         <v>12.5</v>
       </c>
       <c r="AH54">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI54">
         <v>44</v>
@@ -14160,7 +14160,7 @@
         <v>16</v>
       </c>
       <c r="AS54">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT54">
         <v>11</v>
@@ -14187,16 +14187,16 @@
         <v>27</v>
       </c>
       <c r="BB54">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC54">
         <v>17.5</v>
       </c>
       <c r="BD54">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE54">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF54">
         <v>11.5</v>
@@ -14205,13 +14205,13 @@
         <v>18</v>
       </c>
       <c r="BH54">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BI54">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ54">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK54">
         <v>5.8</v>
@@ -14220,43 +14220,43 @@
         <v>1000</v>
       </c>
       <c r="BM54">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BN54">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO54">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP54">
         <v>18</v>
       </c>
       <c r="BQ54">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BR54">
         <v>28</v>
       </c>
       <c r="BS54">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT54">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU54">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV54">
         <v>22</v>
       </c>
       <c r="BW54">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BX54">
         <v>30</v>
       </c>
       <c r="BY54">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ54">
         <v>0</v>
@@ -14315,7 +14315,7 @@
         <v>1.27</v>
       </c>
       <c r="P55">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q55">
         <v>1.79</v>
@@ -14327,10 +14327,10 @@
         <v>2.98</v>
       </c>
       <c r="T55">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U55">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V55">
         <v>1.62</v>
@@ -14527,70 +14527,70 @@
         <v>266</v>
       </c>
       <c r="F56">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="G56">
         <v>13</v>
       </c>
       <c r="H56">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="I56">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="J56">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="K56">
         <v>6.6</v>
       </c>
       <c r="L56">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M56">
         <v>1.02</v>
       </c>
       <c r="N56">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O56">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P56">
         <v>2.48</v>
       </c>
       <c r="Q56">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R56">
         <v>1.59</v>
       </c>
       <c r="S56">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T56">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U56">
         <v>1.89</v>
       </c>
       <c r="V56">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="W56">
         <v>1.08</v>
       </c>
       <c r="X56">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y56">
         <v>11</v>
       </c>
       <c r="Z56">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AA56">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB56">
         <v>40</v>
@@ -14605,7 +14605,7 @@
         <v>16.5</v>
       </c>
       <c r="AF56">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AG56">
         <v>44</v>
@@ -14617,10 +14617,10 @@
         <v>40</v>
       </c>
       <c r="AJ56">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="AK56">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="AL56">
         <v>130</v>
@@ -14629,7 +14629,7 @@
         <v>150</v>
       </c>
       <c r="AN56">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AO56">
         <v>5</v>
@@ -14647,7 +14647,7 @@
         <v>8.6</v>
       </c>
       <c r="AT56">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU56">
         <v>10</v>
@@ -14659,70 +14659,70 @@
         <v>11</v>
       </c>
       <c r="AX56">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY56">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AZ56">
         <v>20</v>
       </c>
       <c r="BA56">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB56">
+        <v>6.6</v>
+      </c>
+      <c r="BC56">
         <v>6.4</v>
       </c>
-      <c r="BC56">
-        <v>6.2</v>
-      </c>
       <c r="BD56">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE56">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF56">
         <v>6.4</v>
       </c>
       <c r="BG56">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BH56">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI56">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ56">
         <v>12</v>
       </c>
       <c r="BK56">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL56">
         <v>1000</v>
       </c>
       <c r="BM56">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN56">
         <v>14</v>
       </c>
       <c r="BO56">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BP56">
         <v>1000</v>
       </c>
       <c r="BQ56">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR56">
+        <v>1000</v>
+      </c>
+      <c r="BS56">
         <v>9</v>
-      </c>
-      <c r="BR56">
-        <v>1000</v>
-      </c>
-      <c r="BS56">
-        <v>8.800000000000001</v>
       </c>
       <c r="BT56">
         <v>4.1</v>
@@ -14734,13 +14734,13 @@
         <v>8</v>
       </c>
       <c r="BW56">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX56">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY56">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ56">
         <v>0</v>
@@ -14775,10 +14775,10 @@
         <v>1.3</v>
       </c>
       <c r="H57">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I57">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J57">
         <v>7</v>
@@ -14793,7 +14793,7 @@
         <v>1.01</v>
       </c>
       <c r="N57">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O57">
         <v>1.11</v>
@@ -14802,19 +14802,19 @@
         <v>3.65</v>
       </c>
       <c r="Q57">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R57">
         <v>2.08</v>
       </c>
       <c r="S57">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="T57">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U57">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V57">
         <v>1.08</v>
@@ -14823,13 +14823,13 @@
         <v>4.3</v>
       </c>
       <c r="X57">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="Y57">
         <v>950</v>
       </c>
       <c r="Z57">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA57">
         <v>390</v>
@@ -14838,10 +14838,10 @@
         <v>17</v>
       </c>
       <c r="AC57">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AD57">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AE57">
         <v>150</v>
@@ -14850,10 +14850,10 @@
         <v>12</v>
       </c>
       <c r="AG57">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH57">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI57">
         <v>110</v>
@@ -14862,43 +14862,43 @@
         <v>12.5</v>
       </c>
       <c r="AK57">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL57">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AM57">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN57">
         <v>3.2</v>
       </c>
       <c r="AO57">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AP57">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="AQ57">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AR57">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AS57">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AT57">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU57">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AV57">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AW57">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX57">
         <v>10.5</v>
@@ -14907,10 +14907,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ57">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA57">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BB57">
         <v>10.5</v>
@@ -14919,16 +14919,16 @@
         <v>11.5</v>
       </c>
       <c r="BD57">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BE57">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF57">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="BG57">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH57">
         <v>6.2</v>
@@ -14940,7 +14940,7 @@
         <v>11.5</v>
       </c>
       <c r="BK57">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BL57">
         <v>1000</v>
@@ -14958,7 +14958,7 @@
         <v>7.4</v>
       </c>
       <c r="BQ57">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BR57">
         <v>18</v>
@@ -14979,7 +14979,7 @@
         <v>9.4</v>
       </c>
       <c r="BX57">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY57">
         <v>9.199999999999999</v>
@@ -14988,7 +14988,7 @@
         <v>7.4</v>
       </c>
       <c r="CA57">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="CB57" t="s">
         <v>283</v>
@@ -15011,13 +15011,13 @@
         <v>268</v>
       </c>
       <c r="F58">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="G58">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H58">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="I58">
         <v>1.59</v>
@@ -15035,7 +15035,7 @@
         <v>1.03</v>
       </c>
       <c r="N58">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O58">
         <v>1.18</v>
@@ -15044,13 +15044,13 @@
         <v>2.78</v>
       </c>
       <c r="Q58">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R58">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S58">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T58">
         <v>1.65</v>
@@ -15059,19 +15059,19 @@
         <v>2.4</v>
       </c>
       <c r="V58">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="W58">
         <v>1.19</v>
       </c>
       <c r="X58">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Y58">
+        <v>13</v>
+      </c>
+      <c r="Z58">
         <v>12.5</v>
-      </c>
-      <c r="Z58">
-        <v>12</v>
       </c>
       <c r="AA58">
         <v>19</v>
@@ -15080,13 +15080,13 @@
         <v>32</v>
       </c>
       <c r="AC58">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD58">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE58">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF58">
         <v>60</v>
@@ -15095,13 +15095,13 @@
         <v>24</v>
       </c>
       <c r="AH58">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI58">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AJ58">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK58">
         <v>75</v>
@@ -15113,28 +15113,28 @@
         <v>75</v>
       </c>
       <c r="AN58">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AO58">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP58">
         <v>23</v>
       </c>
       <c r="AQ58">
+        <v>11.5</v>
+      </c>
+      <c r="AR58">
         <v>10.5</v>
-      </c>
-      <c r="AR58">
-        <v>10</v>
       </c>
       <c r="AS58">
         <v>14</v>
       </c>
       <c r="AT58">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AU58">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AV58">
         <v>9.199999999999999</v>
@@ -15155,7 +15155,7 @@
         <v>22</v>
       </c>
       <c r="BB58">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC58">
         <v>55</v>
@@ -15170,7 +15170,7 @@
         <v>40</v>
       </c>
       <c r="BG58">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH58">
         <v>4.7</v>
@@ -15256,19 +15256,19 @@
         <v>1.04</v>
       </c>
       <c r="G59">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="H59">
         <v>1.04</v>
       </c>
       <c r="I59">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="J59">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="K59">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L59">
         <v>1.01</v>
@@ -15295,16 +15295,16 @@
         <v>1.14</v>
       </c>
       <c r="T59">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U59">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V59">
         <v>1.01</v>
       </c>
       <c r="W59">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X59">
         <v>1000</v>
@@ -15498,10 +15498,10 @@
         <v>4.9</v>
       </c>
       <c r="G60">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H60">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I60">
         <v>1.93</v>
@@ -15522,19 +15522,19 @@
         <v>3.4</v>
       </c>
       <c r="O60">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P60">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q60">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R60">
         <v>1.31</v>
       </c>
       <c r="S60">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T60">
         <v>1.89</v>
@@ -15746,10 +15746,10 @@
         <v>4.2</v>
       </c>
       <c r="I61">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J61">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K61">
         <v>3.9</v>
@@ -15779,10 +15779,10 @@
         <v>3.6</v>
       </c>
       <c r="T61">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U61">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V61">
         <v>1.25</v>
@@ -15845,7 +15845,7 @@
         <v>80</v>
       </c>
       <c r="AP61">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ61">
         <v>5.6</v>
@@ -15869,13 +15869,13 @@
         <v>7.6</v>
       </c>
       <c r="AX61">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AY61">
         <v>4.8</v>
       </c>
       <c r="AZ61">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BA61">
         <v>7.6</v>
@@ -15884,7 +15884,7 @@
         <v>6.2</v>
       </c>
       <c r="BC61">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BD61">
         <v>7</v>
@@ -15982,7 +15982,7 @@
         <v>1.04</v>
       </c>
       <c r="G62">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H62">
         <v>1.04</v>
@@ -15991,7 +15991,7 @@
         <v>990</v>
       </c>
       <c r="J62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K62">
         <v>500</v>
@@ -16030,7 +16030,7 @@
         <v>1.01</v>
       </c>
       <c r="W62">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X62">
         <v>1000</v>
@@ -16233,7 +16233,7 @@
         <v>990</v>
       </c>
       <c r="J63">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K63">
         <v>500</v>
@@ -16269,10 +16269,10 @@
         <v>1.11</v>
       </c>
       <c r="V63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X63">
         <v>1000</v>
@@ -16463,220 +16463,220 @@
         <v>274</v>
       </c>
       <c r="F64">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="G64">
-        <v>990</v>
+        <v>4.8</v>
       </c>
       <c r="H64">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="I64">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="J64">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="K64">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L64">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M64">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N64">
-        <v>1.25</v>
+        <v>2.92</v>
       </c>
       <c r="O64">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P64">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="Q64">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="R64">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="S64">
-        <v>1.52</v>
+        <v>3.55</v>
       </c>
       <c r="T64">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="U64">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="V64">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="W64">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="X64">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y64">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z64">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA64">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB64">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC64">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD64">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE64">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF64">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG64">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH64">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI64">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ64">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK64">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL64">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM64">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN64">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO64">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP64">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ64">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AR64">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AS64">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT64">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU64">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AV64">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW64">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX64">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY64">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ64">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA64">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB64">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC64">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD64">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE64">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF64">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG64">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH64">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI64">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ64">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK64">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL64">
         <v>1000</v>
       </c>
       <c r="BM64">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BN64">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO64">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP64">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ64">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BR64">
         <v>1000</v>
       </c>
       <c r="BS64">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BT64">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU64">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BV64">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW64">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX64">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY64">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BZ64">
         <v>0</v>
@@ -16705,160 +16705,160 @@
         <v>275</v>
       </c>
       <c r="F65">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="G65">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="H65">
+        <v>2.52</v>
+      </c>
+      <c r="I65">
+        <v>2.9</v>
+      </c>
+      <c r="J65">
+        <v>3.1</v>
+      </c>
+      <c r="K65">
+        <v>3.5</v>
+      </c>
+      <c r="L65">
+        <v>1.4</v>
+      </c>
+      <c r="M65">
+        <v>1.1</v>
+      </c>
+      <c r="N65">
+        <v>2.72</v>
+      </c>
+      <c r="O65">
+        <v>1.42</v>
+      </c>
+      <c r="P65">
+        <v>1.63</v>
+      </c>
+      <c r="Q65">
         <v>2.26</v>
       </c>
-      <c r="I65">
-        <v>3.2</v>
-      </c>
-      <c r="J65">
-        <v>3</v>
-      </c>
-      <c r="K65">
-        <v>6.4</v>
-      </c>
-      <c r="L65">
-        <v>1.01</v>
-      </c>
-      <c r="M65">
-        <v>1.01</v>
-      </c>
-      <c r="N65">
-        <v>2.6</v>
-      </c>
-      <c r="O65">
-        <v>1.05</v>
-      </c>
-      <c r="P65">
-        <v>1.56</v>
-      </c>
-      <c r="Q65">
-        <v>2.1</v>
-      </c>
       <c r="R65">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S65">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="T65">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U65">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V65">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W65">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="X65">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y65">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z65">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA65">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB65">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC65">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD65">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE65">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF65">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG65">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH65">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI65">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ65">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK65">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL65">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM65">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN65">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO65">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF65">
         <v>1.01</v>
@@ -16950,19 +16950,19 @@
         <v>1.04</v>
       </c>
       <c r="G66">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="H66">
-        <v>1.49</v>
+        <v>1.04</v>
       </c>
       <c r="I66">
-        <v>130</v>
+        <v>990</v>
       </c>
       <c r="J66">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="K66">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L66">
         <v>1.01</v>
@@ -16971,13 +16971,13 @@
         <v>1.02</v>
       </c>
       <c r="N66">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="O66">
         <v>1.08</v>
       </c>
       <c r="P66">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q66">
         <v>1.08</v>
@@ -16986,19 +16986,19 @@
         <v>1.45</v>
       </c>
       <c r="S66">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="T66">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U66">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V66">
         <v>1.01</v>
       </c>
       <c r="W66">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="X66">
         <v>1000</v>
@@ -17207,7 +17207,7 @@
         <v>3.7</v>
       </c>
       <c r="L67">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M67">
         <v>1.08</v>
@@ -17219,7 +17219,7 @@
         <v>1.38</v>
       </c>
       <c r="P67">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q67">
         <v>2.1</v>
@@ -17273,7 +17273,7 @@
         <v>12.5</v>
       </c>
       <c r="AH67">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI67">
         <v>80</v>
@@ -17306,7 +17306,7 @@
         <v>5.2</v>
       </c>
       <c r="AS67">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT67">
         <v>7</v>
@@ -17330,7 +17330,7 @@
         <v>14.5</v>
       </c>
       <c r="BA67">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB67">
         <v>16</v>
@@ -17342,13 +17342,13 @@
         <v>5.3</v>
       </c>
       <c r="BE67">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF67">
         <v>11</v>
       </c>
       <c r="BG67">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH67">
         <v>3.25</v>
@@ -17372,7 +17372,7 @@
         <v>4.6</v>
       </c>
       <c r="BO67">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP67">
         <v>14.5</v>
@@ -17431,22 +17431,22 @@
         <v>278</v>
       </c>
       <c r="F68">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="G68">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H68">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="I68">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J68">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K68">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L68">
         <v>1.01</v>
@@ -17458,7 +17458,7 @@
         <v>3.05</v>
       </c>
       <c r="O68">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P68">
         <v>1.72</v>
@@ -17467,22 +17467,22 @@
         <v>1.98</v>
       </c>
       <c r="R68">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S68">
-        <v>1.98</v>
+        <v>2.86</v>
       </c>
       <c r="T68">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U68">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V68">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W68">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="X68">
         <v>1000</v>
@@ -17539,52 +17539,52 @@
         <v>1000</v>
       </c>
       <c r="AP68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF68">
         <v>1.01</v>
@@ -17685,7 +17685,7 @@
         <v>1.88</v>
       </c>
       <c r="J69">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K69">
         <v>3.95</v>
@@ -17700,7 +17700,7 @@
         <v>2.9</v>
       </c>
       <c r="O69">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P69">
         <v>1.73</v>
@@ -17781,58 +17781,58 @@
         <v>17</v>
       </c>
       <c r="AP69">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ69">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AR69">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AS69">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT69">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU69">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV69">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AW69">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX69">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY69">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ69">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA69">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB69">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC69">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD69">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE69">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF69">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG69">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH69">
         <v>1000</v>
@@ -17915,220 +17915,220 @@
         <v>280</v>
       </c>
       <c r="F70">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="G70">
-        <v>990</v>
+        <v>1.69</v>
       </c>
       <c r="H70">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="I70">
-        <v>990</v>
+        <v>11</v>
       </c>
       <c r="J70">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="K70">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L70">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M70">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N70">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="O70">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P70">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q70">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="R70">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="S70">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T70">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U70">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="V70">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W70">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="X70">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y70">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z70">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA70">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AB70">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC70">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD70">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE70">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF70">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG70">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH70">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI70">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ70">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK70">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL70">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM70">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN70">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO70">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AP70">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AQ70">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR70">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS70">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT70">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="AU70">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV70">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW70">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX70">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AY70">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ70">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA70">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB70">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BC70">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD70">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE70">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF70">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG70">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH70">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI70">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ70">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK70">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL70">
         <v>1000</v>
       </c>
       <c r="BM70">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BN70">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO70">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BP70">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ70">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR70">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS70">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BT70">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU70">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV70">
         <v>1000</v>
       </c>
       <c r="BW70">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BX70">
         <v>1000</v>
       </c>
       <c r="BY70">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BZ70">
         <v>0</v>
@@ -18160,22 +18160,22 @@
         <v>1.04</v>
       </c>
       <c r="G71">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H71">
         <v>1.04</v>
       </c>
       <c r="I71">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J71">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K71">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L71">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M71">
         <v>1.01</v>
@@ -18199,16 +18199,16 @@
         <v>1.11</v>
       </c>
       <c r="T71">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U71">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X71">
         <v>1000</v>
@@ -18408,7 +18408,7 @@
         <v>5.5</v>
       </c>
       <c r="I72">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J72">
         <v>4.1</v>
@@ -18420,13 +18420,13 @@
         <v>1.35</v>
       </c>
       <c r="M72">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N72">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O72">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P72">
         <v>2.2</v>
@@ -18441,7 +18441,7 @@
         <v>3</v>
       </c>
       <c r="T72">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="U72">
         <v>2.14</v>
@@ -18459,7 +18459,7 @@
         <v>21</v>
       </c>
       <c r="Z72">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AA72">
         <v>1000</v>
@@ -18471,7 +18471,7 @@
         <v>9.6</v>
       </c>
       <c r="AD72">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AE72">
         <v>70</v>
@@ -18561,64 +18561,64 @@
         <v>46</v>
       </c>
       <c r="BH72">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI72">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ72">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK72">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL72">
         <v>1000</v>
       </c>
       <c r="BM72">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN72">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO72">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP72">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ72">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR72">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS72">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT72">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU72">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV72">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW72">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX72">
         <v>1000</v>
       </c>
       <c r="BY72">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ72">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA72">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB72" t="s">
         <v>283</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-31.xlsx
@@ -865,7 +865,7 @@
     <t>Toronto FC</t>
   </si>
   <si>
-    <t>2026-07-30 16:05:48</t>
+    <t>2026-07-30 18:21:09</t>
   </si>
 </sst>
 </file>
@@ -1459,58 +1459,58 @@
         <v>212</v>
       </c>
       <c r="F2">
+        <v>3.5</v>
+      </c>
+      <c r="G2">
         <v>3.6</v>
       </c>
-      <c r="G2">
-        <v>3.65</v>
-      </c>
       <c r="H2">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I2">
         <v>2.5</v>
       </c>
       <c r="J2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="M2">
         <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O2">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P2">
         <v>1.6</v>
       </c>
       <c r="Q2">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R2">
         <v>1.21</v>
       </c>
       <c r="S2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T2">
         <v>2.1</v>
       </c>
       <c r="U2">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X2">
         <v>9</v>
@@ -1519,7 +1519,7 @@
         <v>7.8</v>
       </c>
       <c r="Z2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA2">
         <v>36</v>
@@ -1558,7 +1558,7 @@
         <v>75</v>
       </c>
       <c r="AM2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN2">
         <v>70</v>
@@ -1567,13 +1567,13 @@
         <v>36</v>
       </c>
       <c r="AP2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ2">
         <v>7.4</v>
       </c>
       <c r="AR2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS2">
         <v>32</v>
@@ -1606,13 +1606,13 @@
         <v>60</v>
       </c>
       <c r="BC2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BD2">
         <v>65</v>
       </c>
       <c r="BE2">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="BF2">
         <v>60</v>
@@ -1621,19 +1621,19 @@
         <v>30</v>
       </c>
       <c r="BH2">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BI2">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM2">
         <v>17.5</v>
@@ -1642,25 +1642,25 @@
         <v>6.4</v>
       </c>
       <c r="BO2">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BP2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BR2">
         <v>55</v>
       </c>
       <c r="BS2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BT2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU2">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BV2">
         <v>21</v>
@@ -1710,52 +1710,52 @@
         <v>6.8</v>
       </c>
       <c r="I3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O3">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P3">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T3">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U3">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V3">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W3">
         <v>2.5</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Y3">
         <v>18</v>
@@ -1770,7 +1770,7 @@
         <v>6.6</v>
       </c>
       <c r="AC3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD3">
         <v>28</v>
@@ -1791,10 +1791,10 @@
         <v>140</v>
       </c>
       <c r="AJ3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL3">
         <v>55</v>
@@ -1809,7 +1809,7 @@
         <v>230</v>
       </c>
       <c r="AP3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ3">
         <v>16</v>
@@ -1824,10 +1824,10 @@
         <v>6</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW3">
         <v>70</v>
@@ -1836,7 +1836,7 @@
         <v>7.6</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3">
         <v>25</v>
@@ -1851,22 +1851,22 @@
         <v>18.5</v>
       </c>
       <c r="BD3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BE3">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="BF3">
         <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="BH3">
         <v>3.05</v>
       </c>
       <c r="BI3">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="BJ3">
         <v>12.5</v>
@@ -1878,13 +1878,13 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN3">
         <v>4.1</v>
       </c>
       <c r="BO3">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BP3">
         <v>12</v>
@@ -1893,34 +1893,34 @@
         <v>7.8</v>
       </c>
       <c r="BR3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT3">
         <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV3">
         <v>75</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BY3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="s">
         <v>283</v>
@@ -1943,58 +1943,58 @@
         <v>214</v>
       </c>
       <c r="F4">
+        <v>3.45</v>
+      </c>
+      <c r="G4">
         <v>3.55</v>
       </c>
-      <c r="G4">
-        <v>3.6</v>
-      </c>
       <c r="H4">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I4">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K4">
         <v>3.35</v>
       </c>
       <c r="L4">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S4">
         <v>4.6</v>
       </c>
       <c r="T4">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U4">
         <v>1.96</v>
       </c>
       <c r="V4">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W4">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X4">
         <v>10.5</v>
@@ -2006,7 +2006,7 @@
         <v>14</v>
       </c>
       <c r="AA4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB4">
         <v>11</v>
@@ -2018,25 +2018,25 @@
         <v>11.5</v>
       </c>
       <c r="AE4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ4">
         <v>70</v>
       </c>
       <c r="AK4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL4">
         <v>65</v>
@@ -2048,7 +2048,7 @@
         <v>60</v>
       </c>
       <c r="AO4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP4">
         <v>9.800000000000001</v>
@@ -2057,7 +2057,7 @@
         <v>7.8</v>
       </c>
       <c r="AR4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS4">
         <v>30</v>
@@ -2066,25 +2066,25 @@
         <v>10.5</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV4">
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY4">
         <v>13.5</v>
       </c>
       <c r="AZ4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA4">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB4">
         <v>60</v>
@@ -2093,7 +2093,7 @@
         <v>44</v>
       </c>
       <c r="BD4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE4">
         <v>100</v>
@@ -2102,43 +2102,43 @@
         <v>50</v>
       </c>
       <c r="BG4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH4">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BI4">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN4">
         <v>6.6</v>
       </c>
       <c r="BO4">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BP4">
         <v>32</v>
       </c>
       <c r="BQ4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BT4">
         <v>5.1</v>
@@ -2147,22 +2147,22 @@
         <v>4.5</v>
       </c>
       <c r="BV4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BW4">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="BX4">
         <v>38</v>
       </c>
       <c r="BY4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CA4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CB4" t="s">
         <v>283</v>
@@ -2185,82 +2185,82 @@
         <v>215</v>
       </c>
       <c r="F5">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="G5">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O5">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P5">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q5">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T5">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U5">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="V5">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W5">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="X5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z5">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AA5">
-        <v>380</v>
+        <v>270</v>
       </c>
       <c r="AB5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AE5">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AF5">
         <v>8.6</v>
@@ -2269,25 +2269,25 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI5">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AJ5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM5">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="AN5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO5">
         <v>290</v>
@@ -2296,115 +2296,115 @@
         <v>10.5</v>
       </c>
       <c r="AQ5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR5">
         <v>46</v>
       </c>
       <c r="AS5">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW5">
+        <v>70</v>
+      </c>
+      <c r="AX5">
+        <v>7.8</v>
+      </c>
+      <c r="AY5">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5">
+        <v>24</v>
+      </c>
+      <c r="BA5">
+        <v>70</v>
+      </c>
+      <c r="BB5">
+        <v>14</v>
+      </c>
+      <c r="BC5">
+        <v>17.5</v>
+      </c>
+      <c r="BD5">
+        <v>42</v>
+      </c>
+      <c r="BE5">
+        <v>13</v>
+      </c>
+      <c r="BF5">
         <v>11</v>
       </c>
-      <c r="AX5">
-        <v>7</v>
-      </c>
-      <c r="AY5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ5">
-        <v>22</v>
-      </c>
-      <c r="BA5">
-        <v>11</v>
-      </c>
-      <c r="BB5">
-        <v>12.5</v>
-      </c>
-      <c r="BC5">
-        <v>16</v>
-      </c>
-      <c r="BD5">
-        <v>34</v>
-      </c>
-      <c r="BE5">
-        <v>11</v>
-      </c>
-      <c r="BF5">
-        <v>10</v>
-      </c>
       <c r="BG5">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BH5">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI5">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5">
         <v>12</v>
       </c>
       <c r="BK5">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BN5">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BO5">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="BP5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BR5">
         <v>32</v>
       </c>
       <c r="BS5">
+        <v>8</v>
+      </c>
+      <c r="BT5">
+        <v>10.5</v>
+      </c>
+      <c r="BU5">
+        <v>5.3</v>
+      </c>
+      <c r="BV5">
+        <v>70</v>
+      </c>
+      <c r="BW5">
         <v>9.4</v>
       </c>
-      <c r="BT5">
-        <v>11.5</v>
-      </c>
-      <c r="BU5">
-        <v>6.2</v>
-      </c>
-      <c r="BV5">
+      <c r="BX5">
         <v>80</v>
       </c>
-      <c r="BW5">
-        <v>11.5</v>
-      </c>
-      <c r="BX5">
-        <v>90</v>
-      </c>
       <c r="BY5">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CA5">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="s">
         <v>283</v>
@@ -2427,13 +2427,13 @@
         <v>216</v>
       </c>
       <c r="F6">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G6">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>4.3</v>
@@ -2451,37 +2451,37 @@
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O6">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P6">
+        <v>2.6</v>
+      </c>
+      <c r="Q6">
+        <v>1.55</v>
+      </c>
+      <c r="R6">
+        <v>1.66</v>
+      </c>
+      <c r="S6">
+        <v>2.38</v>
+      </c>
+      <c r="T6">
+        <v>1.56</v>
+      </c>
+      <c r="U6">
         <v>2.64</v>
       </c>
-      <c r="Q6">
-        <v>1.57</v>
-      </c>
-      <c r="R6">
-        <v>1.64</v>
-      </c>
-      <c r="S6">
-        <v>2.44</v>
-      </c>
-      <c r="T6">
-        <v>1.57</v>
-      </c>
-      <c r="U6">
-        <v>2.62</v>
-      </c>
       <c r="V6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X6">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="Y6">
         <v>22</v>
@@ -2493,7 +2493,7 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC6">
         <v>10.5</v>
@@ -2502,10 +2502,10 @@
         <v>17.5</v>
       </c>
       <c r="AE6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG6">
         <v>11</v>
@@ -2526,25 +2526,25 @@
         <v>30</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>840</v>
       </c>
       <c r="AN6">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP6">
         <v>21</v>
       </c>
       <c r="AQ6">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AR6">
         <v>24</v>
       </c>
       <c r="AS6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT6">
         <v>11</v>
@@ -2553,13 +2553,13 @@
         <v>9</v>
       </c>
       <c r="AV6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW6">
         <v>34</v>
       </c>
       <c r="AX6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY6">
         <v>9.6</v>
@@ -2580,13 +2580,13 @@
         <v>19</v>
       </c>
       <c r="BE6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BF6">
         <v>7.6</v>
       </c>
       <c r="BG6">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BH6">
         <v>4.6</v>
@@ -2669,19 +2669,19 @@
         <v>217</v>
       </c>
       <c r="F7">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="G7">
         <v>3.35</v>
       </c>
       <c r="H7">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2693,19 +2693,19 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="O7">
         <v>1.29</v>
       </c>
       <c r="P7">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="Q7">
         <v>1.29</v>
       </c>
       <c r="R7">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="S7">
         <v>1.29</v>
@@ -2717,10 +2717,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="W7">
-        <v>1.42</v>
+        <v>1.78</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2926,7 +2926,7 @@
         <v>3.55</v>
       </c>
       <c r="K8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>1.37</v>
@@ -3153,34 +3153,34 @@
         <v>219</v>
       </c>
       <c r="F9">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G9">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H9">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I9">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J9">
         <v>3.35</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N9">
         <v>3.55</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P9">
         <v>1.93</v>
@@ -3261,52 +3261,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -3395,7 +3395,7 @@
         <v>220</v>
       </c>
       <c r="F10">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="G10">
         <v>2.9</v>
@@ -3640,7 +3640,7 @@
         <v>1.7</v>
       </c>
       <c r="G11">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H11">
         <v>5.9</v>
@@ -3649,7 +3649,7 @@
         <v>6.6</v>
       </c>
       <c r="J11">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K11">
         <v>3.95</v>
@@ -3667,10 +3667,10 @@
         <v>1.43</v>
       </c>
       <c r="P11">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q11">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R11">
         <v>1.25</v>
@@ -3802,7 +3802,7 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="BJ11">
         <v>16</v>
@@ -3814,7 +3814,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="BN11">
         <v>5.6</v>
@@ -3826,34 +3826,34 @@
         <v>18.5</v>
       </c>
       <c r="BQ11">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BR11">
         <v>48</v>
       </c>
       <c r="BS11">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="BT11">
         <v>13</v>
       </c>
       <c r="BU11">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BZ11">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="CA11">
         <v>1.71</v>
@@ -3879,7 +3879,7 @@
         <v>222</v>
       </c>
       <c r="F12">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G12">
         <v>1.76</v>
@@ -3894,7 +3894,7 @@
         <v>4.2</v>
       </c>
       <c r="K12">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L12">
         <v>1.29</v>
@@ -3912,10 +3912,10 @@
         <v>2.22</v>
       </c>
       <c r="Q12">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R12">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S12">
         <v>2.76</v>
@@ -3948,10 +3948,10 @@
         <v>12</v>
       </c>
       <c r="AC12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE12">
         <v>65</v>
@@ -3993,10 +3993,10 @@
         <v>16</v>
       </c>
       <c r="AR12">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS12">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT12">
         <v>8</v>
@@ -4008,7 +4008,7 @@
         <v>15.5</v>
       </c>
       <c r="AW12">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX12">
         <v>8.800000000000001</v>
@@ -4020,7 +4020,7 @@
         <v>14</v>
       </c>
       <c r="BA12">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB12">
         <v>13</v>
@@ -4029,16 +4029,16 @@
         <v>13</v>
       </c>
       <c r="BD12">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE12">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF12">
         <v>6.6</v>
       </c>
       <c r="BG12">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH12">
         <v>3.95</v>
@@ -4136,7 +4136,7 @@
         <v>4</v>
       </c>
       <c r="K13">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L13">
         <v>1.22</v>
@@ -4145,31 +4145,31 @@
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O13">
         <v>1.15</v>
       </c>
       <c r="P13">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q13">
         <v>1.47</v>
       </c>
       <c r="R13">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S13">
         <v>2.14</v>
       </c>
       <c r="T13">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U13">
         <v>2.72</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W13">
         <v>1.8</v>
@@ -4208,7 +4208,7 @@
         <v>17</v>
       </c>
       <c r="AI13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ13">
         <v>30</v>
@@ -4223,64 +4223,64 @@
         <v>50</v>
       </c>
       <c r="AN13">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO13">
+        <v>18.5</v>
+      </c>
+      <c r="AP13">
+        <v>5.8</v>
+      </c>
+      <c r="AQ13">
+        <v>5.3</v>
+      </c>
+      <c r="AR13">
+        <v>5.8</v>
+      </c>
+      <c r="AS13">
+        <v>6.2</v>
+      </c>
+      <c r="AT13">
+        <v>5</v>
+      </c>
+      <c r="AU13">
+        <v>9.4</v>
+      </c>
+      <c r="AV13">
+        <v>5</v>
+      </c>
+      <c r="AW13">
+        <v>5.8</v>
+      </c>
+      <c r="AX13">
+        <v>5.1</v>
+      </c>
+      <c r="AY13">
+        <v>4.4</v>
+      </c>
+      <c r="AZ13">
+        <v>4.9</v>
+      </c>
+      <c r="BA13">
+        <v>5.8</v>
+      </c>
+      <c r="BB13">
         <v>21</v>
       </c>
-      <c r="AP13">
+      <c r="BC13">
         <v>5.3</v>
       </c>
-      <c r="AQ13">
-        <v>4.9</v>
-      </c>
-      <c r="AR13">
-        <v>5.2</v>
-      </c>
-      <c r="AS13">
-        <v>5.7</v>
-      </c>
-      <c r="AT13">
-        <v>4.6</v>
-      </c>
-      <c r="AU13">
-        <v>4.1</v>
-      </c>
-      <c r="AV13">
-        <v>4.6</v>
-      </c>
-      <c r="AW13">
-        <v>5.3</v>
-      </c>
-      <c r="AX13">
-        <v>4.7</v>
-      </c>
-      <c r="AY13">
-        <v>4.1</v>
-      </c>
-      <c r="AZ13">
-        <v>4.5</v>
-      </c>
-      <c r="BA13">
-        <v>5.3</v>
-      </c>
-      <c r="BB13">
-        <v>5.1</v>
-      </c>
-      <c r="BC13">
-        <v>4.8</v>
-      </c>
       <c r="BD13">
+        <v>5.5</v>
+      </c>
+      <c r="BE13">
+        <v>6</v>
+      </c>
+      <c r="BF13">
+        <v>3.9</v>
+      </c>
+      <c r="BG13">
         <v>5</v>
-      </c>
-      <c r="BE13">
-        <v>5.5</v>
-      </c>
-      <c r="BF13">
-        <v>3.8</v>
-      </c>
-      <c r="BG13">
-        <v>4.8</v>
       </c>
       <c r="BH13">
         <v>5</v>
@@ -4363,7 +4363,7 @@
         <v>224</v>
       </c>
       <c r="F14">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G14">
         <v>2.5</v>
@@ -4372,10 +4372,10 @@
         <v>2.96</v>
       </c>
       <c r="I14">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J14">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K14">
         <v>3.9</v>
@@ -4387,31 +4387,31 @@
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O14">
         <v>1.23</v>
       </c>
       <c r="P14">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="Q14">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="R14">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="S14">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="T14">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="U14">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="V14">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W14">
         <v>1.66</v>
@@ -4426,7 +4426,7 @@
         <v>24</v>
       </c>
       <c r="AA14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB14">
         <v>14.5</v>
@@ -4450,16 +4450,16 @@
         <v>15</v>
       </c>
       <c r="AI14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ14">
         <v>36</v>
       </c>
       <c r="AK14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM14">
         <v>60</v>
@@ -4468,7 +4468,7 @@
         <v>14</v>
       </c>
       <c r="AO14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP14">
         <v>17</v>
@@ -4492,7 +4492,7 @@
         <v>12</v>
       </c>
       <c r="AW14">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AX14">
         <v>15.5</v>
@@ -4504,7 +4504,7 @@
         <v>12.5</v>
       </c>
       <c r="BA14">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB14">
         <v>28</v>
@@ -4522,25 +4522,25 @@
         <v>11.5</v>
       </c>
       <c r="BG14">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH14">
         <v>4.3</v>
       </c>
       <c r="BI14">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ14">
         <v>9</v>
       </c>
       <c r="BK14">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN14">
         <v>6</v>
@@ -4555,7 +4555,7 @@
         <v>6.4</v>
       </c>
       <c r="BR14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS14">
         <v>7.4</v>
@@ -4570,16 +4570,16 @@
         <v>21</v>
       </c>
       <c r="BW14">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX14">
         <v>29</v>
       </c>
       <c r="BY14">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA14">
         <v>6.6</v>
@@ -4611,10 +4611,10 @@
         <v>3.65</v>
       </c>
       <c r="H15">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I15">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J15">
         <v>3.1</v>
@@ -4626,19 +4626,19 @@
         <v>1.45</v>
       </c>
       <c r="M15">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N15">
         <v>2.9</v>
       </c>
       <c r="O15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P15">
         <v>1.62</v>
       </c>
       <c r="Q15">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R15">
         <v>1.23</v>
@@ -4647,61 +4647,61 @@
         <v>4.5</v>
       </c>
       <c r="T15">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U15">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V15">
         <v>1.64</v>
       </c>
       <c r="W15">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X15">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y15">
         <v>8.800000000000001</v>
       </c>
       <c r="Z15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA15">
         <v>44</v>
       </c>
       <c r="AB15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC15">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD15">
         <v>14</v>
       </c>
       <c r="AE15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH15">
         <v>23</v>
       </c>
       <c r="AI15">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ15">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AK15">
         <v>60</v>
       </c>
       <c r="AL15">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM15">
         <v>160</v>
@@ -4710,64 +4710,64 @@
         <v>70</v>
       </c>
       <c r="AO15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP15">
         <v>8.6</v>
       </c>
       <c r="AQ15">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR15">
         <v>13</v>
       </c>
       <c r="AS15">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AT15">
         <v>9.199999999999999</v>
       </c>
       <c r="AU15">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV15">
         <v>10</v>
       </c>
       <c r="AW15">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AX15">
         <v>19</v>
       </c>
       <c r="AY15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ15">
         <v>16.5</v>
       </c>
       <c r="BA15">
+        <v>5.6</v>
+      </c>
+      <c r="BB15">
+        <v>5.7</v>
+      </c>
+      <c r="BC15">
+        <v>5.6</v>
+      </c>
+      <c r="BD15">
+        <v>5.7</v>
+      </c>
+      <c r="BE15">
         <v>6</v>
       </c>
-      <c r="BB15">
-        <v>6</v>
-      </c>
-      <c r="BC15">
-        <v>5.9</v>
-      </c>
-      <c r="BD15">
-        <v>6</v>
-      </c>
-      <c r="BE15">
-        <v>6.2</v>
-      </c>
       <c r="BF15">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BG15">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH15">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BI15">
         <v>2.44</v>
@@ -4782,13 +4782,13 @@
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN15">
         <v>6.6</v>
       </c>
       <c r="BO15">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP15">
         <v>32</v>
@@ -4803,22 +4803,22 @@
         <v>9</v>
       </c>
       <c r="BT15">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU15">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV15">
         <v>22</v>
       </c>
       <c r="BW15">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4862,22 +4862,22 @@
         <v>3.15</v>
       </c>
       <c r="K16">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N16">
         <v>3.2</v>
       </c>
       <c r="O16">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="P16">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q16">
         <v>2.14</v>
@@ -4886,7 +4886,7 @@
         <v>1.26</v>
       </c>
       <c r="S16">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T16">
         <v>1.85</v>
@@ -4964,7 +4964,7 @@
         <v>15.5</v>
       </c>
       <c r="AS16">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AT16">
         <v>7</v>
@@ -4988,7 +4988,7 @@
         <v>13.5</v>
       </c>
       <c r="BA16">
-        <v>4.4</v>
+        <v>34</v>
       </c>
       <c r="BB16">
         <v>4.3</v>
@@ -4997,7 +4997,7 @@
         <v>4.2</v>
       </c>
       <c r="BD16">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BE16">
         <v>4.6</v>
@@ -5089,22 +5089,22 @@
         <v>227</v>
       </c>
       <c r="F17">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G17">
         <v>1.81</v>
       </c>
       <c r="H17">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I17">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J17">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K17">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L17">
         <v>1.33</v>
@@ -5119,13 +5119,13 @@
         <v>1.29</v>
       </c>
       <c r="P17">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q17">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R17">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S17">
         <v>3.1</v>
@@ -5143,22 +5143,22 @@
         <v>2.22</v>
       </c>
       <c r="X17">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y17">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="Z17">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA17">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB17">
         <v>9.4</v>
       </c>
       <c r="AC17">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD17">
         <v>21</v>
@@ -5170,7 +5170,7 @@
         <v>13</v>
       </c>
       <c r="AG17">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AH17">
         <v>22</v>
@@ -5194,61 +5194,61 @@
         <v>11</v>
       </c>
       <c r="AO17">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP17">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AQ17">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="AR17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS17">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT17">
         <v>8</v>
       </c>
       <c r="AU17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV17">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AW17">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX17">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="AY17">
         <v>8.6</v>
       </c>
       <c r="AZ17">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BA17">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB17">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="BC17">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BD17">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BE17">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF17">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG17">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH17">
         <v>3.65</v>
@@ -5331,22 +5331,22 @@
         <v>228</v>
       </c>
       <c r="F18">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="G18">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H18">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I18">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J18">
         <v>3.3</v>
       </c>
       <c r="K18">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L18">
         <v>1.42</v>
@@ -5355,13 +5355,13 @@
         <v>1.07</v>
       </c>
       <c r="N18">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O18">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P18">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q18">
         <v>1.99</v>
@@ -5379,7 +5379,7 @@
         <v>2.12</v>
       </c>
       <c r="V18">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W18">
         <v>1.44</v>
@@ -5448,7 +5448,7 @@
         <v>14</v>
       </c>
       <c r="AS18">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="AT18">
         <v>10</v>
@@ -5463,7 +5463,7 @@
         <v>6.8</v>
       </c>
       <c r="AX18">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="AY18">
         <v>10</v>
@@ -5472,16 +5472,16 @@
         <v>14.5</v>
       </c>
       <c r="BA18">
-        <v>18.5</v>
+        <v>7.2</v>
       </c>
       <c r="BB18">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="BC18">
         <v>7.2</v>
       </c>
       <c r="BD18">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="BE18">
         <v>8.199999999999999</v>
@@ -5496,10 +5496,10 @@
         <v>3.45</v>
       </c>
       <c r="BI18">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK18">
         <v>5.1</v>
@@ -5508,7 +5508,7 @@
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN18">
         <v>6.4</v>
@@ -5520,13 +5520,13 @@
         <v>26</v>
       </c>
       <c r="BQ18">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR18">
         <v>38</v>
       </c>
       <c r="BS18">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT18">
         <v>5.7</v>
@@ -5538,19 +5538,19 @@
         <v>20</v>
       </c>
       <c r="BW18">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX18">
         <v>34</v>
       </c>
       <c r="BY18">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ18">
         <v>30</v>
       </c>
       <c r="CA18">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB18" t="s">
         <v>283</v>
@@ -5582,10 +5582,10 @@
         <v>2.46</v>
       </c>
       <c r="I19">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J19">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K19">
         <v>3.65</v>
@@ -5597,7 +5597,7 @@
         <v>1.08</v>
       </c>
       <c r="N19">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O19">
         <v>1.35</v>
@@ -5621,7 +5621,7 @@
         <v>2.08</v>
       </c>
       <c r="V19">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W19">
         <v>1.45</v>
@@ -5648,13 +5648,13 @@
         <v>12</v>
       </c>
       <c r="AE19">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF19">
         <v>21</v>
       </c>
       <c r="AG19">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH19">
         <v>18</v>
@@ -5684,13 +5684,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ19">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AR19">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AS19">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AT19">
         <v>8.6</v>
@@ -5699,7 +5699,7 @@
         <v>6.8</v>
       </c>
       <c r="AV19">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW19">
         <v>6.4</v>
@@ -5714,25 +5714,25 @@
         <v>15.5</v>
       </c>
       <c r="BA19">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BB19">
         <v>7.2</v>
       </c>
       <c r="BC19">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BD19">
         <v>7.2</v>
       </c>
       <c r="BE19">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF19">
         <v>6.8</v>
       </c>
       <c r="BG19">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BH19">
         <v>3.3</v>
@@ -5824,13 +5824,13 @@
         <v>1.95</v>
       </c>
       <c r="I20">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J20">
         <v>3.85</v>
       </c>
       <c r="K20">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L20">
         <v>1.28</v>
@@ -5842,7 +5842,7 @@
         <v>4.7</v>
       </c>
       <c r="O20">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P20">
         <v>2.24</v>
@@ -5854,13 +5854,13 @@
         <v>1.49</v>
       </c>
       <c r="S20">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T20">
         <v>1.63</v>
       </c>
       <c r="U20">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V20">
         <v>1.89</v>
@@ -5875,10 +5875,10 @@
         <v>14</v>
       </c>
       <c r="Z20">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA20">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AB20">
         <v>19</v>
@@ -5890,7 +5890,7 @@
         <v>12.5</v>
       </c>
       <c r="AE20">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF20">
         <v>32</v>
@@ -5899,13 +5899,13 @@
         <v>17</v>
       </c>
       <c r="AH20">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI20">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ20">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AK20">
         <v>48</v>
@@ -5944,10 +5944,10 @@
         <v>8.4</v>
       </c>
       <c r="AW20">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX20">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AY20">
         <v>12</v>
@@ -5956,22 +5956,22 @@
         <v>12.5</v>
       </c>
       <c r="BA20">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BB20">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC20">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD20">
+        <v>5.9</v>
+      </c>
+      <c r="BE20">
+        <v>6</v>
+      </c>
+      <c r="BF20">
         <v>5.5</v>
-      </c>
-      <c r="BE20">
-        <v>5.6</v>
-      </c>
-      <c r="BF20">
-        <v>5.2</v>
       </c>
       <c r="BG20">
         <v>8.4</v>
@@ -5980,7 +5980,7 @@
         <v>4.2</v>
       </c>
       <c r="BI20">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BJ20">
         <v>9.4</v>
@@ -6016,7 +6016,7 @@
         <v>5.3</v>
       </c>
       <c r="BU20">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BV20">
         <v>14</v>
@@ -6299,7 +6299,7 @@
         <v>232</v>
       </c>
       <c r="F22">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G22">
         <v>2.3</v>
@@ -6544,13 +6544,13 @@
         <v>2.46</v>
       </c>
       <c r="G23">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H23">
         <v>2.74</v>
       </c>
       <c r="I23">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J23">
         <v>3.7</v>
@@ -6574,7 +6574,7 @@
         <v>2.24</v>
       </c>
       <c r="Q23">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R23">
         <v>1.49</v>
@@ -6583,16 +6583,16 @@
         <v>2.76</v>
       </c>
       <c r="T23">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U23">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W23">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X23">
         <v>22</v>
@@ -6613,7 +6613,7 @@
         <v>10.5</v>
       </c>
       <c r="AD23">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE23">
         <v>34</v>
@@ -6658,7 +6658,7 @@
         <v>17.5</v>
       </c>
       <c r="AS23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT23">
         <v>10</v>
@@ -6685,10 +6685,10 @@
         <v>5.2</v>
       </c>
       <c r="BB23">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC23">
-        <v>18.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD23">
         <v>5.2</v>
@@ -6703,7 +6703,7 @@
         <v>17.5</v>
       </c>
       <c r="BH23">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI23">
         <v>3.2</v>
@@ -6712,55 +6712,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK23">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN23">
         <v>5.7</v>
       </c>
       <c r="BO23">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BP23">
         <v>17.5</v>
       </c>
       <c r="BQ23">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT23">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU23">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB23" t="s">
         <v>283</v>
@@ -6783,19 +6783,19 @@
         <v>234</v>
       </c>
       <c r="F24">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G24">
         <v>2.3</v>
       </c>
       <c r="H24">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I24">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J24">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K24">
         <v>4.2</v>
@@ -6813,7 +6813,7 @@
         <v>1.23</v>
       </c>
       <c r="P24">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q24">
         <v>1.66</v>
@@ -6837,7 +6837,7 @@
         <v>1.76</v>
       </c>
       <c r="X24">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Y24">
         <v>17</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="AA24">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB24">
         <v>13</v>
@@ -6870,7 +6870,7 @@
         <v>16</v>
       </c>
       <c r="AI24">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ24">
         <v>28</v>
@@ -6882,7 +6882,7 @@
         <v>32</v>
       </c>
       <c r="AM24">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN24">
         <v>13</v>
@@ -6891,7 +6891,7 @@
         <v>27</v>
       </c>
       <c r="AP24">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ24">
         <v>6.4</v>
@@ -6900,13 +6900,13 @@
         <v>7.6</v>
       </c>
       <c r="AS24">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT24">
         <v>5.8</v>
       </c>
       <c r="AU24">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AV24">
         <v>6.2</v>
@@ -6921,22 +6921,22 @@
         <v>5.5</v>
       </c>
       <c r="AZ24">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA24">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB24">
         <v>7.6</v>
       </c>
       <c r="BC24">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BD24">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BE24">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF24">
         <v>5.8</v>
@@ -7031,16 +7031,16 @@
         <v>1.52</v>
       </c>
       <c r="H25">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I25">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="J25">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K25">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -7073,7 +7073,7 @@
         <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="W25">
         <v>2.88</v>
@@ -7133,52 +7133,52 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
         <v>1.01</v>
@@ -7276,7 +7276,7 @@
         <v>5.4</v>
       </c>
       <c r="I26">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J26">
         <v>4.5</v>
@@ -7297,22 +7297,22 @@
         <v>1.16</v>
       </c>
       <c r="P26">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q26">
         <v>1.48</v>
       </c>
       <c r="R26">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S26">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T26">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U26">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V26">
         <v>1.01</v>
@@ -7321,82 +7321,82 @@
         <v>1.01</v>
       </c>
       <c r="X26">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y26">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z26">
         <v>55</v>
       </c>
       <c r="AA26">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
         <v>14.5</v>
       </c>
       <c r="AC26">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE26">
         <v>65</v>
       </c>
       <c r="AF26">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG26">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH26">
         <v>17.5</v>
       </c>
       <c r="AI26">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="AJ26">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK26">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AL26">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM26">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO26">
         <v>48</v>
       </c>
       <c r="AP26">
-        <v>5.5</v>
+        <v>22</v>
       </c>
       <c r="AQ26">
-        <v>5.4</v>
+        <v>19.5</v>
       </c>
       <c r="AR26">
-        <v>5.8</v>
+        <v>27</v>
       </c>
       <c r="AS26">
-        <v>6.2</v>
+        <v>42</v>
       </c>
       <c r="AT26">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU26">
         <v>10</v>
       </c>
       <c r="AV26">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW26">
-        <v>5.9</v>
+        <v>29</v>
       </c>
       <c r="AX26">
         <v>11.5</v>
@@ -7408,7 +7408,7 @@
         <v>15</v>
       </c>
       <c r="BA26">
-        <v>5.8</v>
+        <v>27</v>
       </c>
       <c r="BB26">
         <v>15.5</v>
@@ -7417,16 +7417,16 @@
         <v>13.5</v>
       </c>
       <c r="BD26">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BE26">
-        <v>5.8</v>
+        <v>30</v>
       </c>
       <c r="BF26">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG26">
-        <v>5.7</v>
+        <v>26</v>
       </c>
       <c r="BH26">
         <v>4.8</v>
@@ -7509,19 +7509,19 @@
         <v>237</v>
       </c>
       <c r="F27">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G27">
         <v>3.2</v>
       </c>
       <c r="H27">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="I27">
-        <v>3.65</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="K27">
         <v>950</v>
@@ -7775,7 +7775,7 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O28">
         <v>1.22</v>
@@ -7787,7 +7787,7 @@
         <v>1.22</v>
       </c>
       <c r="R28">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S28">
         <v>1.21</v>
@@ -7859,52 +7859,52 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
         <v>1.01</v>
@@ -7993,22 +7993,22 @@
         <v>239</v>
       </c>
       <c r="F29">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="G29">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="H29">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="I29">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="J29">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="K29">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -8020,7 +8020,7 @@
         <v>6</v>
       </c>
       <c r="O29">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P29">
         <v>2.68</v>
@@ -8029,10 +8029,10 @@
         <v>1.55</v>
       </c>
       <c r="R29">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S29">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T29">
         <v>2.2</v>
@@ -8041,16 +8041,16 @@
         <v>1.7</v>
       </c>
       <c r="V29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W29">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="X29">
         <v>36</v>
       </c>
       <c r="Y29">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="Z29">
         <v>210</v>
@@ -8065,13 +8065,13 @@
         <v>19.5</v>
       </c>
       <c r="AD29">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="AE29">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AF29">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG29">
         <v>14</v>
@@ -8080,7 +8080,7 @@
         <v>44</v>
       </c>
       <c r="AI29">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AJ29">
         <v>10.5</v>
@@ -8104,25 +8104,25 @@
         <v>19.5</v>
       </c>
       <c r="AQ29">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AR29">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS29">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT29">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU29">
         <v>13.5</v>
       </c>
       <c r="AV29">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AW29">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX29">
         <v>6.8</v>
@@ -8131,10 +8131,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ29">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BA29">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB29">
         <v>7.6</v>
@@ -8143,16 +8143,16 @@
         <v>12</v>
       </c>
       <c r="BD29">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE29">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF29">
         <v>3</v>
       </c>
       <c r="BG29">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8250,7 +8250,7 @@
         <v>4</v>
       </c>
       <c r="K30">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L30">
         <v>1.28</v>
@@ -8486,7 +8486,7 @@
         <v>2.26</v>
       </c>
       <c r="I31">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J31">
         <v>3.85</v>
@@ -8507,7 +8507,7 @@
         <v>1.21</v>
       </c>
       <c r="P31">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q31">
         <v>1.63</v>
@@ -8525,7 +8525,7 @@
         <v>2.52</v>
       </c>
       <c r="V31">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W31">
         <v>1.44</v>
@@ -8537,16 +8537,16 @@
         <v>15</v>
       </c>
       <c r="Z31">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA31">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB31">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AD31">
         <v>14</v>
@@ -8558,10 +8558,10 @@
         <v>26</v>
       </c>
       <c r="AG31">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH31">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI31">
         <v>36</v>
@@ -8621,16 +8621,16 @@
         <v>21</v>
       </c>
       <c r="BB31">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BC31">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BD31">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE31">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF31">
         <v>15</v>
@@ -8731,13 +8731,13 @@
         <v>2.52</v>
       </c>
       <c r="J32">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K32">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L32">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M32">
         <v>1.07</v>
@@ -8764,7 +8764,7 @@
         <v>1.72</v>
       </c>
       <c r="U32">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V32">
         <v>1.65</v>
@@ -8842,7 +8842,7 @@
         <v>4.8</v>
       </c>
       <c r="AU32">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV32">
         <v>4.4</v>
@@ -9006,7 +9006,7 @@
         <v>1.72</v>
       </c>
       <c r="U33">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V33">
         <v>1.21</v>
@@ -9126,7 +9126,7 @@
         <v>4.1</v>
       </c>
       <c r="BI33">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ33">
         <v>10</v>
@@ -9314,7 +9314,7 @@
         <v>5.8</v>
       </c>
       <c r="AQ34">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="AR34">
         <v>12.5</v>
@@ -9329,10 +9329,10 @@
         <v>7</v>
       </c>
       <c r="AV34">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="AW34">
-        <v>19.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX34">
         <v>16</v>
@@ -9344,16 +9344,16 @@
         <v>13</v>
       </c>
       <c r="BA34">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="BB34">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="BC34">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="BD34">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="BE34">
         <v>7.6</v>
@@ -9374,7 +9374,7 @@
         <v>9.4</v>
       </c>
       <c r="BK34">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL34">
         <v>1000</v>
@@ -9404,7 +9404,7 @@
         <v>6.2</v>
       </c>
       <c r="BU34">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="BV34">
         <v>21</v>
@@ -9711,7 +9711,7 @@
         <v>1.03</v>
       </c>
       <c r="N36">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O36">
         <v>1.16</v>
@@ -9852,7 +9852,7 @@
         <v>4.9</v>
       </c>
       <c r="BI36">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BJ36">
         <v>8.6</v>
@@ -9929,10 +9929,10 @@
         <v>247</v>
       </c>
       <c r="F37">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G37">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H37">
         <v>5.3</v>
@@ -9965,7 +9965,7 @@
         <v>1.8</v>
       </c>
       <c r="R37">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S37">
         <v>3</v>
@@ -9974,13 +9974,13 @@
         <v>1.82</v>
       </c>
       <c r="U37">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V37">
         <v>1.2</v>
       </c>
       <c r="W37">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X37">
         <v>20</v>
@@ -10028,7 +10028,7 @@
         <v>38</v>
       </c>
       <c r="AM37">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN37">
         <v>10.5</v>
@@ -10046,7 +10046,7 @@
         <v>8.6</v>
       </c>
       <c r="AS37">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT37">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ37">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA37">
         <v>9</v>
@@ -10088,7 +10088,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG37">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH37">
         <v>3.75</v>
@@ -10174,19 +10174,19 @@
         <v>1.76</v>
       </c>
       <c r="G38">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H38">
         <v>4.1</v>
       </c>
       <c r="I38">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J38">
         <v>4.2</v>
       </c>
       <c r="K38">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L38">
         <v>1.24</v>
@@ -10201,7 +10201,7 @@
         <v>1.16</v>
       </c>
       <c r="P38">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q38">
         <v>1.55</v>
@@ -10219,7 +10219,7 @@
         <v>2.48</v>
       </c>
       <c r="V38">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W38">
         <v>2.12</v>
@@ -10431,16 +10431,16 @@
         <v>7.8</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M39">
         <v>1.02</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P39">
         <v>2.86</v>
@@ -10449,10 +10449,10 @@
         <v>1.45</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T39">
         <v>1.96</v>
@@ -10461,10 +10461,10 @@
         <v>1.86</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="X39">
         <v>40</v>
@@ -10545,7 +10545,7 @@
         <v>5</v>
       </c>
       <c r="AX39">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="AY39">
         <v>10</v>
@@ -10575,64 +10575,64 @@
         <v>5</v>
       </c>
       <c r="BH39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ39">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BK39">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BL39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BN39">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO39">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BP39">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BQ39">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BR39">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BS39">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BT39">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BU39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BV39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BX39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BZ39">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="CA39">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="CB39" t="s">
         <v>283</v>
@@ -10658,10 +10658,10 @@
         <v>1.81</v>
       </c>
       <c r="G40">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H40">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I40">
         <v>5.4</v>
@@ -10682,7 +10682,7 @@
         <v>3.55</v>
       </c>
       <c r="O40">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P40">
         <v>1.87</v>
@@ -10706,7 +10706,7 @@
         <v>1.22</v>
       </c>
       <c r="W40">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X40">
         <v>14.5</v>
@@ -10745,7 +10745,7 @@
         <v>80</v>
       </c>
       <c r="AJ40">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK40">
         <v>25</v>
@@ -10769,16 +10769,16 @@
         <v>12</v>
       </c>
       <c r="AR40">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS40">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT40">
         <v>7.2</v>
       </c>
       <c r="AU40">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV40">
         <v>14.5</v>
@@ -10796,7 +10796,7 @@
         <v>14.5</v>
       </c>
       <c r="BA40">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB40">
         <v>14.5</v>
@@ -10805,10 +10805,10 @@
         <v>14.5</v>
       </c>
       <c r="BD40">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BE40">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF40">
         <v>9.6</v>
@@ -10897,7 +10897,7 @@
         <v>251</v>
       </c>
       <c r="F41">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="G41">
         <v>2.34</v>
@@ -10912,7 +10912,7 @@
         <v>3.15</v>
       </c>
       <c r="K41">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L41">
         <v>1.5</v>
@@ -11145,13 +11145,13 @@
         <v>3.85</v>
       </c>
       <c r="H42">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I42">
         <v>2.14</v>
       </c>
       <c r="J42">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K42">
         <v>4.3</v>
@@ -11163,28 +11163,28 @@
         <v>1.04</v>
       </c>
       <c r="N42">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O42">
         <v>1.21</v>
       </c>
       <c r="P42">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q42">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R42">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S42">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="T42">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U42">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V42">
         <v>1.87</v>
@@ -11193,7 +11193,7 @@
         <v>1.35</v>
       </c>
       <c r="X42">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y42">
         <v>13</v>
@@ -11205,19 +11205,19 @@
         <v>25</v>
       </c>
       <c r="AB42">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC42">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD42">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE42">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF42">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AG42">
         <v>15.5</v>
@@ -11241,13 +11241,13 @@
         <v>85</v>
       </c>
       <c r="AN42">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AO42">
         <v>11</v>
       </c>
       <c r="AP42">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AQ42">
         <v>10.5</v>
@@ -11283,10 +11283,10 @@
         <v>16.5</v>
       </c>
       <c r="BB42">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC42">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BD42">
         <v>30</v>
@@ -11390,7 +11390,7 @@
         <v>2.38</v>
       </c>
       <c r="I43">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J43">
         <v>3.15</v>
@@ -11405,13 +11405,13 @@
         <v>1.09</v>
       </c>
       <c r="N43">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O43">
         <v>1.38</v>
       </c>
       <c r="P43">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q43">
         <v>2.12</v>
@@ -11546,7 +11546,7 @@
         <v>3.25</v>
       </c>
       <c r="BI43">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ43">
         <v>10.5</v>
@@ -11623,22 +11623,22 @@
         <v>254</v>
       </c>
       <c r="F44">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G44">
         <v>3.15</v>
       </c>
       <c r="H44">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="I44">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J44">
+        <v>3.6</v>
+      </c>
+      <c r="K44">
         <v>3.65</v>
-      </c>
-      <c r="K44">
-        <v>3.75</v>
       </c>
       <c r="L44">
         <v>1.34</v>
@@ -11671,7 +11671,7 @@
         <v>2.36</v>
       </c>
       <c r="V44">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W44">
         <v>1.47</v>
@@ -11865,7 +11865,7 @@
         <v>255</v>
       </c>
       <c r="F45">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="G45">
         <v>3.15</v>
@@ -11874,10 +11874,10 @@
         <v>2.26</v>
       </c>
       <c r="I45">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="J45">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K45">
         <v>4.2</v>
@@ -11904,16 +11904,16 @@
         <v>1.54</v>
       </c>
       <c r="S45">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T45">
         <v>1.6</v>
       </c>
       <c r="U45">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V45">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W45">
         <v>1.46</v>
@@ -11925,7 +11925,7 @@
         <v>14</v>
       </c>
       <c r="Z45">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA45">
         <v>32</v>
@@ -11955,7 +11955,7 @@
         <v>34</v>
       </c>
       <c r="AJ45">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK45">
         <v>32</v>
@@ -11970,7 +11970,7 @@
         <v>23</v>
       </c>
       <c r="AO45">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP45">
         <v>7.2</v>
@@ -11988,34 +11988,34 @@
         <v>13.5</v>
       </c>
       <c r="AU45">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV45">
         <v>10</v>
       </c>
       <c r="AW45">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="AX45">
-        <v>19.5</v>
+        <v>7.6</v>
       </c>
       <c r="AY45">
         <v>11.5</v>
       </c>
       <c r="AZ45">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="BA45">
         <v>24</v>
       </c>
       <c r="BB45">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC45">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD45">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE45">
         <v>55</v>
@@ -12024,7 +12024,7 @@
         <v>7.4</v>
       </c>
       <c r="BG45">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH45">
         <v>4.2</v>
@@ -12042,19 +12042,19 @@
         <v>1000</v>
       </c>
       <c r="BM45">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN45">
         <v>6.8</v>
       </c>
       <c r="BO45">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP45">
         <v>23</v>
       </c>
       <c r="BQ45">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR45">
         <v>32</v>
@@ -12069,7 +12069,7 @@
         <v>4.4</v>
       </c>
       <c r="BV45">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW45">
         <v>6.2</v>
@@ -12078,7 +12078,7 @@
         <v>27</v>
       </c>
       <c r="BY45">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ45">
         <v>0</v>
@@ -12116,10 +12116,10 @@
         <v>2.16</v>
       </c>
       <c r="I46">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J46">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K46">
         <v>3.55</v>
@@ -12131,16 +12131,16 @@
         <v>1.1</v>
       </c>
       <c r="N46">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O46">
         <v>1.42</v>
       </c>
       <c r="P46">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="Q46">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R46">
         <v>1.25</v>
@@ -12152,10 +12152,10 @@
         <v>1.93</v>
       </c>
       <c r="U46">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V46">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W46">
         <v>1.31</v>
@@ -12349,19 +12349,19 @@
         <v>257</v>
       </c>
       <c r="F47">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G47">
         <v>990</v>
       </c>
       <c r="H47">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I47">
-        <v>8</v>
+        <v>870</v>
       </c>
       <c r="J47">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="K47">
         <v>950</v>
@@ -12373,22 +12373,22 @@
         <v>1.02</v>
       </c>
       <c r="N47">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O47">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P47">
         <v>1.25</v>
       </c>
       <c r="Q47">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="R47">
         <v>1.18</v>
       </c>
       <c r="S47">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="T47">
         <v>1.11</v>
@@ -12603,7 +12603,7 @@
         <v>990</v>
       </c>
       <c r="J48">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="K48">
         <v>950</v>
@@ -12615,7 +12615,7 @@
         <v>1.02</v>
       </c>
       <c r="N48">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O48">
         <v>1.21</v>
@@ -12624,7 +12624,7 @@
         <v>1.25</v>
       </c>
       <c r="Q48">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R48">
         <v>1.18</v>
@@ -12845,10 +12845,10 @@
         <v>990</v>
       </c>
       <c r="J49">
-        <v>1.1</v>
+        <v>1.86</v>
       </c>
       <c r="K49">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L49">
         <v>1.01</v>
@@ -12857,22 +12857,22 @@
         <v>1.02</v>
       </c>
       <c r="N49">
-        <v>1.26</v>
+        <v>5.1</v>
       </c>
       <c r="O49">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P49">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q49">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="R49">
         <v>1.18</v>
       </c>
       <c r="S49">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="T49">
         <v>1.11</v>
@@ -12941,52 +12941,52 @@
         <v>1000</v>
       </c>
       <c r="AP49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF49">
         <v>1.01</v>
@@ -13087,7 +13087,7 @@
         <v>8</v>
       </c>
       <c r="J50">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K50">
         <v>5.5</v>
@@ -13105,22 +13105,22 @@
         <v>1.19</v>
       </c>
       <c r="P50">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q50">
         <v>1.55</v>
       </c>
       <c r="R50">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S50">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T50">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U50">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V50">
         <v>1.14</v>
@@ -13240,7 +13240,7 @@
         <v>4.7</v>
       </c>
       <c r="BI50">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ50">
         <v>10.5</v>
@@ -13323,16 +13323,16 @@
         <v>990</v>
       </c>
       <c r="H51">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="I51">
         <v>990</v>
       </c>
       <c r="J51">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K51">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L51">
         <v>1.01</v>
@@ -13341,16 +13341,16 @@
         <v>1.02</v>
       </c>
       <c r="N51">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O51">
         <v>1.15</v>
       </c>
       <c r="P51">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q51">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="R51">
         <v>1.18</v>
@@ -13365,10 +13365,10 @@
         <v>1.11</v>
       </c>
       <c r="V51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W51">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -13425,52 +13425,52 @@
         <v>1000</v>
       </c>
       <c r="AP51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF51">
         <v>1.01</v>
@@ -13592,7 +13592,7 @@
         <v>2.18</v>
       </c>
       <c r="Q52">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R52">
         <v>1.45</v>
@@ -13616,7 +13616,7 @@
         <v>23</v>
       </c>
       <c r="Y52">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z52">
         <v>60</v>
@@ -13661,7 +13661,7 @@
         <v>110</v>
       </c>
       <c r="AN52">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO52">
         <v>85</v>
@@ -13673,10 +13673,10 @@
         <v>16</v>
       </c>
       <c r="AR52">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS52">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT52">
         <v>7.4</v>
@@ -13688,7 +13688,7 @@
         <v>15.5</v>
       </c>
       <c r="AW52">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX52">
         <v>8.199999999999999</v>
@@ -13700,7 +13700,7 @@
         <v>14</v>
       </c>
       <c r="BA52">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB52">
         <v>12.5</v>
@@ -13709,16 +13709,16 @@
         <v>12</v>
       </c>
       <c r="BD52">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE52">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF52">
         <v>6.6</v>
       </c>
       <c r="BG52">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH52">
         <v>3.95</v>
@@ -13801,7 +13801,7 @@
         <v>263</v>
       </c>
       <c r="F53">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G53">
         <v>2.7</v>
@@ -13930,7 +13930,7 @@
         <v>10</v>
       </c>
       <c r="AW53">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX53">
         <v>13</v>
@@ -13942,16 +13942,16 @@
         <v>13</v>
       </c>
       <c r="BA53">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB53">
         <v>5.6</v>
       </c>
       <c r="BC53">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD53">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE53">
         <v>6</v>
@@ -13972,16 +13972,16 @@
         <v>9.6</v>
       </c>
       <c r="BK53">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL53">
         <v>1000</v>
       </c>
       <c r="BM53">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN53">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO53">
         <v>4.4</v>
@@ -13990,13 +13990,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ53">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR53">
         <v>34</v>
       </c>
       <c r="BS53">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT53">
         <v>6.2</v>
@@ -14008,13 +14008,13 @@
         <v>24</v>
       </c>
       <c r="BW53">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX53">
         <v>1000</v>
       </c>
       <c r="BY53">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ53">
         <v>0</v>
@@ -14073,7 +14073,7 @@
         <v>1.24</v>
       </c>
       <c r="P54">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q54">
         <v>1.71</v>
@@ -14085,7 +14085,7 @@
         <v>2.78</v>
       </c>
       <c r="T54">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U54">
         <v>2.36</v>
@@ -14151,58 +14151,58 @@
         <v>26</v>
       </c>
       <c r="AP54">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ54">
         <v>10.5</v>
       </c>
       <c r="AR54">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS54">
-        <v>5.2</v>
+        <v>32</v>
       </c>
       <c r="AT54">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AU54">
         <v>6.6</v>
       </c>
       <c r="AV54">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AW54">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX54">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AY54">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ54">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BA54">
         <v>27</v>
       </c>
       <c r="BB54">
-        <v>4.9</v>
+        <v>24</v>
       </c>
       <c r="BC54">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BD54">
-        <v>4.9</v>
+        <v>25</v>
       </c>
       <c r="BE54">
         <v>5.4</v>
       </c>
       <c r="BF54">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG54">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BH54">
         <v>3.95</v>
@@ -14291,16 +14291,16 @@
         <v>3.3</v>
       </c>
       <c r="H55">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I55">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J55">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K55">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L55">
         <v>1.32</v>
@@ -14318,7 +14318,7 @@
         <v>2.04</v>
       </c>
       <c r="Q55">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R55">
         <v>1.41</v>
@@ -14333,7 +14333,7 @@
         <v>2.26</v>
       </c>
       <c r="V55">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W55">
         <v>1.43</v>
@@ -14393,10 +14393,10 @@
         <v>19</v>
       </c>
       <c r="AP55">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ55">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR55">
         <v>13</v>
@@ -14408,7 +14408,7 @@
         <v>10.5</v>
       </c>
       <c r="AU55">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV55">
         <v>9</v>
@@ -14432,10 +14432,10 @@
         <v>6</v>
       </c>
       <c r="BC55">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD55">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE55">
         <v>6.2</v>
@@ -14450,7 +14450,7 @@
         <v>3.8</v>
       </c>
       <c r="BI55">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ55">
         <v>9.4</v>
@@ -14530,7 +14530,7 @@
         <v>10.5</v>
       </c>
       <c r="G56">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="H56">
         <v>1.31</v>
@@ -14539,7 +14539,7 @@
         <v>1.36</v>
       </c>
       <c r="J56">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K56">
         <v>6.6</v>
@@ -14551,7 +14551,7 @@
         <v>1.02</v>
       </c>
       <c r="N56">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O56">
         <v>1.19</v>
@@ -14584,7 +14584,7 @@
         <v>30</v>
       </c>
       <c r="Y56">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z56">
         <v>9.4</v>
@@ -14596,97 +14596,97 @@
         <v>40</v>
       </c>
       <c r="AC56">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD56">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE56">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AF56">
         <v>140</v>
       </c>
       <c r="AG56">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AH56">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI56">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ56">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AK56">
         <v>220</v>
       </c>
       <c r="AL56">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AM56">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN56">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AO56">
         <v>5</v>
       </c>
       <c r="AP56">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="AQ56">
+        <v>8.4</v>
+      </c>
+      <c r="AR56">
+        <v>7.6</v>
+      </c>
+      <c r="AS56">
+        <v>8.4</v>
+      </c>
+      <c r="AT56">
+        <v>6.8</v>
+      </c>
+      <c r="AU56">
+        <v>11.5</v>
+      </c>
+      <c r="AV56">
+        <v>9</v>
+      </c>
+      <c r="AW56">
+        <v>10.5</v>
+      </c>
+      <c r="AX56">
+        <v>7.8</v>
+      </c>
+      <c r="AY56">
+        <v>6.8</v>
+      </c>
+      <c r="AZ56">
+        <v>21</v>
+      </c>
+      <c r="BA56">
+        <v>6.6</v>
+      </c>
+      <c r="BB56">
         <v>8</v>
       </c>
-      <c r="AR56">
-        <v>7.2</v>
-      </c>
-      <c r="AS56">
-        <v>8.6</v>
-      </c>
-      <c r="AT56">
-        <v>5.7</v>
-      </c>
-      <c r="AU56">
-        <v>10</v>
-      </c>
-      <c r="AV56">
-        <v>8.4</v>
-      </c>
-      <c r="AW56">
-        <v>11</v>
-      </c>
-      <c r="AX56">
-        <v>6.4</v>
-      </c>
-      <c r="AY56">
-        <v>5.8</v>
-      </c>
-      <c r="AZ56">
-        <v>20</v>
-      </c>
-      <c r="BA56">
-        <v>5.7</v>
-      </c>
-      <c r="BB56">
-        <v>6.6</v>
-      </c>
       <c r="BC56">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD56">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE56">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF56">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BG56">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BH56">
         <v>4.6</v>
@@ -14769,7 +14769,7 @@
         <v>267</v>
       </c>
       <c r="F57">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G57">
         <v>1.3</v>
@@ -14784,37 +14784,37 @@
         <v>7</v>
       </c>
       <c r="K57">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L57">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="M57">
         <v>1.01</v>
       </c>
       <c r="N57">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O57">
         <v>1.11</v>
       </c>
       <c r="P57">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q57">
         <v>1.35</v>
       </c>
       <c r="R57">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="S57">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="T57">
         <v>1.75</v>
       </c>
       <c r="U57">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V57">
         <v>1.08</v>
@@ -14829,13 +14829,13 @@
         <v>950</v>
       </c>
       <c r="Z57">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AA57">
         <v>390</v>
       </c>
       <c r="AB57">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC57">
         <v>18</v>
@@ -14844,10 +14844,10 @@
         <v>44</v>
       </c>
       <c r="AE57">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF57">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG57">
         <v>12</v>
@@ -14859,7 +14859,7 @@
         <v>110</v>
       </c>
       <c r="AJ57">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK57">
         <v>13</v>
@@ -14868,7 +14868,7 @@
         <v>28</v>
       </c>
       <c r="AM57">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN57">
         <v>3.2</v>
@@ -14877,28 +14877,28 @@
         <v>110</v>
       </c>
       <c r="AP57">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="AQ57">
         <v>50</v>
       </c>
       <c r="AR57">
+        <v>14.5</v>
+      </c>
+      <c r="AS57">
+        <v>15.5</v>
+      </c>
+      <c r="AT57">
         <v>14</v>
       </c>
-      <c r="AS57">
-        <v>14</v>
-      </c>
-      <c r="AT57">
-        <v>14.5</v>
-      </c>
       <c r="AU57">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="AV57">
         <v>36</v>
       </c>
       <c r="AW57">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX57">
         <v>10.5</v>
@@ -14910,7 +14910,7 @@
         <v>22</v>
       </c>
       <c r="BA57">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BB57">
         <v>10.5</v>
@@ -14922,13 +14922,13 @@
         <v>22</v>
       </c>
       <c r="BE57">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF57">
         <v>3.05</v>
       </c>
       <c r="BG57">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BH57">
         <v>6.2</v>
@@ -14973,7 +14973,7 @@
         <v>6.2</v>
       </c>
       <c r="BV57">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW57">
         <v>9.4</v>
@@ -15011,25 +15011,25 @@
         <v>268</v>
       </c>
       <c r="F58">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G58">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H58">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="I58">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="J58">
         <v>4.8</v>
       </c>
       <c r="K58">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L58">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M58">
         <v>1.03</v>
@@ -15041,28 +15041,28 @@
         <v>1.18</v>
       </c>
       <c r="P58">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="Q58">
         <v>1.53</v>
       </c>
       <c r="R58">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S58">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T58">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U58">
         <v>2.4</v>
       </c>
       <c r="V58">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="W58">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X58">
         <v>34</v>
@@ -15071,10 +15071,10 @@
         <v>13</v>
       </c>
       <c r="Z58">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA58">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AB58">
         <v>32</v>
@@ -15083,7 +15083,7 @@
         <v>12.5</v>
       </c>
       <c r="AD58">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE58">
         <v>14.5</v>
@@ -15095,25 +15095,25 @@
         <v>24</v>
       </c>
       <c r="AH58">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AI58">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AJ58">
         <v>160</v>
       </c>
       <c r="AK58">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL58">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM58">
         <v>75</v>
       </c>
       <c r="AN58">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO58">
         <v>6.2</v>
@@ -15131,7 +15131,7 @@
         <v>14</v>
       </c>
       <c r="AT58">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AU58">
         <v>10.5</v>
@@ -15143,19 +15143,19 @@
         <v>13</v>
       </c>
       <c r="AX58">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AY58">
         <v>20</v>
       </c>
       <c r="AZ58">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA58">
         <v>22</v>
       </c>
       <c r="BB58">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BC58">
         <v>55</v>
@@ -15164,49 +15164,49 @@
         <v>50</v>
       </c>
       <c r="BE58">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF58">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BG58">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH58">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI58">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BJ58">
         <v>9.6</v>
       </c>
       <c r="BK58">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL58">
         <v>1000</v>
       </c>
       <c r="BM58">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN58">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BO58">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BP58">
         <v>1000</v>
       </c>
       <c r="BQ58">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR58">
         <v>1000</v>
       </c>
       <c r="BS58">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT58">
         <v>4.6</v>
@@ -15215,16 +15215,16 @@
         <v>3.5</v>
       </c>
       <c r="BV58">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BW58">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BX58">
         <v>1000</v>
       </c>
       <c r="BY58">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ58">
         <v>0</v>
@@ -15253,46 +15253,46 @@
         <v>269</v>
       </c>
       <c r="F59">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="G59">
-        <v>990</v>
+        <v>2.06</v>
       </c>
       <c r="H59">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I59">
-        <v>990</v>
+        <v>3.9</v>
       </c>
       <c r="J59">
-        <v>1.55</v>
+        <v>3.85</v>
       </c>
       <c r="K59">
-        <v>500</v>
+        <v>4.9</v>
       </c>
       <c r="L59">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M59">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N59">
-        <v>1.29</v>
+        <v>2.54</v>
       </c>
       <c r="O59">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P59">
-        <v>1.29</v>
+        <v>2.44</v>
       </c>
       <c r="Q59">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="R59">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="S59">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="T59">
         <v>1.11</v>
@@ -15301,10 +15301,10 @@
         <v>1.11</v>
       </c>
       <c r="V59">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W59">
-        <v>1.52</v>
+        <v>1.94</v>
       </c>
       <c r="X59">
         <v>1000</v>
@@ -15498,16 +15498,16 @@
         <v>4.9</v>
       </c>
       <c r="G60">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H60">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="I60">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="J60">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K60">
         <v>3.7</v>
@@ -15519,16 +15519,16 @@
         <v>1.08</v>
       </c>
       <c r="N60">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O60">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P60">
         <v>1.82</v>
       </c>
       <c r="Q60">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R60">
         <v>1.31</v>
@@ -15543,7 +15543,7 @@
         <v>1.96</v>
       </c>
       <c r="V60">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="W60">
         <v>1.22</v>
@@ -15561,7 +15561,7 @@
         <v>22</v>
       </c>
       <c r="AB60">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC60">
         <v>8.4</v>
@@ -15594,10 +15594,10 @@
         <v>85</v>
       </c>
       <c r="AM60">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN60">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO60">
         <v>15</v>
@@ -15639,7 +15639,7 @@
         <v>34</v>
       </c>
       <c r="BB60">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC60">
         <v>50</v>
@@ -15648,7 +15648,7 @@
         <v>60</v>
       </c>
       <c r="BE60">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF60">
         <v>60</v>
@@ -15767,22 +15767,22 @@
         <v>1.33</v>
       </c>
       <c r="P61">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q61">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="R61">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S61">
         <v>3.6</v>
       </c>
       <c r="T61">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U61">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V61">
         <v>1.25</v>
@@ -15839,64 +15839,64 @@
         <v>130</v>
       </c>
       <c r="AN61">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AO61">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP61">
         <v>11.5</v>
       </c>
       <c r="AQ61">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR61">
         <v>23</v>
       </c>
       <c r="AS61">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT61">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU61">
         <v>7</v>
       </c>
       <c r="AV61">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW61">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX61">
         <v>10</v>
       </c>
       <c r="AY61">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AZ61">
         <v>16</v>
       </c>
       <c r="BA61">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB61">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC61">
         <v>18</v>
       </c>
       <c r="BD61">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE61">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF61">
         <v>5.7</v>
       </c>
       <c r="BG61">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH61">
         <v>3.45</v>
@@ -15920,7 +15920,7 @@
         <v>4.7</v>
       </c>
       <c r="BO61">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP61">
         <v>14.5</v>
@@ -15994,7 +15994,7 @@
         <v>1.04</v>
       </c>
       <c r="K62">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L62">
         <v>1.01</v>
@@ -16003,22 +16003,22 @@
         <v>1.01</v>
       </c>
       <c r="N62">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O62">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P62">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q62">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="R62">
         <v>1.16</v>
       </c>
       <c r="S62">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="T62">
         <v>1.11</v>
@@ -16087,52 +16087,52 @@
         <v>1000</v>
       </c>
       <c r="AP62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF62">
         <v>1.01</v>
@@ -16144,61 +16144,61 @@
         <v>1000</v>
       </c>
       <c r="BI62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ62">
         <v>1000</v>
       </c>
       <c r="BK62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL62">
         <v>1000</v>
       </c>
       <c r="BM62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN62">
         <v>1000</v>
       </c>
       <c r="BO62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP62">
         <v>1000</v>
       </c>
       <c r="BQ62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR62">
         <v>1000</v>
       </c>
       <c r="BS62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT62">
         <v>1000</v>
       </c>
       <c r="BU62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV62">
         <v>1000</v>
       </c>
       <c r="BW62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX62">
         <v>1000</v>
       </c>
       <c r="BY62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ62">
         <v>1000</v>
       </c>
       <c r="CA62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB62" t="s">
         <v>283</v>
@@ -16224,7 +16224,7 @@
         <v>1.04</v>
       </c>
       <c r="G63">
-        <v>990</v>
+        <v>2.34</v>
       </c>
       <c r="H63">
         <v>1.04</v>
@@ -16233,10 +16233,10 @@
         <v>990</v>
       </c>
       <c r="J63">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="K63">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L63">
         <v>1.01</v>
@@ -16245,13 +16245,13 @@
         <v>1.01</v>
       </c>
       <c r="N63">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O63">
         <v>1.36</v>
       </c>
       <c r="P63">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q63">
         <v>1.36</v>
@@ -16272,7 +16272,7 @@
         <v>1.02</v>
       </c>
       <c r="W63">
-        <v>1.02</v>
+        <v>1.75</v>
       </c>
       <c r="X63">
         <v>1000</v>
@@ -16329,52 +16329,52 @@
         <v>1000</v>
       </c>
       <c r="AP63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF63">
         <v>1.01</v>
@@ -16463,10 +16463,10 @@
         <v>274</v>
       </c>
       <c r="F64">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G64">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H64">
         <v>2.08</v>
@@ -16475,10 +16475,10 @@
         <v>2.36</v>
       </c>
       <c r="J64">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="K64">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L64">
         <v>1.41</v>
@@ -16487,25 +16487,25 @@
         <v>1.09</v>
       </c>
       <c r="N64">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O64">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P64">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q64">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="R64">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S64">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T64">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U64">
         <v>1.88</v>
@@ -16520,7 +16520,7 @@
         <v>13</v>
       </c>
       <c r="Y64">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z64">
         <v>16</v>
@@ -16529,7 +16529,7 @@
         <v>36</v>
       </c>
       <c r="AB64">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC64">
         <v>9</v>
@@ -16541,10 +16541,10 @@
         <v>34</v>
       </c>
       <c r="AF64">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG64">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AH64">
         <v>25</v>
@@ -16553,7 +16553,7 @@
         <v>60</v>
       </c>
       <c r="AJ64">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AK64">
         <v>70</v>
@@ -16565,70 +16565,70 @@
         <v>170</v>
       </c>
       <c r="AN64">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AO64">
         <v>29</v>
       </c>
       <c r="AP64">
+        <v>3.25</v>
+      </c>
+      <c r="AQ64">
+        <v>3</v>
+      </c>
+      <c r="AR64">
+        <v>3.4</v>
+      </c>
+      <c r="AS64">
+        <v>3.85</v>
+      </c>
+      <c r="AT64">
         <v>3.35</v>
       </c>
-      <c r="AQ64">
-        <v>3.1</v>
-      </c>
-      <c r="AR64">
-        <v>3.55</v>
-      </c>
-      <c r="AS64">
+      <c r="AU64">
+        <v>2.92</v>
+      </c>
+      <c r="AV64">
+        <v>3.25</v>
+      </c>
+      <c r="AW64">
+        <v>3.85</v>
+      </c>
+      <c r="AX64">
+        <v>3.85</v>
+      </c>
+      <c r="AY64">
+        <v>3.6</v>
+      </c>
+      <c r="AZ64">
+        <v>3.7</v>
+      </c>
+      <c r="BA64">
         <v>4</v>
       </c>
-      <c r="AT64">
-        <v>3.45</v>
-      </c>
-      <c r="AU64">
-        <v>3</v>
-      </c>
-      <c r="AV64">
-        <v>3.4</v>
-      </c>
-      <c r="AW64">
-        <v>4</v>
-      </c>
-      <c r="AX64">
-        <v>4</v>
-      </c>
-      <c r="AY64">
-        <v>3.7</v>
-      </c>
-      <c r="AZ64">
-        <v>3.85</v>
-      </c>
-      <c r="BA64">
+      <c r="BB64">
+        <v>4.1</v>
+      </c>
+      <c r="BC64">
+        <v>4.1</v>
+      </c>
+      <c r="BD64">
+        <v>4.1</v>
+      </c>
+      <c r="BE64">
         <v>4.2</v>
       </c>
-      <c r="BB64">
-        <v>4.3</v>
-      </c>
-      <c r="BC64">
-        <v>4.3</v>
-      </c>
-      <c r="BD64">
-        <v>4.3</v>
-      </c>
-      <c r="BE64">
-        <v>4.4</v>
-      </c>
       <c r="BF64">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BG64">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BH64">
         <v>3.1</v>
       </c>
       <c r="BI64">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ64">
         <v>11</v>
@@ -16655,7 +16655,7 @@
         <v>2.26</v>
       </c>
       <c r="BR64">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS64">
         <v>2.3</v>
@@ -16705,16 +16705,16 @@
         <v>275</v>
       </c>
       <c r="F65">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G65">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H65">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I65">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J65">
         <v>3.1</v>
@@ -16729,34 +16729,34 @@
         <v>1.1</v>
       </c>
       <c r="N65">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="O65">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P65">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q65">
         <v>2.26</v>
       </c>
       <c r="R65">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S65">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T65">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U65">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V65">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W65">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X65">
         <v>12</v>
@@ -16780,10 +16780,10 @@
         <v>14.5</v>
       </c>
       <c r="AE65">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF65">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG65">
         <v>14</v>
@@ -16798,7 +16798,7 @@
         <v>65</v>
       </c>
       <c r="AK65">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL65">
         <v>60</v>
@@ -16813,58 +16813,58 @@
         <v>42</v>
       </c>
       <c r="AP65">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ65">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR65">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS65">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT65">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AU65">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV65">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW65">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX65">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY65">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ65">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA65">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB65">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BC65">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD65">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BE65">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF65">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG65">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH65">
         <v>1000</v>
@@ -16947,7 +16947,7 @@
         <v>276</v>
       </c>
       <c r="F66">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G66">
         <v>1.47</v>
@@ -16959,10 +16959,10 @@
         <v>990</v>
       </c>
       <c r="J66">
-        <v>1.75</v>
+        <v>3.3</v>
       </c>
       <c r="K66">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L66">
         <v>1.01</v>
@@ -16986,7 +16986,7 @@
         <v>1.45</v>
       </c>
       <c r="S66">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="T66">
         <v>1.11</v>
@@ -16998,7 +16998,7 @@
         <v>1.01</v>
       </c>
       <c r="W66">
-        <v>1.72</v>
+        <v>2.88</v>
       </c>
       <c r="X66">
         <v>1000</v>
@@ -17189,7 +17189,7 @@
         <v>277</v>
       </c>
       <c r="F67">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G67">
         <v>2.02</v>
@@ -17240,7 +17240,7 @@
         <v>1.23</v>
       </c>
       <c r="W67">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="X67">
         <v>15</v>
@@ -17354,7 +17354,7 @@
         <v>3.25</v>
       </c>
       <c r="BI67">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="BJ67">
         <v>11</v>
@@ -17372,7 +17372,7 @@
         <v>4.6</v>
       </c>
       <c r="BO67">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP67">
         <v>14.5</v>
@@ -17431,22 +17431,22 @@
         <v>278</v>
       </c>
       <c r="F68">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="G68">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="H68">
         <v>3.6</v>
       </c>
       <c r="I68">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="J68">
         <v>3.25</v>
       </c>
       <c r="K68">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L68">
         <v>1.01</v>
@@ -17455,22 +17455,22 @@
         <v>1.01</v>
       </c>
       <c r="N68">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="O68">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P68">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q68">
         <v>1.98</v>
       </c>
       <c r="R68">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S68">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="T68">
         <v>1.11</v>
@@ -17479,10 +17479,10 @@
         <v>1.11</v>
       </c>
       <c r="V68">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W68">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="X68">
         <v>1000</v>
@@ -17539,52 +17539,52 @@
         <v>1000</v>
       </c>
       <c r="AP68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF68">
         <v>1.01</v>
@@ -17602,55 +17602,55 @@
         <v>1000</v>
       </c>
       <c r="BK68">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BL68">
         <v>1000</v>
       </c>
       <c r="BM68">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BN68">
         <v>1000</v>
       </c>
       <c r="BO68">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BP68">
         <v>1000</v>
       </c>
       <c r="BQ68">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BR68">
         <v>1000</v>
       </c>
       <c r="BS68">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BT68">
         <v>1000</v>
       </c>
       <c r="BU68">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BV68">
         <v>1000</v>
       </c>
       <c r="BW68">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BX68">
         <v>1000</v>
       </c>
       <c r="BY68">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BZ68">
         <v>1000</v>
       </c>
       <c r="CA68">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="CB68" t="s">
         <v>283</v>
@@ -17838,61 +17838,61 @@
         <v>1000</v>
       </c>
       <c r="BI69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ69">
         <v>1000</v>
       </c>
       <c r="BK69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL69">
         <v>1000</v>
       </c>
       <c r="BM69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN69">
         <v>1000</v>
       </c>
       <c r="BO69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP69">
         <v>1000</v>
       </c>
       <c r="BQ69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR69">
         <v>1000</v>
       </c>
       <c r="BS69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT69">
         <v>1000</v>
       </c>
       <c r="BU69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV69">
         <v>1000</v>
       </c>
       <c r="BW69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX69">
         <v>1000</v>
       </c>
       <c r="BY69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ69">
         <v>1000</v>
       </c>
       <c r="CA69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB69" t="s">
         <v>283</v>
@@ -17915,28 +17915,28 @@
         <v>280</v>
       </c>
       <c r="F70">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="G70">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="H70">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="I70">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="J70">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K70">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L70">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M70">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N70">
         <v>2.46</v>
@@ -17945,67 +17945,67 @@
         <v>1.43</v>
       </c>
       <c r="P70">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q70">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="R70">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S70">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="T70">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U70">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V70">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="W70">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="X70">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y70">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z70">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AA70">
-        <v>430</v>
+        <v>340</v>
       </c>
       <c r="AB70">
         <v>7.4</v>
       </c>
       <c r="AC70">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD70">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AE70">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AF70">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG70">
         <v>13</v>
       </c>
       <c r="AH70">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI70">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AJ70">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK70">
         <v>26</v>
@@ -18014,121 +18014,121 @@
         <v>70</v>
       </c>
       <c r="AM70">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AN70">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO70">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="AP70">
+        <v>3.4</v>
+      </c>
+      <c r="AQ70">
+        <v>3.85</v>
+      </c>
+      <c r="AR70">
+        <v>4.4</v>
+      </c>
+      <c r="AS70">
+        <v>4.6</v>
+      </c>
+      <c r="AT70">
+        <v>2.86</v>
+      </c>
+      <c r="AU70">
         <v>3.25</v>
       </c>
-      <c r="AQ70">
-        <v>3.7</v>
-      </c>
-      <c r="AR70">
+      <c r="AV70">
         <v>4.1</v>
       </c>
-      <c r="AS70">
-        <v>4.3</v>
-      </c>
-      <c r="AT70">
-        <v>2.74</v>
-      </c>
-      <c r="AU70">
+      <c r="AW70">
+        <v>4.5</v>
+      </c>
+      <c r="AX70">
         <v>3.15</v>
       </c>
-      <c r="AV70">
+      <c r="AY70">
+        <v>3.45</v>
+      </c>
+      <c r="AZ70">
+        <v>4.1</v>
+      </c>
+      <c r="BA70">
+        <v>4.5</v>
+      </c>
+      <c r="BB70">
+        <v>3.75</v>
+      </c>
+      <c r="BC70">
         <v>3.95</v>
       </c>
-      <c r="AW70">
-        <v>4.3</v>
-      </c>
-      <c r="AX70">
-        <v>3</v>
-      </c>
-      <c r="AY70">
-        <v>3.25</v>
-      </c>
-      <c r="AZ70">
-        <v>3.9</v>
-      </c>
-      <c r="BA70">
-        <v>4.3</v>
-      </c>
-      <c r="BB70">
-        <v>3.5</v>
-      </c>
-      <c r="BC70">
-        <v>3.75</v>
-      </c>
       <c r="BD70">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE70">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF70">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BG70">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH70">
         <v>3.1</v>
       </c>
       <c r="BI70">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BJ70">
         <v>13.5</v>
       </c>
       <c r="BK70">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BL70">
         <v>1000</v>
       </c>
       <c r="BM70">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="BN70">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BO70">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BP70">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BQ70">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BR70">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS70">
+        <v>2.18</v>
+      </c>
+      <c r="BT70">
+        <v>11</v>
+      </c>
+      <c r="BU70">
+        <v>4.9</v>
+      </c>
+      <c r="BV70">
+        <v>1000</v>
+      </c>
+      <c r="BW70">
+        <v>2.24</v>
+      </c>
+      <c r="BX70">
+        <v>1000</v>
+      </c>
+      <c r="BY70">
         <v>2.26</v>
-      </c>
-      <c r="BT70">
-        <v>12</v>
-      </c>
-      <c r="BU70">
-        <v>5.7</v>
-      </c>
-      <c r="BV70">
-        <v>1000</v>
-      </c>
-      <c r="BW70">
-        <v>2.36</v>
-      </c>
-      <c r="BX70">
-        <v>1000</v>
-      </c>
-      <c r="BY70">
-        <v>2.36</v>
       </c>
       <c r="BZ70">
         <v>0</v>
@@ -18172,7 +18172,7 @@
         <v>1.04</v>
       </c>
       <c r="K71">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L71">
         <v>1.01</v>
@@ -18181,7 +18181,7 @@
         <v>1.01</v>
       </c>
       <c r="N71">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O71">
         <v>1.11</v>
@@ -18411,10 +18411,10 @@
         <v>5.7</v>
       </c>
       <c r="J72">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K72">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L72">
         <v>1.35</v>
@@ -18435,7 +18435,7 @@
         <v>1.79</v>
       </c>
       <c r="R72">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S72">
         <v>3</v>
@@ -18459,7 +18459,7 @@
         <v>21</v>
       </c>
       <c r="Z72">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AA72">
         <v>1000</v>
@@ -18471,7 +18471,7 @@
         <v>9.6</v>
       </c>
       <c r="AD72">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AE72">
         <v>70</v>
@@ -18480,7 +18480,7 @@
         <v>11</v>
       </c>
       <c r="AG72">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH72">
         <v>20</v>
@@ -18489,7 +18489,7 @@
         <v>1000</v>
       </c>
       <c r="AJ72">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK72">
         <v>17</v>
@@ -18561,64 +18561,64 @@
         <v>46</v>
       </c>
       <c r="BH72">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI72">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ72">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK72">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL72">
         <v>1000</v>
       </c>
       <c r="BM72">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN72">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO72">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP72">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ72">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR72">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS72">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT72">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU72">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV72">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW72">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX72">
         <v>1000</v>
       </c>
       <c r="BY72">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ72">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA72">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="CB72" t="s">
         <v>283</v>
